--- a/Documents/Health-RI_v2.1.0-for-FDP.xlsx
+++ b/Documents/Health-RI_v2.1.0-for-FDP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anakonrad/Library/health-ri-metadata/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C5EF60-EBA0-9B49-9A20-AD78D1F67BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD6E6F3-2A43-CE40-85E3-7C2803DFE556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17380" firstSheet="9" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4660" yWindow="-18400" windowWidth="30240" windowHeight="17420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="14" r:id="rId1"/>
@@ -27,15 +27,16 @@
     <sheet name="DataService" sheetId="6" r:id="rId12"/>
     <sheet name="adms_Identifier" sheetId="15" r:id="rId13"/>
     <sheet name="PeriodOfTime" sheetId="9" r:id="rId14"/>
-    <sheet name="Attribution" sheetId="16" r:id="rId15"/>
-    <sheet name="Relationship" sheetId="17" r:id="rId16"/>
-    <sheet name="QualityCertificate" sheetId="19" r:id="rId17"/>
-    <sheet name="Activity" sheetId="27" r:id="rId18"/>
-    <sheet name="CatalogueRecord" sheetId="10" state="hidden" r:id="rId19"/>
-    <sheet name="Checksum" sheetId="11" r:id="rId20"/>
-    <sheet name="TableGroup" sheetId="21" r:id="rId21"/>
-    <sheet name="Table" sheetId="22" r:id="rId22"/>
-    <sheet name="Column" sheetId="23" r:id="rId23"/>
+    <sheet name="ProvenanceStatement" sheetId="28" r:id="rId15"/>
+    <sheet name="Attribution" sheetId="16" r:id="rId16"/>
+    <sheet name="Relationship" sheetId="17" r:id="rId17"/>
+    <sheet name="QualityCertificate" sheetId="19" r:id="rId18"/>
+    <sheet name="Activity" sheetId="27" r:id="rId19"/>
+    <sheet name="CatalogueRecord" sheetId="10" state="hidden" r:id="rId20"/>
+    <sheet name="Checksum" sheetId="11" r:id="rId21"/>
+    <sheet name="TableGroup" sheetId="21" r:id="rId22"/>
+    <sheet name="Table" sheetId="22" r:id="rId23"/>
+    <sheet name="Column" sheetId="23" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Agent!$A$1:$J$9</definedName>
@@ -66,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2736" uniqueCount="919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2760" uniqueCount="929">
   <si>
     <t>Property label</t>
   </si>
@@ -1206,9 +1207,6 @@
     <t>Dataset-type authority table</t>
   </si>
   <si>
-    <t>A recommended controlled vocabulary data-type is foreseen. Health datasets with personal information must use 'personal data'. This list supports dataset categorization for the EU Open Data Portal. Currently, 'PERSONAL_DATA' is not included in the EU vocabulary and cannot be filled out.</t>
-  </si>
-  <si>
     <t>version</t>
   </si>
   <si>
@@ -2767,9 +2765,6 @@
     <t>dcat</t>
   </si>
   <si>
-    <t>https://www.w3.org/ns/dcat#</t>
-  </si>
-  <si>
     <t>dct</t>
   </si>
   <si>
@@ -2806,12 +2801,6 @@
     <t>http://www.w3.org/ns/prov#</t>
   </si>
   <si>
-    <t>dcatv3</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/ns/dcat/3#</t>
-  </si>
-  <si>
     <t>vcard</t>
   </si>
   <si>
@@ -2899,9 +2888,6 @@
     <t>hri</t>
   </si>
   <si>
-    <t>http://data.health-ri.nl/core/p2#</t>
-  </si>
-  <si>
     <t>dcatap</t>
   </si>
   <si>
@@ -3179,9 +3165,6 @@
   </si>
   <si>
     <t>dpv:PersonalData (IRI)</t>
-  </si>
-  <si>
-    <t>dct:ProvenanceStatement (IRI)</t>
   </si>
   <si>
     <t>dpv:Purpose (IRI)</t>
@@ -3412,20 +3395,10 @@
     <t>schema</t>
   </si>
   <si>
-    <t>https://schema.org/</t>
-  </si>
-  <si>
     <t>Health Activity NAL</t>
   </si>
   <si>
-    <t>Indicate the type of Activity that was used to generate the Dataset.</t>
-  </si>
-  <si>
     <t>Relates a dataset to a SNOMED CT, ICD-10, or ORPHAcode concept representing a disease, disorder, or other clinical condition that the dataset concerns as a whole.</t>
-  </si>
-  <si>
-    <t>Use this property to describe health conditions of interest in dataset-level metadata and catalogue records. Multiple values may be provided. Select only SNOMED CT, ICD-10, or ORPHAcode concepts that represent diseases, disorders, or other clinical conditions. The relation does not assert that any individual participant has been diagnosed with a condition and is not intended to enumerate diagnoses in individual records.
-Example: A Dataset concerning myocardial infarction can use http://snomed.info/id/22298006.</t>
   </si>
   <si>
     <t>In this context, the definition should be considered as: The data domain(s) present in the Dataset.</t>
@@ -3618,6 +3591,65 @@
   </si>
   <si>
     <t>Specifics about the observational study design.</t>
+  </si>
+  <si>
+    <t>Use this property to describe health conditions of interest in dataset-level metadata. Multiple values may be provided. Select only SNOMED CT, ICD-10, or ORPHAcode concepts that represent diseases, disorders, or other clinical conditions. The relation does not assert that any individual participant has been diagnosed with a condition and is not intended to enumerate diagnoses in individual records.
+Example: A Dataset concerning myocardial infarction can use http://snomed.info/id/22298006.</t>
+  </si>
+  <si>
+    <t>Choose the type of Activity that was used to generate the Dataset from the Health Activity controlled vocabulary.</t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>rdfs:label</t>
+  </si>
+  <si>
+    <t>In this context the definition should be considered as: A textual statement describing the provenance of the Dataset, including information about its origin, history, or activities involved in its creation or modification.</t>
+  </si>
+  <si>
+    <t>dct:ProvenanceStatement</t>
+  </si>
+  <si>
+    <t>Provide a short textual statement describing the provenance of the Dataset, such as its origin, how it was created or collected, or any relevant processing or transformations it has undergone. This statement should describe the provenance of the Dataset as a whole and be provided as free text.  You can repeat this property in multiple languages</t>
+  </si>
+  <si>
+    <t>Value: activity (Dataset A)</t>
+  </si>
+  <si>
+    <t>Value:activity (Dataset B)</t>
+  </si>
+  <si>
+    <t>Value: activity (Dataset C)</t>
+  </si>
+  <si>
+    <t>Add more columns if you need to describe additional instances of prov:Activity.</t>
+  </si>
+  <si>
+    <t>Value: provenance (Dataset 1)</t>
+  </si>
+  <si>
+    <t>Value: provenance (Dataset 2)</t>
+  </si>
+  <si>
+    <t>Add more columns if you need to describe additional instances of dct:ProvenanceStatement for provenance of additional classes (additional instances of Dataset)</t>
+  </si>
+  <si>
+    <t>ProvenanceStatement</t>
+  </si>
+  <si>
+    <t>hri:ProvenanceStatement</t>
+  </si>
+  <si>
+    <t>A Dataset may be associated with multiple types.
+The EU Dataset-type controlled vocabulary SHOULD be used.</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/dcat#</t>
+  </si>
+  <si>
+    <t>http://schema.org/</t>
   </si>
 </sst>
 </file>
@@ -4007,7 +4039,6 @@
       <sz val="11"/>
       <color theme="5"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -4847,9 +4878,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
@@ -4898,13 +4926,16 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="59" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent1" xfId="2" builtinId="29"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="320">
+  <dxfs count="356">
     <dxf>
       <font>
         <color theme="1"/>
@@ -6211,7 +6242,37 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="2"/>
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6482,6 +6543,336 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -9832,45 +10223,45 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
+        <v>403</v>
+      </c>
+      <c r="M1" s="223" t="s">
         <v>404</v>
       </c>
-      <c r="M1" s="223" t="s">
-        <v>405</v>
-      </c>
       <c r="N1" s="92" t="s">
+        <v>820</v>
+      </c>
+      <c r="O1" s="92" t="s">
+        <v>821</v>
+      </c>
+      <c r="P1" s="92" t="s">
+        <v>822</v>
+      </c>
+      <c r="Q1" s="92" t="s">
+        <v>823</v>
+      </c>
+      <c r="R1" s="92" t="s">
+        <v>824</v>
+      </c>
+      <c r="S1" s="92" t="s">
         <v>825</v>
-      </c>
-      <c r="O1" s="92" t="s">
-        <v>826</v>
-      </c>
-      <c r="P1" s="92" t="s">
-        <v>827</v>
-      </c>
-      <c r="Q1" s="92" t="s">
-        <v>828</v>
-      </c>
-      <c r="R1" s="92" t="s">
-        <v>829</v>
-      </c>
-      <c r="S1" s="92" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="121" t="s">
+        <v>405</v>
+      </c>
+      <c r="B2" s="35" t="s">
         <v>406</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="C2" s="121" t="s">
         <v>407</v>
-      </c>
-      <c r="C2" s="121" t="s">
-        <v>408</v>
       </c>
       <c r="D2" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="35" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>17</v>
@@ -9888,37 +10279,37 @@
         <v>37</v>
       </c>
       <c r="K2" s="98" t="s">
+        <v>409</v>
+      </c>
+      <c r="L2" s="141" t="s">
         <v>410</v>
       </c>
-      <c r="L2" s="141" t="s">
-        <v>411</v>
-      </c>
       <c r="M2" s="141" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="O2" s="243" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="P2" s="243" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="S2" s="156"/>
     </row>
     <row r="3" spans="1:19" ht="64" x14ac:dyDescent="0.2">
       <c r="A3" s="125" t="s">
+        <v>411</v>
+      </c>
+      <c r="B3" s="74" t="s">
         <v>412</v>
       </c>
-      <c r="B3" s="74" t="s">
+      <c r="C3" s="125" t="s">
         <v>413</v>
-      </c>
-      <c r="C3" s="125" t="s">
-        <v>414</v>
       </c>
       <c r="D3" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="85" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F3" s="127" t="s">
         <v>35</v>
@@ -9936,15 +10327,15 @@
         <v>37</v>
       </c>
       <c r="K3" s="98" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L3" s="129"/>
       <c r="M3" s="129"/>
       <c r="O3" s="243" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P3" s="243" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S3" s="156"/>
     </row>
@@ -9962,7 +10353,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>17</v>
@@ -9985,28 +10376,28 @@
       <c r="L4" s="107"/>
       <c r="M4" s="107"/>
       <c r="O4" s="243" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P4" s="243" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S4" s="156"/>
     </row>
     <row r="5" spans="1:19" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="131" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="C5" s="121" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="D5" s="245" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="F5" s="124" t="s">
         <v>17</v>
@@ -10032,25 +10423,25 @@
     </row>
     <row r="6" spans="1:19" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="125" t="s">
+        <v>417</v>
+      </c>
+      <c r="B6" s="74" t="s">
         <v>418</v>
       </c>
-      <c r="B6" s="74" t="s">
+      <c r="C6" s="134" t="s">
         <v>419</v>
-      </c>
-      <c r="C6" s="134" t="s">
-        <v>420</v>
       </c>
       <c r="D6" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="126" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F6" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="127" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H6" s="127" t="s">
         <v>81</v>
@@ -10062,39 +10453,39 @@
         <v>29</v>
       </c>
       <c r="K6" s="98" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L6" s="129"/>
       <c r="M6" s="129"/>
       <c r="O6" s="243" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="P6" s="243" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="S6" s="156"/>
     </row>
     <row r="7" spans="1:19" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" s="121" t="s">
+        <v>423</v>
+      </c>
+      <c r="B7" s="35" t="s">
         <v>424</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="C7" s="121" t="s">
         <v>425</v>
-      </c>
-      <c r="C7" s="121" t="s">
-        <v>426</v>
       </c>
       <c r="D7" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F7" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="128" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H7" s="124" t="s">
         <v>81</v>
@@ -10106,46 +10497,46 @@
         <v>29</v>
       </c>
       <c r="K7" s="98" t="s">
+        <v>428</v>
+      </c>
+      <c r="L7" s="107" t="s">
         <v>429</v>
       </c>
-      <c r="L7" s="107" t="s">
-        <v>430</v>
-      </c>
       <c r="M7" s="107" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="O7" s="243" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="P7" s="243" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="S7" s="156"/>
     </row>
     <row r="8" spans="1:19" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" s="125" t="s">
+        <v>430</v>
+      </c>
+      <c r="B8" s="74" t="s">
         <v>431</v>
       </c>
-      <c r="B8" s="74" t="s">
+      <c r="C8" s="134" t="s">
         <v>432</v>
       </c>
-      <c r="C8" s="134" t="s">
+      <c r="D8" s="185" t="s">
         <v>433</v>
       </c>
-      <c r="D8" s="185" t="s">
+      <c r="E8" s="126" t="s">
         <v>434</v>
-      </c>
-      <c r="E8" s="126" t="s">
-        <v>435</v>
       </c>
       <c r="F8" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G8" s="156" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H8" s="127" t="s">
         <v>81</v>
@@ -10157,15 +10548,15 @@
         <v>29</v>
       </c>
       <c r="K8" s="98" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L8" s="129"/>
       <c r="M8" s="129"/>
       <c r="O8" s="243" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P8" s="243" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S8" s="156"/>
     </row>
@@ -10183,7 +10574,7 @@
         <v>16</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F9" s="124" t="s">
         <v>17</v>
@@ -10201,15 +10592,15 @@
         <v>29</v>
       </c>
       <c r="K9" s="98" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="L9" s="107"/>
       <c r="M9" s="107"/>
       <c r="O9" s="243" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="P9" s="243" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="S9" s="156" t="b">
         <v>1</v>
@@ -10229,7 +10620,7 @@
         <v>16</v>
       </c>
       <c r="E10" s="126" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F10" s="127" t="s">
         <v>17</v>
@@ -10247,33 +10638,33 @@
         <v>29</v>
       </c>
       <c r="K10" s="98" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L10" s="129"/>
       <c r="M10" s="129"/>
       <c r="O10" s="243" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P10" s="243" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S10" s="156"/>
     </row>
     <row r="11" spans="1:19" ht="48" x14ac:dyDescent="0.2">
       <c r="A11" s="121" t="s">
+        <v>441</v>
+      </c>
+      <c r="B11" s="35" t="s">
         <v>442</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="C11" s="141" t="s">
         <v>443</v>
-      </c>
-      <c r="C11" s="141" t="s">
-        <v>444</v>
       </c>
       <c r="D11" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F11" s="124" t="s">
         <v>17</v>
@@ -10291,39 +10682,39 @@
         <v>37</v>
       </c>
       <c r="K11" s="98" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L11" s="107"/>
       <c r="M11" s="107"/>
       <c r="O11" s="243" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P11" s="243" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S11" s="156"/>
     </row>
     <row r="12" spans="1:19" ht="48" x14ac:dyDescent="0.2">
       <c r="A12" s="125" t="s">
+        <v>446</v>
+      </c>
+      <c r="B12" s="74" t="s">
         <v>447</v>
       </c>
-      <c r="B12" s="74" t="s">
+      <c r="C12" s="125" t="s">
         <v>448</v>
       </c>
-      <c r="C12" s="125" t="s">
+      <c r="D12" s="154" t="s">
         <v>449</v>
       </c>
-      <c r="D12" s="154" t="s">
-        <v>450</v>
-      </c>
       <c r="E12" s="126" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="F12" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G12" s="127" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H12" s="127" t="s">
         <v>81</v>
@@ -10335,15 +10726,15 @@
         <v>29</v>
       </c>
       <c r="K12" s="99" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L12" s="129"/>
       <c r="M12" s="129"/>
       <c r="O12" s="243" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P12" s="243" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S12" s="156"/>
     </row>
@@ -10361,7 +10752,7 @@
         <v>85</v>
       </c>
       <c r="E13" s="138" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F13" s="124" t="s">
         <v>17</v>
@@ -10379,21 +10770,21 @@
         <v>29</v>
       </c>
       <c r="K13" s="98" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L13" s="107"/>
       <c r="M13" s="107"/>
       <c r="O13" s="243" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P13" s="243" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S13" s="156"/>
     </row>
     <row r="14" spans="1:19" ht="80" x14ac:dyDescent="0.2">
       <c r="A14" s="125" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B14" s="74" t="s">
         <v>90</v>
@@ -10405,13 +10796,13 @@
         <v>92</v>
       </c>
       <c r="E14" s="80" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F14" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G14" s="127" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H14" s="127">
         <v>1</v>
@@ -10423,21 +10814,21 @@
         <v>37</v>
       </c>
       <c r="K14" s="98" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L14" s="129"/>
       <c r="M14" s="129"/>
       <c r="O14" s="243" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P14" s="243" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S14" s="156"/>
     </row>
     <row r="15" spans="1:19" ht="80" x14ac:dyDescent="0.2">
       <c r="A15" s="121" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B15" s="35" t="s">
         <v>173</v>
@@ -10449,7 +10840,7 @@
         <v>16</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F15" s="124" t="s">
         <v>17</v>
@@ -10467,39 +10858,39 @@
         <v>29</v>
       </c>
       <c r="K15" s="98" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L15" s="107"/>
       <c r="M15" s="107"/>
       <c r="O15" s="243" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P15" s="243" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S15" s="156"/>
     </row>
     <row r="16" spans="1:19" ht="112" x14ac:dyDescent="0.2">
       <c r="A16" s="125" t="s">
+        <v>461</v>
+      </c>
+      <c r="B16" s="74" t="s">
         <v>462</v>
       </c>
-      <c r="B16" s="74" t="s">
+      <c r="C16" s="125" t="s">
         <v>463</v>
       </c>
-      <c r="C16" s="125" t="s">
+      <c r="D16" s="185" t="s">
+        <v>433</v>
+      </c>
+      <c r="E16" s="80" t="s">
         <v>464</v>
-      </c>
-      <c r="D16" s="185" t="s">
-        <v>434</v>
-      </c>
-      <c r="E16" s="80" t="s">
-        <v>465</v>
       </c>
       <c r="F16" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G16" s="127" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H16" s="127" t="s">
         <v>81</v>
@@ -10511,15 +10902,15 @@
         <v>29</v>
       </c>
       <c r="K16" s="98" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L16" s="129"/>
       <c r="M16" s="129"/>
       <c r="O16" s="243" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P16" s="243" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S16" s="156"/>
     </row>
@@ -10553,43 +10944,43 @@
         <v>29</v>
       </c>
       <c r="K17" s="98" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L17" s="107"/>
       <c r="M17" s="107"/>
       <c r="N17" s="32"/>
       <c r="O17" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="P17" s="32" t="s">
+        <v>833</v>
+      </c>
+      <c r="Q17" s="32" t="s">
         <v>838</v>
-      </c>
-      <c r="Q17" s="32" t="s">
-        <v>843</v>
       </c>
       <c r="S17" s="99"/>
     </row>
     <row r="18" spans="1:19" ht="48" x14ac:dyDescent="0.2">
       <c r="A18" s="125" t="s">
+        <v>467</v>
+      </c>
+      <c r="B18" s="74" t="s">
         <v>468</v>
       </c>
-      <c r="B18" s="74" t="s">
+      <c r="C18" s="125" t="s">
         <v>469</v>
       </c>
-      <c r="C18" s="125" t="s">
+      <c r="D18" s="185" t="s">
+        <v>433</v>
+      </c>
+      <c r="E18" s="74" t="s">
         <v>470</v>
-      </c>
-      <c r="D18" s="185" t="s">
-        <v>434</v>
-      </c>
-      <c r="E18" s="74" t="s">
-        <v>471</v>
       </c>
       <c r="F18" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G18" s="127" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H18" s="127" t="s">
         <v>81</v>
@@ -10601,15 +10992,15 @@
         <v>29</v>
       </c>
       <c r="K18" s="98" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L18" s="129"/>
       <c r="M18" s="129"/>
       <c r="O18" s="243" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P18" s="243" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S18" s="156"/>
     </row>
@@ -10627,7 +11018,7 @@
         <v>16</v>
       </c>
       <c r="E19" s="132" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F19" s="124" t="s">
         <v>17</v>
@@ -10645,19 +11036,19 @@
         <v>29</v>
       </c>
       <c r="K19" s="98" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L19" s="107"/>
       <c r="M19" s="107"/>
       <c r="N19" s="32"/>
       <c r="O19" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="P19" s="32" t="s">
+        <v>833</v>
+      </c>
+      <c r="Q19" s="32" t="s">
         <v>838</v>
-      </c>
-      <c r="Q19" s="32" t="s">
-        <v>843</v>
       </c>
       <c r="S19" s="99"/>
     </row>
@@ -10669,11 +11060,11 @@
         <v>300</v>
       </c>
       <c r="C20" s="125" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D20" s="126"/>
       <c r="E20" s="74" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="F20" s="127" t="s">
         <v>17</v>
@@ -10692,19 +11083,19 @@
       </c>
       <c r="K20" s="104"/>
       <c r="L20" s="129" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M20" s="129" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="O20" s="243" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="P20" s="243" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="S20" s="156"/>
     </row>
@@ -10722,7 +11113,7 @@
         <v>16</v>
       </c>
       <c r="E21" s="79" t="s">
-        <v>910</v>
+        <v>901</v>
       </c>
       <c r="F21" s="190" t="s">
         <v>17</v>
@@ -10740,15 +11131,15 @@
         <v>29</v>
       </c>
       <c r="K21" s="99" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L21" s="107"/>
       <c r="M21" s="107"/>
       <c r="O21" s="243" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P21" s="243" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S21" s="156"/>
     </row>
@@ -10763,10 +11154,10 @@
         <v>315</v>
       </c>
       <c r="D22" s="154" t="s">
+        <v>477</v>
+      </c>
+      <c r="E22" s="81" t="s">
         <v>478</v>
-      </c>
-      <c r="E22" s="81" t="s">
-        <v>479</v>
       </c>
       <c r="F22" s="127" t="s">
         <v>17</v>
@@ -10784,15 +11175,15 @@
         <v>29</v>
       </c>
       <c r="K22" s="98" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="L22" s="129"/>
       <c r="M22" s="129"/>
       <c r="O22" s="243" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P22" s="243" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S22" s="156"/>
     </row>
@@ -10810,7 +11201,7 @@
         <v>16</v>
       </c>
       <c r="E23" s="132" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F23" s="124" t="s">
         <v>17</v>
@@ -10831,10 +11222,10 @@
       <c r="L23" s="107"/>
       <c r="M23" s="107"/>
       <c r="O23" s="243" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="P23" s="243" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="S23" s="156"/>
     </row>
@@ -10852,7 +11243,7 @@
         <v>16</v>
       </c>
       <c r="E24" s="126" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F24" s="127" t="s">
         <v>17</v>
@@ -10870,15 +11261,15 @@
         <v>29</v>
       </c>
       <c r="K24" s="98" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L24" s="129"/>
       <c r="M24" s="129"/>
       <c r="O24" s="243" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="P24" s="243" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="S24" s="156" t="b">
         <v>1</v>
@@ -11226,54 +11617,54 @@
     <sortCondition ref="A2:A24"/>
   </sortState>
   <conditionalFormatting sqref="F2:F54">
-    <cfRule type="cellIs" dxfId="238" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="274" priority="16" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H54">
-    <cfRule type="cellIs" dxfId="237" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="273" priority="17" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="236" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="272" priority="18" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F54">
-    <cfRule type="cellIs" dxfId="235" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="271" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="234" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="270" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="233" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="269" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="232" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="268" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J54">
-    <cfRule type="containsText" dxfId="231" priority="13" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="267" priority="13" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="230" priority="14" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="266" priority="14" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="229" priority="15" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="265" priority="15" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:S1">
-    <cfRule type="cellIs" dxfId="228" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="264" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="227" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="263" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="226" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="262" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="225" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="261" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11376,25 +11767,25 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="M1" s="92" t="s">
+        <v>820</v>
+      </c>
+      <c r="N1" s="92" t="s">
+        <v>821</v>
+      </c>
+      <c r="O1" s="92" t="s">
+        <v>822</v>
+      </c>
+      <c r="P1" s="92" t="s">
+        <v>823</v>
+      </c>
+      <c r="Q1" s="92" t="s">
+        <v>824</v>
+      </c>
+      <c r="R1" s="92" t="s">
         <v>825</v>
-      </c>
-      <c r="N1" s="92" t="s">
-        <v>826</v>
-      </c>
-      <c r="O1" s="92" t="s">
-        <v>827</v>
-      </c>
-      <c r="P1" s="92" t="s">
-        <v>828</v>
-      </c>
-      <c r="Q1" s="92" t="s">
-        <v>829</v>
-      </c>
-      <c r="R1" s="92" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="16" x14ac:dyDescent="0.2">
@@ -11411,7 +11802,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="74" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>17</v>
@@ -11429,14 +11820,14 @@
         <v>29</v>
       </c>
       <c r="K2" s="98" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="L2" s="129"/>
       <c r="N2" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O2" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="64" x14ac:dyDescent="0.2">
@@ -11471,19 +11862,19 @@
         <v>29</v>
       </c>
       <c r="K3" s="98" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L3" s="107" t="s">
         <v>39</v>
       </c>
       <c r="M3" s="32" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="N3" s="32" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="O3" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="16" x14ac:dyDescent="0.2">
@@ -11500,7 +11891,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="126" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F4" s="127" t="s">
         <v>35</v>
@@ -11518,14 +11909,14 @@
         <v>29</v>
       </c>
       <c r="K4" s="99" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L4" s="129"/>
       <c r="N4" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="O4" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="R4" s="32" t="b">
         <v>1</v>
@@ -11545,7 +11936,7 @@
         <v>193</v>
       </c>
       <c r="E5" s="135" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F5" s="124" t="s">
         <v>17</v>
@@ -11565,117 +11956,117 @@
       <c r="K5" s="105"/>
       <c r="L5" s="107"/>
       <c r="N5" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O5" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" s="261" t="s">
+      <c r="A6" s="260" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="262" t="s">
+      <c r="B6" s="261" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="261" t="s">
+      <c r="C6" s="260" t="s">
         <v>62</v>
       </c>
       <c r="D6" s="215" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="263" t="s">
+      <c r="E6" s="262" t="s">
         <v>196</v>
       </c>
-      <c r="F6" s="260" t="s">
+      <c r="F6" s="259" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="260" t="s">
+      <c r="G6" s="259" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="260" t="s">
+      <c r="H6" s="259" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="258" t="s">
+      <c r="I6" s="257" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="251" t="s">
+      <c r="J6" s="250" t="s">
         <v>66</v>
       </c>
-      <c r="K6" s="259" t="s">
-        <v>491</v>
-      </c>
-      <c r="L6" s="258"/>
+      <c r="K6" s="258" t="s">
+        <v>490</v>
+      </c>
+      <c r="L6" s="257"/>
       <c r="N6" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O6" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" s="261"/>
-      <c r="B7" s="262"/>
-      <c r="C7" s="261"/>
+      <c r="A7" s="260"/>
+      <c r="B7" s="261"/>
+      <c r="C7" s="260"/>
       <c r="D7" s="216" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="263"/>
-      <c r="F7" s="260"/>
-      <c r="G7" s="260"/>
-      <c r="H7" s="260"/>
-      <c r="I7" s="258"/>
-      <c r="J7" s="251"/>
-      <c r="K7" s="259"/>
-      <c r="L7" s="258"/>
+      <c r="E7" s="262"/>
+      <c r="F7" s="259"/>
+      <c r="G7" s="259"/>
+      <c r="H7" s="259"/>
+      <c r="I7" s="257"/>
+      <c r="J7" s="250"/>
+      <c r="K7" s="258"/>
+      <c r="L7" s="257"/>
     </row>
     <row r="8" spans="1:18" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="261"/>
-      <c r="B8" s="262"/>
-      <c r="C8" s="261"/>
+      <c r="A8" s="260"/>
+      <c r="B8" s="261"/>
+      <c r="C8" s="260"/>
       <c r="D8" s="216" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="263"/>
-      <c r="F8" s="260"/>
-      <c r="G8" s="260"/>
-      <c r="H8" s="260"/>
-      <c r="I8" s="258"/>
-      <c r="J8" s="251"/>
-      <c r="K8" s="259"/>
-      <c r="L8" s="258"/>
+      <c r="E8" s="262"/>
+      <c r="F8" s="259"/>
+      <c r="G8" s="259"/>
+      <c r="H8" s="259"/>
+      <c r="I8" s="257"/>
+      <c r="J8" s="250"/>
+      <c r="K8" s="258"/>
+      <c r="L8" s="257"/>
     </row>
     <row r="9" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="261"/>
-      <c r="B9" s="262"/>
-      <c r="C9" s="261"/>
+      <c r="A9" s="260"/>
+      <c r="B9" s="261"/>
+      <c r="C9" s="260"/>
       <c r="D9" s="139" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="263"/>
-      <c r="F9" s="260"/>
-      <c r="G9" s="260"/>
-      <c r="H9" s="260"/>
-      <c r="I9" s="258"/>
-      <c r="J9" s="251"/>
-      <c r="K9" s="259"/>
-      <c r="L9" s="258"/>
+      <c r="E9" s="262"/>
+      <c r="F9" s="259"/>
+      <c r="G9" s="259"/>
+      <c r="H9" s="259"/>
+      <c r="I9" s="257"/>
+      <c r="J9" s="250"/>
+      <c r="K9" s="258"/>
+      <c r="L9" s="257"/>
     </row>
     <row r="10" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="261"/>
-      <c r="B10" s="262"/>
-      <c r="C10" s="261"/>
+      <c r="A10" s="260"/>
+      <c r="B10" s="261"/>
+      <c r="C10" s="260"/>
       <c r="D10" s="139" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="263"/>
-      <c r="F10" s="260"/>
-      <c r="G10" s="260"/>
-      <c r="H10" s="260"/>
-      <c r="I10" s="258"/>
-      <c r="J10" s="251"/>
-      <c r="K10" s="259"/>
-      <c r="L10" s="258"/>
+      <c r="E10" s="262"/>
+      <c r="F10" s="259"/>
+      <c r="G10" s="259"/>
+      <c r="H10" s="259"/>
+      <c r="I10" s="257"/>
+      <c r="J10" s="250"/>
+      <c r="K10" s="258"/>
+      <c r="L10" s="257"/>
     </row>
     <row r="11" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="121" t="s">
@@ -11691,7 +12082,7 @@
         <v>16</v>
       </c>
       <c r="E11" s="132" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F11" s="124" t="s">
         <v>17</v>
@@ -11709,17 +12100,17 @@
         <v>29</v>
       </c>
       <c r="K11" s="99" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L11" s="107"/>
       <c r="N11" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="O11" s="32" t="s">
+        <v>833</v>
+      </c>
+      <c r="P11" s="32" t="s">
         <v>838</v>
-      </c>
-      <c r="P11" s="32" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="32" x14ac:dyDescent="0.2">
@@ -11736,7 +12127,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="126" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F12" s="124" t="s">
         <v>17</v>
@@ -11754,19 +12145,19 @@
         <v>29</v>
       </c>
       <c r="K12" s="98" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L12" s="129" t="s">
         <v>46</v>
       </c>
       <c r="M12" s="32" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="N12" s="32" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="O12" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="32" x14ac:dyDescent="0.2">
@@ -11783,7 +12174,7 @@
         <v>16</v>
       </c>
       <c r="E13" s="132" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>17</v>
@@ -11801,17 +12192,17 @@
         <v>29</v>
       </c>
       <c r="K13" s="98" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L13" s="107"/>
       <c r="N13" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="O13" s="32" t="s">
+        <v>833</v>
+      </c>
+      <c r="P13" s="32" t="s">
         <v>838</v>
-      </c>
-      <c r="P13" s="32" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="49" customHeight="1" x14ac:dyDescent="0.2">
@@ -11828,7 +12219,7 @@
         <v>16</v>
       </c>
       <c r="E14" s="126" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F14" s="124" t="s">
         <v>17</v>
@@ -11846,19 +12237,19 @@
         <v>29</v>
       </c>
       <c r="K14" s="98" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="L14" s="129" t="s">
         <v>302</v>
       </c>
       <c r="M14" s="32" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="N14" s="32" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="O14" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="16" x14ac:dyDescent="0.2">
@@ -11875,7 +12266,7 @@
         <v>16</v>
       </c>
       <c r="E15" s="121" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>35</v>
@@ -11897,10 +12288,10 @@
       </c>
       <c r="L15" s="107"/>
       <c r="N15" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="O15" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="R15" s="32" t="b">
         <v>1</v>
@@ -12042,65 +12433,65 @@
     <mergeCell ref="J6:J10"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F6 F11:F15">
-    <cfRule type="cellIs" dxfId="224" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="260" priority="11" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H6 H11 G12:I12">
-    <cfRule type="cellIs" dxfId="223" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="259" priority="12" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="222" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="258" priority="13" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F6 F11:F15">
-    <cfRule type="cellIs" dxfId="221" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="257" priority="14" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="220" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="256" priority="15" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="219" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="255" priority="16" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="218" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="254" priority="17" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="containsText" dxfId="217" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="253" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="216" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="252" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="215" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="251" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J15">
-    <cfRule type="containsText" dxfId="214" priority="8" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="250" priority="8" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="213" priority="9" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="249" priority="9" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="212" priority="10" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="248" priority="10" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:R1">
-    <cfRule type="cellIs" dxfId="211" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="247" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="210" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="246" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="209" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="245" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="208" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="244" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12197,25 +12588,25 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="M1" s="92" t="s">
+        <v>820</v>
+      </c>
+      <c r="N1" s="92" t="s">
+        <v>821</v>
+      </c>
+      <c r="O1" s="92" t="s">
+        <v>822</v>
+      </c>
+      <c r="P1" s="92" t="s">
+        <v>823</v>
+      </c>
+      <c r="Q1" s="92" t="s">
+        <v>824</v>
+      </c>
+      <c r="R1" s="92" t="s">
         <v>825</v>
-      </c>
-      <c r="N1" s="92" t="s">
-        <v>826</v>
-      </c>
-      <c r="O1" s="92" t="s">
-        <v>827</v>
-      </c>
-      <c r="P1" s="92" t="s">
-        <v>828</v>
-      </c>
-      <c r="Q1" s="92" t="s">
-        <v>829</v>
-      </c>
-      <c r="R1" s="92" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="84" x14ac:dyDescent="0.2">
@@ -12232,7 +12623,7 @@
         <v>152</v>
       </c>
       <c r="E2" s="82" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>35</v>
@@ -12250,14 +12641,14 @@
         <v>37</v>
       </c>
       <c r="K2" s="107" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L2" s="186"/>
       <c r="N2" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O2" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="32" x14ac:dyDescent="0.2">
@@ -12292,15 +12683,15 @@
       <c r="K3" s="106"/>
       <c r="L3" s="129"/>
       <c r="N3" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O3" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="121" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B4" s="35" t="s">
         <v>173</v>
@@ -12312,7 +12703,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="194" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>17</v>
@@ -12332,10 +12723,10 @@
       <c r="K4" s="107"/>
       <c r="L4" s="107"/>
       <c r="N4" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O4" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="64" x14ac:dyDescent="0.2">
@@ -12374,13 +12765,13 @@
         <v>39</v>
       </c>
       <c r="M5" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="N5" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="O5" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="160" x14ac:dyDescent="0.2">
@@ -12419,13 +12810,13 @@
         <v>46</v>
       </c>
       <c r="M6" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="N6" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="O6" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="32" x14ac:dyDescent="0.2">
@@ -12460,10 +12851,10 @@
       <c r="K7" s="107"/>
       <c r="L7" s="129"/>
       <c r="N7" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O7" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="42" x14ac:dyDescent="0.2">
@@ -12480,7 +12871,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="82" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F8" s="124" t="s">
         <v>35</v>
@@ -12498,14 +12889,14 @@
         <v>37</v>
       </c>
       <c r="K8" s="107" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L8" s="107"/>
       <c r="N8" s="107" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="O8" s="107" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -12513,25 +12904,25 @@
     </row>
     <row r="9" spans="1:18" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="125" t="s">
+        <v>506</v>
+      </c>
+      <c r="B9" s="74" t="s">
         <v>507</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="C9" s="125" t="s">
         <v>508</v>
-      </c>
-      <c r="C9" s="125" t="s">
-        <v>509</v>
       </c>
       <c r="D9" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="212" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>35</v>
       </c>
       <c r="G9" s="127" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H9" s="127">
         <v>1</v>
@@ -12543,37 +12934,37 @@
         <v>37</v>
       </c>
       <c r="K9" s="106" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="L9" s="129"/>
       <c r="N9" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O9" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" s="121" t="s">
+        <v>511</v>
+      </c>
+      <c r="B10" s="35" t="s">
         <v>512</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="C10" s="121" t="s">
         <v>513</v>
-      </c>
-      <c r="C10" s="121" t="s">
-        <v>514</v>
       </c>
       <c r="D10" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F10" s="124" t="s">
         <v>35</v>
       </c>
       <c r="G10" s="124" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H10" s="133">
         <v>1</v>
@@ -12585,35 +12976,35 @@
         <v>37</v>
       </c>
       <c r="K10" s="106" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L10" s="107"/>
       <c r="N10" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O10" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="48" x14ac:dyDescent="0.2">
       <c r="A11" s="125" t="s">
+        <v>446</v>
+      </c>
+      <c r="B11" s="74" t="s">
         <v>447</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="C11" s="134" t="s">
         <v>448</v>
       </c>
-      <c r="C11" s="134" t="s">
+      <c r="D11" s="154" t="s">
         <v>449</v>
-      </c>
-      <c r="D11" s="154" t="s">
-        <v>450</v>
       </c>
       <c r="E11" s="126"/>
       <c r="F11" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="127" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H11" s="127" t="s">
         <v>19</v>
@@ -12627,21 +13018,21 @@
       <c r="K11" s="107"/>
       <c r="L11" s="129"/>
       <c r="N11" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O11" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="121" t="s">
+        <v>516</v>
+      </c>
+      <c r="B12" s="35" t="s">
         <v>517</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="C12" s="121" t="s">
         <v>518</v>
-      </c>
-      <c r="C12" s="121" t="s">
-        <v>519</v>
       </c>
       <c r="D12" s="132" t="s">
         <v>16</v>
@@ -12665,10 +13056,10 @@
       <c r="K12" s="106"/>
       <c r="L12" s="107"/>
       <c r="N12" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O12" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="64" x14ac:dyDescent="0.2">
@@ -12685,7 +13076,7 @@
         <v>16</v>
       </c>
       <c r="E13" s="126" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F13" s="127" t="s">
         <v>35</v>
@@ -12705,10 +13096,10 @@
       <c r="K13" s="106"/>
       <c r="L13" s="129"/>
       <c r="N13" s="107" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="O13" s="107" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="16" x14ac:dyDescent="0.2">
@@ -12743,27 +13134,27 @@
       <c r="K14" s="106"/>
       <c r="L14" s="107"/>
       <c r="N14" s="107" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="O14" s="107" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="64" x14ac:dyDescent="0.2">
       <c r="A15" s="125" t="s">
+        <v>520</v>
+      </c>
+      <c r="B15" s="74" t="s">
         <v>521</v>
       </c>
-      <c r="B15" s="74" t="s">
+      <c r="C15" s="125" t="s">
         <v>522</v>
-      </c>
-      <c r="C15" s="125" t="s">
-        <v>523</v>
       </c>
       <c r="D15" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="126" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F15" s="127" t="s">
         <v>17</v>
@@ -12783,10 +13174,10 @@
       <c r="K15" s="106"/>
       <c r="L15" s="129"/>
       <c r="N15" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O15" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="48" x14ac:dyDescent="0.2">
@@ -12803,7 +13194,7 @@
         <v>85</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F16" s="124" t="s">
         <v>17</v>
@@ -12823,10 +13214,10 @@
       <c r="K16" s="106"/>
       <c r="L16" s="107"/>
       <c r="N16" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O16" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="64" x14ac:dyDescent="0.2">
@@ -12843,7 +13234,7 @@
         <v>92</v>
       </c>
       <c r="E17" s="80" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F17" s="127" t="s">
         <v>35</v>
@@ -12861,14 +13252,14 @@
         <v>37</v>
       </c>
       <c r="K17" s="107" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L17" s="129"/>
       <c r="N17" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O17" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="48" x14ac:dyDescent="0.2">
@@ -12885,7 +13276,7 @@
         <v>16</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F18" s="124" t="s">
         <v>17</v>
@@ -12905,13 +13296,13 @@
       <c r="K18" s="106"/>
       <c r="L18" s="107"/>
       <c r="N18" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="O18" t="s">
+        <v>833</v>
+      </c>
+      <c r="P18" s="32" t="s">
         <v>838</v>
-      </c>
-      <c r="P18" s="32" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="16" x14ac:dyDescent="0.2">
@@ -12945,16 +13336,16 @@
       </c>
       <c r="K19" s="106"/>
       <c r="L19" s="129" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="M19" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="N19" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="O19" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="48" x14ac:dyDescent="0.2">
@@ -12971,7 +13362,7 @@
         <v>16</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F20" s="124" t="s">
         <v>35</v>
@@ -12993,30 +13384,30 @@
         <v>46</v>
       </c>
       <c r="M20" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="N20" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="O20" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" s="125" t="s">
+        <v>530</v>
+      </c>
+      <c r="B21" s="74" t="s">
         <v>531</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="C21" s="125" t="s">
         <v>532</v>
-      </c>
-      <c r="C21" s="125" t="s">
-        <v>533</v>
       </c>
       <c r="D21" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="126" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F21" s="127" t="s">
         <v>17</v>
@@ -13034,16 +13425,16 @@
         <v>29</v>
       </c>
       <c r="K21" s="107" t="s">
+        <v>534</v>
+      </c>
+      <c r="L21" s="192" t="s">
         <v>535</v>
       </c>
-      <c r="L21" s="192" t="s">
-        <v>536</v>
-      </c>
       <c r="N21" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O21" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="48" x14ac:dyDescent="0.2">
@@ -13060,7 +13451,7 @@
         <v>326</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F22" s="124" t="s">
         <v>35</v>
@@ -13080,10 +13471,10 @@
       <c r="K22" s="106"/>
       <c r="L22" s="107"/>
       <c r="N22" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O22" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="32" x14ac:dyDescent="0.2">
@@ -13100,7 +13491,7 @@
         <v>16</v>
       </c>
       <c r="E23" s="126" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F23" s="127" t="s">
         <v>35</v>
@@ -13118,14 +13509,14 @@
         <v>29</v>
       </c>
       <c r="K23" s="106" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="L23" s="195"/>
       <c r="N23" s="107" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="O23" s="107" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="R23" t="b">
         <v>1</v>
@@ -13539,54 +13930,54 @@
     <sortCondition ref="A2:A23"/>
   </sortState>
   <conditionalFormatting sqref="F2:F53">
-    <cfRule type="cellIs" dxfId="207" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="243" priority="12" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H53">
-    <cfRule type="cellIs" dxfId="206" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="242" priority="13" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="205" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="241" priority="14" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F53">
-    <cfRule type="cellIs" dxfId="204" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="240" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="203" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="239" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="202" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="238" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="201" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="237" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J53">
-    <cfRule type="containsText" dxfId="200" priority="9" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="236" priority="9" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="199" priority="10" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="235" priority="10" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="198" priority="11" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="234" priority="11" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:R1">
-    <cfRule type="cellIs" dxfId="197" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="233" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="196" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="232" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="195" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="231" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="194" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="230" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13674,51 +14065,51 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>539</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>540</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="227" t="s">
         <v>541</v>
       </c>
-      <c r="N1" s="227" t="s">
+      <c r="O1" s="233" t="s">
         <v>542</v>
       </c>
-      <c r="O1" s="233" t="s">
-        <v>543</v>
-      </c>
       <c r="P1" s="92" t="s">
+        <v>820</v>
+      </c>
+      <c r="Q1" s="92" t="s">
+        <v>821</v>
+      </c>
+      <c r="R1" s="92" t="s">
+        <v>822</v>
+      </c>
+      <c r="S1" s="92" t="s">
+        <v>823</v>
+      </c>
+      <c r="T1" s="92" t="s">
+        <v>824</v>
+      </c>
+      <c r="U1" s="92" t="s">
         <v>825</v>
-      </c>
-      <c r="Q1" s="92" t="s">
-        <v>826</v>
-      </c>
-      <c r="R1" s="92" t="s">
-        <v>827</v>
-      </c>
-      <c r="S1" s="92" t="s">
-        <v>828</v>
-      </c>
-      <c r="T1" s="92" t="s">
-        <v>829</v>
-      </c>
-      <c r="U1" s="92" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="80" x14ac:dyDescent="0.2">
       <c r="A2" s="196" t="s">
+        <v>543</v>
+      </c>
+      <c r="B2" s="45" t="s">
         <v>544</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="C2" s="76" t="s">
         <v>545</v>
-      </c>
-      <c r="C2" s="76" t="s">
-        <v>546</v>
       </c>
       <c r="D2" s="196" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="197" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F2" s="198" t="s">
         <v>35</v>
@@ -13727,7 +14118,7 @@
         <v>58</v>
       </c>
       <c r="H2" s="198" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="I2" s="160" t="s">
         <v>20</v>
@@ -13740,21 +14131,21 @@
       <c r="M2" s="186"/>
       <c r="N2" s="186"/>
       <c r="Q2" s="156" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="R2" s="156" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="68" t="s">
+        <v>548</v>
+      </c>
+      <c r="B3" s="61" t="s">
         <v>549</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="C3" s="77" t="s">
         <v>550</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>551</v>
       </c>
       <c r="D3" s="68" t="s">
         <v>16</v>
@@ -13780,57 +14171,57 @@
       <c r="M3" s="195"/>
       <c r="N3" s="195"/>
       <c r="Q3" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="R3" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="193" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="229" priority="9" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="192" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="228" priority="10" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="191" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="227" priority="11" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="190" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="226" priority="12" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="189" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="225" priority="13" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="188" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="224" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="187" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="223" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="186" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="222" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="185" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="221" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1:U1">
-    <cfRule type="cellIs" dxfId="184" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="220" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="183" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="219" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="182" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="218" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="181" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="217" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13913,54 +14304,54 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>551</v>
+      </c>
+      <c r="M1" s="220" t="s">
         <v>552</v>
       </c>
-      <c r="M1" s="220" t="s">
+      <c r="N1" s="226" t="s">
         <v>553</v>
       </c>
-      <c r="N1" s="226" t="s">
+      <c r="O1" s="230" t="s">
         <v>554</v>
       </c>
-      <c r="O1" s="230" t="s">
+      <c r="P1" s="227" t="s">
         <v>555</v>
       </c>
-      <c r="P1" s="227" t="s">
+      <c r="Q1" s="231" t="s">
         <v>556</v>
       </c>
-      <c r="Q1" s="231" t="s">
+      <c r="R1" s="233" t="s">
         <v>557</v>
       </c>
-      <c r="R1" s="233" t="s">
-        <v>558</v>
-      </c>
       <c r="S1" s="92" t="s">
+        <v>820</v>
+      </c>
+      <c r="T1" s="92" t="s">
+        <v>821</v>
+      </c>
+      <c r="U1" s="92" t="s">
+        <v>822</v>
+      </c>
+      <c r="V1" s="92" t="s">
+        <v>823</v>
+      </c>
+      <c r="W1" s="92" t="s">
+        <v>824</v>
+      </c>
+      <c r="X1" s="92" t="s">
         <v>825</v>
-      </c>
-      <c r="T1" s="92" t="s">
-        <v>826</v>
-      </c>
-      <c r="U1" s="92" t="s">
-        <v>827</v>
-      </c>
-      <c r="V1" s="92" t="s">
-        <v>828</v>
-      </c>
-      <c r="W1" s="92" t="s">
-        <v>829</v>
-      </c>
-      <c r="X1" s="92" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="58" t="s">
+        <v>558</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>559</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="C2" s="76" t="s">
         <v>560</v>
-      </c>
-      <c r="C2" s="76" t="s">
-        <v>561</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
@@ -13986,24 +14377,24 @@
       <c r="P2" s="221"/>
       <c r="Q2" s="221"/>
       <c r="T2" s="2" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="U2" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="V2" s="32" t="s">
         <v>838</v>
-      </c>
-      <c r="V2" s="32" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="48" t="s">
+        <v>561</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>562</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>563</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>564</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>16</v>
@@ -14032,13 +14423,13 @@
       <c r="P3" s="222"/>
       <c r="Q3" s="222"/>
       <c r="T3" s="2" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="U3" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="V3" s="32" t="s">
         <v>838</v>
-      </c>
-      <c r="V3" s="32" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.2">
@@ -14528,85 +14919,85 @@
     <sortCondition ref="A2:A3"/>
   </sortState>
   <conditionalFormatting sqref="A41:B42">
-    <cfRule type="cellIs" dxfId="180" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="216" priority="15" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="179" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="215" priority="16" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="178" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="214" priority="17" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="177" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="213" priority="18" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E42">
-    <cfRule type="cellIs" dxfId="176" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="212" priority="19" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="175" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="211" priority="20" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="174" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="210" priority="21" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="173" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="209" priority="22" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F52">
-    <cfRule type="cellIs" dxfId="172" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="208" priority="9" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="171" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="207" priority="10" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="170" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="206" priority="11" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="205" priority="12" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="204" priority="13" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H9 H11:H15 H17:H25 H27:H41 H50:H52">
-    <cfRule type="cellIs" dxfId="167" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="203" priority="23" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="202" priority="24" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F52">
-    <cfRule type="cellIs" dxfId="165" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="201" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="164" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="200" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="163" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="199" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="198" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S1:X1">
-    <cfRule type="cellIs" dxfId="161" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="197" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="196" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="159" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="195" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="194" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14633,6 +15024,438 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C4D8ABF-9A9D-204F-A1CC-972CCEA8D26A}">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:T23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.83203125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="28.5" style="9" customWidth="1"/>
+    <col min="3" max="4" width="17.83203125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="27.83203125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="26.5" style="2" customWidth="1"/>
+    <col min="8" max="10" width="17.83203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.83203125" style="2" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="17.5" style="2" customWidth="1"/>
+    <col min="13" max="13" width="19.5" style="2" customWidth="1"/>
+    <col min="14" max="14" width="33.1640625" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9.1640625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="89" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="91" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="89" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="89" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="89" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="90" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="90" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="219" t="s">
+        <v>921</v>
+      </c>
+      <c r="M1" s="226" t="s">
+        <v>922</v>
+      </c>
+      <c r="N1" s="233" t="s">
+        <v>923</v>
+      </c>
+      <c r="O1" s="97" t="s">
+        <v>820</v>
+      </c>
+      <c r="P1" s="97" t="s">
+        <v>821</v>
+      </c>
+      <c r="Q1" s="97" t="s">
+        <v>822</v>
+      </c>
+      <c r="R1" s="97" t="s">
+        <v>823</v>
+      </c>
+      <c r="S1" s="97" t="s">
+        <v>824</v>
+      </c>
+      <c r="T1" s="97" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="176" x14ac:dyDescent="0.2">
+      <c r="A2" s="44" t="s">
+        <v>912</v>
+      </c>
+      <c r="B2" s="57" t="s">
+        <v>914</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>913</v>
+      </c>
+      <c r="D2" s="78" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="197" t="s">
+        <v>916</v>
+      </c>
+      <c r="F2" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="204" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="47"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A4" s="13"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A5" s="13"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A6" s="13"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A7" s="13"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A8" s="13"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A9" s="13"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A10" s="13"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A11" s="13"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A12" s="13"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A13" s="13"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A14" s="13"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A15" s="13"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A16" s="13"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="13"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="13"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="3"/>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="13"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="13"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="13"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="13"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="13"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="4"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A12:B13 F1:F23">
+    <cfRule type="cellIs" dxfId="193" priority="15" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="192" priority="16" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="191" priority="17" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="190" priority="18" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11:E13">
+    <cfRule type="cellIs" dxfId="189" priority="19" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="188" priority="20" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="187" priority="21" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="186" priority="22" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2">
+    <cfRule type="cellIs" dxfId="185" priority="5" operator="equal">
+      <formula>"Not added"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="184" priority="6" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="183" priority="7" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="182" priority="8" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="181" priority="9" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F23">
+    <cfRule type="cellIs" dxfId="180" priority="10" operator="equal">
+      <formula>"Not added"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2">
+    <cfRule type="cellIs" dxfId="179" priority="11" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="178" priority="12" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="177" priority="13" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="176" priority="14" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H21:H23 H3:H12">
+    <cfRule type="cellIs" dxfId="175" priority="23" operator="greaterThan">
+      <formula>"reviewd"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="174" priority="24" operator="equal">
+      <formula>"needs review"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:I1">
+    <cfRule type="cellIs" dxfId="173" priority="1" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="172" priority="2" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="171" priority="3" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="170" priority="4" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="6">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2 J1" xr:uid="{CED5B826-6896-3342-B452-425CD14A7B2A}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H21:H23 H3:H12" xr:uid="{A82ACB8B-ECF7-7141-BF4D-F9A93C7C3E22}">
+      <formula1>"0..n, 0..1, 1, 1..n"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F2" xr:uid="{10A34254-13CE-144B-9CC4-2FE394860C91}">
+      <formula1>"Mandatory, Recommended, Optional, Conditional"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F23" xr:uid="{02510F7B-64FD-D74A-AD53-F948E2A03A6B}">
+      <formula1>"Mandatory, Recommended, Optional, Conditional, Not added"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576" xr:uid="{0402257D-18C7-244C-8AF5-478FD7E382E9}">
+      <formula1>"DCAT-AP v3, HealthDCAT-AP, DCAT-AP NL, HRI v1"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576" xr:uid="{5BD389D6-D5E7-884B-83B3-F713EF56609E}">
+      <formula1>"Identical to v1, Adapted from v1, new"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867942C9-96CB-4978-90BF-B2185B8D3DE2}">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -14688,51 +15511,51 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>564</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>565</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="227" t="s">
         <v>566</v>
       </c>
-      <c r="N1" s="227" t="s">
+      <c r="O1" s="233" t="s">
         <v>567</v>
       </c>
-      <c r="O1" s="233" t="s">
-        <v>568</v>
-      </c>
       <c r="P1" s="97" t="s">
+        <v>820</v>
+      </c>
+      <c r="Q1" s="97" t="s">
+        <v>821</v>
+      </c>
+      <c r="R1" s="97" t="s">
+        <v>822</v>
+      </c>
+      <c r="S1" s="97" t="s">
+        <v>823</v>
+      </c>
+      <c r="T1" s="97" t="s">
+        <v>824</v>
+      </c>
+      <c r="U1" s="97" t="s">
         <v>825</v>
-      </c>
-      <c r="Q1" s="97" t="s">
-        <v>826</v>
-      </c>
-      <c r="R1" s="97" t="s">
-        <v>827</v>
-      </c>
-      <c r="S1" s="97" t="s">
-        <v>828</v>
-      </c>
-      <c r="T1" s="97" t="s">
-        <v>829</v>
-      </c>
-      <c r="U1" s="97" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="84" t="s">
+        <v>568</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>569</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="C2" s="58" t="s">
         <v>570</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>571</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>17</v>
@@ -14760,30 +15583,30 @@
         <v>46</v>
       </c>
       <c r="P2" s="84" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="Q2" s="84" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="R2" s="84" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="144" x14ac:dyDescent="0.2">
       <c r="A3" s="48" t="s">
+        <v>572</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>573</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>574</v>
       </c>
-      <c r="C3" s="77" t="s">
+      <c r="D3" s="234" t="s">
         <v>575</v>
       </c>
-      <c r="D3" s="234" t="s">
+      <c r="E3" s="50" t="s">
         <v>576</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>577</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
@@ -14805,43 +15628,43 @@
       <c r="M3" s="120"/>
       <c r="N3" s="120"/>
       <c r="Q3" s="84" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="R3" s="84" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="157" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="169" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="156" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="168" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="155" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="167" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="154" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="166" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="165" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="152" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="164" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="163" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="150" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="162" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="149" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="161" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14864,7 +15687,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93B4AF5D-EA02-42A0-B703-BF6CFA3342C2}">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -14915,51 +15738,51 @@
         <v>10</v>
       </c>
       <c r="L1" s="218" t="s">
+        <v>577</v>
+      </c>
+      <c r="M1" s="229" t="s">
         <v>578</v>
       </c>
-      <c r="M1" s="229" t="s">
+      <c r="N1" s="228" t="s">
         <v>579</v>
       </c>
-      <c r="N1" s="228" t="s">
+      <c r="O1" s="233" t="s">
         <v>580</v>
       </c>
-      <c r="O1" s="233" t="s">
-        <v>581</v>
-      </c>
       <c r="P1" s="97" t="s">
+        <v>820</v>
+      </c>
+      <c r="Q1" s="97" t="s">
+        <v>821</v>
+      </c>
+      <c r="R1" s="97" t="s">
+        <v>822</v>
+      </c>
+      <c r="S1" s="97" t="s">
+        <v>823</v>
+      </c>
+      <c r="T1" s="97" t="s">
+        <v>824</v>
+      </c>
+      <c r="U1" s="97" t="s">
         <v>825</v>
-      </c>
-      <c r="Q1" s="97" t="s">
-        <v>826</v>
-      </c>
-      <c r="R1" s="97" t="s">
-        <v>827</v>
-      </c>
-      <c r="S1" s="97" t="s">
-        <v>828</v>
-      </c>
-      <c r="T1" s="97" t="s">
-        <v>829</v>
-      </c>
-      <c r="U1" s="97" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="160" x14ac:dyDescent="0.2">
       <c r="A2" s="84" t="s">
+        <v>581</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>573</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>574</v>
+      </c>
+      <c r="D2" s="59" t="s">
         <v>582</v>
       </c>
-      <c r="B2" s="44" t="s">
-        <v>574</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>575</v>
-      </c>
-      <c r="D2" s="59" t="s">
+      <c r="E2" s="59" t="s">
         <v>583</v>
-      </c>
-      <c r="E2" s="59" t="s">
-        <v>584</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>35</v>
@@ -14978,27 +15801,27 @@
       </c>
       <c r="K2" s="2"/>
       <c r="Q2" s="2" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="48" t="s">
+        <v>584</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>585</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>586</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>587</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>35</v>
@@ -15020,43 +15843,43 @@
       <c r="M3" s="113"/>
       <c r="N3" s="113"/>
       <c r="Q3" s="2" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="148" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="160" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="147" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="159" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="146" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="158" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="145" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="157" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="156" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="143" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="155" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="154" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="153" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="152" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15079,7 +15902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB048F93-E797-4F9D-B044-1487CE8C21FF}">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -15130,51 +15953,51 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>588</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>589</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="227" t="s">
         <v>590</v>
       </c>
-      <c r="N1" s="227" t="s">
+      <c r="O1" s="233" t="s">
         <v>591</v>
       </c>
-      <c r="O1" s="233" t="s">
-        <v>592</v>
-      </c>
       <c r="P1" s="97" t="s">
+        <v>820</v>
+      </c>
+      <c r="Q1" s="97" t="s">
+        <v>821</v>
+      </c>
+      <c r="R1" s="97" t="s">
+        <v>822</v>
+      </c>
+      <c r="S1" s="97" t="s">
+        <v>823</v>
+      </c>
+      <c r="T1" s="97" t="s">
+        <v>824</v>
+      </c>
+      <c r="U1" s="97" t="s">
         <v>825</v>
-      </c>
-      <c r="Q1" s="97" t="s">
-        <v>826</v>
-      </c>
-      <c r="R1" s="97" t="s">
-        <v>827</v>
-      </c>
-      <c r="S1" s="97" t="s">
-        <v>828</v>
-      </c>
-      <c r="T1" s="97" t="s">
-        <v>829</v>
-      </c>
-      <c r="U1" s="97" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="112" x14ac:dyDescent="0.2">
       <c r="A2" s="84" t="s">
+        <v>592</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>593</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="C2" s="58" t="s">
         <v>594</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>595</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>17</v>
@@ -15193,27 +16016,27 @@
       </c>
       <c r="K2" s="2"/>
       <c r="Q2" s="2" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A3" s="48" t="s">
+        <v>596</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>597</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="77" t="s">
         <v>598</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>599</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
@@ -15235,43 +16058,43 @@
       <c r="M3" s="113"/>
       <c r="N3" s="113"/>
       <c r="Q3" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="R3" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="139" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="151" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="138" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="150" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="149" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="148" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="147" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="134" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="146" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="145" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="144" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="143" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15294,7 +16117,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F1C235-242D-5746-8BD9-938F9C2E883D}">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -15310,7 +16133,7 @@
     <col min="15" max="15" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="80" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="89" t="s">
         <v>0</v>
       </c>
@@ -15345,37 +16168,37 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
-        <v>589</v>
+        <v>917</v>
       </c>
       <c r="M1" s="226" t="s">
-        <v>590</v>
+        <v>918</v>
       </c>
       <c r="N1" s="227" t="s">
-        <v>591</v>
+        <v>919</v>
       </c>
       <c r="O1" s="233" t="s">
-        <v>592</v>
+        <v>920</v>
       </c>
       <c r="P1" s="97" t="s">
+        <v>820</v>
+      </c>
+      <c r="Q1" s="97" t="s">
+        <v>821</v>
+      </c>
+      <c r="R1" s="97" t="s">
+        <v>822</v>
+      </c>
+      <c r="S1" s="97" t="s">
+        <v>823</v>
+      </c>
+      <c r="T1" s="97" t="s">
+        <v>824</v>
+      </c>
+      <c r="U1" s="97" t="s">
         <v>825</v>
       </c>
-      <c r="Q1" s="97" t="s">
-        <v>826</v>
-      </c>
-      <c r="R1" s="97" t="s">
-        <v>827</v>
-      </c>
-      <c r="S1" s="97" t="s">
-        <v>828</v>
-      </c>
-      <c r="T1" s="97" t="s">
-        <v>829</v>
-      </c>
-      <c r="U1" s="97" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:21" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="84" t="s">
         <v>329</v>
       </c>
@@ -15385,17 +16208,17 @@
       <c r="C2" s="58" t="s">
         <v>331</v>
       </c>
-      <c r="D2" s="250" t="s">
-        <v>901</v>
+      <c r="D2" s="249" t="s">
+        <v>894</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>902</v>
+        <v>911</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="46" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="H2" s="60" t="s">
         <v>19</v>
@@ -15403,72 +16226,90 @@
       <c r="I2" s="47"/>
       <c r="J2" s="47"/>
       <c r="K2" s="2"/>
-      <c r="Q2" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>832</v>
-      </c>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
     </row>
     <row r="3" spans="1:21" ht="48" x14ac:dyDescent="0.2">
-      <c r="A3" s="43" t="s">
-        <v>873</v>
-      </c>
-      <c r="B3" s="44" t="s">
-        <v>918</v>
-      </c>
-      <c r="C3" s="172" t="s">
-        <v>877</v>
-      </c>
-      <c r="D3" s="249" t="s">
-        <v>878</v>
-      </c>
-      <c r="E3" s="53" t="s">
-        <v>896</v>
+      <c r="A3" s="48" t="s">
+        <v>867</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>909</v>
+      </c>
+      <c r="C3" s="50" t="s">
+        <v>871</v>
+      </c>
+      <c r="D3" s="265" t="s">
+        <v>872</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>890</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="H3" s="51" t="s">
         <v>19</v>
       </c>
       <c r="I3" s="52"/>
-      <c r="J3" s="47"/>
+      <c r="J3" s="52"/>
       <c r="K3" s="5"/>
       <c r="L3" s="113"/>
       <c r="M3" s="113"/>
       <c r="N3" s="113"/>
-      <c r="Q3" t="s">
-        <v>831</v>
-      </c>
-      <c r="R3" t="s">
-        <v>832</v>
-      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="130" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="142" priority="13" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="129" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="141" priority="14" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="128" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="15" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="139" priority="16" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="138" priority="17" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
+    <cfRule type="cellIs" dxfId="137" priority="9" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="136" priority="10" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="135" priority="11" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="134" priority="12" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:C3">
+    <cfRule type="cellIs" dxfId="129" priority="5" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="128" priority="6" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="127" priority="7" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="126" priority="8" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:E3">
     <cfRule type="cellIs" dxfId="125" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
@@ -15504,7 +16345,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7E2C641-7C5D-47E8-9C29-F3A4B74AE3E2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28D9DD92-C939-4751-8A55-ABA6494CBB01}">
   <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -15533,7 +16384,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="56" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E1" s="56" t="s">
         <v>4</v>
@@ -15556,13 +16407,13 @@
     </row>
     <row r="2" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="63" t="s">
+        <v>601</v>
+      </c>
+      <c r="B2" s="53" t="s">
         <v>602</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="C2" s="44" t="s">
         <v>603</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>604</v>
       </c>
       <c r="D2" s="43" t="s">
         <v>16</v>
@@ -15570,7 +16421,7 @@
       <c r="E2" s="45"/>
       <c r="F2" s="64"/>
       <c r="G2" s="63" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H2" s="65" t="s">
         <v>81</v>
@@ -15584,13 +16435,13 @@
     </row>
     <row r="3" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="67" t="s">
+        <v>605</v>
+      </c>
+      <c r="B3" s="50" t="s">
         <v>606</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="C3" s="49" t="s">
         <v>607</v>
-      </c>
-      <c r="C3" s="49" t="s">
-        <v>608</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>16</v>
@@ -15598,10 +16449,10 @@
       <c r="E3" s="50"/>
       <c r="F3" s="68"/>
       <c r="G3" s="69" t="s">
+        <v>608</v>
+      </c>
+      <c r="H3" s="48" t="s">
         <v>609</v>
-      </c>
-      <c r="H3" s="48" t="s">
-        <v>610</v>
       </c>
       <c r="I3" s="69" t="s">
         <v>20</v>
@@ -15612,13 +16463,13 @@
     </row>
     <row r="4" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="63" t="s">
+        <v>610</v>
+      </c>
+      <c r="B4" s="53" t="s">
         <v>611</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="C4" s="44" t="s">
         <v>612</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>613</v>
       </c>
       <c r="D4" s="43" t="s">
         <v>16</v>
@@ -15626,10 +16477,10 @@
       <c r="E4" s="53"/>
       <c r="F4" s="64"/>
       <c r="G4" s="63" t="s">
+        <v>613</v>
+      </c>
+      <c r="H4" s="65" t="s">
         <v>614</v>
-      </c>
-      <c r="H4" s="65" t="s">
-        <v>615</v>
       </c>
       <c r="I4" s="66" t="s">
         <v>20</v>
@@ -15640,26 +16491,26 @@
     </row>
     <row r="5" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="67" t="s">
+        <v>615</v>
+      </c>
+      <c r="B5" s="50" t="s">
         <v>616</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="C5" s="49" t="s">
         <v>617</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>618</v>
       </c>
       <c r="D5" s="48" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F5" s="68"/>
       <c r="G5" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="H5" s="48" t="s">
         <v>620</v>
-      </c>
-      <c r="H5" s="48" t="s">
-        <v>621</v>
       </c>
       <c r="I5" s="69" t="s">
         <v>20</v>
@@ -15670,13 +16521,13 @@
     </row>
     <row r="6" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="63" t="s">
+        <v>621</v>
+      </c>
+      <c r="B6" s="73" t="s">
         <v>622</v>
       </c>
-      <c r="B6" s="73" t="s">
+      <c r="C6" s="44" t="s">
         <v>623</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>624</v>
       </c>
       <c r="D6" s="43" t="s">
         <v>16</v>
@@ -15687,7 +16538,7 @@
         <v>98</v>
       </c>
       <c r="H6" s="65" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="I6" s="66" t="s">
         <v>20</v>
@@ -15698,13 +16549,13 @@
     </row>
     <row r="7" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="B7" s="50" t="s">
         <v>625</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="C7" s="49" t="s">
         <v>626</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>627</v>
       </c>
       <c r="D7" s="48" t="s">
         <v>16</v>
@@ -15726,23 +16577,23 @@
     </row>
     <row r="8" spans="1:10" ht="80" x14ac:dyDescent="0.2">
       <c r="A8" s="63" t="s">
+        <v>627</v>
+      </c>
+      <c r="B8" s="53" t="s">
         <v>628</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="C8" s="44" t="s">
         <v>629</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>630</v>
       </c>
       <c r="D8" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F8" s="47"/>
       <c r="G8" s="63" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H8" s="65">
         <v>1</v>
@@ -15756,13 +16607,13 @@
     </row>
     <row r="9" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="67" t="s">
+        <v>632</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>633</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="C9" s="49" t="s">
         <v>634</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>635</v>
       </c>
       <c r="D9" s="48" t="s">
         <v>16</v>
@@ -15770,7 +16621,7 @@
       <c r="E9" s="50"/>
       <c r="F9" s="68"/>
       <c r="G9" s="69" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H9" s="48" t="s">
         <v>81</v>
@@ -15784,23 +16635,23 @@
     </row>
     <row r="10" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="63" t="s">
+        <v>636</v>
+      </c>
+      <c r="B10" s="72" t="s">
         <v>637</v>
       </c>
-      <c r="B10" s="72" t="s">
+      <c r="C10" s="44" t="s">
         <v>638</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>639</v>
       </c>
       <c r="D10" s="43" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="72" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F10" s="64"/>
       <c r="G10" s="63" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H10" s="65" t="s">
         <v>19</v>
@@ -16208,17 +17059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7E2C641-7C5D-47E8-9C29-F3A4B74AE3E2}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AED35DC-FECA-41E4-9CA3-956572264BDD}">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -16275,54 +17116,54 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>640</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>641</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="233" t="s">
         <v>642</v>
       </c>
-      <c r="N1" s="233" t="s">
-        <v>643</v>
-      </c>
       <c r="O1" s="97" t="s">
+        <v>820</v>
+      </c>
+      <c r="P1" s="97" t="s">
+        <v>821</v>
+      </c>
+      <c r="Q1" s="97" t="s">
+        <v>822</v>
+      </c>
+      <c r="R1" s="97" t="s">
+        <v>823</v>
+      </c>
+      <c r="S1" s="97" t="s">
+        <v>824</v>
+      </c>
+      <c r="T1" s="97" t="s">
         <v>825</v>
-      </c>
-      <c r="P1" s="97" t="s">
-        <v>826</v>
-      </c>
-      <c r="Q1" s="97" t="s">
-        <v>827</v>
-      </c>
-      <c r="R1" s="97" t="s">
-        <v>828</v>
-      </c>
-      <c r="S1" s="97" t="s">
-        <v>829</v>
-      </c>
-      <c r="T1" s="97" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" s="44" t="s">
+        <v>643</v>
+      </c>
+      <c r="B2" s="57" t="s">
         <v>644</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="C2" s="58" t="s">
         <v>645</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="D2" s="78" t="s">
         <v>646</v>
       </c>
-      <c r="D2" s="78" t="s">
+      <c r="E2" s="197" t="s">
         <v>647</v>
-      </c>
-      <c r="E2" s="197" t="s">
-        <v>648</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="204" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H2" s="47">
         <v>1</v>
@@ -16334,21 +17175,21 @@
         <v>29</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="49" t="s">
+        <v>649</v>
+      </c>
+      <c r="B3" s="61" t="s">
         <v>650</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="C3" s="48" t="s">
         <v>651</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>652</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>16</v>
@@ -16358,7 +17199,7 @@
         <v>35</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H3" s="52">
         <v>1</v>
@@ -16373,10 +17214,10 @@
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
       <c r="P3" s="2" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
@@ -16976,7 +17817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67277BAE-CBA0-C04C-8D1F-19B83637B929}">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
@@ -17033,54 +17874,54 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>681</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>682</v>
       </c>
-      <c r="M1" s="226" t="s">
+      <c r="N1" s="233" t="s">
         <v>683</v>
       </c>
-      <c r="N1" s="233" t="s">
-        <v>684</v>
-      </c>
       <c r="O1" s="97" t="s">
+        <v>820</v>
+      </c>
+      <c r="P1" s="97" t="s">
+        <v>821</v>
+      </c>
+      <c r="Q1" s="97" t="s">
+        <v>822</v>
+      </c>
+      <c r="R1" s="97" t="s">
+        <v>823</v>
+      </c>
+      <c r="S1" s="97" t="s">
+        <v>824</v>
+      </c>
+      <c r="T1" s="97" t="s">
         <v>825</v>
-      </c>
-      <c r="P1" s="97" t="s">
-        <v>826</v>
-      </c>
-      <c r="Q1" s="97" t="s">
-        <v>827</v>
-      </c>
-      <c r="R1" s="97" t="s">
-        <v>828</v>
-      </c>
-      <c r="S1" s="97" t="s">
-        <v>829</v>
-      </c>
-      <c r="T1" s="97" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" s="44" t="s">
+        <v>676</v>
+      </c>
+      <c r="B2" s="57" t="s">
         <v>677</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="C2" s="58" t="s">
         <v>678</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>679</v>
       </c>
       <c r="D2" s="78" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="197" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="239" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H2" s="47" t="s">
         <v>52</v>
@@ -17092,13 +17933,13 @@
         <v>66</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="P2" s="32" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="Q2" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
@@ -17692,7 +18533,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7708DCAE-0CF1-3848-BA07-512C5955A6D7}">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
@@ -17749,54 +18590,54 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>681</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>682</v>
       </c>
-      <c r="M1" s="226" t="s">
-        <v>683</v>
-      </c>
       <c r="N1" s="233" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="O1" s="97" t="s">
+        <v>820</v>
+      </c>
+      <c r="P1" s="97" t="s">
+        <v>821</v>
+      </c>
+      <c r="Q1" s="97" t="s">
+        <v>822</v>
+      </c>
+      <c r="R1" s="97" t="s">
+        <v>823</v>
+      </c>
+      <c r="S1" s="97" t="s">
+        <v>824</v>
+      </c>
+      <c r="T1" s="97" t="s">
         <v>825</v>
-      </c>
-      <c r="P1" s="97" t="s">
-        <v>826</v>
-      </c>
-      <c r="Q1" s="97" t="s">
-        <v>827</v>
-      </c>
-      <c r="R1" s="97" t="s">
-        <v>828</v>
-      </c>
-      <c r="S1" s="97" t="s">
-        <v>829</v>
-      </c>
-      <c r="T1" s="97" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="80" x14ac:dyDescent="0.2">
       <c r="A2" s="44" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D2" s="78" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="197" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H2" s="204" t="s">
         <v>81</v>
@@ -17808,10 +18649,10 @@
         <v>66</v>
       </c>
       <c r="P2" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q2" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="48" x14ac:dyDescent="0.2">
@@ -17819,7 +18660,7 @@
         <v>131</v>
       </c>
       <c r="B3" s="45" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C3" s="43" t="s">
         <v>133</v>
@@ -17828,7 +18669,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="71" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F3" s="46" t="s">
         <v>35</v>
@@ -17846,10 +18687,10 @@
         <v>66</v>
       </c>
       <c r="P3" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q3" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="42" x14ac:dyDescent="0.2">
@@ -17857,7 +18698,7 @@
         <v>224</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>226</v>
@@ -17866,7 +18707,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>17</v>
@@ -17884,33 +18725,33 @@
         <v>66</v>
       </c>
       <c r="P4" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q4" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="96" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D5" s="78" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>35</v>
       </c>
       <c r="G5" s="238" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>52</v>
@@ -17922,13 +18763,13 @@
         <v>66</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="P5" s="32" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="Q5" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
@@ -18502,7 +19343,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C65873-9AF7-7944-82C8-6D469506ACC7}">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
@@ -18559,48 +19400,48 @@
         <v>10</v>
       </c>
       <c r="L1" s="219" t="s">
+        <v>717</v>
+      </c>
+      <c r="M1" s="226" t="s">
         <v>718</v>
       </c>
-      <c r="M1" s="226" t="s">
-        <v>719</v>
-      </c>
       <c r="N1" s="233" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="O1" s="97" t="s">
+        <v>820</v>
+      </c>
+      <c r="P1" s="97" t="s">
+        <v>821</v>
+      </c>
+      <c r="Q1" s="97" t="s">
+        <v>822</v>
+      </c>
+      <c r="R1" s="97" t="s">
+        <v>823</v>
+      </c>
+      <c r="S1" s="97" t="s">
+        <v>824</v>
+      </c>
+      <c r="T1" s="97" t="s">
         <v>825</v>
-      </c>
-      <c r="P1" s="97" t="s">
-        <v>826</v>
-      </c>
-      <c r="Q1" s="97" t="s">
-        <v>827</v>
-      </c>
-      <c r="R1" s="97" t="s">
-        <v>828</v>
-      </c>
-      <c r="S1" s="97" t="s">
-        <v>829</v>
-      </c>
-      <c r="T1" s="97" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="80" x14ac:dyDescent="0.2">
       <c r="A2" s="44" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D2" s="78" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="197" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="F2" s="46" t="s">
         <v>35</v>
@@ -18618,10 +19459,10 @@
         <v>66</v>
       </c>
       <c r="P2" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q2" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="32" x14ac:dyDescent="0.2">
@@ -18629,16 +19470,16 @@
         <v>131</v>
       </c>
       <c r="B3" s="45" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D3" s="236" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="71" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F3" s="46" t="s">
         <v>35</v>
@@ -18656,10 +19497,10 @@
         <v>66</v>
       </c>
       <c r="P3" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q3" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="84" x14ac:dyDescent="0.2">
@@ -18667,7 +19508,7 @@
         <v>54</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>56</v>
@@ -18676,7 +19517,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>35</v>
@@ -18694,27 +19535,27 @@
         <v>66</v>
       </c>
       <c r="P4" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q4" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="112" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D5" s="78" t="s">
+        <v>715</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>716</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>717</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>35</v>
@@ -18732,33 +19573,33 @@
         <v>66</v>
       </c>
       <c r="P5" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q5" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="168" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D6" s="78" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>81</v>
@@ -18770,10 +19611,10 @@
         <v>66</v>
       </c>
       <c r="P6" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q6" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
@@ -19342,343 +20183,327 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D71F60E-3931-4345-8656-736171C91DD3}">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1" t="s">
         <v>721</v>
-      </c>
-      <c r="B1" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>722</v>
+      </c>
+      <c r="B2" s="240" t="s">
         <v>723</v>
-      </c>
-      <c r="B2" s="240" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B3" s="240" t="s">
-        <v>726</v>
+        <v>927</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B4" s="240" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B5" s="240" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B6" s="240" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B7" s="240" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B8" s="240" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B9" s="240" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B10" s="240" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B11" s="240" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B12" s="240" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B13" s="240" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B14" s="240" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B15" s="240" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>751</v>
+        <v>727</v>
       </c>
       <c r="B16" s="240" t="s">
-        <v>752</v>
+        <v>728</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>729</v>
+        <v>749</v>
       </c>
       <c r="B17" s="240" t="s">
-        <v>730</v>
+        <v>750</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B18" s="240" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B19" s="240" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B20" s="240" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B21" s="240" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B22" s="240" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B23" s="240" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B24" s="240" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>766</v>
+      </c>
+      <c r="B25" s="240" t="s">
         <v>767</v>
-      </c>
-      <c r="B25" s="240" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>768</v>
+      </c>
+      <c r="B26" s="240" t="s">
         <v>769</v>
-      </c>
-      <c r="B26" s="240" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>770</v>
+      </c>
+      <c r="B27" s="240" t="s">
         <v>771</v>
-      </c>
-      <c r="B27" s="240" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>772</v>
+      </c>
+      <c r="B28" s="240" t="s">
         <v>773</v>
-      </c>
-      <c r="B28" s="240" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>774</v>
+      </c>
+      <c r="B29" s="240" t="s">
         <v>775</v>
-      </c>
-      <c r="B29" s="240" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>776</v>
+      </c>
+      <c r="B30" s="240" t="s">
         <v>777</v>
-      </c>
-      <c r="B30" s="240" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>778</v>
+      </c>
+      <c r="B31" s="240" t="s">
         <v>779</v>
-      </c>
-      <c r="B31" s="240" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>780</v>
+      </c>
+      <c r="B32" t="s">
         <v>781</v>
-      </c>
-      <c r="B32" s="240" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>783</v>
-      </c>
-      <c r="B33" s="240" t="s">
-        <v>784</v>
+        <v>753</v>
+      </c>
+      <c r="B33" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B34" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>757</v>
+        <v>784</v>
       </c>
       <c r="B35" t="s">
-        <v>758</v>
+        <v>785</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>787</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>789</v>
-      </c>
-      <c r="B37" t="s">
-        <v>790</v>
+        <v>862</v>
+      </c>
+      <c r="B37" s="240" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>313</v>
-      </c>
-      <c r="B38" t="s">
-        <v>791</v>
+        <v>765</v>
+      </c>
+      <c r="B38" s="240" t="s">
+        <v>882</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>868</v>
+        <v>891</v>
       </c>
       <c r="B39" s="240" t="s">
-        <v>869</v>
+        <v>892</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>769</v>
+        <v>893</v>
       </c>
       <c r="B40" s="240" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>897</v>
-      </c>
-      <c r="B41" s="240" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>899</v>
-      </c>
-      <c r="B42" s="240" t="s">
-        <v>900</v>
+        <v>928</v>
       </c>
     </row>
   </sheetData>
@@ -19691,34 +20516,32 @@
     <hyperlink ref="B7" r:id="rId6" xr:uid="{61AA2307-7814-AD4A-8C1F-F200F39CEBF3}"/>
     <hyperlink ref="B8" r:id="rId7" xr:uid="{E8014167-7FAC-C847-A70C-782606C94FBC}"/>
     <hyperlink ref="B9" r:id="rId8" xr:uid="{D4E102B5-97A5-9544-9AD4-331D89771779}"/>
-    <hyperlink ref="B10" r:id="rId9" xr:uid="{45064AEC-CEEF-5B47-BC6A-5667063241D3}"/>
-    <hyperlink ref="B11" r:id="rId10" xr:uid="{6E62A389-A471-5246-8B13-C6255B16F4AD}"/>
-    <hyperlink ref="B12" r:id="rId11" xr:uid="{550C48D6-3175-DF46-9F20-D3A8DF253815}"/>
-    <hyperlink ref="B13" r:id="rId12" xr:uid="{EB351E0A-AC29-DA47-AAC6-8C92EF024E4A}"/>
-    <hyperlink ref="B14" r:id="rId13" xr:uid="{780BA805-8E9F-C948-BF8F-D03958277AD3}"/>
-    <hyperlink ref="B15" r:id="rId14" xr:uid="{EB9F6689-61A8-1E4C-B90D-65AF3835EF06}"/>
-    <hyperlink ref="B16" r:id="rId15" xr:uid="{B24E8545-5ADF-B24F-B250-52C325DFDBF9}"/>
-    <hyperlink ref="B17" r:id="rId16" xr:uid="{B912B7BE-48A3-9540-82D3-81C2B463AF61}"/>
-    <hyperlink ref="B18" r:id="rId17" xr:uid="{EBAE73BD-F850-4B49-A5A7-1EE585B2FBE0}"/>
-    <hyperlink ref="B19" r:id="rId18" xr:uid="{36728002-A7DA-4F4E-98B9-7D22209483F3}"/>
-    <hyperlink ref="B20" r:id="rId19" xr:uid="{F55C952F-7D7F-C944-A5DE-2F3C5B518B6F}"/>
-    <hyperlink ref="B21" r:id="rId20" xr:uid="{915EEF9D-CB6E-874A-A01E-0C002FA02E27}"/>
-    <hyperlink ref="B22" r:id="rId21" xr:uid="{25EA60E3-D9F5-194E-8DA6-D5AA8B37D525}"/>
-    <hyperlink ref="B23" r:id="rId22" xr:uid="{1E995EFE-8CBD-E243-B5A7-650708AF2350}"/>
-    <hyperlink ref="B24" r:id="rId23" xr:uid="{FF9AB7DA-85A3-CA41-9D11-BF5F5286EE8D}"/>
-    <hyperlink ref="B25" r:id="rId24" xr:uid="{35EE502C-0412-7340-8A73-B7E573BACC25}"/>
-    <hyperlink ref="B26" r:id="rId25" xr:uid="{58FEFCCC-0719-134A-872F-EEE762DC3ABD}"/>
-    <hyperlink ref="B27" r:id="rId26" xr:uid="{9FF6ED2E-7306-C348-9BE1-5535BF7C30B3}"/>
-    <hyperlink ref="B28" r:id="rId27" xr:uid="{26C80822-7C09-1647-9FB1-FA3142B403B6}"/>
-    <hyperlink ref="B29" r:id="rId28" xr:uid="{9FC45DA6-3DA5-A641-954D-FA77593AFB08}"/>
-    <hyperlink ref="B30" r:id="rId29" xr:uid="{6648A9E8-693B-6442-A97E-D5435B85BBFD}"/>
-    <hyperlink ref="B31" r:id="rId30" xr:uid="{1F76A0AB-EB23-BA4C-B1A0-5B6BD86AEDBD}"/>
-    <hyperlink ref="B33" r:id="rId31" xr:uid="{56C313E7-7C15-444C-BDF6-8ABB298472E7}"/>
-    <hyperlink ref="B32" r:id="rId32" xr:uid="{014D7820-F85D-1A46-ACAF-5444A9CD98BA}"/>
-    <hyperlink ref="B39" r:id="rId33" xr:uid="{5FCE1711-D002-8945-9534-40B1577D372F}"/>
-    <hyperlink ref="B40" r:id="rId34" xr:uid="{96CE141A-F82D-CC4A-ABE7-E3B5C147F762}"/>
-    <hyperlink ref="B41" r:id="rId35" xr:uid="{EC6D7424-ED52-CE48-9C0F-D9F4B42A9C45}"/>
-    <hyperlink ref="B42" r:id="rId36" xr:uid="{97ABC642-FEDF-6549-9137-EF98F43FC179}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{6E62A389-A471-5246-8B13-C6255B16F4AD}"/>
+    <hyperlink ref="B11" r:id="rId10" xr:uid="{550C48D6-3175-DF46-9F20-D3A8DF253815}"/>
+    <hyperlink ref="B12" r:id="rId11" xr:uid="{EB351E0A-AC29-DA47-AAC6-8C92EF024E4A}"/>
+    <hyperlink ref="B13" r:id="rId12" xr:uid="{780BA805-8E9F-C948-BF8F-D03958277AD3}"/>
+    <hyperlink ref="B14" r:id="rId13" xr:uid="{EB9F6689-61A8-1E4C-B90D-65AF3835EF06}"/>
+    <hyperlink ref="B15" r:id="rId14" xr:uid="{B24E8545-5ADF-B24F-B250-52C325DFDBF9}"/>
+    <hyperlink ref="B16" r:id="rId15" xr:uid="{B912B7BE-48A3-9540-82D3-81C2B463AF61}"/>
+    <hyperlink ref="B17" r:id="rId16" xr:uid="{EBAE73BD-F850-4B49-A5A7-1EE585B2FBE0}"/>
+    <hyperlink ref="B18" r:id="rId17" xr:uid="{36728002-A7DA-4F4E-98B9-7D22209483F3}"/>
+    <hyperlink ref="B19" r:id="rId18" xr:uid="{F55C952F-7D7F-C944-A5DE-2F3C5B518B6F}"/>
+    <hyperlink ref="B20" r:id="rId19" xr:uid="{915EEF9D-CB6E-874A-A01E-0C002FA02E27}"/>
+    <hyperlink ref="B21" r:id="rId20" xr:uid="{25EA60E3-D9F5-194E-8DA6-D5AA8B37D525}"/>
+    <hyperlink ref="B22" r:id="rId21" xr:uid="{1E995EFE-8CBD-E243-B5A7-650708AF2350}"/>
+    <hyperlink ref="B23" r:id="rId22" xr:uid="{FF9AB7DA-85A3-CA41-9D11-BF5F5286EE8D}"/>
+    <hyperlink ref="B24" r:id="rId23" xr:uid="{35EE502C-0412-7340-8A73-B7E573BACC25}"/>
+    <hyperlink ref="B25" r:id="rId24" xr:uid="{9FF6ED2E-7306-C348-9BE1-5535BF7C30B3}"/>
+    <hyperlink ref="B26" r:id="rId25" xr:uid="{26C80822-7C09-1647-9FB1-FA3142B403B6}"/>
+    <hyperlink ref="B27" r:id="rId26" xr:uid="{9FC45DA6-3DA5-A641-954D-FA77593AFB08}"/>
+    <hyperlink ref="B28" r:id="rId27" xr:uid="{6648A9E8-693B-6442-A97E-D5435B85BBFD}"/>
+    <hyperlink ref="B29" r:id="rId28" xr:uid="{1F76A0AB-EB23-BA4C-B1A0-5B6BD86AEDBD}"/>
+    <hyperlink ref="B31" r:id="rId29" xr:uid="{56C313E7-7C15-444C-BDF6-8ABB298472E7}"/>
+    <hyperlink ref="B30" r:id="rId30" xr:uid="{014D7820-F85D-1A46-ACAF-5444A9CD98BA}"/>
+    <hyperlink ref="B37" r:id="rId31" xr:uid="{5FCE1711-D002-8945-9534-40B1577D372F}"/>
+    <hyperlink ref="B38" r:id="rId32" xr:uid="{96CE141A-F82D-CC4A-ABE7-E3B5C147F762}"/>
+    <hyperlink ref="B39" r:id="rId33" xr:uid="{EC6D7424-ED52-CE48-9C0F-D9F4B42A9C45}"/>
+    <hyperlink ref="B40" r:id="rId34" xr:uid="{97ABC642-FEDF-6549-9137-EF98F43FC179}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19726,7 +20549,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F5C693-9CC4-1645-8994-DD08C7CC659E}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
@@ -19735,35 +20558,35 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="B1" t="s">
         <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="D1" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="C2" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="D2" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="C3" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="D3" t="s">
         <v>51</v>
@@ -19771,10 +20594,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="C4" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="D4" t="s">
         <v>27</v>
@@ -19782,10 +20605,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="C5" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="D5" t="s">
         <v>44</v>
@@ -19793,10 +20616,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="C6" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="D6" t="s">
         <v>36</v>
@@ -19804,10 +20627,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C7" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="D7" t="s">
         <v>159</v>
@@ -19815,10 +20638,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="C8" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="D8" t="s">
         <v>216</v>
@@ -19826,10 +20649,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C9" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="D9" t="s">
         <v>119</v>
@@ -19837,10 +20660,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="C10" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="D10" t="s">
         <v>262</v>
@@ -19848,10 +20671,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="C11" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="D11" t="s">
         <v>124</v>
@@ -19859,10 +20682,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="C12" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="D12" t="s">
         <v>284</v>
@@ -19870,10 +20693,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="C13" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="D13" t="s">
         <v>290</v>
@@ -19881,10 +20704,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C14" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="D14" t="s">
         <v>296</v>
@@ -19892,56 +20715,67 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="C15" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="D15" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="C16" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="D16" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="C17" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="D17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="C18" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="D18" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
       <c r="C19" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="D19" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>924</v>
+      </c>
+      <c r="C20" t="s">
+        <v>925</v>
+      </c>
+      <c r="D20" t="s">
         <v>915</v>
       </c>
     </row>
@@ -19990,69 +20824,69 @@
         <v>10</v>
       </c>
       <c r="L1" s="108" t="s">
+        <v>819</v>
+      </c>
+      <c r="M1" s="92" t="s">
+        <v>820</v>
+      </c>
+      <c r="N1" s="92" t="s">
+        <v>821</v>
+      </c>
+      <c r="O1" s="92" t="s">
+        <v>822</v>
+      </c>
+      <c r="P1" s="92" t="s">
+        <v>823</v>
+      </c>
+      <c r="Q1" s="92" t="s">
         <v>824</v>
       </c>
-      <c r="M1" s="92" t="s">
+      <c r="R1" s="241" t="s">
         <v>825</v>
-      </c>
-      <c r="N1" s="92" t="s">
-        <v>826</v>
-      </c>
-      <c r="O1" s="92" t="s">
-        <v>827</v>
-      </c>
-      <c r="P1" s="92" t="s">
-        <v>828</v>
-      </c>
-      <c r="Q1" s="92" t="s">
-        <v>829</v>
-      </c>
-      <c r="R1" s="241" t="s">
-        <v>830</v>
       </c>
       <c r="S1" s="241"/>
       <c r="T1" s="241"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F1 H1:I1">
-    <cfRule type="cellIs" dxfId="319" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="355" priority="9" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="318" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="354" priority="10" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="317" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="353" priority="11" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="316" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="352" priority="12" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1">
-    <cfRule type="cellIs" dxfId="315" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="351" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="314" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="350" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="313" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="349" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="312" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="348" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:Q1">
-    <cfRule type="cellIs" dxfId="311" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="347" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="310" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="346" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="309" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="345" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="308" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="344" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20131,22 +20965,22 @@
         <v>12</v>
       </c>
       <c r="N1" s="92" t="s">
+        <v>820</v>
+      </c>
+      <c r="O1" s="92" t="s">
+        <v>821</v>
+      </c>
+      <c r="P1" s="92" t="s">
+        <v>822</v>
+      </c>
+      <c r="Q1" s="92" t="s">
+        <v>823</v>
+      </c>
+      <c r="R1" s="92" t="s">
+        <v>824</v>
+      </c>
+      <c r="S1" s="92" t="s">
         <v>825</v>
-      </c>
-      <c r="O1" s="92" t="s">
-        <v>826</v>
-      </c>
-      <c r="P1" s="92" t="s">
-        <v>827</v>
-      </c>
-      <c r="Q1" s="92" t="s">
-        <v>828</v>
-      </c>
-      <c r="R1" s="92" t="s">
-        <v>829</v>
-      </c>
-      <c r="S1" s="92" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="16" x14ac:dyDescent="0.2">
@@ -20184,10 +21018,10 @@
       <c r="L2" s="107"/>
       <c r="M2" s="107"/>
       <c r="O2" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P2" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S2" s="99"/>
     </row>
@@ -20228,10 +21062,10 @@
       </c>
       <c r="M3" s="129"/>
       <c r="O3" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P3" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S3" s="99"/>
     </row>
@@ -20276,13 +21110,13 @@
         <v>39</v>
       </c>
       <c r="N4" s="32" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="O4" s="32" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="P4" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="S4" s="99"/>
     </row>
@@ -20325,13 +21159,13 @@
         <v>46</v>
       </c>
       <c r="N5" s="32" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="O5" s="32" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="P5" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="S5" s="99"/>
     </row>
@@ -20410,150 +21244,150 @@
       <c r="L7" s="129"/>
       <c r="M7" s="129"/>
       <c r="O7" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="P7" s="32" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="S7" s="99" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="253" t="s">
+      <c r="A8" s="252" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="254" t="s">
+      <c r="B8" s="253" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="253" t="s">
+      <c r="C8" s="252" t="s">
         <v>62</v>
       </c>
       <c r="D8" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="255" t="s">
+      <c r="E8" s="254" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="252" t="s">
+      <c r="F8" s="251" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="252" t="s">
+      <c r="G8" s="251" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="252" t="s">
+      <c r="H8" s="251" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="251" t="s">
+      <c r="I8" s="250" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="251" t="s">
+      <c r="J8" s="250" t="s">
         <v>66</v>
       </c>
       <c r="K8" s="137"/>
-      <c r="L8" s="251"/>
-      <c r="M8" s="251"/>
+      <c r="L8" s="250"/>
+      <c r="M8" s="250"/>
       <c r="O8" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P8" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S8" s="99"/>
     </row>
     <row r="9" spans="1:19" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="253"/>
-      <c r="B9" s="254"/>
-      <c r="C9" s="253"/>
+      <c r="A9" s="252"/>
+      <c r="B9" s="253"/>
+      <c r="C9" s="252"/>
       <c r="D9" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="255"/>
-      <c r="F9" s="252"/>
-      <c r="G9" s="252"/>
-      <c r="H9" s="252"/>
-      <c r="I9" s="251"/>
-      <c r="J9" s="251"/>
+      <c r="E9" s="254"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="250"/>
+      <c r="J9" s="250"/>
       <c r="K9" s="137"/>
-      <c r="L9" s="251"/>
-      <c r="M9" s="251"/>
+      <c r="L9" s="250"/>
+      <c r="M9" s="250"/>
       <c r="O9" s="32" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="P9" s="32" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="S9" s="99"/>
     </row>
     <row r="10" spans="1:19" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="253"/>
-      <c r="B10" s="254"/>
-      <c r="C10" s="253"/>
+      <c r="A10" s="252"/>
+      <c r="B10" s="253"/>
+      <c r="C10" s="252"/>
       <c r="D10" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="255"/>
-      <c r="F10" s="252"/>
-      <c r="G10" s="252"/>
-      <c r="H10" s="252"/>
-      <c r="I10" s="251"/>
-      <c r="J10" s="251"/>
+      <c r="E10" s="254"/>
+      <c r="F10" s="251"/>
+      <c r="G10" s="251"/>
+      <c r="H10" s="251"/>
+      <c r="I10" s="250"/>
+      <c r="J10" s="250"/>
       <c r="K10" s="137"/>
-      <c r="L10" s="251"/>
-      <c r="M10" s="251"/>
+      <c r="L10" s="250"/>
+      <c r="M10" s="250"/>
       <c r="O10" s="32" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="P10" s="32" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="S10" s="99"/>
     </row>
     <row r="11" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="253"/>
-      <c r="B11" s="254"/>
-      <c r="C11" s="253"/>
+      <c r="A11" s="252"/>
+      <c r="B11" s="253"/>
+      <c r="C11" s="252"/>
       <c r="D11" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="255"/>
-      <c r="F11" s="252"/>
-      <c r="G11" s="252"/>
-      <c r="H11" s="252"/>
-      <c r="I11" s="251"/>
-      <c r="J11" s="251"/>
+      <c r="E11" s="254"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="250"/>
+      <c r="J11" s="250"/>
       <c r="K11" s="153"/>
-      <c r="L11" s="251"/>
-      <c r="M11" s="251"/>
+      <c r="L11" s="250"/>
+      <c r="M11" s="250"/>
       <c r="O11" s="32" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="P11" s="32" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="S11" s="99"/>
     </row>
     <row r="12" spans="1:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="253"/>
-      <c r="B12" s="254"/>
-      <c r="C12" s="253"/>
+      <c r="A12" s="252"/>
+      <c r="B12" s="253"/>
+      <c r="C12" s="252"/>
       <c r="D12" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="255"/>
-      <c r="F12" s="252"/>
-      <c r="G12" s="252"/>
-      <c r="H12" s="252"/>
-      <c r="I12" s="251"/>
-      <c r="J12" s="251"/>
+      <c r="E12" s="254"/>
+      <c r="F12" s="251"/>
+      <c r="G12" s="251"/>
+      <c r="H12" s="251"/>
+      <c r="I12" s="250"/>
+      <c r="J12" s="250"/>
       <c r="K12" s="137"/>
-      <c r="L12" s="251"/>
-      <c r="M12" s="251"/>
+      <c r="L12" s="250"/>
+      <c r="M12" s="250"/>
       <c r="O12" s="32" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="P12" s="32" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="S12" s="99"/>
     </row>
@@ -20594,10 +21428,10 @@
       </c>
       <c r="M13" s="129"/>
       <c r="O13" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P13" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S13" s="99"/>
     </row>
@@ -20636,10 +21470,10 @@
       <c r="L14" s="107"/>
       <c r="M14" s="107"/>
       <c r="O14" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P14" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S14" s="99"/>
     </row>
@@ -20680,10 +21514,10 @@
       <c r="L15" s="129"/>
       <c r="M15" s="129"/>
       <c r="O15" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P15" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S15" s="99"/>
     </row>
@@ -20701,7 +21535,7 @@
         <v>92</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F16" s="124" t="s">
         <v>17</v>
@@ -20724,10 +21558,10 @@
       <c r="L16" s="107"/>
       <c r="M16" s="107"/>
       <c r="O16" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P16" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S16" s="99"/>
     </row>
@@ -20766,13 +21600,13 @@
       <c r="L17" s="129"/>
       <c r="M17" s="129"/>
       <c r="O17" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="P17" s="32" t="s">
+        <v>833</v>
+      </c>
+      <c r="Q17" s="32" t="s">
         <v>838</v>
-      </c>
-      <c r="Q17" s="32" t="s">
-        <v>843</v>
       </c>
       <c r="S17" s="99"/>
     </row>
@@ -20817,13 +21651,13 @@
         <v>46</v>
       </c>
       <c r="N18" s="32" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="O18" s="32" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="P18" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="S18" s="99"/>
     </row>
@@ -20862,13 +21696,13 @@
       <c r="L19" s="129"/>
       <c r="M19" s="129"/>
       <c r="O19" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="P19" s="32" t="s">
+        <v>833</v>
+      </c>
+      <c r="Q19" s="32" t="s">
         <v>838</v>
-      </c>
-      <c r="Q19" s="32" t="s">
-        <v>843</v>
       </c>
       <c r="S19" s="99"/>
     </row>
@@ -20907,10 +21741,10 @@
       <c r="L20" s="107"/>
       <c r="M20" s="107"/>
       <c r="O20" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P20" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S20" s="99"/>
     </row>
@@ -20951,10 +21785,10 @@
       </c>
       <c r="M21" s="129"/>
       <c r="O21" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P21" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S21" s="99"/>
     </row>
@@ -20993,13 +21827,13 @@
       <c r="L22" s="107"/>
       <c r="M22" s="107"/>
       <c r="N22" s="32" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="O22" s="32" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="P22" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="S22" s="99"/>
     </row>
@@ -21038,10 +21872,10 @@
       <c r="L23" s="129"/>
       <c r="M23" s="129"/>
       <c r="O23" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="P23" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S23" s="99"/>
     </row>
@@ -21082,10 +21916,10 @@
       <c r="L24" s="107"/>
       <c r="M24" s="107"/>
       <c r="O24" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="P24" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="S24" s="99" t="b">
         <v>1</v>
@@ -21485,85 +22319,85 @@
     <mergeCell ref="J8:J12"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F8">
-    <cfRule type="cellIs" dxfId="307" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="343" priority="20" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13:F56">
-    <cfRule type="cellIs" dxfId="306" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="342" priority="30" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="305" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="341" priority="33" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="304" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="340" priority="34" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="303" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="339" priority="35" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="302" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="338" priority="36" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H8 H13:H56">
-    <cfRule type="cellIs" dxfId="301" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="337" priority="21" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="300" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="336" priority="22" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F8">
-    <cfRule type="cellIs" dxfId="299" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="335" priority="9" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="298" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="334" priority="10" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="297" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="333" priority="11" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="296" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="332" priority="12" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J8 J13:J56">
-    <cfRule type="containsText" dxfId="295" priority="17" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="331" priority="17" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="294" priority="18" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="330" priority="18" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="293" priority="19" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="329" priority="19" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1">
-    <cfRule type="cellIs" dxfId="292" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="328" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="291" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="327" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="290" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="326" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="289" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="325" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:S1">
-    <cfRule type="cellIs" dxfId="288" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="324" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="287" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="323" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="286" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="322" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="285" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="321" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21678,22 +22512,22 @@
         <v>148</v>
       </c>
       <c r="O1" s="92" t="s">
+        <v>820</v>
+      </c>
+      <c r="P1" s="92" t="s">
+        <v>821</v>
+      </c>
+      <c r="Q1" s="92" t="s">
+        <v>822</v>
+      </c>
+      <c r="R1" s="92" t="s">
+        <v>823</v>
+      </c>
+      <c r="S1" s="92" t="s">
+        <v>824</v>
+      </c>
+      <c r="T1" s="92" t="s">
         <v>825</v>
-      </c>
-      <c r="P1" s="92" t="s">
-        <v>826</v>
-      </c>
-      <c r="Q1" s="92" t="s">
-        <v>827</v>
-      </c>
-      <c r="R1" s="92" t="s">
-        <v>828</v>
-      </c>
-      <c r="S1" s="92" t="s">
-        <v>829</v>
-      </c>
-      <c r="T1" s="92" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="209.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21732,27 +22566,27 @@
       </c>
       <c r="L2" s="107"/>
       <c r="P2" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q2" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="209.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="125" t="s">
+        <v>661</v>
+      </c>
+      <c r="B3" s="74" t="s">
         <v>662</v>
       </c>
-      <c r="B3" s="74" t="s">
+      <c r="C3" s="125" t="s">
         <v>663</v>
-      </c>
-      <c r="C3" s="125" t="s">
-        <v>664</v>
       </c>
       <c r="D3" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="74" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F3" s="124" t="s">
         <v>17</v>
@@ -21774,10 +22608,10 @@
       <c r="M3" s="129"/>
       <c r="N3" s="129"/>
       <c r="P3" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q3" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="112" customHeight="1" x14ac:dyDescent="0.2">
@@ -21793,7 +22627,7 @@
       <c r="D4" s="131" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="265" t="s">
+      <c r="E4" s="264" t="s">
         <v>158</v>
       </c>
       <c r="F4" s="127" t="s">
@@ -21818,27 +22652,27 @@
         <v>161</v>
       </c>
       <c r="P4" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q4" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="80" x14ac:dyDescent="0.2">
       <c r="A5" s="125" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="B5" s="74" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="C5" s="125" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="D5" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="74" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="F5" s="127" t="s">
         <v>17</v>
@@ -21870,7 +22704,7 @@
         <v>16</v>
       </c>
       <c r="E6" s="132" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F6" s="124" t="s">
         <v>35</v>
@@ -21892,13 +22726,13 @@
       </c>
       <c r="L6" s="107"/>
       <c r="P6" s="117" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q6" s="117" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S6" s="117" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="80" x14ac:dyDescent="0.2">
@@ -21915,7 +22749,7 @@
         <v>16</v>
       </c>
       <c r="E7" s="126" t="s">
-        <v>916</v>
+        <v>907</v>
       </c>
       <c r="F7" s="127" t="s">
         <v>17</v>
@@ -21939,10 +22773,10 @@
       <c r="M7" s="129"/>
       <c r="N7" s="129"/>
       <c r="P7" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q7" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="64" x14ac:dyDescent="0.2">
@@ -21959,7 +22793,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="132" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="F8" s="124" t="s">
         <v>17</v>
@@ -21981,10 +22815,10 @@
       </c>
       <c r="L8" s="107"/>
       <c r="P8" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q8" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="80" x14ac:dyDescent="0.2">
@@ -22001,7 +22835,7 @@
         <v>16</v>
       </c>
       <c r="E9" s="74" t="s">
-        <v>907</v>
+        <v>898</v>
       </c>
       <c r="F9" s="127" t="s">
         <v>17</v>
@@ -22025,10 +22859,10 @@
       <c r="M9" s="129"/>
       <c r="N9" s="129"/>
       <c r="P9" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q9" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="123.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22075,13 +22909,13 @@
         <v>39</v>
       </c>
       <c r="O10" s="32" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="P10" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q10" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="176" x14ac:dyDescent="0.2">
@@ -22128,13 +22962,13 @@
         <v>46</v>
       </c>
       <c r="O11" s="32" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="P11" s="32" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="Q11" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="64" x14ac:dyDescent="0.2">
@@ -22173,10 +23007,10 @@
       </c>
       <c r="L12" s="107"/>
       <c r="P12" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q12" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="T12" s="32" t="b">
         <v>1</v>
@@ -22225,10 +23059,10 @@
       </c>
       <c r="O13" s="242"/>
       <c r="P13" s="242" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q13" s="242" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S13" s="242"/>
       <c r="T13" s="242"/>
@@ -22269,27 +23103,27 @@
       </c>
       <c r="L14" s="107"/>
       <c r="P14" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q14" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="96" x14ac:dyDescent="0.2">
       <c r="A15" s="121" t="s">
-        <v>895</v>
-      </c>
-      <c r="B15" s="264" t="s">
-        <v>905</v>
+        <v>889</v>
+      </c>
+      <c r="B15" s="263" t="s">
+        <v>896</v>
       </c>
       <c r="C15" s="121" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="D15" s="247" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="E15" s="244" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="F15" s="124" t="s">
         <v>17</v>
@@ -22345,115 +23179,115 @@
       <c r="M16" s="129"/>
       <c r="N16" s="129"/>
       <c r="P16" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q16" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A17" s="253" t="s">
+      <c r="A17" s="252" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="257" t="s">
+      <c r="B17" s="256" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="253" t="s">
+      <c r="C17" s="252" t="s">
         <v>62</v>
       </c>
       <c r="D17" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="255" t="s">
+      <c r="E17" s="254" t="s">
         <v>196</v>
       </c>
-      <c r="F17" s="252" t="s">
+      <c r="F17" s="251" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="252" t="s">
+      <c r="G17" s="251" t="s">
         <v>65</v>
       </c>
-      <c r="H17" s="252" t="s">
+      <c r="H17" s="251" t="s">
         <v>19</v>
       </c>
-      <c r="I17" s="251" t="s">
+      <c r="I17" s="250" t="s">
         <v>20</v>
       </c>
-      <c r="J17" s="251" t="s">
+      <c r="J17" s="250" t="s">
         <v>66</v>
       </c>
-      <c r="K17" s="256"/>
-      <c r="L17" s="251"/>
+      <c r="K17" s="255"/>
+      <c r="L17" s="250"/>
       <c r="P17" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q17" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A18" s="253"/>
-      <c r="B18" s="257"/>
-      <c r="C18" s="253"/>
+      <c r="A18" s="252"/>
+      <c r="B18" s="256"/>
+      <c r="C18" s="252"/>
       <c r="D18" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="E18" s="255"/>
-      <c r="F18" s="252"/>
-      <c r="G18" s="252"/>
-      <c r="H18" s="252"/>
-      <c r="I18" s="251"/>
-      <c r="J18" s="251"/>
-      <c r="K18" s="256"/>
-      <c r="L18" s="251"/>
+      <c r="E18" s="254"/>
+      <c r="F18" s="251"/>
+      <c r="G18" s="251"/>
+      <c r="H18" s="251"/>
+      <c r="I18" s="250"/>
+      <c r="J18" s="250"/>
+      <c r="K18" s="255"/>
+      <c r="L18" s="250"/>
     </row>
     <row r="19" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A19" s="253"/>
-      <c r="B19" s="257"/>
-      <c r="C19" s="253"/>
+      <c r="A19" s="252"/>
+      <c r="B19" s="256"/>
+      <c r="C19" s="252"/>
       <c r="D19" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="255"/>
-      <c r="F19" s="252"/>
-      <c r="G19" s="252"/>
-      <c r="H19" s="252"/>
-      <c r="I19" s="251"/>
-      <c r="J19" s="251"/>
-      <c r="K19" s="256"/>
-      <c r="L19" s="251"/>
+      <c r="E19" s="254"/>
+      <c r="F19" s="251"/>
+      <c r="G19" s="251"/>
+      <c r="H19" s="251"/>
+      <c r="I19" s="250"/>
+      <c r="J19" s="250"/>
+      <c r="K19" s="255"/>
+      <c r="L19" s="250"/>
     </row>
     <row r="20" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="253"/>
-      <c r="B20" s="257"/>
-      <c r="C20" s="253"/>
+      <c r="A20" s="252"/>
+      <c r="B20" s="256"/>
+      <c r="C20" s="252"/>
       <c r="D20" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="255"/>
-      <c r="F20" s="252"/>
-      <c r="G20" s="252"/>
-      <c r="H20" s="252"/>
-      <c r="I20" s="251"/>
-      <c r="J20" s="251"/>
-      <c r="K20" s="256"/>
-      <c r="L20" s="251"/>
+      <c r="E20" s="254"/>
+      <c r="F20" s="251"/>
+      <c r="G20" s="251"/>
+      <c r="H20" s="251"/>
+      <c r="I20" s="250"/>
+      <c r="J20" s="250"/>
+      <c r="K20" s="255"/>
+      <c r="L20" s="250"/>
     </row>
     <row r="21" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="253"/>
-      <c r="B21" s="257"/>
-      <c r="C21" s="253"/>
+      <c r="A21" s="252"/>
+      <c r="B21" s="256"/>
+      <c r="C21" s="252"/>
       <c r="D21" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="255"/>
-      <c r="F21" s="252"/>
-      <c r="G21" s="252"/>
-      <c r="H21" s="252"/>
-      <c r="I21" s="251"/>
-      <c r="J21" s="251"/>
-      <c r="K21" s="256"/>
-      <c r="L21" s="251"/>
+      <c r="E21" s="254"/>
+      <c r="F21" s="251"/>
+      <c r="G21" s="251"/>
+      <c r="H21" s="251"/>
+      <c r="I21" s="250"/>
+      <c r="J21" s="250"/>
+      <c r="K21" s="255"/>
+      <c r="L21" s="250"/>
     </row>
     <row r="22" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="125" t="s">
@@ -22495,27 +23329,27 @@
       <c r="M22" s="129"/>
       <c r="N22" s="129"/>
       <c r="P22" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q22" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="112" x14ac:dyDescent="0.2">
       <c r="A23" s="121" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
       <c r="C23" s="121" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="D23" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E23" s="138" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="F23" s="124" t="s">
         <v>17</v>
@@ -22549,7 +23383,7 @@
         <v>16</v>
       </c>
       <c r="E24" s="79" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="F24" s="124" t="s">
         <v>17</v>
@@ -22571,10 +23405,10 @@
       </c>
       <c r="L24" s="107"/>
       <c r="P24" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q24" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="96" x14ac:dyDescent="0.2">
@@ -22615,10 +23449,10 @@
       <c r="M25" s="129"/>
       <c r="N25" s="129"/>
       <c r="P25" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q25" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="16" x14ac:dyDescent="0.2">
@@ -22657,10 +23491,10 @@
         <v>217</v>
       </c>
       <c r="P26" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q26" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="32" x14ac:dyDescent="0.2">
@@ -22701,10 +23535,10 @@
       <c r="M27" s="129"/>
       <c r="N27" s="129"/>
       <c r="P27" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q27" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="48" x14ac:dyDescent="0.2">
@@ -22743,27 +23577,27 @@
       </c>
       <c r="L28" s="107"/>
       <c r="P28" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q28" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="128" x14ac:dyDescent="0.2">
       <c r="A29" s="121" t="s">
+        <v>665</v>
+      </c>
+      <c r="B29" s="35" t="s">
         <v>666</v>
       </c>
-      <c r="B29" s="35" t="s">
-        <v>667</v>
-      </c>
       <c r="C29" s="141" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D29" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E29" s="71" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="F29" s="124" t="s">
         <v>17</v>
@@ -22783,10 +23617,10 @@
       <c r="K29" s="106"/>
       <c r="L29" s="107"/>
       <c r="P29" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q29" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="48" x14ac:dyDescent="0.2">
@@ -22827,10 +23661,10 @@
       <c r="M30" s="129"/>
       <c r="N30" s="129"/>
       <c r="P30" s="99" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q30" s="99" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="160" x14ac:dyDescent="0.2">
@@ -22847,13 +23681,13 @@
         <v>233</v>
       </c>
       <c r="E31" s="132" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F31" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="124" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H31" s="124" t="s">
         <v>19</v>
@@ -22869,10 +23703,10 @@
       </c>
       <c r="L31" s="107"/>
       <c r="P31" s="99" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q31" s="99" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="32" x14ac:dyDescent="0.2">
@@ -22913,10 +23747,10 @@
       <c r="M32" s="129"/>
       <c r="N32" s="129"/>
       <c r="P32" s="99" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q32" s="99" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="33" spans="1:51" ht="32" x14ac:dyDescent="0.2">
@@ -22955,27 +23789,27 @@
       </c>
       <c r="L33" s="107"/>
       <c r="P33" s="99" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q33" s="99" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="34" spans="1:51" ht="209.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="121" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="B34" s="35" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="C34" s="141" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="D34" s="246" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="E34" s="132" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="F34" s="124" t="s">
         <v>17</v>
@@ -23068,13 +23902,13 @@
       <c r="M35" s="129"/>
       <c r="N35" s="129"/>
       <c r="P35" s="99" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q35" s="99" t="s">
+        <v>833</v>
+      </c>
+      <c r="R35" s="32" t="s">
         <v>838</v>
-      </c>
-      <c r="R35" s="32" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="36" spans="1:51" ht="16" x14ac:dyDescent="0.2">
@@ -23113,10 +23947,10 @@
       </c>
       <c r="L36" s="107"/>
       <c r="P36" s="99" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q36" s="99" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="37" spans="1:51" ht="16" x14ac:dyDescent="0.2">
@@ -23157,10 +23991,10 @@
       <c r="M37" s="129"/>
       <c r="N37" s="129"/>
       <c r="P37" s="99" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q37" s="99" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="38" spans="1:51" ht="64" x14ac:dyDescent="0.2">
@@ -23199,13 +24033,13 @@
       </c>
       <c r="L38" s="107"/>
       <c r="O38" s="32" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="P38" s="99" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="Q38" s="99" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="39" spans="1:51" ht="64" x14ac:dyDescent="0.2">
@@ -23228,7 +24062,7 @@
         <v>17</v>
       </c>
       <c r="G39" s="127" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="H39" s="127" t="s">
         <v>19</v>
@@ -23246,10 +24080,10 @@
       <c r="M39" s="129"/>
       <c r="N39" s="129"/>
       <c r="P39" s="99" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="Q39" s="99" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="40" spans="1:51" ht="59" customHeight="1" x14ac:dyDescent="0.2">
@@ -23288,33 +24122,33 @@
       </c>
       <c r="L40" s="107"/>
       <c r="P40" s="99" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q40" s="99" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="41" spans="1:51" ht="92" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="121" t="s">
+        <v>667</v>
+      </c>
+      <c r="B41" s="35" t="s">
         <v>668</v>
       </c>
-      <c r="B41" s="35" t="s">
+      <c r="C41" s="121" t="s">
         <v>669</v>
-      </c>
-      <c r="C41" s="121" t="s">
-        <v>670</v>
       </c>
       <c r="D41" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E41" s="132" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="F41" s="124" t="s">
         <v>17</v>
       </c>
-      <c r="G41" s="124" t="s">
-        <v>864</v>
+      <c r="G41" s="128" t="s">
+        <v>915</v>
       </c>
       <c r="H41" s="124" t="s">
         <v>19</v>
@@ -23328,10 +24162,10 @@
       <c r="K41" s="106"/>
       <c r="L41" s="107"/>
       <c r="P41" s="99" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q41" s="99" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="42" spans="1:51" ht="112" x14ac:dyDescent="0.2">
@@ -23378,13 +24212,13 @@
         <v>46</v>
       </c>
       <c r="O42" s="32" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="P42" s="32" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="Q42" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="43" spans="1:51" ht="64" x14ac:dyDescent="0.2">
@@ -23401,13 +24235,13 @@
         <v>279</v>
       </c>
       <c r="E43" s="138" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F43" s="124" t="s">
         <v>17</v>
       </c>
       <c r="G43" s="124" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="H43" s="124" t="s">
         <v>19</v>
@@ -23423,10 +24257,10 @@
       </c>
       <c r="L43" s="107"/>
       <c r="P43" s="32" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="Q43" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="44" spans="1:51" ht="228" customHeight="1" x14ac:dyDescent="0.2">
@@ -23471,13 +24305,13 @@
         <v>285</v>
       </c>
       <c r="O44" s="32" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="P44" s="32" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="Q44" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="45" spans="1:51" ht="48" x14ac:dyDescent="0.2">
@@ -23524,13 +24358,13 @@
         <v>291</v>
       </c>
       <c r="O45" s="32" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="P45" s="32" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="Q45" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="46" spans="1:51" ht="48" x14ac:dyDescent="0.2">
@@ -23575,13 +24409,13 @@
         <v>297</v>
       </c>
       <c r="O46" s="32" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="P46" s="32" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="Q46" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="47" spans="1:51" ht="32" x14ac:dyDescent="0.2">
@@ -23620,13 +24454,13 @@
       </c>
       <c r="L47" s="107"/>
       <c r="P47" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q47" s="32" t="s">
+        <v>833</v>
+      </c>
+      <c r="R47" s="32" t="s">
         <v>838</v>
-      </c>
-      <c r="R47" s="32" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="48" spans="1:51" ht="160" x14ac:dyDescent="0.2">
@@ -23643,7 +24477,7 @@
         <v>16</v>
       </c>
       <c r="E48" s="74" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="F48" s="127" t="s">
         <v>17</v>
@@ -23673,13 +24507,13 @@
         <v>302</v>
       </c>
       <c r="O48" s="32" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="P48" s="32" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="Q48" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="49" spans="1:20" ht="64" x14ac:dyDescent="0.2">
@@ -23722,10 +24556,10 @@
       <c r="M49" s="107"/>
       <c r="N49" s="107"/>
       <c r="P49" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q49" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="50" spans="1:20" ht="32" x14ac:dyDescent="0.2">
@@ -23768,10 +24602,10 @@
       <c r="M50" s="129"/>
       <c r="N50" s="129"/>
       <c r="P50" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q50" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="51" spans="1:20" ht="64" x14ac:dyDescent="0.2">
@@ -23812,10 +24646,10 @@
       <c r="M51" s="107"/>
       <c r="N51" s="107"/>
       <c r="P51" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q51" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="52" spans="1:20" ht="32" x14ac:dyDescent="0.2">
@@ -23862,13 +24696,13 @@
         <v>302</v>
       </c>
       <c r="O52" s="32" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="P52" s="32" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="Q52" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="53" spans="1:20" ht="64" x14ac:dyDescent="0.2">
@@ -23909,10 +24743,10 @@
       <c r="M53" s="107"/>
       <c r="N53" s="107"/>
       <c r="P53" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q53" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="54" spans="1:20" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23953,13 +24787,13 @@
       <c r="M54" s="129"/>
       <c r="N54" s="129"/>
       <c r="P54" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q54" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S54" s="234" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
     </row>
     <row r="55" spans="1:20" ht="32" x14ac:dyDescent="0.2">
@@ -24000,16 +24834,16 @@
       <c r="M55" s="107"/>
       <c r="N55" s="107"/>
       <c r="P55" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q55" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="T55" s="32" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="64" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:20" ht="32" x14ac:dyDescent="0.2">
       <c r="A56" s="125" t="s">
         <v>329</v>
       </c>
@@ -24023,7 +24857,7 @@
         <v>332</v>
       </c>
       <c r="E56" s="83" t="s">
-        <v>333</v>
+        <v>926</v>
       </c>
       <c r="F56" s="127" t="s">
         <v>17</v>
@@ -24048,35 +24882,35 @@
       <c r="N56" s="129"/>
       <c r="O56" s="118"/>
       <c r="P56" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q56" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="R56" s="118"/>
       <c r="T56" s="118"/>
     </row>
     <row r="57" spans="1:20" ht="80" x14ac:dyDescent="0.2">
       <c r="A57" s="125" t="s">
+        <v>672</v>
+      </c>
+      <c r="B57" s="74" t="s">
+        <v>674</v>
+      </c>
+      <c r="C57" s="125" t="s">
         <v>673</v>
-      </c>
-      <c r="B57" s="74" t="s">
-        <v>675</v>
-      </c>
-      <c r="C57" s="125" t="s">
-        <v>674</v>
       </c>
       <c r="D57" s="217" t="s">
         <v>16</v>
       </c>
       <c r="E57" s="83" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="F57" s="127" t="s">
         <v>17</v>
       </c>
       <c r="G57" s="128" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H57" s="127" t="s">
         <v>19</v>
@@ -24089,39 +24923,39 @@
       </c>
       <c r="K57" s="130"/>
       <c r="L57" s="129" t="s">
+        <v>685</v>
+      </c>
+      <c r="M57" s="129" t="s">
         <v>686</v>
       </c>
-      <c r="M57" s="129" t="s">
-        <v>687</v>
-      </c>
       <c r="N57" s="129" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="O57" s="32" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="P57" s="32" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="Q57" s="32" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="58" spans="1:20" ht="32" x14ac:dyDescent="0.2">
       <c r="A58" s="121" t="s">
+        <v>333</v>
+      </c>
+      <c r="B58" s="35" t="s">
         <v>334</v>
       </c>
-      <c r="B58" s="35" t="s">
+      <c r="C58" s="121" t="s">
         <v>335</v>
-      </c>
-      <c r="C58" s="121" t="s">
-        <v>336</v>
       </c>
       <c r="D58" s="132" t="s">
         <v>16</v>
       </c>
       <c r="E58" s="132" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F58" s="124" t="s">
         <v>17</v>
@@ -24145,28 +24979,28 @@
       <c r="M58" s="107"/>
       <c r="N58" s="107"/>
       <c r="P58" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q58" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="S58" s="118"/>
     </row>
     <row r="59" spans="1:20" ht="32" x14ac:dyDescent="0.2">
       <c r="A59" s="125" t="s">
+        <v>337</v>
+      </c>
+      <c r="B59" s="74" t="s">
         <v>338</v>
       </c>
-      <c r="B59" s="74" t="s">
+      <c r="C59" s="125" t="s">
         <v>339</v>
-      </c>
-      <c r="C59" s="125" t="s">
-        <v>340</v>
       </c>
       <c r="D59" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E59" s="74" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F59" s="127" t="s">
         <v>17</v>
@@ -24190,10 +25024,10 @@
       <c r="M59" s="129"/>
       <c r="N59" s="129"/>
       <c r="P59" s="32" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Q59" s="32" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="T59" s="32" t="b">
         <v>1</v>
@@ -24201,13 +25035,13 @@
     </row>
     <row r="60" spans="1:20" ht="84.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="121" t="s">
+        <v>341</v>
+      </c>
+      <c r="B60" s="35" t="s">
         <v>342</v>
       </c>
-      <c r="B60" s="35" t="s">
+      <c r="C60" s="121" t="s">
         <v>343</v>
-      </c>
-      <c r="C60" s="121" t="s">
-        <v>344</v>
       </c>
       <c r="D60" s="132" t="s">
         <v>16</v>
@@ -24216,7 +25050,7 @@
         <v>17</v>
       </c>
       <c r="G60" s="124" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="H60" s="124" t="s">
         <v>19</v>
@@ -24232,10 +25066,10 @@
       <c r="M60" s="107"/>
       <c r="N60" s="107"/>
       <c r="P60" s="32" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Q60" s="32" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="61" spans="1:20" s="118" customFormat="1" x14ac:dyDescent="0.2">
@@ -24271,68 +25105,68 @@
     <mergeCell ref="J17:J21"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F17 F22:F61">
-    <cfRule type="cellIs" dxfId="284" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="320" priority="12" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16:H17 H22:H61 H2:H14">
-    <cfRule type="cellIs" dxfId="283" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="319" priority="21" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="282" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="318" priority="22" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F17 F22:F61">
-    <cfRule type="cellIs" dxfId="281" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="317" priority="23" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="280" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="316" priority="24" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="279" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="315" priority="25" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="278" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="314" priority="26" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J16:J17 J22:J61 J2:J14">
-    <cfRule type="containsText" dxfId="277" priority="9" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="313" priority="9" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="276" priority="10" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="312" priority="10" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="275" priority="11" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="311" priority="11" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1">
-    <cfRule type="cellIs" dxfId="274" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="310" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="273" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="309" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="272" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="308" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="271" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="307" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:T1">
-    <cfRule type="cellIs" dxfId="270" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="306" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="269" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="305" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="268" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="304" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="267" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="303" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24449,60 +25283,60 @@
         <v>10</v>
       </c>
       <c r="L1" s="223" t="s">
+        <v>344</v>
+      </c>
+      <c r="M1" s="223" t="s">
         <v>345</v>
       </c>
-      <c r="M1" s="223" t="s">
+      <c r="N1" s="108" t="s">
         <v>346</v>
       </c>
-      <c r="N1" s="108" t="s">
+      <c r="O1" s="108" t="s">
         <v>347</v>
       </c>
-      <c r="O1" s="108" t="s">
+      <c r="P1" s="223" t="s">
         <v>348</v>
       </c>
-      <c r="P1" s="223" t="s">
+      <c r="Q1" s="223" t="s">
         <v>349</v>
       </c>
-      <c r="Q1" s="223" t="s">
+      <c r="R1" s="224" t="s">
         <v>350</v>
       </c>
-      <c r="R1" s="224" t="s">
+      <c r="S1" s="224" t="s">
         <v>351</v>
       </c>
-      <c r="S1" s="224" t="s">
+      <c r="T1" s="224" t="s">
         <v>352</v>
       </c>
-      <c r="T1" s="224" t="s">
+      <c r="U1" s="224" t="s">
         <v>353</v>
       </c>
-      <c r="U1" s="224" t="s">
+      <c r="V1" s="233" t="s">
         <v>354</v>
       </c>
-      <c r="V1" s="233" t="s">
-        <v>355</v>
-      </c>
       <c r="W1" s="92" t="s">
+        <v>820</v>
+      </c>
+      <c r="X1" s="92" t="s">
+        <v>821</v>
+      </c>
+      <c r="Y1" s="92" t="s">
+        <v>822</v>
+      </c>
+      <c r="Z1" s="92" t="s">
+        <v>823</v>
+      </c>
+      <c r="AA1" s="92" t="s">
+        <v>824</v>
+      </c>
+      <c r="AB1" s="92" t="s">
         <v>825</v>
-      </c>
-      <c r="X1" s="92" t="s">
-        <v>826</v>
-      </c>
-      <c r="Y1" s="92" t="s">
-        <v>827</v>
-      </c>
-      <c r="Z1" s="92" t="s">
-        <v>828</v>
-      </c>
-      <c r="AA1" s="92" t="s">
-        <v>829</v>
-      </c>
-      <c r="AB1" s="92" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="64" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B2" s="157" t="s">
         <v>61</v>
@@ -24511,10 +25345,10 @@
         <v>62</v>
       </c>
       <c r="D2" s="152" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E2" s="235" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F2" s="159" t="s">
         <v>17</v>
@@ -24532,33 +25366,33 @@
       <c r="K2" s="161"/>
       <c r="L2" s="107"/>
       <c r="X2" s="136" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Y2" s="136" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="128" x14ac:dyDescent="0.2">
       <c r="A3" s="68" t="s">
+        <v>357</v>
+      </c>
+      <c r="B3" s="61" t="s">
+        <v>902</v>
+      </c>
+      <c r="C3" s="68" t="s">
         <v>358</v>
-      </c>
-      <c r="B3" s="61" t="s">
-        <v>911</v>
-      </c>
-      <c r="C3" s="68" t="s">
-        <v>359</v>
       </c>
       <c r="D3" s="162" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="184" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="F3" s="163" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="163" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H3" s="163">
         <v>1</v>
@@ -24570,7 +25404,7 @@
         <v>66</v>
       </c>
       <c r="K3" s="136" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="L3" s="129"/>
       <c r="M3" s="129"/>
@@ -24583,13 +25417,13 @@
       <c r="T3" s="129"/>
       <c r="U3" s="129"/>
       <c r="X3" s="136" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Y3" s="136" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="Z3" s="84" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="112" x14ac:dyDescent="0.2">
@@ -24603,10 +25437,10 @@
         <v>209</v>
       </c>
       <c r="D4" s="71" t="s">
+        <v>361</v>
+      </c>
+      <c r="E4" s="158" t="s">
         <v>362</v>
-      </c>
-      <c r="E4" s="158" t="s">
-        <v>363</v>
       </c>
       <c r="F4" s="159" t="s">
         <v>35</v>
@@ -24621,34 +25455,34 @@
         <v>28</v>
       </c>
       <c r="J4" s="160" t="s">
+        <v>363</v>
+      </c>
+      <c r="K4" s="136" t="s">
         <v>364</v>
-      </c>
-      <c r="K4" s="136" t="s">
-        <v>365</v>
       </c>
       <c r="L4" s="107"/>
       <c r="X4" s="136" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Y4" s="136" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="165" t="s">
+        <v>365</v>
+      </c>
+      <c r="B5" s="75" t="s">
         <v>366</v>
       </c>
-      <c r="B5" s="75" t="s">
+      <c r="C5" s="165" t="s">
         <v>367</v>
-      </c>
-      <c r="C5" s="165" t="s">
-        <v>368</v>
       </c>
       <c r="D5" s="126" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="75" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F5" s="166" t="s">
         <v>35</v>
@@ -24666,7 +25500,7 @@
         <v>29</v>
       </c>
       <c r="K5" s="136" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="L5" s="129"/>
       <c r="M5" s="129"/>
@@ -24679,10 +25513,10 @@
       <c r="T5" s="129"/>
       <c r="U5" s="129"/>
       <c r="X5" s="136" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Y5" s="136" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="AB5" s="136" t="b">
         <v>1</v>
@@ -24690,19 +25524,19 @@
     </row>
     <row r="6" spans="1:28" ht="96" x14ac:dyDescent="0.2">
       <c r="A6" s="168" t="s">
+        <v>370</v>
+      </c>
+      <c r="B6" s="151" t="s">
         <v>371</v>
       </c>
-      <c r="B6" s="151" t="s">
+      <c r="C6" s="168" t="s">
         <v>372</v>
-      </c>
-      <c r="C6" s="168" t="s">
-        <v>373</v>
       </c>
       <c r="D6" s="169" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="151" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F6" s="133" t="s">
         <v>17</v>
@@ -24722,10 +25556,10 @@
       <c r="K6" s="161"/>
       <c r="L6" s="107"/>
       <c r="X6" s="136" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Y6" s="136" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="AB6" s="136" t="b">
         <v>1</v>
@@ -24733,19 +25567,19 @@
     </row>
     <row r="7" spans="1:28" ht="112" x14ac:dyDescent="0.2">
       <c r="A7" s="125" t="s">
+        <v>373</v>
+      </c>
+      <c r="B7" s="74" t="s">
         <v>374</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="C7" s="125" t="s">
         <v>375</v>
       </c>
-      <c r="C7" s="125" t="s">
+      <c r="D7" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="D7" s="171" t="s">
-        <v>377</v>
-      </c>
       <c r="E7" s="81" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="F7" s="127" t="s">
         <v>17</v>
@@ -24774,10 +25608,10 @@
       <c r="T7" s="129"/>
       <c r="U7" s="129"/>
       <c r="X7" s="136" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Y7" s="136" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="32" x14ac:dyDescent="0.2">
@@ -24791,10 +25625,10 @@
         <v>331</v>
       </c>
       <c r="D8" s="143" t="s">
+        <v>376</v>
+      </c>
+      <c r="E8" s="135" t="s">
         <v>377</v>
-      </c>
-      <c r="E8" s="135" t="s">
-        <v>378</v>
       </c>
       <c r="F8" s="159" t="s">
         <v>17</v>
@@ -24812,19 +25646,19 @@
         <v>29</v>
       </c>
       <c r="K8" s="136" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L8" s="107"/>
       <c r="X8" s="136" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Y8" s="136" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="165" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B9" s="75" t="s">
         <v>77</v>
@@ -24836,7 +25670,7 @@
         <v>16</v>
       </c>
       <c r="E9" s="173" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F9" s="166" t="s">
         <v>35</v>
@@ -24854,7 +25688,7 @@
         <v>66</v>
       </c>
       <c r="K9" s="136" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="L9" s="129"/>
       <c r="M9" s="129"/>
@@ -24867,10 +25701,10 @@
       <c r="T9" s="129"/>
       <c r="U9" s="129"/>
       <c r="X9" s="136" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Y9" s="136" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -25476,54 +26310,54 @@
     <sortCondition ref="A2:A9"/>
   </sortState>
   <conditionalFormatting sqref="F2:F55">
-    <cfRule type="cellIs" dxfId="266" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="302" priority="12" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H55">
-    <cfRule type="cellIs" dxfId="265" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="301" priority="13" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="264" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="300" priority="14" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F55">
-    <cfRule type="cellIs" dxfId="263" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="299" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="262" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="298" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="261" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="297" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="260" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="296" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J55">
-    <cfRule type="containsText" dxfId="259" priority="9" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="295" priority="9" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="258" priority="10" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="294" priority="10" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="257" priority="11" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="293" priority="11" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W1:AB1">
-    <cfRule type="cellIs" dxfId="256" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="292" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="255" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="291" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="254" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="290" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="253" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="289" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25619,63 +26453,63 @@
         <v>10</v>
       </c>
       <c r="L1" s="225" t="s">
+        <v>382</v>
+      </c>
+      <c r="M1" s="108" t="s">
         <v>383</v>
       </c>
-      <c r="M1" s="108" t="s">
+      <c r="N1" s="223" t="s">
         <v>384</v>
       </c>
-      <c r="N1" s="223" t="s">
+      <c r="O1" s="224" t="s">
         <v>385</v>
       </c>
-      <c r="O1" s="224" t="s">
+      <c r="P1" s="232" t="s">
         <v>386</v>
       </c>
-      <c r="P1" s="232" t="s">
+      <c r="Q1" s="233" t="s">
         <v>387</v>
       </c>
-      <c r="Q1" s="233" t="s">
-        <v>388</v>
-      </c>
       <c r="R1" s="92" t="s">
+        <v>820</v>
+      </c>
+      <c r="S1" s="92" t="s">
+        <v>821</v>
+      </c>
+      <c r="T1" s="92" t="s">
+        <v>822</v>
+      </c>
+      <c r="U1" s="92" t="s">
+        <v>823</v>
+      </c>
+      <c r="V1" s="92" t="s">
+        <v>824</v>
+      </c>
+      <c r="W1" s="92" t="s">
         <v>825</v>
-      </c>
-      <c r="S1" s="92" t="s">
-        <v>826</v>
-      </c>
-      <c r="T1" s="92" t="s">
-        <v>827</v>
-      </c>
-      <c r="U1" s="92" t="s">
-        <v>828</v>
-      </c>
-      <c r="V1" s="92" t="s">
-        <v>829</v>
-      </c>
-      <c r="W1" s="92" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="64.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="64" t="s">
+        <v>388</v>
+      </c>
+      <c r="B2" s="45" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="C2" s="172" t="s">
         <v>390</v>
-      </c>
-      <c r="C2" s="172" t="s">
-        <v>391</v>
       </c>
       <c r="D2" s="64" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="88" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F2" s="159" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="159" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H2" s="159" t="s">
         <v>19</v>
@@ -25687,37 +26521,37 @@
         <v>29</v>
       </c>
       <c r="K2" s="156" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L2" s="136"/>
       <c r="S2" s="136" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="T2" s="136" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="128" x14ac:dyDescent="0.2">
       <c r="A3" s="68" t="s">
+        <v>393</v>
+      </c>
+      <c r="B3" s="61" t="s">
         <v>394</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="C3" s="68" t="s">
         <v>395</v>
-      </c>
-      <c r="C3" s="68" t="s">
-        <v>396</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="184" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="F3" s="163" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="163" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H3" s="163">
         <v>1</v>
@@ -25729,7 +26563,7 @@
         <v>29</v>
       </c>
       <c r="K3" s="156" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L3" s="75"/>
       <c r="M3" s="61"/>
@@ -25737,36 +26571,36 @@
       <c r="O3" s="61"/>
       <c r="P3" s="61"/>
       <c r="S3" s="136" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="T3" s="136" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="U3" s="84" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="64" t="s">
+        <v>397</v>
+      </c>
+      <c r="B4" s="45" t="s">
         <v>398</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="C4" s="64" t="s">
         <v>399</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>400</v>
       </c>
       <c r="D4" s="64" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="88" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F4" s="159" t="s">
         <v>17</v>
       </c>
       <c r="G4" s="159" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H4" s="159" t="s">
         <v>81</v>
@@ -25778,14 +26612,14 @@
         <v>29</v>
       </c>
       <c r="K4" s="156" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="L4" s="136"/>
       <c r="S4" s="136" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="T4" s="136" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
@@ -26488,54 +27322,54 @@
     <sortCondition ref="A2:A4"/>
   </sortState>
   <conditionalFormatting sqref="F2:F53">
-    <cfRule type="cellIs" dxfId="252" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="288" priority="12" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H53">
-    <cfRule type="cellIs" dxfId="251" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="287" priority="13" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="250" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="286" priority="14" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F53">
-    <cfRule type="cellIs" dxfId="249" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="285" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="248" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="284" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="247" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="283" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="246" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="282" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J53">
-    <cfRule type="containsText" dxfId="245" priority="9" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="281" priority="9" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="244" priority="10" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="280" priority="10" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="243" priority="11" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="279" priority="11" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:W1">
-    <cfRule type="cellIs" dxfId="242" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="278" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="241" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="277" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="240" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="276" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="239" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="275" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Documents/Health-RI_v2.1.0-for-FDP.xlsx
+++ b/Documents/Health-RI_v2.1.0-for-FDP.xlsx
@@ -179,7 +179,7 @@
         <scheme val="major"/>
       </rPr>
       <t xml:space="preserve">This property points to a contact point that can answer questions about the dataset. Details on how to describe these are provided under class vcard:Kind.
-Whenever possible, use a </t>
+Whenever possible, use </t>
     </r>
     <r>
       <rPr>
@@ -198,7 +198,7 @@
         <rFont val="Aptos Display"/>
         <scheme val="major"/>
       </rPr>
-      <t xml:space="preserve"> (for example from a department) instead of contact information of an individual.</t>
+      <t xml:space="preserve"> (for example from a department) instead of the contact information of an individual.</t>
     </r>
   </si>
   <si>
@@ -227,7 +227,7 @@
   </si>
   <si>
     <t>The creator is the entity responsible for making the resource. According to Dutch databank and copyright law, this is in most cases the organisation / employer bearing investment risk, instead of an individual (e.g. individual researcher). Therefore, in many cases, this might be the same Agent as the dct:publisher, being the organisation (not a department or subdivision of the organisation) where the catalogue was created.
-In case there are multiple (collaborating) organisation involved in data creation, all of them can be stated as dct:creator, as the model allows more than one creator.
+In case there are multiple (collaborating) organisations involved in data creation, all of them can be stated as dct:creator, as the model allows more than one creator.
 Note that the Health-RI model diverges from DCAT-AP NL here, which reduces the maximum number of creators to 1. The Health-RI model allows the specification of multiple creators of a catalogue.</t>
   </si>
   <si>
@@ -551,7 +551,7 @@
     <t>access rights</t>
   </si>
   <si>
-    <t>Information about who access the resource or an indication of its security status.</t>
+    <t>Information about who can access the resource or an indication of its security status.</t>
   </si>
   <si>
     <t>dct:accessRights</t>
@@ -560,10 +560,10 @@
     <t>http://publications.europa.eu/resource/authority/access-right</t>
   </si>
   <si>
-    <t>Information that indicates whether the Dataset is publicly accessible, has access restrictions or is not public. It is foreseen that one of the three options have to be used: public, restricted, non-public.
+    <t>Information that indicates whether the Dataset is publicly accessible, has access restrictions or is not public. It is foreseen that one of the three options has to be used: public, restricted, non-public.
     Open Data (Public): The dataset is available under general open data rules, such as those covered by the High Value Datasets Implementing Regulation.
     Protected Data (Restricted): The dataset contains protected data and is accessible only under specific conditions, as outlined in regulations like the Data Governance Act.
-    Sensitive Data (Non public): The dataset includes resources that may contain sensitive or personal information, falling under regulations such as the EHDS Regulation.
+    Sensitive Data (Non-public): The dataset includes resources that may contain sensitive or personal information, falling under regulations such as the EHDS Regulation.
 Since most data contain personal information, these datasets will need to take the value 'non-public' for the access rights property.</t>
   </si>
   <si>
@@ -579,7 +579,7 @@
     <t>healthdcatap:analytics</t>
   </si>
   <si>
-    <t>Publishers are encouraged to provide URLs pointing to document repositories where users can access or request associated resources such as technical reports of the dataset, quality measurements, usability indicators,... Note that HealthDCAT-AP mentions also API endpoints or analytics services, but these would not be Distriutions but rather DatasetServices.</t>
+    <t>Publishers are encouraged to provide URLs pointing to document repositories where users can access or request associated resources such as technical reports of the dataset, quality measurements, usability indicators, etc. Note that HealthDCAT-AP also mentions API endpoints or analytics services, but these would not be Distributions but rather DatasetServices.</t>
   </si>
   <si>
     <t>dcat:Distribution</t>
@@ -637,8 +637,8 @@
   </si>
   <si>
     <t>The creator (of the dataset) is the entity responsible for making the resource. According to Dutch databank and copyright law, this is in most cases the organisation / employer bearing investment risk, instead of an individual (e.g. individual researcher). Therefore, in many cases, this might be the same Agent as the dct:publisher, being the organisation (not a department or subdivision of the organisation) where the dataset was created.
-In case there are multiple (collaborating) organisation involved in data creation, all of them can be stated as dct:creator, as the model allows more than one creator.
-In case you wish to credit other contributors to the dataset, you can use the prov:qualifiedAttribution property. This could be useful if you wish to indicate, for example, the funding organisation(s), collaborating organosation(s) or name specific individuals (e.g., principal investigator) involved in creation or managing of the dataset.</t>
+In case there are multiple (collaborating) organisations involved in data creation, all of them can be stated as dct:creator, as the model allows more than one creator.
+In case you wish to credit other contributors to the dataset, you can use the prov:qualifiedAttribution property. This could be useful if you wish to indicate, for example, the funding organisation(s), collaborating organisation(s) or name specific individuals (e.g., principal investigator) involved in creating or managing the dataset.</t>
   </si>
   <si>
     <t>custom:creator_</t>
@@ -696,7 +696,7 @@
     <t>custom:frequency</t>
   </si>
   <si>
-    <t>The EU Vocabularies Name Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, Geonames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocab can be used. However, it might in many cases be desirable to keep the geographical coverage broader (eg. indicating that NL is covered), to not expose detailed information of subject's locations.</t>
+    <t>The EU Vocabularies Name Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, Geonames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocab can be used. However, it might in many cases be desirable to keep the geographical coverage broader (e.g. indicating that NL is covered), to avoid exposing detailed information about subjects' locations.</t>
   </si>
   <si>
     <t>has version</t>
@@ -738,7 +738,7 @@
     <t>dct:identifier</t>
   </si>
   <si>
-    <t>Current status: Health-RI is currently working on a strategy for persistant identifiers for, among other things, datasets. Until a solid solution has been found, we propose the following temporary solution:
+    <t>Current status: Health-RI is currently working on a strategy for persistent identifiers for, among other things, datasets. Until a solid solution has been found, we propose the following temporary solution:
 If your data is published in a repository, fill in with the provided DOI (Example: https://doi.org/10.34894/ZLOYOJ). If not, use the identifier of the dataset as generated in the FAIR data point (FDP). Ensure that metadata is updated if your situation changes.</t>
   </si>
   <si>
@@ -1322,7 +1322,7 @@
 Wikidata: https://www.wikidata.org/wiki/Wikidata:Main_Page</t>
   </si>
   <si>
-    <t>Specify the entity (person or organization) by providing an identifier. We recommend using an ORCID identifier for a person or ROR identifier for organization. Dutch governmenta organization are listed in TOOI. If these are not available, you can use ISNI, or Wikidata or any other identifier you may have. If you have multiple identifiers, you should provide them all.</t>
+    <t>Specify the entity (person or organization) by providing an identifier. We recommend using an ORCID identifier for a person or ROR identifier for an organization. Dutch government organizations are listed in TOOI. If these are not available, you can use ISNI, or Wikidata or any other identifier you may have. If you have multiple identifiers, you should provide them all.</t>
   </si>
   <si>
     <t>HRI v1</t>
@@ -1433,7 +1433,7 @@
     <t>vcard:hasURL</t>
   </si>
   <si>
-    <t>A webpage that either allows to make contact (i.e. a webform) or the information contains how to get into contact.</t>
+    <t>A webpage that either allows contact (i.e. a web form) or contains information on how to make contact.</t>
   </si>
   <si>
     <t>custom:{property}_url</t>
@@ -1520,7 +1520,7 @@
     <t>dcat:byteSize</t>
   </si>
   <si>
-    <t>Describes the size of the distribution (the actual file) in bytes, and is therefore expressed as a non-negative integer. If the actual size is not know, it can be estimated.</t>
+    <t>Describes the size of the distribution (the actual file) in bytes, and is therefore expressed as a non-negative integer. If the actual size is not known, it can be estimated.</t>
   </si>
   <si>
     <t>xsd:nonNegativeInteger</t>
@@ -1637,7 +1637,7 @@
         <scheme val="major"/>
       </rPr>
       <t xml:space="preserve"> used in the Distribution, indicated with a value from the EU controlled vocabulary. Not all distributions might have a language, for example imaging data.
-Note that here the Health-RI model diverges from DCAT-AP NL, which allows maximum of 1 languages per Distribution. The Health-RI model allows multiple languages in the same Distribution.</t>
+Note that here the Health-RI model diverges from DCAT-AP NL, which allows a maximum of 1 language per Distribution. The Health-RI model allows multiple languages in the same Distribution.</t>
     </r>
   </si>
   <si>
@@ -1674,7 +1674,7 @@
     <t>dcat:mediaType</t>
   </si>
   <si>
-    <t>Use the specified vocabularies, prioritizing IANA media types whenever possible. If unavailable, consider other ontologies, such as ZonMw generic terms, to descibe the format.
+    <t>Use the specified vocabularies, prioritizing IANA media types whenever possible. If unavailable, consider other ontologies, such as ZonMw generic terms, to describe the format.
 Example: https://www.iana.org/assignments/media-types/text/csv (for csv)
 If IANA media types do not sufficiently describe the format, use "format" to describe it in more detail.</t>
   </si>
@@ -1758,7 +1758,7 @@
     <t>data_series::coverage</t>
   </si>
   <si>
-    <t>This is not equal to the most recent modified dataset in the collection of the dataset series.</t>
+    <t>This is not equal to the most recently modified dataset in the collection of the dataset series.</t>
   </si>
   <si>
     <t xml:space="preserve">The publisher of the dataset series may not be the publisher of all datasets.  E.g. a digital archive could take over the publishing of older datasets in the series. </t>
@@ -1773,7 +1773,7 @@
     <t>data_series:issued</t>
   </si>
   <si>
-    <t>When temporal coverage is a dimension in the dataset series then the temporal coverage of each dataset in the collection should be part of the temporal coverage. In that case, an open ended value is recommended, e.g. after 2012.</t>
+    <t>When temporal coverage is a dimension in the dataset series then the temporal coverage of each dataset in the collection should be part of the temporal coverage. In that case, an open-ended value is recommended, e.g. after 2012.</t>
   </si>
   <si>
     <t>data_series::temporal</t>
@@ -1834,7 +1834,7 @@
     <t>application profile</t>
   </si>
   <si>
-    <t>The standards referred here SHOULD describe the Data Service and not the data it serves. The latter is provided by the dataset with which this Data Service is connected. For instance the data service adheres to the OGC WFS API standard, while the associated dataset adheres to the INSPIRE Address data model.</t>
+    <t>The standards referred to here SHOULD describe the Data Service and not the data it serves. The latter is provided by the dataset with which this Data Service is connected. For instance, the data service adheres to the OGC WFS API standard, while the associated dataset adheres to the INSPIRE Address data model.</t>
   </si>
   <si>
     <t>Briefly describe the data service provided. You can repeat this description in multiple languages. Example: A data service that provides API access to real-time electrocardiogram (ECG) monitoring data for clinical research applications.</t>
@@ -2121,7 +2121,7 @@
     <t>agent</t>
   </si>
   <si>
-    <t>The prov:agent property references an prov:Agent which influenced a resource.</t>
+    <t>The prov:agent property references a prov:Agent which influenced a resource.</t>
   </si>
   <si>
     <t>prov:agent</t>
@@ -2444,7 +2444,7 @@
     <t>checksum value</t>
   </si>
   <si>
-    <t>The checksumValue property provides a lower case hexidecimal encoded digest value produced using a specific algorithm.</t>
+    <t>The checksumValue property provides a lowercase hexadecimal-encoded digest value produced using a specific algorithm.</t>
   </si>
   <si>
     <t>spdx:checksumValue</t>
@@ -2479,12 +2479,12 @@
   </si>
   <si>
     <t>The legal basis can be provided as a value from the dpv taxonomy (see Controlled vocabulary column).
-While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property described the legal basis for initial collection and processing of (personal) data.
+While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property describes the legal basis for initial collection and processing of (personal) data.
 This property should always be filled if the dataset contains personal data and the applicable legislation is GDPR.
 Example value for this property could be: dpv:Consent</t>
   </si>
   <si>
-    <t>One (or many) categoiesy or sub-categories of the purposes can be chosen from the taxonomy provided by dpv (see controlled vocabulary column). Try to be as specific as possible.
+    <t>One (or many) categories or sub-categories of the purposes can be chosen from the taxonomy provided by dpv (see controlled vocabulary column). Try to be as specific as possible.
 Example value could be: dpv:ResearchAndDevelopment.</t>
   </si>
   <si>
@@ -2644,7 +2644,7 @@
     <t xml:space="preserve">A keyword or tag describing the table.	</t>
   </si>
   <si>
-    <t>Variable (column) defines metadata about one field in the CSV file.</t>
+    <t>A variable (column) defines metadata about one field in the CSV file.</t>
   </si>
   <si>
     <t>csvw:url</t>
@@ -2665,7 +2665,7 @@
     <t>Provides a set of keywords to support search and discovery of the table.</t>
   </si>
   <si>
-    <t>Each variable (column) node defines characteristics such as name, title, datatype, etc., for one column of the CSV. Should be either a blank node or IRI referring to a csvw:Column.</t>
+    <t>Each variable (column) node defines characteristics such as name, title, datatype, etc., for one column of the CSV. It should be either a blank node or an IRI referring to a csvw:Column.</t>
   </si>
   <si>
     <t>csvw:Column</t>
@@ -2680,10 +2680,10 @@
     <t>property URL</t>
   </si>
   <si>
-    <t>A Technical name given to the Variable as it appears in the CSV file.</t>
-  </si>
-  <si>
-    <t>A Human-readable name given to the Variable.</t>
+    <t>A technical name given to the Variable as it appears in the CSV file.</t>
+  </si>
+  <si>
+    <t>A human-readable name given to the Variable.</t>
   </si>
   <si>
     <t>Variable description.</t>
@@ -3363,7 +3363,7 @@
     </r>
   </si>
   <si>
-    <t>Information about how the data was collected, including methodologies, tools, and protocols used, this property can be repeated for different versions of the provenance (e.g. the provenance in different languages).
+    <t>Information about how the data was collected, including methodologies, tools, and protocols used. This property can be repeated for different versions of the provenance (e.g. the provenance in different languages).
 This is where the collection-method statements not captured by dedicated properties can be listed.</t>
   </si>
   <si>
@@ -3422,7 +3422,7 @@
         <scheme val="major"/>
       </rPr>
       <t>: The use of wikidata URIs will be replaced with the terms from a controlled vocabulary in the next major release.
-This property provides informatio on which coding systems are in use inside your dataset. For this, wikidata URIs must be used.</t>
+This property provides information on which coding systems are in use in your dataset. For this, wikidata URIs must be used.</t>
     </r>
   </si>
   <si>
@@ -3505,12 +3505,12 @@
     </r>
   </si>
   <si>
-    <t>A statement that concerns all rights not addressed in fields License or Access rights. In case of not open data (as specified in the dct:licence property), further agreements regarding data reuse (eg. Data Transfer Agreement, DTA,) should be stated in this property.
-The rights statement should be a free-text statement placed at an web-accessible location such that the value of this property is the IRI pointing to that statement.</t>
+    <t>A statement that concerns all rights not addressed in fields License or Access rights. In case of not open data (as specified in the dct:licence property), further agreements regarding data reuse (e.g. Data Transfer Agreement, DTA) should be stated in this property.
+The rights statement should be a free-text statement placed at a web-accessible location such that the value of this property is the IRI pointing to that statement.</t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">A email address via which contact can be made. This property </t>
+      <t xml:space="preserve">An email address via which contact can be made. This property </t>
     </r>
     <r>
       <rPr>

--- a/Documents/Health-RI_v2.1.0-for-FDP.xlsx
+++ b/Documents/Health-RI_v2.1.0-for-FDP.xlsx
@@ -78,7 +78,7 @@
     <t>Property URI</t>
   </si>
   <si>
-    <t>Controlled vocabluary (if applicable)</t>
+    <t>Controlled vocabulary (if applicable)</t>
   </si>
   <si>
     <t>Usage note</t>
@@ -138,16 +138,16 @@
     <t>custom:applicable_legislation</t>
   </si>
   <si>
-    <t>catalog</t>
-  </si>
-  <si>
-    <t>A catalog that is listed in the catalog.</t>
+    <t>catalogue</t>
+  </si>
+  <si>
+    <t>A catalogue that is listed in the catalogue.</t>
   </si>
   <si>
     <t>dcat:catalog</t>
   </si>
   <si>
-    <t>For certain research projects, multiple catalogs may need to be organized in a nested manner. This property serves to connect the different catalogs with each other.</t>
+    <t>For certain research projects, multiple catalogues may need to be organised in a nested manner. This property serves to connect the different catalogues with each other.</t>
   </si>
   <si>
     <t>dcat:Catalog</t>
@@ -165,7 +165,7 @@
     <t>contact point</t>
   </si>
   <si>
-    <t>Relevant contact information for the cataloged resource.</t>
+    <t>Relevant contact information for the catalogued resource.</t>
   </si>
   <si>
     <t>dcat:contactPoint</t>
@@ -178,7 +178,7 @@
         <rFont val="Aptos Display"/>
         <scheme val="major"/>
       </rPr>
-      <t xml:space="preserve">This property points to a contact point that can answer questions about the dataset. Details on how to describe these are provided under class vcard:Kind.
+      <t xml:space="preserve">This property points to a contact point that can answer questions about the dataset. Details on how to describe these are provided under the vcard:Kind class.
 Whenever possible, use </t>
     </r>
     <r>
@@ -198,7 +198,7 @@
         <rFont val="Aptos Display"/>
         <scheme val="major"/>
       </rPr>
-      <t xml:space="preserve"> (for example from a department) instead of the contact information of an individual.</t>
+      <t xml:space="preserve"> (for example, from a department) instead of the contact information of an individual.</t>
     </r>
   </si>
   <si>
@@ -214,7 +214,7 @@
     <t>custom:contact</t>
   </si>
   <si>
-    <t>fill in in 'Kind' tab</t>
+    <t>Enter the value on the 'Kind' tab.</t>
   </si>
   <si>
     <t>creator</t>
@@ -226,8 +226,8 @@
     <t>dct:creator</t>
   </si>
   <si>
-    <t>The creator is the entity responsible for making the resource. According to Dutch databank and copyright law, this is in most cases the organisation / employer bearing investment risk, instead of an individual (e.g. individual researcher). Therefore, in many cases, this might be the same Agent as the dct:publisher, being the organisation (not a department or subdivision of the organisation) where the catalogue was created.
-In case there are multiple (collaborating) organisations involved in data creation, all of them can be stated as dct:creator, as the model allows more than one creator.
+    <t>The creator is the entity responsible for making the resource. According to Dutch databank and copyright law, this is in most cases the organisation/employer bearing investment risk, instead of an individual (e.g. an individual researcher). Therefore, in many cases, this might be the same Agent as the dct:publisher: the organisation (not a department or subdivision of the organisation) where the catalogue was created.
+If there are multiple (collaborating) organisations involved in data creation, all of them can be stated as dct:creator, as the model allows more than one creator.
 Note that the Health-RI model diverges from DCAT-AP NL here, which reduces the maximum number of creators to 1. The Health-RI model allows the specification of multiple creators of a catalogue.</t>
   </si>
   <si>
@@ -237,19 +237,19 @@
     <t>custom:creator</t>
   </si>
   <si>
-    <t>fill in in 'Agent' tab</t>
+    <t>Enter the value on the 'Agent' tab.</t>
   </si>
   <si>
     <t>dataset</t>
   </si>
   <si>
-    <t>A dataset that is listed in the catalog.</t>
+    <t>A dataset that is listed in the catalogue.</t>
   </si>
   <si>
     <t>dcat:dataset</t>
   </si>
   <si>
-    <t>Each catalog contains one or more datasets. This property serves to link datasets to a catalogue. Therefore, a dataset is always contained inside a catalogue.</t>
+    <t>Each catalogue contains one or more datasets. This property serves to link datasets to a catalogue. Therefore, a dataset is always contained inside a catalogue.</t>
   </si>
   <si>
     <t>dcat:Dataset</t>
@@ -270,7 +270,7 @@
     <t>dct:description</t>
   </si>
   <si>
-    <t>Briefly describe the catalog and what it contains. You can repeat this in multiple languages.</t>
+    <t>Briefly describe the catalogue and what it contains. You can repeat this in multiple languages.</t>
   </si>
   <si>
     <t>rdfs:Literal</t>
@@ -291,7 +291,7 @@
     <t>EU Vocabularies Continents Named Authority List</t>
   </si>
   <si>
-    <t>The EU Vocabularies Name Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, Geonames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocab can be used.</t>
+    <t>The EU Vocabularies Named Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, GeoNames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocabulary can be used.</t>
   </si>
   <si>
     <t>dct:Location (IRI)</t>
@@ -306,7 +306,7 @@
     <t>EU Vocabularies Places Named Authority List</t>
   </si>
   <si>
-    <t>Geonames</t>
+    <t>GeoNames</t>
   </si>
   <si>
     <t>https://vocabs.cbs.nl/nl/</t>
@@ -322,10 +322,10 @@
   </si>
   <si>
     <t>Use this property to establish another catalogue in this catalogue.
-Note that deeply nested structures should be avoided, and can currently not be displayed in the National Health Data Catalogue.</t>
-  </si>
-  <si>
-    <t>If applicable, add URI to dcat:Catalog that is part of this catalogue</t>
+Note that deeply nested structures should be avoided, and cannot currently be displayed in the National Health Data Catalogue.</t>
+  </si>
+  <si>
+    <t>If applicable, add the URI of the dcat:Catalog that is part of this catalogue.</t>
   </si>
   <si>
     <t>home page</t>
@@ -410,7 +410,7 @@
     <t>dct:publisher</t>
   </si>
   <si>
-    <t>The organisation or individual that is holder of the intellectual property rights of a dataset. For more details about the publisher, see the class Agent. Example: Radboudumc.</t>
+    <t>The organisation or individual that is the holder of the intellectual property rights of a dataset. For more details about the publisher, see the class Agent. Example: Radboudumc.</t>
   </si>
   <si>
     <t>Adapted from v1</t>
@@ -449,13 +449,13 @@
     <t>service</t>
   </si>
   <si>
-    <t>A service that is listed in the catalog.</t>
+    <t>A service that is listed in the catalogue.</t>
   </si>
   <si>
     <t>dcat:service</t>
   </si>
   <si>
-    <t>Some datasets may have real-time Data Services (e.g., Beacon API counting individuals). IT teams should define the relationship between the catalog and the Data Service via this property. While crucial for interoperability, this property is not relevant for end-users to collect.</t>
+    <t>Some datasets may have real-time Data Services (e.g., Beacon API counting individuals). IT teams should define the relationship between the catalogue and the Data Service via this property. While crucial for interoperability, this property is not relevant for end users to collect.</t>
   </si>
   <si>
     <t>dcat:DataService</t>
@@ -488,7 +488,7 @@
     <t>dcat:themeTaxonomy</t>
   </si>
   <si>
-    <t>This property refers to a knowledge organisation system used to classify the Catalogue's Datasets. It must have at least the value NAL:data-theme as this is the mandatory controlled vocabulary for dcat:theme.</t>
+    <t>This property refers to a knowledge organisation system used to classify the Catalogue's Datasets. It must include at least the value NAL:data-theme as this is the mandatory controlled vocabulary for dcat:theme.</t>
   </si>
   <si>
     <t>skos:ConceptScheme</t>
@@ -503,7 +503,7 @@
     <t>dct:title</t>
   </si>
   <si>
-    <t>Provide a unique title for your catalog, which can be repeated in multiple languages. Example: Healthy Brain Study.</t>
+    <t>Provide a unique title for your catalogue, which can be repeated in multiple languages. Example: Healthy Brain Study.</t>
   </si>
   <si>
     <t>custom:purpose</t>
@@ -515,10 +515,10 @@
     <t>custom:retention_period</t>
   </si>
   <si>
-    <t>(issue on github)</t>
-  </si>
-  <si>
-    <t>issue on ckan github</t>
+    <t>(issue on GitHub)</t>
+  </si>
+  <si>
+    <t>issue on CKAN GitHub</t>
   </si>
   <si>
     <t>custom:status</t>
@@ -588,7 +588,7 @@
     <t>custom:analytics</t>
   </si>
   <si>
-    <t>If available, add URI to analytics distribution here</t>
+    <t>If available, add the URI for the analytics distribution here.</t>
   </si>
   <si>
     <t>code values</t>
@@ -609,7 +609,7 @@
     <t>coding system</t>
   </si>
   <si>
-    <t>Coding systems in use (ex: ICD-10-CM, DGRs, SNOMED=CT, ...)</t>
+    <t>Coding systems in use (e.g. ICD-10-CM, DGRs, SNOMED CT, ...)</t>
   </si>
   <si>
     <t>healthdcatap:hasCodingSystem</t>
@@ -636,15 +636,15 @@
     <t>custom:contact_</t>
   </si>
   <si>
-    <t>The creator (of the dataset) is the entity responsible for making the resource. According to Dutch databank and copyright law, this is in most cases the organisation / employer bearing investment risk, instead of an individual (e.g. individual researcher). Therefore, in many cases, this might be the same Agent as the dct:publisher, being the organisation (not a department or subdivision of the organisation) where the dataset was created.
-In case there are multiple (collaborating) organisations involved in data creation, all of them can be stated as dct:creator, as the model allows more than one creator.
+    <t>The creator (of the dataset) is the entity responsible for making the resource. According to Dutch databank and copyright law, this is in most cases the organisation/employer bearing investment risk, instead of an individual (e.g. an individual researcher). Therefore, in many cases, this might be the same Agent as the dct:publisher: the organisation (not a department or subdivision of the organisation) where the dataset was created.
+If there are multiple (collaborating) organisations involved in data creation, all of them can be stated as dct:creator, as the model allows more than one creator.
 In case you wish to credit other contributors to the dataset, you can use the prov:qualifiedAttribution property. This could be useful if you wish to indicate, for example, the funding organisation(s), collaborating organisation(s) or name specific individuals (e.g., principal investigator) involved in creating or managing the dataset.</t>
   </si>
   <si>
     <t>custom:creator_</t>
   </si>
   <si>
-    <t>Brief description of the dataset. You can repeat this property in multiple languages. Example: ''Collection of physiological data of Healthy Brain Study participants. This collection includes measurements via biowearables for heart rate, oxygenation, systolic and diastolic measures and stress levels.''</t>
+    <t>Brief description of the dataset. You can repeat this property in multiple languages. Example: ‘Collection of physiological data of Healthy Brain Study participants. This collection includes measurements via biowearables for heart rate, oxygenation, systolic and diastolic measures and stress levels.’</t>
   </si>
   <si>
     <t>distribution</t>
@@ -659,7 +659,7 @@
     <t>Metadata element used as a key link to the class Distribution.</t>
   </si>
   <si>
-    <t>fill in URI to dcat:Distribution</t>
+    <t>Enter the URI for dcat:Distribution.</t>
   </si>
   <si>
     <t>documentation</t>
@@ -671,7 +671,7 @@
     <t>foaf:page</t>
   </si>
   <si>
-    <t>The value of this property is the IRI directing to the web-page or document about the dataset.</t>
+    <t>The value of this property is the IRI pointing to the web page or document about the dataset.</t>
   </si>
   <si>
     <t>custom:documentation</t>
@@ -696,7 +696,7 @@
     <t>custom:frequency</t>
   </si>
   <si>
-    <t>The EU Vocabularies Name Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, Geonames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocab can be used. However, it might in many cases be desirable to keep the geographical coverage broader (e.g. indicating that NL is covered), to avoid exposing detailed information about subjects' locations.</t>
+    <t>The EU Vocabularies Named Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, GeoNames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocabulary can be used. However, it might in many cases be desirable to keep the geographical coverage broader (e.g. indicating that NL is covered), to avoid exposing detailed information about subjects' locations.</t>
   </si>
   <si>
     <t>has version</t>
@@ -708,7 +708,7 @@
     <t>dcat:hasVersion</t>
   </si>
   <si>
-    <t>Indicate the dataset which is the other version of the current dataset.</t>
+    <t>Indicate the dataset that is another version of the current dataset.</t>
   </si>
   <si>
     <t>custom:has_version</t>
@@ -739,7 +739,7 @@
   </si>
   <si>
     <t>Current status: Health-RI is currently working on a strategy for persistent identifiers for, among other things, datasets. Until a solid solution has been found, we propose the following temporary solution:
-If your data is published in a repository, fill in with the provided DOI (Example: https://doi.org/10.34894/ZLOYOJ). If not, use the identifier of the dataset as generated in the FAIR data point (FDP). Ensure that metadata is updated if your situation changes.</t>
+If your data is published in a repository, enter the provided DOI (Example: https://doi.org/10.34894/ZLOYOJ). If not, use the identifier of the dataset as generated in the FAIR data point (FDP). Ensure that metadata is updated if your situation changes.</t>
   </si>
   <si>
     <t>custom:alternate_identifier</t>
@@ -754,13 +754,13 @@
     <t>dcat:inSeries</t>
   </si>
   <si>
-    <t xml:space="preserve">This property points to which Dataset Series the Dataset is part of. </t>
+    <t xml:space="preserve">This property points to the Dataset Series of which the Dataset is part. </t>
   </si>
   <si>
     <t>dcat:DatasetSeries</t>
   </si>
   <si>
-    <t>If applicable, add URI to dataset series here</t>
+    <t>If applicable, add the URI for the dataset series here.</t>
   </si>
   <si>
     <t>is referenced by</t>
@@ -772,7 +772,7 @@
     <t>dct:isReferencedBy</t>
   </si>
   <si>
-    <t>The value of this property is the IRI of the doi to the publication or other related resource.
+    <t>The value of this property is the IRI of the DOI for the publication or other related resource.
 For example: https://doi.org/10.1186/s13690-021-00709-x</t>
   </si>
   <si>
@@ -884,7 +884,7 @@
     <t>adms:identifier</t>
   </si>
   <si>
-    <t>Examples for secondary identifiers are MAST/ADS, DataCite, DOI, EZID or W3ID (if not used for the original identifier). This property makes use of another, small class: adms:Identifier, where you provide the identifier and the name of the identifier schema (eg. DOI).</t>
+    <t>Examples of secondary identifiers include MAST/ADS, DataCite, DOI, EZID or W3ID (if not used for the original identifier). This property makes use of another small class: adms:Identifier, where you provide the identifier and the name of the identifier schema (e.g. DOI).</t>
   </si>
   <si>
     <t>adms:Identifier</t>
@@ -905,7 +905,7 @@
     <t>https://w3c.github.io/dpv/2.0/pd/</t>
   </si>
   <si>
-    <t>The different types of personal information that are collected in the dataset can be indicated with this property. Values can be picked from the dpv taxonomy (see controlled vocabulary column).
+    <t>The different types of personal information that are collected in the dataset can be indicated with this property. Values can be picked from the DPV taxonomy (see the Controlled vocabulary column).
 For example: dpv-pd:Gender</t>
   </si>
   <si>
@@ -921,13 +921,13 @@
     <t>healthdcatap:populationCoverage</t>
   </si>
   <si>
-    <t>This field is a free text description of the population covered in the dataset. For example, "Adults aged 18–65 diagnosed with type 2 diabetes in the Netherlands between 2015 and 2020".</t>
+    <t>This field is a free-text description of the population covered in the dataset. For example, "Adults aged 18–65 diagnosed with type 2 diabetes in the Netherlands between 2015 and 2020".</t>
   </si>
   <si>
     <t>custom:populatiion_coverage</t>
   </si>
   <si>
-    <t>This property identifies the organisation or individual responsible for making the dataset available. For datasets, this is typically the employer of the data creators. In simple cases, the dataset publisher may be the same as the catalog publisher. In more complex settings, such as when datasets come from multiple institutions within a consortium, the consortium should be listed as the publisher where possible. If no formal consortium can be specified, provide the information of the contributing organizations or individuals under dct:creator instead. For more details, refer to the Agent class.</t>
+    <t>This property identifies the organisation or individual responsible for making the dataset available. For datasets, this is typically the employer of the data creators. In simple cases, the dataset publisher may be the same as the catalogue publisher. In more complex settings, such as when datasets come from multiple institutions within a consortium, the consortium should be listed as the publisher where possible. If no formal consortium can be specified, provide information about the contributing organisations or individuals under dct:creator instead. For more details, refer to the Agent class.</t>
   </si>
   <si>
     <t>purpose</t>
@@ -1007,7 +1007,7 @@
     <t>prov:Attribution</t>
   </si>
   <si>
-    <t>fill in in 'Attribution' tab</t>
+    <t>Enter the value on the 'Attribution' tab.</t>
   </si>
   <si>
     <t>qualified relation</t>
@@ -1025,7 +1025,7 @@
     <t>dcat:Relationship</t>
   </si>
   <si>
-    <t>fill in in 'Relationship' tab</t>
+    <t>Enter the value on the 'Relationship' tab.</t>
   </si>
   <si>
     <t>quality annotation</t>
@@ -1043,7 +1043,7 @@
     <t>dqv:QualityCertificate</t>
   </si>
   <si>
-    <t>fill in in 'QualityCertificate' tab</t>
+    <t>Enter the value on the 'QualityCertificate' tab.</t>
   </si>
   <si>
     <r>
@@ -1098,13 +1098,13 @@
     <t>retention period</t>
   </si>
   <si>
-    <t>A temporal period which the dataset is available for secondary use.</t>
+    <t>A temporal period during which the dataset is available for secondary use.</t>
   </si>
   <si>
     <t>healthdcatap:retentionPeriod</t>
   </si>
   <si>
-    <t>fill in in 'Period of Time' tab</t>
+    <t>Enter the value on the 'PeriodOfTime' tab.</t>
   </si>
   <si>
     <t>sample</t>
@@ -1116,10 +1116,10 @@
     <t>adms:sample</t>
   </si>
   <si>
-    <t>This property makes use of the dcat:Distribution class to describe a sample distribution of the dataset, which can be anonymized or synthetic data, or the data dictionary provided in CSVW format. This is currently further developed by the TEHDAS2 program. More information can be found here: https://healthdcat-ap.github.io/#sample-distribution</t>
-  </si>
-  <si>
-    <t>If available, add URI to sample distribution here</t>
+    <t>This property makes use of the dcat:Distribution class to describe a sample distribution of the dataset, which can consist of anonymised or synthetic data, or a data dictionary provided in CSVW format. This is currently being further developed by the TEHDAS2 programme. More information can be found here: https://healthdcat-ap.github.io/#sample-distribution</t>
+  </si>
+  <si>
+    <t>If available, add the URI for the sample distribution here.</t>
   </si>
   <si>
     <t>source</t>
@@ -1134,7 +1134,7 @@
     <t>Indicate the dataset on which this described dataset is based.</t>
   </si>
   <si>
-    <t>If applicable, add URI to source dataset here</t>
+    <t>If applicable, add the URI for the source dataset here.</t>
   </si>
   <si>
     <t>status</t>
@@ -1165,7 +1165,7 @@
     <t>dcat:temporalResolution</t>
   </si>
   <si>
-    <t>If the dataset is a time-series, this should correspond to the spacing of items in the series. For other kinds of dataset, this property will usually indicate the smallest time difference between items in the dataset. The time period has to be provided in the xsd:duration format.</t>
+    <t>If the dataset is a time-series, this should correspond to the spacing of items in the series. For other kinds of datasets, this property will usually indicate the smallest time difference between items in the dataset. The time period has to be provided in the xsd:duration format.</t>
   </si>
   <si>
     <t>xsd:duration</t>
@@ -1219,7 +1219,7 @@
     <t>adms:versionNotes</t>
   </si>
   <si>
-    <t>Provide a short description of changes made to the dataset from the previous version.</t>
+    <t>Provide a short description of changes made to the dataset since the previous version.</t>
   </si>
   <si>
     <t>was generated by</t>
@@ -1284,7 +1284,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t xml:space="preserve"> of additional classes  (additional instances of Dataset, DatasetSeries, DataService or Catalogue)</t>
+      <t xml:space="preserve"> of additional classes (additional instances of Dataset, DatasetSeries, DataService or Catalogue).</t>
     </r>
   </si>
   <si>
@@ -1313,7 +1313,7 @@
 Wikidata: https://www.wikidata.org/wiki/Wikidata:Main_Page</t>
   </si>
   <si>
-    <t>Specify the entity (person or organization) by providing an identifier. We recommend using an ORCID identifier for a person or ROR identifier for an organization. Dutch government organizations are listed in TOOI. If these are not available, you can use ISNI, or Wikidata or any other identifier you may have. If you have multiple identifiers, you should provide them all.</t>
+    <t>Specify the entity (person or organisation) by providing an identifier. We recommend using an ORCID identifier for a person or a ROR identifier for an organisation. Dutch government organisations are listed in TOOI. If these are not available, you can use ISNI, Wikidata or any other identifier you may have. If you have multiple identifiers, you should provide them all.</t>
   </si>
   <si>
     <t>HRI v1</t>
@@ -1331,7 +1331,7 @@
     <t>foaf:name</t>
   </si>
   <si>
-    <t>This property refers to the given name of the entity. Example: Jane Doe (for a person) and Radboudumc (for an organization). This property can be repeated for different versions of the name (e.g. the name in different languages).</t>
+    <t>This property refers to the given name of the entity. Example: Jane Doe (for a person) and Radboudumc (for an organisation). This property can be repeated for different versions of the name (e.g. the name in different languages).</t>
   </si>
   <si>
     <t>_name</t>
@@ -1340,7 +1340,7 @@
     <t>publisher note</t>
   </si>
   <si>
-    <t>A description of the publisher activities.</t>
+    <t>A description of the publisher's activities.</t>
   </si>
   <si>
     <t>healthdcatap:publishernote</t>
@@ -1358,7 +1358,7 @@
     <t>https://raw.githubusercontent.com/SEMICeu/ADMS-AP/master/purl.org/ADMS_SKOS_v1.00.rdf</t>
   </si>
   <si>
-    <t>This property should be filled using ADMS vocabulary (http://purl.org/adms/publishertype/1.0)</t>
+    <t>This property should be filled using ADMS vocabulary (http://purl.org/adms/publishertype/1.0).</t>
   </si>
   <si>
     <t>_type</t>
@@ -1411,7 +1411,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t xml:space="preserve"> of additional classes ( (additional instances of Dataset, DatasetSeries, DataService or Catalogue)</t>
+      <t xml:space="preserve"> of additional classes (additional instances of Dataset, DatasetSeries, DataService or Catalogue).</t>
     </r>
   </si>
   <si>
@@ -1481,10 +1481,10 @@
     <t>resource:access_services</t>
   </si>
   <si>
-    <t>If applicable, fill in URI to dcat:DatasService</t>
-  </si>
-  <si>
-    <t>access url</t>
+    <t>If applicable, enter the URI for dcat:DataService.</t>
+  </si>
+  <si>
+    <t>access URL</t>
   </si>
   <si>
     <t>A URL of the resource that gives access to a distribution of the dataset. E.g., landing page, feed, SPARQL endpoint.</t>
@@ -1529,7 +1529,7 @@
     <t>spdx:checksum</t>
   </si>
   <si>
-    <t>The checksum is related to the downloadURL. This property makes use of the spdx:Checksum class, which itself has two properties to indicate checksum algorithm and checksum value (see Checksum class for further details).</t>
+    <t>The checksum is related to the downloadURL. This property makes use of the spdx:Checksum class, which itself has two properties to indicate the checksum algorithm and checksum value (see Checksum class for further details).</t>
   </si>
   <si>
     <t>spdx:Checksum</t>
@@ -1538,13 +1538,13 @@
     <t>resource:hash_algorithm/resource:hash_algorithm</t>
   </si>
   <si>
-    <t>fill in in 'Checksum' tab</t>
+    <t>Enter the value on the 'Checksum' tab.</t>
   </si>
   <si>
     <t>compression format</t>
   </si>
   <si>
-    <t>The compression format of the distribution in which the data is contained in a compressed form, e.g., to reduce the size of the downloadable file.</t>
+    <t>The compression format of the distribution in which the data is compressed, e.g., to reduce the size of the downloadable file.</t>
   </si>
   <si>
     <t>dcat:compressFormat</t>
@@ -1608,7 +1608,7 @@
   </si>
   <si>
     <r>
-      <t>Indicates the </t>
+      <t xml:space="preserve">Indicates the </t>
     </r>
     <r>
       <rPr>
@@ -1627,7 +1627,7 @@
         <rFont val="Aptos Display"/>
         <scheme val="major"/>
       </rPr>
-      <t xml:space="preserve"> used in the Distribution, indicated with a value from the EU controlled vocabulary. Not all distributions might have a language, for example imaging data.
+      <t xml:space="preserve"> used in the Distribution, using a value from the EU controlled vocabulary. Not all distributions might have a language, for example imaging data.
 Note that here the Health-RI model diverges from DCAT-AP NL, which allows a maximum of 1 language per Distribution. The Health-RI model allows multiple languages in the same Distribution.</t>
     </r>
   </si>
@@ -1635,10 +1635,10 @@
     <t>resource:language</t>
   </si>
   <si>
-    <t>license</t>
-  </si>
-  <si>
-    <t>For public data, use a Creative Commons (CC) license (see Geonovum options in the Controlled Vocabulary column). For most National Health Data Catalogue distributions, where data is not public, use the 'not open' license from Geonovum and specify data reuse agreements in the dct:rights property.</t>
+    <t>licence</t>
+  </si>
+  <si>
+    <t>For public data, use a Creative Commons (CC) licence (see Geonovum options in the Controlled Vocabulary column). For most National Health Data Catalogue distributions, where data is not public, use the 'not open' licence from Geonovum and specify data reuse agreements in the dct:rights property.</t>
   </si>
   <si>
     <t>resource:license</t>
@@ -1662,7 +1662,7 @@
     <t>dcat:mediaType</t>
   </si>
   <si>
-    <t>Use the specified vocabularies, prioritizing IANA media types whenever possible. If unavailable, consider other ontologies, such as ZonMw generic terms, to describe the format.
+    <t>Use the specified vocabularies, prioritising IANA media types whenever possible. If unavailable, consider other ontologies, such as ZonMw generic terms, to describe the format.
 Example: https://www.iana.org/assignments/media-types/text/csv (for csv)
 If IANA media types do not sufficiently describe the format, use "format" to describe it in more detail.</t>
   </si>
@@ -1697,7 +1697,7 @@
     <t>healthdcatap:retentionperiod</t>
   </si>
   <si>
-    <t>fill in in 'Periof of Time' tab</t>
+    <t>Enter the value on the 'PeriodOfTime' tab.</t>
   </si>
   <si>
     <t>resource:rights</t>
@@ -1707,16 +1707,16 @@
 EU Vocabularies Distribution Status</t>
   </si>
   <si>
-    <t>It MUST take one of the values Completed, Deprecated, Under Development, Withdrawn from the provided controlled vocabulary.</t>
+    <t>It MUST take one of the following values from the provided controlled vocabulary: Completed, Deprecated, Under Development or Withdrawn.</t>
   </si>
   <si>
     <t>resource:status</t>
   </si>
   <si>
-    <t>If applicable, this property indicates the minimum time period resolvable in the dataset distribution, expressed in xsd:duration format (see for more information here: https://www.w3schools.com/xml/schema_dtypes_date.asp)</t>
-  </si>
-  <si>
-    <t>A title given to the distribution. e.g., Data Access Request of Healthy Brain study</t>
+    <t>If applicable, this property indicates the minimum time period resolvable in the dataset distribution, expressed in xsd:duration format (for more information, see: https://www.w3schools.com/xml/schema_dtypes_date.asp).</t>
+  </si>
+  <si>
+    <t>A title given to the distribution, e.g. Data Access Request for the Healthy Brain Study</t>
   </si>
   <si>
     <t>resource:name</t>
@@ -1734,7 +1734,7 @@
     <t>data_series::contact</t>
   </si>
   <si>
-    <t xml:space="preserve">Briefly describe the dataset series in the catalog. You can repeat this in multiple languages. </t>
+    <t xml:space="preserve">Briefly describe the dataset series in the catalogue. You can repeat this in multiple languages. </t>
   </si>
   <si>
     <t>data_series::modified</t>
@@ -1749,7 +1749,7 @@
     <t>This is not equal to the most recently modified dataset in the collection of the dataset series.</t>
   </si>
   <si>
-    <t xml:space="preserve">The publisher of the dataset series may not be the publisher of all datasets.  E.g. a digital archive could take over the publishing of older datasets in the series. </t>
+    <t xml:space="preserve">The publisher of the dataset series may not be the publisher of all datasets. For example, a digital archive could take over the publishing of older datasets in the series. </t>
   </si>
   <si>
     <t>data_series::publisher</t>
@@ -1761,7 +1761,7 @@
     <t>data_series:issued</t>
   </si>
   <si>
-    <t>When temporal coverage is a dimension in the dataset series then the temporal coverage of each dataset in the collection should be part of the temporal coverage. In that case, an open-ended value is recommended, e.g. after 2012.</t>
+    <t>When temporal coverage is a dimension in the dataset series, the temporal coverage of each dataset in the collection should be part of the series' temporal coverage. In that case, an open-ended value is recommended, e.g. after 2012.</t>
   </si>
   <si>
     <t>data_series::temporal</t>
@@ -1774,7 +1774,7 @@
   </si>
   <si>
     <r>
-      <t>Information that indicates whether the Dataset is publicly accessible, has access restrictions or is not public. This property is required to adopt one of the predefined values listed in the </t>
+      <t>Information that indicates whether the Dataset is publicly accessible, has access restrictions or is not public. This property must take one of the predefined values listed in the </t>
     </r>
     <r>
       <rPr>
@@ -1831,10 +1831,10 @@
     <t>access_service:description</t>
   </si>
   <si>
-    <t>end point description</t>
-  </si>
-  <si>
-    <t>A description of the services available via the end-points, including their operations, parameters etc.</t>
+    <t>endpoint description</t>
+  </si>
+  <si>
+    <t>A description of the services available via the endpoints, including their operations, parameters, etc.</t>
   </si>
   <si>
     <t>dcat:endpointDescription</t>
@@ -1846,7 +1846,7 @@
     <t>access_service:endpoint_description</t>
   </si>
   <si>
-    <t>end point URL</t>
+    <t>endpoint URL</t>
   </si>
   <si>
     <t>The root location or primary endpoint of the service (a Web-resolvable IRI).</t>
@@ -1870,22 +1870,22 @@
     <t>Provide a unique identifier for the data service. This could be a globally unique and persistent identifier, such as a DOI, URN, or UUID. If no persistent identifier is available, you may use the accessURL or endpointURL as the identifier, provided it is stable and unique to the service.</t>
   </si>
   <si>
-    <t>landing Page</t>
-  </si>
-  <si>
-    <t>A Web page that can be navigated to in a Web browser to gain access to the catalog, a dataset, its distributions and/or additional information.</t>
+    <t>landing page</t>
+  </si>
+  <si>
+    <t>A Web page that can be navigated to in a Web browser to gain access to the catalogue, a dataset, its distributions and/or additional information.</t>
   </si>
   <si>
     <t>dcat:landingPage</t>
   </si>
   <si>
-    <t>It is intended to point to a landing page at the original data service provider, not to a page on a site of a third party, such as an aggregator.</t>
+    <t>It is intended to point to a landing page at the original data service provider, not to a page on a third-party site, such as an aggregator.</t>
   </si>
   <si>
     <t>Indicates the natural language used in the data service, indicated with a value from the EU controlled vocabulary.</t>
   </si>
   <si>
-    <t>For public data, use a Creative Commons (CC) license (see Geonovum options in the Controlled Vocabulary column). For most National Health Data Catalogue data services, where data is not public, use the 'not open' license from Geonovum and specify data reuse agreements in the dct:rights property.</t>
+    <t>For public data, use a Creative Commons (CC) licence (see Geonovum options in the Controlled Vocabulary column). For most National Health Data Catalogue data services, where data is not public, use the 'not open' licence from Geonovum and specify data reuse agreements in the dct:rights property.</t>
   </si>
   <si>
     <t>access_service:license</t>
@@ -1894,10 +1894,10 @@
     <t>This property indicates the date of the last changes to the dataset, not the metadata record. An absent value may mean the resource hasn't changed since publication, the modification date is unknown, or the resource is continuously updated.</t>
   </si>
   <si>
-    <t>fill in in 'adms_Identifier' tab</t>
-  </si>
-  <si>
-    <t>The organization or individual responsible for making the data service available. In the context of data services, the publisher is typically the organization that manages or provides access to the service. For details, see the class Agent.</t>
+    <t>Enter the value on the 'adms_Identifier' tab.</t>
+  </si>
+  <si>
+    <t>The organisation or individual responsible for making the data service available. In the context of data services, the publisher is typically the organisation that manages or provides access to the service. For details, see the class Agent.</t>
   </si>
   <si>
     <t>serves dataset</t>
@@ -1915,13 +1915,13 @@
     <t>access_service:serves_dataset</t>
   </si>
   <si>
-    <t>fill in URI to dcat:Dataset that this data service serves</t>
+    <t>Enter the URI for the dcat:Dataset that this data service serves.</t>
   </si>
   <si>
     <t>This property should use a controlled vocabulary. In the Health Data Catalogue, most data services will use NAL:data-theme 'HEAL', but additional values from the same vocabulary are allowed.</t>
   </si>
   <si>
-    <t>Provide a unique title for your data service, which can be repeated in multiple languages. Example: Patient counts per available diagnosis</t>
+    <t>Provide a unique title for your data service, which can be repeated in multiple languages. Example: Patient counts per available diagnosis.</t>
   </si>
   <si>
     <t>access_service:title</t>
@@ -1959,7 +1959,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t xml:space="preserve"> of additional classes (additional instances of Dataset or DataService)</t>
+      <t xml:space="preserve"> of additional classes (additional instances of Dataset or DataService).</t>
     </r>
   </si>
   <si>
@@ -2045,7 +2045,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t xml:space="preserve"> of additional classes (additional instances of Catalogue, Dataset, Distribution or Dataset Series)</t>
+      <t xml:space="preserve"> of additional classes (additional instances of Catalogue, Dataset, Distribution or Dataset Series).</t>
     </r>
   </si>
   <si>
@@ -2067,13 +2067,13 @@
     <t>dcat:startDate</t>
   </si>
   <si>
-    <t>Value: qualified Attribution (Dataset A)</t>
-  </si>
-  <si>
-    <t>Value: qualified Attribution (Dataset B)</t>
-  </si>
-  <si>
-    <t>Value: qualified Attribution (Dataset C)</t>
+    <t>Value: qualified attribution (Dataset A)</t>
+  </si>
+  <si>
+    <t>Value: qualified attribution (Dataset B)</t>
+  </si>
+  <si>
+    <t>Value: qualified attribution (Dataset C)</t>
   </si>
   <si>
     <r>
@@ -2099,14 +2099,14 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t xml:space="preserve"> of additional classes (additional instances of Dataset)</t>
+      <t xml:space="preserve"> of additional classes (additional instances of Dataset).</t>
     </r>
   </si>
   <si>
     <t>agent</t>
   </si>
   <si>
-    <t>The prov:agent property references a prov:Agent which influenced a resource.</t>
+    <t>The prov:agent property references a prov:Agent that influenced a resource.</t>
   </si>
   <si>
     <t>prov:agent</t>
@@ -2131,16 +2131,16 @@
   <si>
     <t>Choose one of the roles as listed in the controlled vocabulary. Note that for HealthDCAT-AP, the list of roles might be extended in the future.
 Example: https://standards.iso.org/iso/19115/resources/Codelists/gml/CI_RoleCode.xml#processor
-Next to the CI_RoleCode, we also propose to use the CRediT Taxonomy to specify roles of contributors.</t>
-  </si>
-  <si>
-    <t>Value qualified Relation (Dataset A)</t>
-  </si>
-  <si>
-    <t>Value qualified Relation (Dataset B)</t>
-  </si>
-  <si>
-    <t>Value qualified Relation (Dataset C)</t>
+In addition to CI_RoleCode, we also propose to use the CRediT Taxonomy to specify roles of contributors.</t>
+  </si>
+  <si>
+    <t>Value: qualified relation (Dataset A)</t>
+  </si>
+  <si>
+    <t>Value: qualified relation (Dataset B)</t>
+  </si>
+  <si>
+    <t>Value: qualified relation (Dataset C)</t>
   </si>
   <si>
     <r>
@@ -2166,7 +2166,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t>of additional classes (additional instances of Dataset)</t>
+      <t>of additional classes (additional instances of Dataset).</t>
     </r>
   </si>
   <si>
@@ -2226,7 +2226,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t xml:space="preserve"> of additional classes (additional instances of Dataset)</t>
+      <t xml:space="preserve"> of additional classes (additional instances of Dataset).</t>
     </r>
   </si>
   <si>
@@ -2240,7 +2240,7 @@
   </si>
   <si>
     <t>This property has to be filled with the same value as the dct:identifier of the dataset described, in order to link the quality certificate to that dataset.
-See also example in HealthDCAT-AP: https://healthdcat-ap.github.io/#dqvhasqualityannotation</t>
+See also the example in HealthDCAT-AP: https://healthdcat-ap.github.io/#dqvhasqualityannotation</t>
   </si>
   <si>
     <t>body</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">foaf:primaryTopic </t>
   </si>
   <si>
-    <t xml:space="preserve">A catalogue record will refer to one entity in a catalogue. This can be either a Dataset or a Data Service. To ensure an unambigous reading of the cardinality the range is set to Catalogued Resource. However it is not the intend with this range to require the explicit use of the class Catalogued Record. As abstract class, an subclass should be used. </t>
+    <t xml:space="preserve">A catalogue record will refer to one entity in a catalogue. This can be either a Dataset or a Data Service. To ensure an unambiguous reading of the cardinality, the range is set to Catalogued Resource. However, this range is not intended to require the explicit use of the class Catalogued Record. Since this is an abstract class, a subclass should be used. </t>
   </si>
   <si>
     <t xml:space="preserve">dcat:Resource </t>
@@ -2404,7 +2404,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t xml:space="preserve"> of additional classes (additional instances of Distribution)</t>
+      <t xml:space="preserve"> of additional classes (additional instances of Distribution).</t>
     </r>
   </si>
   <si>
@@ -2420,7 +2420,7 @@
     <t>https://spdx.org/rdf/terms/#d4e2129</t>
   </si>
   <si>
-    <t>Choose one member of the checksum algorithm members as indicated on the webpage linked in the Controlled Vocabulary column.</t>
+    <t>Choose one of the checksum algorithms as indicated on the webpage linked in the Controlled Vocabulary column.</t>
   </si>
   <si>
     <t>spdx:ChecksumAlgorithm (IRI)</t>
@@ -2440,13 +2440,13 @@
   <si>
     <t>It is preferred to provide a general email address of the appropriate institution or department instead of a personal email address, even if an individual is described with this instance of foaf:Agent.
 This protects their privacy and enables contact about the resource even after the individual has left the institution.
-The email address has to be provided starting with mailto: prefix.
+The email address must start with the mailto: prefix.
 For example: mailto:info@example.com</t>
   </si>
   <si>
     <t>It is preferred to provide a general email address of the appropriate institution or department instead of a personal email address, even if an individual is described with this instance of vcard:Kind.
 This protects their privacy and enables contact about the resource even after the individual has left the institution.
-The email address has to be provided starting with mailto: prefix.
+The email address must start with the mailto: prefix.
 For example: mailto:info@example.com</t>
   </si>
   <si>
@@ -2459,21 +2459,21 @@
   <si>
     <t>The ELI of the EHDS was published in March 2025 and can now be included as the applicable legislation mandating that the dataset has to be made public.
 For health datasets, the value must include the ELI of the EHDS Regulation (http://data.europa.eu/eli/reg/2025/327/oj).
-As multiple legislations may apply to the resource the maximum cardinality is not limited. Note that the relation with other legislations is complex and is being looked into by legal experts.
-While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property (also in Datasets) described the legal basis for initial collection and processing of (personal) data.</t>
-  </si>
-  <si>
-    <t>The legal basis can be provided as a value from the dpv taxonomy (see Controlled vocabulary column).
+As multiple pieces of legislation may apply to the resource, the maximum cardinality is not limited. Note that the relationship with other legislation is complex and is being looked into by legal experts.
+While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property (also in Datasets) describes the legal basis for initial collection and processing of (personal) data.</t>
+  </si>
+  <si>
+    <t>The legal basis can be provided as a value from the DPV taxonomy (see the Controlled vocabulary column).
 While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property describes the legal basis for initial collection and processing of (personal) data.
 This property should always be filled if the dataset contains personal data and the applicable legislation is GDPR.
-Example value for this property could be: dpv:Consent</t>
-  </si>
-  <si>
-    <t>One (or many) categories or sub-categories of the purposes can be chosen from the taxonomy provided by dpv (see controlled vocabulary column). Try to be as specific as possible.
-Example value could be: dpv:ResearchAndDevelopment.</t>
-  </si>
-  <si>
-    <t>Indicate with this property in case the Dataset is only available for secondary use for a specific period of time (e.g. due to data protection, contractual, or project constraints).
+An example value for this property could be dpv:Consent.</t>
+  </si>
+  <si>
+    <t>One or more categories or sub-categories of purposes can be chosen from the taxonomy provided by dpv (see the Controlled vocabulary column). Try to be as specific as possible.
+An example value could be dpv:ResearchAndDevelopment.</t>
+  </si>
+  <si>
+    <t>Use this property if the Dataset is only available for secondary use for a specific period of time (e.g. due to data protection, contractual, or project constraints).
 This property makes use of the class dct:PeriodOfTime, in which a start and end date can be provided.
 If the Dataset is available indefinitely, leave the property empty (cardinality is 0..1; it is only meaningful when a retention limit applies).
 If only a start is known, provide dcat:startDate only (open-ended interval, as allowed by dct:PeriodOfTime).
@@ -2576,7 +2576,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Display"/>
       </rPr>
-      <t>: The variables  have been added to the metadata model version 2.1 for testing purposes. For now it is not yet planned to be added to the national catalogue's front end.
+      <t>: The variables have been added to the metadata model version 2.1 for testing purposes. For now, their inclusion in the national catalogue's front end is not yet planned.
 Use this property to link a structured dataset to a CSVW TableGroup that documents its data variables, columns, or fields in a machine-readable way.</t>
     </r>
   </si>
@@ -2602,16 +2602,16 @@
     <t>Value: table 2</t>
   </si>
   <si>
-    <t>Add more columns if you need to describe additional instances of csvw:TableGroup</t>
+    <t>Add more columns if you need to describe additional instances of csvw:TableGroup.</t>
   </si>
   <si>
     <t>csvw:TableGroup</t>
   </si>
   <si>
-    <t>fill in in 'TableGroup' tab</t>
-  </si>
-  <si>
-    <t>fill in in 'TableGroup'  tab</t>
+    <t>Enter the value on the 'TableGroup' tab.</t>
+  </si>
+  <si>
+    <t>Enter the value on the 'TableGroup' tab.</t>
   </si>
   <si>
     <t>url</t>
@@ -2626,7 +2626,7 @@
     <t>Table title.</t>
   </si>
   <si>
-    <t xml:space="preserve">A keyword or tag describing the table.	</t>
+    <t xml:space="preserve">A keyword or tag describing the table.</t>
   </si>
   <si>
     <t>A variable (column) defines metadata about one field in the CSV file.</t>
@@ -2641,7 +2641,7 @@
     <t>csvw:column</t>
   </si>
   <si>
-    <t>The URL should be a valid IRI and should point to the CSV file (synthetic, anonymized representation of the real data) for this table.</t>
+    <t>The URL should be a valid IRI and should point to the CSV file (a synthetic, anonymised representation of the real data) for this table.</t>
   </si>
   <si>
     <t>Used to provide a human-readable title for the table. Can appear in multiple languages.</t>
@@ -2656,7 +2656,7 @@
     <t>csvw:Column</t>
   </si>
   <si>
-    <t>Add more columns if you need to describe additional instances of csvw:Table</t>
+    <t>Add more columns if you need to describe additional instances of csvw:Table.</t>
   </si>
   <si>
     <t>datatype</t>
@@ -2699,7 +2699,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Should match the </t>
+      <t xml:space="preserve">The value should match the </t>
     </r>
     <r>
       <rPr>
@@ -2719,7 +2719,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> of one of the CSVW types as defined in the Built-in datatypes from XML Schema. https://w3c.github.io/csvw/metadata/#datatypes Example: string, integer, boolean …</t>
+      <t xml:space="preserve"> of one of the CSVW types as defined in the Built-in datatypes from XML Schema. See: https://w3c.github.io/csvw/metadata/#datatypes
+Example: string, integer, boolean …</t>
     </r>
   </si>
   <si>
@@ -3179,7 +3180,7 @@
     <t>availability</t>
   </si>
   <si>
-    <t>An indication how long it is planned to keep the Distribution of the Dataset available.</t>
+    <t>An indication of how long it is planned to keep the Distribution of the Dataset available.</t>
   </si>
   <si>
     <t>dcatap:availability</t>
@@ -3209,7 +3210,7 @@
         <scheme val="major"/>
       </rPr>
       <t>: This property will be deprecated in the upcoming major release. It is recommended to indicate the planned availability of the distribution with the newly added Distribution.availability property. 
-Indicate with this property in case the Distribution is only available for secondary use for a specific period of time (e.g. due to data protection, contractual, or project constraints).
+Use this property if the Distribution is only available for secondary use for a specific period of time (e.g. due to data protection, contractual, or project constraints).
 This property makes use of the class dct:PeriodOfTime, in which a start and end date can be provided.
 If the Distribution is available indefinitely, leave the property empty (cardinality is 0..1; it is only meaningful when a retention limit applies).
 If only a start is known, provide dcat:startDate only (open-ended interval, as allowed by dct:PeriodOfTime).
@@ -3265,7 +3266,7 @@
         <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> for identifiers of the Dataset, such as DOI; use </t>
+      <t xml:space="preserve"> for identifiers of the Dataset, such as a DOI; use </t>
     </r>
     <r>
       <rPr>
@@ -3327,7 +3328,7 @@
     </r>
   </si>
   <si>
-    <t>Information about how the data was collected, including methodologies, tools, and protocols used. This property can be repeated for different versions of the provenance (e.g. the provenance in different languages).
+    <t>Information about how the data was collected, including methodologies, tools, and protocols used. This property can be repeated for different versions of the provenance (e.g. in different languages).
 This is where the collection-method statements not captured by dedicated properties can be listed.</t>
   </si>
   <si>
@@ -3341,7 +3342,7 @@
   </si>
   <si>
     <t>Use this property to indicate which anatomical parts of the body are covered by the Dataset. Select the relevant anatomical structure from SNOMED CT. Multiple anatomical locations can be provided.
-Example: Dataset containing lung imaging data can use Lung structure (http://snomed.info/id/39607008).</t>
+Example: A dataset containing lung imaging data can use Lung structure (http://snomed.info/id/39607008).</t>
   </si>
   <si>
     <t>domain of the data</t>
@@ -3382,8 +3383,8 @@
         <rFont val="Aptos Display"/>
         <scheme val="major"/>
       </rPr>
-      <t>: The use of wikidata URIs will be replaced with the terms from a controlled vocabulary in the next major release.
-This property provides information on which coding systems are in use in your dataset. For this, wikidata URIs must be used.</t>
+      <t>: The use of Wikidata URIs will be replaced with the terms from a controlled vocabulary in the next major release.
+This property provides information on which coding systems are in use in your dataset. For this, Wikidata URIs must be used.</t>
     </r>
   </si>
   <si>
@@ -3404,8 +3405,8 @@
         <rFont val="Aptos Display"/>
         <scheme val="major"/>
       </rPr>
-      <t>: The use of wikidata URIs will be replaced with the terms from a controlled vocabulary in the next major release.
-If your data conforms to an established standard or specification, use this property to indicate which one. The wikidata URI of the specification must be used. Example: https://www.wikidata.org/wiki/Q19597236 for FHIR.</t>
+      <t>: The use of Wikidata URIs will be replaced with the terms from a controlled vocabulary in the next major release.
+If your data conforms to an established standard or specification, use this property to indicate which one. The Wikidata URI of the specification must be used. Example: https://www.wikidata.org/wiki/Q19597236 for FHIR.</t>
     </r>
   </si>
   <si>
@@ -3424,8 +3425,8 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Display"/>
       </rPr>
-      <t>: The use of wikidata URIs will be replaced with the terms from a controlled vocabulary in the next major release.
-This property is a structured way to tag the dataset with different health themes. This could include, for example, the specific disease the dataset is about. More details can be provided, if desirable, in the keywords property.  The wikidata URI of the health theme must be used here.</t>
+      <t>: The use of Wikidata URIs will be replaced with the terms from a controlled vocabulary in the next major release.
+This property is a structured way to tag the dataset with different health themes. This could include, for example, the specific disease the dataset is about. More details can be provided, if desirable, in the keywords property.  The Wikidata URI of the health theme must be used here.</t>
     </r>
   </si>
   <si>
@@ -3466,7 +3467,7 @@
     </r>
   </si>
   <si>
-    <t>A statement that concerns all rights not addressed in fields License or Access rights. In case of not open data (as specified in the dct:licence property), further agreements regarding data reuse (e.g. Data Transfer Agreement, DTA) should be stated in this property.
+    <t>A statement that concerns all rights not addressed in the Licence or Access rights fields. For data that is not open (as specified in the dct:license property), further agreements regarding data reuse (e.g. Data Transfer Agreement, DTA) should be stated in this property.
 The rights statement should be a free-text statement placed at a web-accessible location such that the value of this property is the IRI pointing to that statement.</t>
   </si>
   <si>
@@ -3490,7 +3491,7 @@
         <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> be used to provide the email address of the Agent, specified using fully qualified mailto: URI scheme RFC6068. The email </t>
+      <t xml:space="preserve"> be used to provide the email address of the Agent, specified using the fully qualified mailto: URI scheme defined in RFC 6068. The email </t>
     </r>
     <r>
       <rPr>
@@ -3542,8 +3543,8 @@
         <rFont val="Aptos Display"/>
         <scheme val="major"/>
       </rPr>
-      <t>: The use of wikidata URIs will be replaced with free text in the next major release.
-Inside this property, you can provide the coding system of the dataset in the form of wikidata URI (example: https://www.wikidata.org/entity/P494 for ICD-10 ID) and the URI of the value that describes the dataset (example: https://icd.who.int/browse10/2019/en#/Y59.0 for viral vaccines)</t>
+      <t>: The use of Wikidata URIs will be replaced with free text in the next major release.
+Inside this property, you can provide the coding system of the dataset in the form of a Wikidata URI (example: https://www.wikidata.org/entity/P494 for ICD-10 ID) and the URI of the value that describes the dataset (example: https://icd.who.int/browse10/2019/en#/Y59.0 for viral vaccines).</t>
     </r>
   </si>
   <si>
@@ -3563,19 +3564,19 @@
     <t>rdfs:label</t>
   </si>
   <si>
-    <t>In this context the definition should be considered as: A textual statement describing the provenance of the Dataset, including information about its origin, history, or activities involved in its creation or modification.</t>
+    <t>In this context, the definition should be considered as: A textual statement describing the provenance of the Dataset, including information about its origin, history, or activities involved in its creation or modification.</t>
   </si>
   <si>
     <t>dct:ProvenanceStatement</t>
   </si>
   <si>
-    <t>Provide a short textual statement describing the provenance of the Dataset, such as its origin, how it was created or collected, or any relevant processing or transformations it has undergone. This statement should describe the provenance of the Dataset as a whole and be provided as free text.  You can repeat this property in multiple languages</t>
+    <t>Provide a short textual statement describing the provenance of the Dataset, such as its origin, how it was created or collected, or any relevant processing or transformations it has undergone. This statement should describe the provenance of the Dataset as a whole and be provided as free text. You can repeat this property in multiple languages.</t>
   </si>
   <si>
     <t>Value: activity (Dataset A)</t>
   </si>
   <si>
-    <t>Value:activity (Dataset B)</t>
+    <t>Value: activity (Dataset B)</t>
   </si>
   <si>
     <t>Value: activity (Dataset C)</t>
@@ -3590,7 +3591,7 @@
     <t>Value: provenance (Dataset 2)</t>
   </si>
   <si>
-    <t>Add more columns if you need to describe additional instances of dct:ProvenanceStatement for provenance of additional classes (additional instances of Dataset)</t>
+    <t>Add more columns if you need to describe additional instances of dct:ProvenanceStatement for provenance of additional classes (additional instances of Dataset).</t>
   </si>
   <si>
     <t>ProvenanceStatement</t>
@@ -3610,7 +3611,8 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Select data domain(s) from the predefined value list, available at this link: https://github.com/Health-RI/health-ri-metadata/blob/v2.1-changes/Formalisation(shacl)/Core/ValueLists/edam-has-topic.tsv </t>
+      <t xml:space="preserve">Select data domain(s) from the predefined value list, available at this link: https://github.com/Health-RI/health-ri-metadata/blob/v2.1-changes/Formalisation(shacl)/Core/ValueLists/edam-has-topic.tsv
+</t>
     </r>
     <r>
       <rPr>
@@ -3629,7 +3631,7 @@
         <rFont val="Aptos Display"/>
         <scheme val="major"/>
       </rPr>
-      <t>: This is a temporary location and it will change with the release . 
+      <t>: This is a temporary location and it will change with the release. 
 A data domain refers to the broader scientific or health-related area covered by the Dataset. Select the domain that best represents the Dataset as a whole, rather than a specific data element within it. If the dataset contains data from more than one domain, you can select multiple.
 See the property "measurement technique" for more information about the technique(s) used to generate the data in the Dataset.</t>
     </r>
@@ -3673,8 +3675,9 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Select a suitable value or suitable values from the value list to indicate the technique(s) used to generate data in the dataset.
-The value list is  available at this link: https://github.com/Health-RI/health-ri-metadata/blob/v2.1-changes/Formalisation(shacl)/Core/ValueLists/schema-measurement-technique.tsv </t>
+      <t xml:space="preserve">Select one or more suitable values from the value list to indicate the technique(s) used to generate data in the dataset.
+The value list is available at this link: https://github.com/Health-RI/health-ri-metadata/blob/v2.1-changes/Formalisation(shacl)/Core/ValueLists/schema-measurement-technique.tsv
+</t>
     </r>
     <r>
       <rPr>
@@ -3693,14 +3696,14 @@
         <rFont val="Aptos Display"/>
         <scheme val="major"/>
       </rPr>
-      <t xml:space="preserve">: This is a temporary location and it will change with the next release . </t>
+      <t xml:space="preserve">: This is a temporary location and it will change with the next release. </t>
     </r>
   </si>
   <si>
     <t>number of unique individuals</t>
   </si>
   <si>
-    <t>fill in in 'ProvenanceStatement' tab</t>
+    <t>Enter the value on the 'ProvenanceStatement' tab.</t>
   </si>
 </sst>
 </file>

--- a/Documents/Health-RI_v2.1.0-for-FDP.xlsx
+++ b/Documents/Health-RI_v2.1.0-for-FDP.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="17980" yWindow="800" windowWidth="18020" windowHeight="20540" tabRatio="600" firstSheet="15" activeTab="18" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20" yWindow="-28180" windowWidth="34380" windowHeight="28200" tabRatio="600" firstSheet="8" activeTab="11" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" state="visible" r:id="rId1"/>
@@ -1053,10 +1053,13 @@
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1069,9 +1072,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -4899,7 +4899,7 @@
           <t>This property links the distribution class to the corresponding data service(s).</t>
         </is>
       </c>
-      <c r="F2" s="213" t="inlineStr">
+      <c r="F2" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -4919,7 +4919,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J2" s="219" t="inlineStr">
+      <c r="J2" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -4939,15 +4939,23 @@
           <t>If applicable, enter the URI for dcat:DataService.</t>
         </is>
       </c>
-      <c r="O2" s="203" t="n"/>
-      <c r="P2" s="203" t="n"/>
+      <c r="O2" s="203" t="inlineStr">
+        <is>
+          <t>dash:URIViewer</t>
+        </is>
+      </c>
+      <c r="P2" s="203" t="inlineStr">
+        <is>
+          <t>dash:URIEditor</t>
+        </is>
+      </c>
       <c r="S2" s="121" t="n"/>
       <c r="T2" s="221" t="n"/>
       <c r="U2" s="221" t="n"/>
       <c r="V2" s="221" t="n"/>
     </row>
     <row r="3" ht="64" customHeight="1">
-      <c r="A3" s="217" t="inlineStr">
+      <c r="A3" s="218" t="inlineStr">
         <is>
           <t>access URL</t>
         </is>
@@ -4957,7 +4965,7 @@
           <t>A URL of the resource that gives access to a distribution of the dataset. E.g., landing page, feed, SPARQL endpoint.</t>
         </is>
       </c>
-      <c r="C3" s="217" t="inlineStr">
+      <c r="C3" s="218" t="inlineStr">
         <is>
           <t>dcat:accessURL</t>
         </is>
@@ -4967,7 +4975,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E3" s="218" t="inlineStr">
+      <c r="E3" s="219" t="inlineStr">
         <is>
           <t>Add a link that points to where the dataset can be found. If it’s hosted in a Data Repository, include the link to its entry. For datasets not in a repository (like registries), but still available for secondary use, provide a link to an access request form or a webpage with instructions for accessing the data.</t>
         </is>
@@ -4977,7 +4985,7 @@
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G3" s="213" t="inlineStr">
+      <c r="G3" s="215" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
@@ -4985,12 +4993,12 @@
       <c r="H3" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="219" t="inlineStr">
+      <c r="I3" s="213" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J3" s="219" t="inlineStr">
+      <c r="J3" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -5000,8 +5008,8 @@
           <t>resource:access_url</t>
         </is>
       </c>
-      <c r="L3" s="219" t="n"/>
-      <c r="M3" s="219" t="n"/>
+      <c r="L3" s="213" t="n"/>
+      <c r="M3" s="213" t="n"/>
       <c r="O3" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -5013,9 +5021,9 @@
         </is>
       </c>
       <c r="S3" s="121" t="n"/>
-      <c r="T3" s="217" t="n"/>
-      <c r="U3" s="217" t="n"/>
-      <c r="V3" s="217" t="n"/>
+      <c r="T3" s="218" t="n"/>
+      <c r="U3" s="218" t="n"/>
+      <c r="V3" s="218" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="221" t="inlineStr">
@@ -5043,7 +5051,7 @@
           <t>The legislation that mandates the creation or management of the Distribution.</t>
         </is>
       </c>
-      <c r="F4" s="213" t="inlineStr">
+      <c r="F4" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -5063,7 +5071,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="219" t="inlineStr">
+      <c r="J4" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -5101,7 +5109,7 @@
           <t>An indication of how long it is planned to keep the Distribution of the Dataset available.</t>
         </is>
       </c>
-      <c r="C5" s="217" t="inlineStr">
+      <c r="C5" s="218" t="inlineStr">
         <is>
           <t>dcatap:availability</t>
         </is>
@@ -5116,12 +5124,12 @@
           <t>To indicate the planned availability of the Distribution, the EU planned-availability controlled vocabulary MUST be used.</t>
         </is>
       </c>
-      <c r="F5" s="213" t="inlineStr">
+      <c r="F5" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G5" s="213" t="inlineStr">
+      <c r="G5" s="215" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
@@ -5131,19 +5139,19 @@
           <t>0..1</t>
         </is>
       </c>
-      <c r="I5" s="219" t="inlineStr">
+      <c r="I5" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="219" t="inlineStr">
+      <c r="J5" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K5" s="69" t="n"/>
-      <c r="L5" s="219" t="n"/>
-      <c r="M5" s="219" t="n"/>
+      <c r="L5" s="213" t="n"/>
+      <c r="M5" s="213" t="n"/>
       <c r="O5" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -5205,7 +5213,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="219" t="inlineStr">
+      <c r="J6" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5233,7 +5241,7 @@
       <c r="V6" s="221" t="n"/>
     </row>
     <row r="7" ht="64" customHeight="1">
-      <c r="A7" s="217" t="inlineStr">
+      <c r="A7" s="218" t="inlineStr">
         <is>
           <t>checksum</t>
         </is>
@@ -5243,7 +5251,7 @@
           <t>The checksum property provides a mechanism that can be used to verify that the contents of a file or package have not changed.</t>
         </is>
       </c>
-      <c r="C7" s="217" t="inlineStr">
+      <c r="C7" s="218" t="inlineStr">
         <is>
           <t>spdx:checksum</t>
         </is>
@@ -5258,7 +5266,7 @@
           <t>The checksum is related to the downloadURL. This property makes use of the spdx:Checksum class, which itself has two properties to indicate the checksum algorithm and checksum value (see Checksum class for further details).</t>
         </is>
       </c>
-      <c r="F7" s="213" t="inlineStr">
+      <c r="F7" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -5268,17 +5276,17 @@
           <t>spdx:Checksum</t>
         </is>
       </c>
-      <c r="H7" s="213" t="inlineStr">
+      <c r="H7" s="215" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I7" s="219" t="inlineStr">
+      <c r="I7" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J7" s="219" t="inlineStr">
+      <c r="J7" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5288,12 +5296,12 @@
           <t>resource:hash_algorithm/resource:hash_algorithm</t>
         </is>
       </c>
-      <c r="L7" s="219" t="inlineStr">
+      <c r="L7" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Checksum' tab.</t>
         </is>
       </c>
-      <c r="M7" s="219" t="inlineStr">
+      <c r="M7" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Checksum' tab.</t>
         </is>
@@ -5314,9 +5322,9 @@
         </is>
       </c>
       <c r="S7" s="121" t="n"/>
-      <c r="T7" s="217" t="n"/>
-      <c r="U7" s="217" t="n"/>
-      <c r="V7" s="217" t="n"/>
+      <c r="T7" s="218" t="n"/>
+      <c r="U7" s="218" t="n"/>
+      <c r="V7" s="218" t="n"/>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="221" t="inlineStr">
@@ -5364,7 +5372,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="219" t="inlineStr">
+      <c r="J8" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5392,7 +5400,7 @@
       <c r="V8" s="221" t="n"/>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="217" t="inlineStr">
+      <c r="A9" s="218" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -5402,7 +5410,7 @@
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C9" s="217" t="inlineStr">
+      <c r="C9" s="218" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -5417,27 +5425,27 @@
           <t>Provide specific details about the distribution here, complementing the description of the related Dataset. This field can be repeated for different language versions of the description.</t>
         </is>
       </c>
-      <c r="F9" s="213" t="inlineStr">
+      <c r="F9" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G9" s="213" t="inlineStr">
+      <c r="G9" s="215" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H9" s="213" t="inlineStr">
+      <c r="H9" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I9" s="219" t="inlineStr">
+      <c r="I9" s="213" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J9" s="219" t="inlineStr">
+      <c r="J9" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5447,8 +5455,8 @@
           <t>resource:description</t>
         </is>
       </c>
-      <c r="L9" s="219" t="n"/>
-      <c r="M9" s="219" t="n"/>
+      <c r="L9" s="213" t="n"/>
+      <c r="M9" s="213" t="n"/>
       <c r="O9" s="203" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -5456,15 +5464,15 @@
       </c>
       <c r="P9" s="203" t="inlineStr">
         <is>
-          <t>dash:TextFieldEditor</t>
+          <t>dash:TextAreaEditor</t>
         </is>
       </c>
       <c r="S9" s="121" t="b">
         <v>1</v>
       </c>
-      <c r="T9" s="217" t="n"/>
-      <c r="U9" s="217" t="n"/>
-      <c r="V9" s="217" t="n"/>
+      <c r="T9" s="218" t="n"/>
+      <c r="U9" s="218" t="n"/>
+      <c r="V9" s="218" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="221" t="inlineStr">
@@ -5512,7 +5520,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J10" s="219" t="inlineStr">
+      <c r="J10" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5540,7 +5548,7 @@
       <c r="V10" s="221" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="217" t="inlineStr">
+      <c r="A11" s="218" t="inlineStr">
         <is>
           <t>download URL</t>
         </is>
@@ -5565,27 +5573,27 @@
           <t>If the dataset is openly accessible and available in a repository, you can directly include a link to the downloadable file here.</t>
         </is>
       </c>
-      <c r="F11" s="213" t="inlineStr">
+      <c r="F11" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G11" s="213" t="inlineStr">
+      <c r="G11" s="215" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
       </c>
-      <c r="H11" s="213" t="inlineStr">
+      <c r="H11" s="215" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I11" s="219" t="inlineStr">
+      <c r="I11" s="213" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J11" s="219" t="inlineStr">
+      <c r="J11" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -5595,8 +5603,8 @@
           <t>resource:download_url</t>
         </is>
       </c>
-      <c r="L11" s="219" t="n"/>
-      <c r="M11" s="219" t="n"/>
+      <c r="L11" s="213" t="n"/>
+      <c r="M11" s="213" t="n"/>
       <c r="O11" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -5608,9 +5616,9 @@
         </is>
       </c>
       <c r="S11" s="121" t="n"/>
-      <c r="T11" s="217" t="n"/>
-      <c r="U11" s="217" t="n"/>
-      <c r="V11" s="217" t="n"/>
+      <c r="T11" s="218" t="n"/>
+      <c r="U11" s="218" t="n"/>
+      <c r="V11" s="218" t="n"/>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="221" t="inlineStr">
@@ -5658,7 +5666,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J12" s="219" t="inlineStr">
+      <c r="J12" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5686,7 +5694,7 @@
       <c r="V12" s="221" t="n"/>
     </row>
     <row r="13" ht="99" customHeight="1">
-      <c r="A13" s="217" t="inlineStr">
+      <c r="A13" s="218" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -5696,7 +5704,7 @@
           <t>A language of the resource.</t>
         </is>
       </c>
-      <c r="C13" s="217" t="inlineStr">
+      <c r="C13" s="218" t="inlineStr">
         <is>
           <t>dct:language</t>
         </is>
@@ -5706,33 +5714,33 @@
           <t>http://publications.europa.eu/resource/authority/language</t>
         </is>
       </c>
-      <c r="E13" s="218" t="inlineStr">
+      <c r="E13" s="219" t="inlineStr">
         <is>
           <t>Indicates the natural language used in the Distribution, using a value from the EU controlled vocabulary. Not all distributions might have a language, for example imaging data.
 Note that here the Health-RI model diverges from DCAT-AP NL, which allows a maximum of 1 language per Distribution. The Health-RI model allows multiple languages in the same Distribution.</t>
         </is>
       </c>
-      <c r="F13" s="213" t="inlineStr">
+      <c r="F13" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G13" s="213" t="inlineStr">
+      <c r="G13" s="215" t="inlineStr">
         <is>
           <t>dct:LinguisticSystem (IRI)</t>
         </is>
       </c>
-      <c r="H13" s="213" t="inlineStr">
+      <c r="H13" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I13" s="219" t="inlineStr">
+      <c r="I13" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J13" s="219" t="inlineStr">
+      <c r="J13" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5742,8 +5750,8 @@
           <t>resource:language</t>
         </is>
       </c>
-      <c r="L13" s="219" t="n"/>
-      <c r="M13" s="219" t="n"/>
+      <c r="L13" s="213" t="n"/>
+      <c r="M13" s="213" t="n"/>
       <c r="O13" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -5755,9 +5763,9 @@
         </is>
       </c>
       <c r="S13" s="121" t="n"/>
-      <c r="T13" s="217" t="n"/>
-      <c r="U13" s="217" t="n"/>
-      <c r="V13" s="217" t="n"/>
+      <c r="T13" s="218" t="n"/>
+      <c r="U13" s="218" t="n"/>
+      <c r="V13" s="218" t="n"/>
     </row>
     <row r="14" ht="80" customHeight="1">
       <c r="A14" s="221" t="inlineStr">
@@ -5803,7 +5811,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J14" s="219" t="inlineStr">
+      <c r="J14" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -5831,7 +5839,7 @@
       <c r="V14" s="221" t="n"/>
     </row>
     <row r="15" ht="80" customHeight="1">
-      <c r="A15" s="217" t="inlineStr">
+      <c r="A15" s="218" t="inlineStr">
         <is>
           <t>linked schemas</t>
         </is>
@@ -5841,7 +5849,7 @@
           <t>An established standard to which the described resource conforms.</t>
         </is>
       </c>
-      <c r="C15" s="217" t="inlineStr">
+      <c r="C15" s="218" t="inlineStr">
         <is>
           <t>dct:conformsTo</t>
         </is>
@@ -5856,27 +5864,27 @@
           <t xml:space="preserve">This property SHOULD be used to indicate the model, schema, ontology, view or profile that this representation of a dataset conforms to, in a machine-readable form. This is (generally) a complementary concern to the media-type or format. Use a reference to the official publication of the respective schema. </t>
         </is>
       </c>
-      <c r="F15" s="213" t="inlineStr">
+      <c r="F15" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G15" s="213" t="inlineStr">
+      <c r="G15" s="215" t="inlineStr">
         <is>
           <t>dct:Standard (IRI)</t>
         </is>
       </c>
-      <c r="H15" s="213" t="inlineStr">
+      <c r="H15" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I15" s="219" t="inlineStr">
+      <c r="I15" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J15" s="219" t="inlineStr">
+      <c r="J15" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5886,8 +5894,8 @@
           <t>resource:conforms_to</t>
         </is>
       </c>
-      <c r="L15" s="219" t="n"/>
-      <c r="M15" s="219" t="n"/>
+      <c r="L15" s="213" t="n"/>
+      <c r="M15" s="213" t="n"/>
       <c r="O15" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -5899,9 +5907,9 @@
         </is>
       </c>
       <c r="S15" s="121" t="n"/>
-      <c r="T15" s="217" t="n"/>
-      <c r="U15" s="217" t="n"/>
-      <c r="V15" s="217" t="n"/>
+      <c r="T15" s="218" t="n"/>
+      <c r="U15" s="218" t="n"/>
+      <c r="V15" s="218" t="n"/>
     </row>
     <row r="16" ht="112" customHeight="1">
       <c r="A16" s="221" t="inlineStr">
@@ -5951,7 +5959,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J16" s="219" t="inlineStr">
+      <c r="J16" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5979,7 +5987,7 @@
       <c r="V16" s="221" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="217" t="inlineStr">
+      <c r="A17" s="218" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
@@ -6000,27 +6008,27 @@
         </is>
       </c>
       <c r="E17" s="98" t="n"/>
-      <c r="F17" s="213" t="inlineStr">
+      <c r="F17" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G17" s="213" t="inlineStr">
+      <c r="G17" s="215" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H17" s="213" t="inlineStr">
+      <c r="H17" s="215" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I17" s="219" t="inlineStr">
+      <c r="I17" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J17" s="219" t="inlineStr">
+      <c r="J17" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6030,8 +6038,8 @@
           <t>resource:modified</t>
         </is>
       </c>
-      <c r="L17" s="219" t="n"/>
-      <c r="M17" s="219" t="n"/>
+      <c r="L17" s="213" t="n"/>
+      <c r="M17" s="213" t="n"/>
       <c r="N17" s="214" t="n"/>
       <c r="O17" s="214" t="inlineStr">
         <is>
@@ -6049,9 +6057,9 @@
         </is>
       </c>
       <c r="S17" s="69" t="n"/>
-      <c r="T17" s="217" t="n"/>
-      <c r="U17" s="217" t="n"/>
-      <c r="V17" s="217" t="n"/>
+      <c r="T17" s="218" t="n"/>
+      <c r="U17" s="218" t="n"/>
+      <c r="V17" s="218" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="221" t="inlineStr">
@@ -6099,7 +6107,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J18" s="219" t="inlineStr">
+      <c r="J18" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6127,7 +6135,7 @@
       <c r="V18" s="221" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="217" t="inlineStr">
+      <c r="A19" s="218" t="inlineStr">
         <is>
           <t>release date</t>
         </is>
@@ -6137,7 +6145,7 @@
           <t>Date of formal issuance of the resource.</t>
         </is>
       </c>
-      <c r="C19" s="217" t="inlineStr">
+      <c r="C19" s="218" t="inlineStr">
         <is>
           <t>dct:issued</t>
         </is>
@@ -6152,27 +6160,27 @@
           <t>The date the dataset distribution was issued.</t>
         </is>
       </c>
-      <c r="F19" s="213" t="inlineStr">
+      <c r="F19" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G19" s="213" t="inlineStr">
+      <c r="G19" s="215" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H19" s="213" t="inlineStr">
+      <c r="H19" s="215" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I19" s="219" t="inlineStr">
+      <c r="I19" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J19" s="219" t="inlineStr">
+      <c r="J19" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6182,8 +6190,8 @@
           <t>resource:issued</t>
         </is>
       </c>
-      <c r="L19" s="219" t="n"/>
-      <c r="M19" s="219" t="n"/>
+      <c r="L19" s="213" t="n"/>
+      <c r="M19" s="213" t="n"/>
       <c r="N19" s="214" t="n"/>
       <c r="O19" s="214" t="inlineStr">
         <is>
@@ -6201,9 +6209,9 @@
         </is>
       </c>
       <c r="S19" s="69" t="n"/>
-      <c r="T19" s="217" t="n"/>
-      <c r="U19" s="217" t="n"/>
-      <c r="V19" s="217" t="n"/>
+      <c r="T19" s="218" t="n"/>
+      <c r="U19" s="218" t="n"/>
+      <c r="V19" s="218" t="n"/>
     </row>
     <row r="20" ht="231" customHeight="1">
       <c r="A20" s="221" t="inlineStr">
@@ -6252,7 +6260,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J20" s="219" t="inlineStr">
+      <c r="J20" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -6289,7 +6297,7 @@
       <c r="V20" s="221" t="n"/>
     </row>
     <row r="21" ht="112" customHeight="1">
-      <c r="A21" s="217" t="inlineStr">
+      <c r="A21" s="218" t="inlineStr">
         <is>
           <t>rights</t>
         </is>
@@ -6299,7 +6307,7 @@
           <t>Information about rights held in and over the resource.</t>
         </is>
       </c>
-      <c r="C21" s="217" t="inlineStr">
+      <c r="C21" s="218" t="inlineStr">
         <is>
           <t>dct:rights</t>
         </is>
@@ -6320,7 +6328,7 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G21" s="213" t="inlineStr">
+      <c r="G21" s="215" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
@@ -6330,12 +6338,12 @@
           <t>0..1</t>
         </is>
       </c>
-      <c r="I21" s="219" t="inlineStr">
+      <c r="I21" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J21" s="219" t="inlineStr">
+      <c r="J21" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6345,8 +6353,8 @@
           <t>resource:rights</t>
         </is>
       </c>
-      <c r="L21" s="219" t="n"/>
-      <c r="M21" s="219" t="n"/>
+      <c r="L21" s="213" t="n"/>
+      <c r="M21" s="213" t="n"/>
       <c r="O21" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -6358,9 +6366,9 @@
         </is>
       </c>
       <c r="S21" s="121" t="n"/>
-      <c r="T21" s="217" t="n"/>
-      <c r="U21" s="217" t="n"/>
-      <c r="V21" s="217" t="n"/>
+      <c r="T21" s="218" t="n"/>
+      <c r="U21" s="218" t="n"/>
+      <c r="V21" s="218" t="n"/>
     </row>
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="221" t="inlineStr">
@@ -6409,7 +6417,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="219" t="inlineStr">
+      <c r="J22" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6437,7 +6445,7 @@
       <c r="V22" s="221" t="n"/>
     </row>
     <row r="23" ht="64" customHeight="1">
-      <c r="A23" s="217" t="inlineStr">
+      <c r="A23" s="218" t="inlineStr">
         <is>
           <t>temporal resolution</t>
         </is>
@@ -6447,7 +6455,7 @@
           <t>Minimum time period resolvable in the dataset.</t>
         </is>
       </c>
-      <c r="C23" s="217" t="inlineStr">
+      <c r="C23" s="218" t="inlineStr">
         <is>
           <t>dcat:temporalResolution</t>
         </is>
@@ -6462,34 +6470,34 @@
           <t>If applicable, this property indicates the minimum time period resolvable in the dataset distribution, expressed in xsd:duration format (for more information, see: https://www.w3schools.com/xml/schema_dtypes_date.asp).</t>
         </is>
       </c>
-      <c r="F23" s="213" t="inlineStr">
+      <c r="F23" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G23" s="213" t="inlineStr">
+      <c r="G23" s="215" t="inlineStr">
         <is>
           <t>xsd:duration</t>
         </is>
       </c>
-      <c r="H23" s="213" t="inlineStr">
+      <c r="H23" s="215" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I23" s="219" t="inlineStr">
+      <c r="I23" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J23" s="219" t="inlineStr">
+      <c r="J23" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K23" s="74" t="n"/>
-      <c r="L23" s="219" t="n"/>
-      <c r="M23" s="219" t="n"/>
+      <c r="L23" s="213" t="n"/>
+      <c r="M23" s="213" t="n"/>
       <c r="O23" s="203" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -6501,9 +6509,9 @@
         </is>
       </c>
       <c r="S23" s="121" t="n"/>
-      <c r="T23" s="217" t="n"/>
-      <c r="U23" s="217" t="n"/>
-      <c r="V23" s="217" t="n"/>
+      <c r="T23" s="218" t="n"/>
+      <c r="U23" s="218" t="n"/>
+      <c r="V23" s="218" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="221" t="inlineStr">
@@ -6551,7 +6559,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J24" s="219" t="inlineStr">
+      <c r="J24" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7111,11 +7119,11 @@
   <dimension ref="A1:U55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col width="22.5" customWidth="1" style="216" min="1" max="1"/>
-    <col width="43.5" bestFit="1" customWidth="1" style="216" min="2" max="2"/>
-    <col width="26.5" customWidth="1" style="216" min="3" max="3"/>
+    <col width="22.5" customWidth="1" style="217" min="1" max="1"/>
+    <col width="43.5" bestFit="1" customWidth="1" style="217" min="2" max="2"/>
+    <col width="26.5" customWidth="1" style="217" min="3" max="3"/>
     <col width="24" customWidth="1" style="223" min="4" max="4"/>
-    <col width="76.5" customWidth="1" style="216" min="5" max="5"/>
+    <col width="76.5" customWidth="1" style="217" min="5" max="5"/>
     <col width="16.5" bestFit="1" customWidth="1" style="214" min="6" max="6"/>
     <col width="20.1640625" bestFit="1" customWidth="1" style="214" min="7" max="7"/>
     <col width="11.83203125" customWidth="1" style="214" min="8" max="8"/>
@@ -7262,7 +7270,7 @@
           <t>The legislation that mandates the creation or management of the Dataset Series.</t>
         </is>
       </c>
-      <c r="F2" s="213" t="inlineStr">
+      <c r="F2" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -7282,7 +7290,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="219" t="inlineStr">
+      <c r="J2" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7308,7 +7316,7 @@
       <c r="U2" s="155" t="n"/>
     </row>
     <row r="3" ht="64" customHeight="1">
-      <c r="A3" s="217" t="inlineStr">
+      <c r="A3" s="218" t="inlineStr">
         <is>
           <t>contact point</t>
         </is>
@@ -7318,7 +7326,7 @@
           <t>Relevant contact information for the catalogued resource.</t>
         </is>
       </c>
-      <c r="C3" s="217" t="inlineStr">
+      <c r="C3" s="218" t="inlineStr">
         <is>
           <t>dcat:contactPoint</t>
         </is>
@@ -7334,7 +7342,7 @@
 Whenever possible, use general contact information (for example, from a department) instead of the contact information of an individual.</t>
         </is>
       </c>
-      <c r="F3" s="213" t="inlineStr">
+      <c r="F3" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -7344,17 +7352,17 @@
           <t>vcard:Kind</t>
         </is>
       </c>
-      <c r="H3" s="213" t="inlineStr">
+      <c r="H3" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I3" s="219" t="inlineStr">
+      <c r="I3" s="213" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J3" s="219" t="inlineStr">
+      <c r="J3" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7364,7 +7372,7 @@
           <t>data_series::contact</t>
         </is>
       </c>
-      <c r="L3" s="219" t="inlineStr">
+      <c r="L3" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
@@ -7384,9 +7392,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S3" s="217" t="n"/>
-      <c r="T3" s="217" t="n"/>
-      <c r="U3" s="217" t="n"/>
+      <c r="S3" s="218" t="n"/>
+      <c r="T3" s="218" t="n"/>
+      <c r="U3" s="218" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="221" t="inlineStr">
@@ -7434,7 +7442,7 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J4" s="219" t="inlineStr">
+      <c r="J4" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7452,7 +7460,7 @@
       </c>
       <c r="O4" s="214" t="inlineStr">
         <is>
-          <t>dash:TextFieldEditor</t>
+          <t>dash:TextAreaEditor</t>
         </is>
       </c>
       <c r="R4" s="214" t="b">
@@ -7463,7 +7471,7 @@
       <c r="U4" s="221" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="217" t="inlineStr">
+      <c r="A5" s="218" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
@@ -7473,7 +7481,7 @@
           <t>The frequency with which items are added to a collection.</t>
         </is>
       </c>
-      <c r="C5" s="217" t="inlineStr">
+      <c r="C5" s="218" t="inlineStr">
         <is>
           <t>dct:accrualPeriodicity</t>
         </is>
@@ -7488,33 +7496,33 @@
           <t>The frequency of a dataset series is not equal to the frequency of the dataset in the collection.</t>
         </is>
       </c>
-      <c r="F5" s="213" t="inlineStr">
+      <c r="F5" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G5" s="213" t="inlineStr">
+      <c r="G5" s="215" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H5" s="213" t="inlineStr">
+      <c r="H5" s="215" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I5" s="219" t="inlineStr">
+      <c r="I5" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="219" t="inlineStr">
+      <c r="J5" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K5" s="74" t="n"/>
-      <c r="L5" s="219" t="n"/>
+      <c r="L5" s="213" t="n"/>
       <c r="N5" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -7525,9 +7533,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S5" s="217" t="n"/>
-      <c r="T5" s="217" t="n"/>
-      <c r="U5" s="217" t="n"/>
+      <c r="S5" s="218" t="n"/>
+      <c r="T5" s="218" t="n"/>
+      <c r="U5" s="218" t="n"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="221" t="inlineStr">
@@ -7575,7 +7583,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="219" t="inlineStr">
+      <c r="J6" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -7629,7 +7637,7 @@
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="217" t="inlineStr">
+      <c r="A11" s="218" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
@@ -7639,7 +7647,7 @@
           <t>Date on which the resource was changed.</t>
         </is>
       </c>
-      <c r="C11" s="217" t="inlineStr">
+      <c r="C11" s="218" t="inlineStr">
         <is>
           <t>dct:modified</t>
         </is>
@@ -7654,27 +7662,27 @@
           <t>This is not equal to the most recently modified dataset in the collection of the dataset series.</t>
         </is>
       </c>
-      <c r="F11" s="213" t="inlineStr">
+      <c r="F11" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G11" s="213" t="inlineStr">
+      <c r="G11" s="215" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H11" s="213" t="inlineStr">
+      <c r="H11" s="215" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I11" s="219" t="inlineStr">
+      <c r="I11" s="213" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J11" s="219" t="inlineStr">
+      <c r="J11" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7684,7 +7692,7 @@
           <t>data_series::modified</t>
         </is>
       </c>
-      <c r="L11" s="219" t="n"/>
+      <c r="L11" s="213" t="n"/>
       <c r="N11" s="214" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -7700,9 +7708,9 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="S11" s="217" t="n"/>
-      <c r="T11" s="217" t="n"/>
-      <c r="U11" s="217" t="n"/>
+      <c r="S11" s="218" t="n"/>
+      <c r="T11" s="218" t="n"/>
+      <c r="U11" s="218" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="221" t="inlineStr">
@@ -7730,7 +7738,7 @@
           <t xml:space="preserve">The publisher of the dataset series may not be the publisher of all datasets. For example, a digital archive could take over the publishing of older datasets in the series. </t>
         </is>
       </c>
-      <c r="F12" s="213" t="inlineStr">
+      <c r="F12" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -7750,7 +7758,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J12" s="219" t="inlineStr">
+      <c r="J12" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7785,7 +7793,7 @@
       <c r="U12" s="221" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="217" t="inlineStr">
+      <c r="A13" s="218" t="inlineStr">
         <is>
           <t>release date</t>
         </is>
@@ -7795,7 +7803,7 @@
           <t>Date of formal issuance of the resource.</t>
         </is>
       </c>
-      <c r="C13" s="217" t="inlineStr">
+      <c r="C13" s="218" t="inlineStr">
         <is>
           <t>dct:issued</t>
         </is>
@@ -7815,22 +7823,22 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G13" s="213" t="inlineStr">
+      <c r="G13" s="215" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H13" s="213" t="inlineStr">
+      <c r="H13" s="215" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I13" s="213" t="inlineStr">
+      <c r="I13" s="215" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J13" s="219" t="inlineStr">
+      <c r="J13" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7840,7 +7848,7 @@
           <t>data_series:issued</t>
         </is>
       </c>
-      <c r="L13" s="219" t="n"/>
+      <c r="L13" s="213" t="n"/>
       <c r="N13" s="214" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -7856,9 +7864,9 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="S13" s="217" t="n"/>
-      <c r="T13" s="217" t="n"/>
-      <c r="U13" s="217" t="n"/>
+      <c r="S13" s="218" t="n"/>
+      <c r="T13" s="218" t="n"/>
+      <c r="U13" s="218" t="n"/>
     </row>
     <row r="14" ht="49" customHeight="1">
       <c r="A14" s="221" t="inlineStr">
@@ -7886,7 +7894,7 @@
           <t>When temporal coverage is a dimension in the dataset series, the temporal coverage of each dataset in the collection should be part of the series' temporal coverage. In that case, an open-ended value is recommended, e.g. after 2012.</t>
         </is>
       </c>
-      <c r="F14" s="213" t="inlineStr">
+      <c r="F14" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -7906,7 +7914,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="219" t="inlineStr">
+      <c r="J14" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7941,17 +7949,17 @@
       <c r="U14" s="221" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="217" t="inlineStr">
+      <c r="A15" s="218" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B15" s="217" t="inlineStr">
+      <c r="B15" s="218" t="inlineStr">
         <is>
           <t>A name given to the resource.</t>
         </is>
       </c>
-      <c r="C15" s="217" t="inlineStr">
+      <c r="C15" s="218" t="inlineStr">
         <is>
           <t>dct:title</t>
         </is>
@@ -7961,7 +7969,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E15" s="217" t="inlineStr">
+      <c r="E15" s="218" t="inlineStr">
         <is>
           <t xml:space="preserve">Provide a unique title for your Dataset Series, which can be repeated in multiple languages. </t>
         </is>
@@ -7971,22 +7979,22 @@
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G15" s="213" t="inlineStr">
+      <c r="G15" s="215" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H15" s="213" t="inlineStr">
+      <c r="H15" s="215" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I15" s="213" t="inlineStr">
+      <c r="I15" s="215" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J15" s="219" t="inlineStr">
+      <c r="J15" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7996,7 +8004,7 @@
           <t>title</t>
         </is>
       </c>
-      <c r="L15" s="219" t="n"/>
+      <c r="L15" s="213" t="n"/>
       <c r="N15" s="214" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -8010,9 +8018,9 @@
       <c r="R15" s="214" t="b">
         <v>1</v>
       </c>
-      <c r="S15" s="217" t="n"/>
-      <c r="T15" s="217" t="n"/>
-      <c r="U15" s="217" t="n"/>
+      <c r="S15" s="218" t="n"/>
+      <c r="T15" s="218" t="n"/>
+      <c r="U15" s="218" t="n"/>
     </row>
     <row r="16">
       <c r="K16" s="214" t="n"/>
@@ -8137,16 +8145,16 @@
   </sheetData>
   <autoFilter ref="A1:L15"/>
   <mergeCells count="11">
+    <mergeCell ref="K6:K10"/>
+    <mergeCell ref="H6:H10"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="E6:E10"/>
+    <mergeCell ref="C6:C10"/>
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="G6:G10"/>
+    <mergeCell ref="L6:L10"/>
     <mergeCell ref="J6:J10"/>
-    <mergeCell ref="G6:G10"/>
-    <mergeCell ref="I6:I10"/>
-    <mergeCell ref="B6:B10"/>
     <mergeCell ref="F6:F10"/>
-    <mergeCell ref="C6:C10"/>
-    <mergeCell ref="H6:H10"/>
-    <mergeCell ref="E6:E10"/>
-    <mergeCell ref="L6:L10"/>
-    <mergeCell ref="K6:K10"/>
     <mergeCell ref="A6:A10"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F6 F11:F15">
@@ -8391,7 +8399,7 @@
           <t>Information about who can access the resource or an indication of its security status.</t>
         </is>
       </c>
-      <c r="C2" s="217" t="inlineStr">
+      <c r="C2" s="218" t="inlineStr">
         <is>
           <t>dct:accessRights</t>
         </is>
@@ -8406,30 +8414,30 @@
           <t>Information that indicates whether the Dataset is publicly accessible, has access restrictions or is not public. This property must take one of the predefined values listed in the Access Rights Named Authority List provided by the Publications Office. This designation informs data users whether the dataset is considered open data or is classified as non-public. For example, for non-public data, use the value: http://publications.europa.eu/resource/authority/access-right/NON_PUBLIC</t>
         </is>
       </c>
-      <c r="F2" s="213" t="inlineStr">
+      <c r="F2" s="215" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G2" s="213" t="inlineStr">
+      <c r="G2" s="215" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
       </c>
-      <c r="H2" s="213" t="n">
+      <c r="H2" s="215" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="219" t="inlineStr">
+      <c r="I2" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="219" t="inlineStr">
+      <c r="J2" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K2" s="219" t="inlineStr">
+      <c r="K2" s="213" t="inlineStr">
         <is>
           <t>access_service:access_rights</t>
         </is>
@@ -8491,7 +8499,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J3" s="219" t="inlineStr">
+      <c r="J3" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -8513,7 +8521,7 @@
       <c r="U3" s="221" t="n"/>
     </row>
     <row r="4" ht="92.25" customHeight="1">
-      <c r="A4" s="217" t="inlineStr">
+      <c r="A4" s="218" t="inlineStr">
         <is>
           <t>application profile</t>
         </is>
@@ -8523,7 +8531,7 @@
           <t>An established standard to which the described resource conforms.</t>
         </is>
       </c>
-      <c r="C4" s="217" t="inlineStr">
+      <c r="C4" s="218" t="inlineStr">
         <is>
           <t>dct:conformsTo</t>
         </is>
@@ -8538,33 +8546,33 @@
           <t>The standards referred to here SHOULD describe the Data Service and not the data it serves. The latter is provided by the dataset with which this Data Service is connected. For instance, the data service adheres to the OGC WFS API standard, while the associated dataset adheres to the INSPIRE Address data model.</t>
         </is>
       </c>
-      <c r="F4" s="213" t="inlineStr">
+      <c r="F4" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G4" s="213" t="inlineStr">
+      <c r="G4" s="215" t="inlineStr">
         <is>
           <t>dct:Standard (IRI)</t>
         </is>
       </c>
-      <c r="H4" s="213" t="inlineStr">
+      <c r="H4" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I4" s="219" t="inlineStr">
+      <c r="I4" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="219" t="inlineStr">
+      <c r="J4" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K4" s="219" t="n"/>
-      <c r="L4" s="219" t="n"/>
+      <c r="K4" s="213" t="n"/>
+      <c r="L4" s="213" t="n"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -8575,9 +8583,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S4" s="217" t="n"/>
-      <c r="T4" s="217" t="n"/>
-      <c r="U4" s="217" t="n"/>
+      <c r="S4" s="218" t="n"/>
+      <c r="T4" s="218" t="n"/>
+      <c r="U4" s="218" t="n"/>
     </row>
     <row r="5" ht="64" customHeight="1">
       <c r="A5" s="155" t="inlineStr">
@@ -8624,7 +8632,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="219" t="inlineStr">
+      <c r="J5" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -8655,7 +8663,7 @@
       <c r="U5" s="155" t="n"/>
     </row>
     <row r="6" ht="160" customHeight="1">
-      <c r="A6" s="217" t="inlineStr">
+      <c r="A6" s="218" t="inlineStr">
         <is>
           <t>creator</t>
         </is>
@@ -8665,7 +8673,7 @@
           <t>An entity responsible for making the resource.</t>
         </is>
       </c>
-      <c r="C6" s="217" t="inlineStr">
+      <c r="C6" s="218" t="inlineStr">
         <is>
           <t>dct:creator</t>
         </is>
@@ -8682,7 +8690,7 @@
 Note that the Health-RI model diverges from DCAT-AP NL here, which reduces the maximum number of creators to 1. The Health-RI model allows the specification of multiple creators of a catalogue.</t>
         </is>
       </c>
-      <c r="F6" s="213" t="inlineStr">
+      <c r="F6" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -8692,23 +8700,23 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H6" s="213" t="inlineStr">
+      <c r="H6" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I6" s="219" t="inlineStr">
+      <c r="I6" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="219" t="inlineStr">
+      <c r="J6" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K6" s="75" t="n"/>
-      <c r="L6" s="219" t="inlineStr">
+      <c r="L6" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -8728,9 +8736,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S6" s="217" t="n"/>
-      <c r="T6" s="217" t="n"/>
-      <c r="U6" s="217" t="n"/>
+      <c r="S6" s="218" t="n"/>
+      <c r="T6" s="218" t="n"/>
+      <c r="U6" s="218" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="221" t="inlineStr">
@@ -8774,12 +8782,12 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J7" s="219" t="inlineStr">
+      <c r="J7" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K7" s="219" t="n"/>
+      <c r="K7" s="213" t="n"/>
       <c r="L7" s="220" t="n"/>
       <c r="N7" t="inlineStr">
         <is>
@@ -8806,7 +8814,7 @@
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C8" s="217" t="inlineStr">
+      <c r="C8" s="218" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -8821,43 +8829,43 @@
           <t>Briefly describe the data service provided. You can repeat this description in multiple languages. Example: A data service that provides API access to real-time electrocardiogram (ECG) monitoring data for clinical research applications.</t>
         </is>
       </c>
-      <c r="F8" s="213" t="inlineStr">
+      <c r="F8" s="215" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G8" s="213" t="inlineStr">
+      <c r="G8" s="215" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H8" s="213" t="inlineStr">
+      <c r="H8" s="215" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I8" s="219" t="inlineStr">
+      <c r="I8" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="219" t="inlineStr">
+      <c r="J8" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K8" s="219" t="inlineStr">
+      <c r="K8" s="213" t="inlineStr">
         <is>
           <t>access_service:description</t>
         </is>
       </c>
-      <c r="L8" s="219" t="n"/>
-      <c r="N8" s="219" t="inlineStr">
+      <c r="L8" s="213" t="n"/>
+      <c r="N8" s="213" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O8" s="219" t="inlineStr">
+      <c r="O8" s="213" t="inlineStr">
         <is>
           <t>dash:TextAreaEditor</t>
         </is>
@@ -8913,7 +8921,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J9" s="219" t="inlineStr">
+      <c r="J9" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -8939,7 +8947,7 @@
       <c r="U9" s="221" t="n"/>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="217" t="inlineStr">
+      <c r="A10" s="218" t="inlineStr">
         <is>
           <t>endpoint URL</t>
         </is>
@@ -8949,7 +8957,7 @@
           <t>The root location or primary endpoint of the service (a Web-resolvable IRI).</t>
         </is>
       </c>
-      <c r="C10" s="217" t="inlineStr">
+      <c r="C10" s="218" t="inlineStr">
         <is>
           <t>dcat:endpointURL</t>
         </is>
@@ -8964,12 +8972,12 @@
           <t>Provide the URL of the endpoint that users can interact with to access the data service. This should be a direct link to the service's endpoint, such as an API URL, SPARQL endpoint, or similar.</t>
         </is>
       </c>
-      <c r="F10" s="213" t="inlineStr">
+      <c r="F10" s="215" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G10" s="213" t="inlineStr">
+      <c r="G10" s="215" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
@@ -8977,12 +8985,12 @@
       <c r="H10" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="219" t="inlineStr">
+      <c r="I10" s="213" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J10" s="219" t="inlineStr">
+      <c r="J10" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -8992,7 +9000,7 @@
           <t>access_service:endpoint_url</t>
         </is>
       </c>
-      <c r="L10" s="219" t="n"/>
+      <c r="L10" s="213" t="n"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -9003,9 +9011,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S10" s="217" t="n"/>
-      <c r="T10" s="217" t="n"/>
-      <c r="U10" s="217" t="n"/>
+      <c r="S10" s="218" t="n"/>
+      <c r="T10" s="218" t="n"/>
+      <c r="U10" s="218" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="221" t="inlineStr">
@@ -9049,12 +9057,12 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J11" s="219" t="inlineStr">
+      <c r="J11" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K11" s="219" t="n"/>
+      <c r="K11" s="213" t="n"/>
       <c r="L11" s="220" t="n"/>
       <c r="N11" t="inlineStr">
         <is>
@@ -9071,7 +9079,7 @@
       <c r="U11" s="221" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="217" t="inlineStr">
+      <c r="A12" s="218" t="inlineStr">
         <is>
           <t>HVD Category</t>
         </is>
@@ -9081,7 +9089,7 @@
           <t>A data category defined in the High Value Dataset Implementing Regulation.</t>
         </is>
       </c>
-      <c r="C12" s="217" t="inlineStr">
+      <c r="C12" s="218" t="inlineStr">
         <is>
           <t>dcatap:hvdCategory</t>
         </is>
@@ -9092,33 +9100,33 @@
         </is>
       </c>
       <c r="E12" s="98" t="n"/>
-      <c r="F12" s="213" t="inlineStr">
+      <c r="F12" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G12" s="213" t="inlineStr">
+      <c r="G12" s="215" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H12" s="213" t="inlineStr">
+      <c r="H12" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I12" s="219" t="inlineStr">
+      <c r="I12" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J12" s="219" t="inlineStr">
+      <c r="J12" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K12" s="75" t="n"/>
-      <c r="L12" s="219" t="n"/>
+      <c r="L12" s="213" t="n"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -9129,9 +9137,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S12" s="217" t="n"/>
-      <c r="T12" s="217" t="n"/>
-      <c r="U12" s="217" t="n"/>
+      <c r="S12" s="218" t="n"/>
+      <c r="T12" s="218" t="n"/>
+      <c r="U12" s="218" t="n"/>
     </row>
     <row r="13" ht="64" customHeight="1">
       <c r="A13" s="155" t="inlineStr">
@@ -9177,19 +9185,19 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J13" s="219" t="inlineStr">
+      <c r="J13" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K13" s="75" t="n"/>
       <c r="L13" s="220" t="n"/>
-      <c r="N13" s="219" t="inlineStr">
+      <c r="N13" s="213" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O13" s="219" t="inlineStr">
+      <c r="O13" s="213" t="inlineStr">
         <is>
           <t>dash:TextFieldEditor</t>
         </is>
@@ -9199,7 +9207,7 @@
       <c r="U13" s="155" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="217" t="inlineStr">
+      <c r="A14" s="218" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -9209,7 +9217,7 @@
           <t>A keyword or tag describing the resource.</t>
         </is>
       </c>
-      <c r="C14" s="217" t="inlineStr">
+      <c r="C14" s="218" t="inlineStr">
         <is>
           <t>dcat:keyword</t>
         </is>
@@ -9220,46 +9228,46 @@
         </is>
       </c>
       <c r="E14" s="29" t="n"/>
-      <c r="F14" s="213" t="inlineStr">
+      <c r="F14" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G14" s="213" t="inlineStr">
+      <c r="G14" s="215" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H14" s="213" t="inlineStr">
+      <c r="H14" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I14" s="219" t="inlineStr">
+      <c r="I14" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="219" t="inlineStr">
+      <c r="J14" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K14" s="75" t="n"/>
-      <c r="L14" s="219" t="n"/>
-      <c r="N14" s="219" t="inlineStr">
+      <c r="L14" s="213" t="n"/>
+      <c r="N14" s="213" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O14" s="219" t="inlineStr">
+      <c r="O14" s="213" t="inlineStr">
         <is>
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="S14" s="217" t="n"/>
-      <c r="T14" s="217" t="n"/>
-      <c r="U14" s="217" t="n"/>
+      <c r="S14" s="218" t="n"/>
+      <c r="T14" s="218" t="n"/>
+      <c r="U14" s="218" t="n"/>
     </row>
     <row r="15" ht="64" customHeight="1">
       <c r="A15" s="221" t="inlineStr">
@@ -9307,7 +9315,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J15" s="219" t="inlineStr">
+      <c r="J15" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9329,7 +9337,7 @@
       <c r="U15" s="221" t="n"/>
     </row>
     <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="217" t="inlineStr">
+      <c r="A16" s="218" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -9339,7 +9347,7 @@
           <t>A language of the resource.</t>
         </is>
       </c>
-      <c r="C16" s="217" t="inlineStr">
+      <c r="C16" s="218" t="inlineStr">
         <is>
           <t>dct:language</t>
         </is>
@@ -9354,33 +9362,33 @@
           <t>Indicates the natural language used in the data service, indicated with a value from the EU controlled vocabulary.</t>
         </is>
       </c>
-      <c r="F16" s="213" t="inlineStr">
+      <c r="F16" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G16" s="213" t="inlineStr">
+      <c r="G16" s="215" t="inlineStr">
         <is>
           <t>dct:LinguisticSystem (IRI)</t>
         </is>
       </c>
-      <c r="H16" s="213" t="inlineStr">
+      <c r="H16" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I16" s="219" t="inlineStr">
+      <c r="I16" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J16" s="219" t="inlineStr">
+      <c r="J16" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K16" s="75" t="n"/>
-      <c r="L16" s="219" t="n"/>
+      <c r="L16" s="213" t="n"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -9391,9 +9399,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S16" s="217" t="n"/>
-      <c r="T16" s="217" t="n"/>
-      <c r="U16" s="217" t="n"/>
+      <c r="S16" s="218" t="n"/>
+      <c r="T16" s="218" t="n"/>
+      <c r="U16" s="218" t="n"/>
     </row>
     <row r="17" ht="64" customHeight="1">
       <c r="A17" s="221" t="inlineStr">
@@ -9439,12 +9447,12 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J17" s="219" t="inlineStr">
+      <c r="J17" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K17" s="219" t="inlineStr">
+      <c r="K17" s="213" t="inlineStr">
         <is>
           <t>access_service:license</t>
         </is>
@@ -9465,7 +9473,7 @@
       <c r="U17" s="221" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="217" t="inlineStr">
+      <c r="A18" s="218" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
@@ -9475,7 +9483,7 @@
           <t>Date on which the resource was changed.</t>
         </is>
       </c>
-      <c r="C18" s="217" t="inlineStr">
+      <c r="C18" s="218" t="inlineStr">
         <is>
           <t>dct:modified</t>
         </is>
@@ -9490,33 +9498,33 @@
           <t>This property indicates the date of the last changes to the dataset, not the metadata record. An absent value may mean the resource hasn't changed since publication, the modification date is unknown, or the resource is continuously updated.</t>
         </is>
       </c>
-      <c r="F18" s="213" t="inlineStr">
+      <c r="F18" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G18" s="213" t="inlineStr">
+      <c r="G18" s="215" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H18" s="213" t="inlineStr">
+      <c r="H18" s="215" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I18" s="219" t="inlineStr">
+      <c r="I18" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J18" s="219" t="inlineStr">
+      <c r="J18" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K18" s="75" t="n"/>
-      <c r="L18" s="219" t="n"/>
+      <c r="L18" s="213" t="n"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -9532,9 +9540,9 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="S18" s="217" t="n"/>
-      <c r="T18" s="217" t="n"/>
-      <c r="U18" s="217" t="n"/>
+      <c r="S18" s="218" t="n"/>
+      <c r="T18" s="218" t="n"/>
+      <c r="U18" s="218" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="221" t="inlineStr">
@@ -9578,7 +9586,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J19" s="219" t="inlineStr">
+      <c r="J19" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -9609,7 +9617,7 @@
       <c r="U19" s="221" t="n"/>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="217" t="inlineStr">
+      <c r="A20" s="218" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
@@ -9619,7 +9627,7 @@
           <t>An entity responsible for making the resource available.</t>
         </is>
       </c>
-      <c r="C20" s="217" t="inlineStr">
+      <c r="C20" s="218" t="inlineStr">
         <is>
           <t>dct:publisher</t>
         </is>
@@ -9634,7 +9642,7 @@
           <t>The organisation or individual responsible for making the data service available. In the context of data services, the publisher is typically the organisation that manages or provides access to the service. For details, see the class Agent.</t>
         </is>
       </c>
-      <c r="F20" s="213" t="inlineStr">
+      <c r="F20" s="215" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -9644,21 +9652,21 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H20" s="213" t="n">
+      <c r="H20" s="215" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="219" t="inlineStr">
+      <c r="I20" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J20" s="219" t="inlineStr">
+      <c r="J20" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K20" s="219" t="n"/>
-      <c r="L20" s="219" t="inlineStr">
+      <c r="K20" s="213" t="n"/>
+      <c r="L20" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -9678,9 +9686,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S20" s="217" t="n"/>
-      <c r="T20" s="217" t="n"/>
-      <c r="U20" s="217" t="n"/>
+      <c r="S20" s="218" t="n"/>
+      <c r="T20" s="218" t="n"/>
+      <c r="U20" s="218" t="n"/>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="221" t="inlineStr">
@@ -9728,12 +9736,12 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J21" s="219" t="inlineStr">
+      <c r="J21" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K21" s="219" t="inlineStr">
+      <c r="K21" s="213" t="inlineStr">
         <is>
           <t>access_service:serves_dataset</t>
         </is>
@@ -9758,7 +9766,7 @@
       <c r="U21" s="221" t="n"/>
     </row>
     <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="217" t="inlineStr">
+      <c r="A22" s="218" t="inlineStr">
         <is>
           <t>theme</t>
         </is>
@@ -9768,7 +9776,7 @@
           <t>A main category of the resource. A resource can have multiple themes.</t>
         </is>
       </c>
-      <c r="C22" s="217" t="inlineStr">
+      <c r="C22" s="218" t="inlineStr">
         <is>
           <t>dcat:theme</t>
         </is>
@@ -9783,33 +9791,33 @@
           <t>This property should use a controlled vocabulary. In the Health Data Catalogue, most data services will use NAL:data-theme 'HEAL', but additional values from the same vocabulary are allowed.</t>
         </is>
       </c>
-      <c r="F22" s="213" t="inlineStr">
+      <c r="F22" s="215" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G22" s="213" t="inlineStr">
+      <c r="G22" s="215" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H22" s="213" t="inlineStr">
+      <c r="H22" s="215" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I22" s="219" t="inlineStr">
+      <c r="I22" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="219" t="inlineStr">
+      <c r="J22" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K22" s="75" t="n"/>
-      <c r="L22" s="219" t="n"/>
+      <c r="L22" s="213" t="n"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -9820,9 +9828,14 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S22" s="217" t="n"/>
-      <c r="T22" s="217" t="n"/>
-      <c r="U22" s="217" t="n"/>
+      <c r="Q22" s="200" t="inlineStr">
+        <is>
+          <t>http://publications.europa.eu/resource/authority/data-theme/HEAL</t>
+        </is>
+      </c>
+      <c r="S22" s="218" t="n"/>
+      <c r="T22" s="218" t="n"/>
+      <c r="U22" s="218" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="221" t="inlineStr">
@@ -9870,7 +9883,7 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J23" s="219" t="inlineStr">
+      <c r="J23" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9881,12 +9894,12 @@
         </is>
       </c>
       <c r="L23" s="159" t="n"/>
-      <c r="N23" s="219" t="inlineStr">
+      <c r="N23" s="213" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O23" s="219" t="inlineStr">
+      <c r="O23" s="213" t="inlineStr">
         <is>
           <t>dash:TextFieldEditor</t>
         </is>
@@ -10472,6 +10485,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" tooltip="http://publications.europa.eu/resource/authority/data-theme/heal" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12065,6 +12079,9 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
+      <c r="T2" s="229" t="b">
+        <v>1</v>
+      </c>
       <c r="U2" s="31" t="n"/>
       <c r="V2" s="31" t="n"/>
       <c r="W2" s="31" t="n"/>
@@ -13657,12 +13674,12 @@
       <c r="I2" s="34" t="n"/>
       <c r="J2" s="34" t="n"/>
       <c r="K2" s="229" t="n"/>
-      <c r="Q2" s="229" t="inlineStr">
+      <c r="Q2" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
         </is>
       </c>
-      <c r="R2" s="229" t="inlineStr">
+      <c r="R2" s="214" t="inlineStr">
         <is>
           <t>dash:URIEditor</t>
         </is>
@@ -13719,12 +13736,12 @@
       <c r="L3" s="80" t="n"/>
       <c r="M3" s="80" t="n"/>
       <c r="N3" s="80" t="n"/>
-      <c r="Q3" s="229" t="inlineStr">
+      <c r="Q3" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
         </is>
       </c>
-      <c r="R3" s="229" t="inlineStr">
+      <c r="R3" s="214" t="inlineStr">
         <is>
           <t>dash:URIEditor</t>
         </is>
@@ -14078,7 +14095,7 @@
       </c>
       <c r="Q3" s="229" t="inlineStr">
         <is>
-          <t>dash:TextAreaEditor</t>
+          <t>dash:TextFieldEditor</t>
         </is>
       </c>
       <c r="U3" s="36" t="n"/>
@@ -16048,6 +16065,9 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
+      <c r="T3" s="229" t="b">
+        <v>1</v>
+      </c>
       <c r="U3" s="36" t="n"/>
       <c r="V3" s="36" t="n"/>
       <c r="W3" s="36" t="n"/>
@@ -17081,7 +17101,7 @@
       </c>
       <c r="H2" s="168" t="inlineStr">
         <is>
-          <t>1..n</t>
+          <t>1..1</t>
         </is>
       </c>
       <c r="I2" s="229" t="inlineStr">
@@ -17169,6 +17189,9 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
+      <c r="T3" s="229" t="b">
+        <v>1</v>
+      </c>
       <c r="U3" s="36" t="n"/>
       <c r="V3" s="36" t="n"/>
       <c r="W3" s="36" t="n"/>
@@ -17231,8 +17254,11 @@
       </c>
       <c r="Q4" s="214" t="inlineStr">
         <is>
-          <t>dash:TextFieldEditor</t>
-        </is>
+          <t>dash:TextAreaEditor</t>
+        </is>
+      </c>
+      <c r="T4" s="229" t="b">
+        <v>1</v>
       </c>
       <c r="U4" s="13" t="n"/>
       <c r="V4" s="13" t="n"/>
@@ -18336,6 +18362,11 @@
           <t>edam</t>
         </is>
       </c>
+      <c r="B22" s="200" t="inlineStr">
+        <is>
+          <t>http://edamontology.org/</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -18343,6 +18374,11 @@
           <t>oa</t>
         </is>
       </c>
+      <c r="B23" s="200" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/ns/oa#</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -18350,11 +18386,21 @@
           <t>prov</t>
         </is>
       </c>
+      <c r="B24" s="200" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/ns/prov#</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
           <t>schema</t>
+        </is>
+      </c>
+      <c r="B25" s="200" t="inlineStr">
+        <is>
+          <t>http://schema.org/</t>
         </is>
       </c>
     </row>
@@ -18378,6 +18424,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" tooltip="http://edamontology.org/" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" tooltip="http://www.w3.org/ns/oa#" display="http://www.w3.org/ns/oa" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" tooltip="http://www.w3.org/ns/prov#" display="http://www.w3.org/ns/prov" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" tooltip="http://schema.org/" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18972,11 +19022,11 @@
   <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col width="20" bestFit="1" customWidth="1" style="216" min="1" max="1"/>
-    <col width="40.5" customWidth="1" style="216" min="2" max="2"/>
-    <col width="25.5" bestFit="1" customWidth="1" style="216" min="3" max="3"/>
+    <col width="20" bestFit="1" customWidth="1" style="217" min="1" max="1"/>
+    <col width="40.5" customWidth="1" style="217" min="2" max="2"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="217" min="3" max="3"/>
     <col width="25.5" customWidth="1" style="223" min="4" max="4"/>
-    <col width="54.5" customWidth="1" style="216" min="5" max="5"/>
+    <col width="54.5" customWidth="1" style="217" min="5" max="5"/>
     <col width="22.1640625" customWidth="1" style="214" min="6" max="6"/>
     <col width="24" bestFit="1" customWidth="1" style="214" min="7" max="7"/>
     <col width="10.5" bestFit="1" customWidth="1" style="214" min="8" max="8"/>
@@ -19125,12 +19175,12 @@
         </is>
       </c>
       <c r="E2" s="98" t="n"/>
-      <c r="F2" s="213" t="inlineStr">
+      <c r="F2" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G2" s="213" t="inlineStr">
+      <c r="G2" s="215" t="inlineStr">
         <is>
           <t>eli:LegalResource (IRI)</t>
         </is>
@@ -19140,12 +19190,12 @@
           <t>0..n</t>
         </is>
       </c>
-      <c r="I2" s="219" t="inlineStr">
+      <c r="I2" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="219" t="inlineStr">
+      <c r="J2" s="213" t="inlineStr">
         <is>
           <t>Health and NL</t>
         </is>
@@ -19155,8 +19205,8 @@
           <t>custom:applicable_legislation</t>
         </is>
       </c>
-      <c r="L2" s="219" t="n"/>
-      <c r="M2" s="219" t="n"/>
+      <c r="L2" s="213" t="n"/>
+      <c r="M2" s="213" t="n"/>
       <c r="O2" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -19218,7 +19268,7 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J3" s="219" t="inlineStr">
+      <c r="J3" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -19256,7 +19306,7 @@
           <t>Relevant contact information for the catalogued resource.</t>
         </is>
       </c>
-      <c r="C4" s="217" t="inlineStr">
+      <c r="C4" s="218" t="inlineStr">
         <is>
           <t>dcat:contactPoint</t>
         </is>
@@ -19272,7 +19322,7 @@
 Whenever possible, use general contact information (for example, from a department) instead of the contact information of an individual.</t>
         </is>
       </c>
-      <c r="F4" s="213" t="inlineStr">
+      <c r="F4" s="215" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -19282,30 +19332,30 @@
           <t>vcard:Kind</t>
         </is>
       </c>
-      <c r="H4" s="213" t="n">
+      <c r="H4" s="215" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="219" t="inlineStr">
+      <c r="I4" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="219" t="inlineStr">
+      <c r="J4" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K4" s="219" t="inlineStr">
+      <c r="K4" s="213" t="inlineStr">
         <is>
           <t>custom:contact</t>
         </is>
       </c>
-      <c r="L4" s="219" t="inlineStr">
+      <c r="L4" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
       </c>
-      <c r="M4" s="219" t="inlineStr">
+      <c r="M4" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
@@ -19378,7 +19428,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="219" t="n"/>
+      <c r="J5" s="213" t="n"/>
       <c r="K5" s="227" t="inlineStr">
         <is>
           <t>custom:creator</t>
@@ -19415,7 +19465,7 @@
       <c r="V5" s="221" t="n"/>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="217" t="inlineStr">
+      <c r="A6" s="218" t="inlineStr">
         <is>
           <t>dataset</t>
         </is>
@@ -19425,7 +19475,7 @@
           <t>A dataset that is listed in the catalogue.</t>
         </is>
       </c>
-      <c r="C6" s="217" t="inlineStr">
+      <c r="C6" s="218" t="inlineStr">
         <is>
           <t>dcat:dataset</t>
         </is>
@@ -19440,7 +19490,7 @@
           <t>Each catalogue contains one or more datasets. This property serves to link datasets to a catalogue. Therefore, a dataset is always contained inside a catalogue.</t>
         </is>
       </c>
-      <c r="F6" s="213" t="inlineStr">
+      <c r="F6" s="215" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -19455,12 +19505,12 @@
           <t>0..n</t>
         </is>
       </c>
-      <c r="I6" s="219" t="inlineStr">
+      <c r="I6" s="213" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J6" s="219" t="inlineStr">
+      <c r="J6" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -19471,21 +19521,21 @@
           <t>Add URI to all datasets contained in this catalogue</t>
         </is>
       </c>
-      <c r="M6" s="219" t="n"/>
-      <c r="O6" t="inlineStr">
+      <c r="M6" s="213" t="n"/>
+      <c r="O6" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="214" t="inlineStr">
         <is>
           <t>dash:URIEditor</t>
         </is>
       </c>
       <c r="S6" s="69" t="n"/>
-      <c r="T6" s="217" t="n"/>
-      <c r="U6" s="217" t="n"/>
-      <c r="V6" s="217" t="n"/>
+      <c r="T6" s="218" t="n"/>
+      <c r="U6" s="218" t="n"/>
+      <c r="V6" s="218" t="n"/>
     </row>
     <row r="7" ht="29" customHeight="1">
       <c r="A7" s="221" t="inlineStr">
@@ -19533,7 +19583,7 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J7" s="219" t="inlineStr">
+      <c r="J7" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -19563,17 +19613,17 @@
       <c r="V7" s="221" t="n"/>
     </row>
     <row r="8" ht="29" customHeight="1">
-      <c r="A8" s="217" t="inlineStr">
+      <c r="A8" s="218" t="inlineStr">
         <is>
           <t>geographical coverage</t>
         </is>
       </c>
-      <c r="B8" s="215" t="inlineStr">
+      <c r="B8" s="216" t="inlineStr">
         <is>
           <t>Spatial characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C8" s="217" t="inlineStr">
+      <c r="C8" s="218" t="inlineStr">
         <is>
           <t>dct:spatial</t>
         </is>
@@ -19583,42 +19633,42 @@
           <t>EU Vocabularies Continents Named Authority List</t>
         </is>
       </c>
-      <c r="E8" s="218" t="inlineStr">
+      <c r="E8" s="219" t="inlineStr">
         <is>
           <t>The EU Vocabularies Named Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, GeoNames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocabulary can be used.</t>
         </is>
       </c>
-      <c r="F8" s="213" t="inlineStr">
+      <c r="F8" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G8" s="213" t="inlineStr">
+      <c r="G8" s="215" t="inlineStr">
         <is>
           <t>dct:Location (IRI)</t>
         </is>
       </c>
-      <c r="H8" s="213" t="inlineStr">
+      <c r="H8" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I8" s="219" t="inlineStr">
+      <c r="I8" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="219" t="inlineStr">
+      <c r="J8" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K8" s="103" t="n"/>
-      <c r="L8" s="219" t="n"/>
-      <c r="M8" s="219" t="n"/>
+      <c r="L8" s="213" t="n"/>
+      <c r="M8" s="213" t="n"/>
       <c r="O8" s="214" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="P8" s="214" t="inlineStr">
@@ -19627,9 +19677,9 @@
         </is>
       </c>
       <c r="S8" s="69" t="n"/>
-      <c r="T8" s="217" t="n"/>
-      <c r="U8" s="217" t="n"/>
-      <c r="V8" s="217" t="n"/>
+      <c r="T8" s="218" t="n"/>
+      <c r="U8" s="218" t="n"/>
+      <c r="V8" s="218" t="n"/>
     </row>
     <row r="9" ht="29" customHeight="1">
       <c r="D9" s="177" t="inlineStr">
@@ -19714,7 +19764,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J13" s="219" t="inlineStr">
+      <c r="J13" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -19742,7 +19792,7 @@
       <c r="V13" s="221" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="217" t="inlineStr">
+      <c r="A14" s="218" t="inlineStr">
         <is>
           <t>home page</t>
         </is>
@@ -19752,7 +19802,7 @@
           <t>A homepage for some thing.</t>
         </is>
       </c>
-      <c r="C14" s="217" t="inlineStr">
+      <c r="C14" s="218" t="inlineStr">
         <is>
           <t>foaf:homepage</t>
         </is>
@@ -19767,34 +19817,34 @@
           <t>The home page of the catalogue, if available.</t>
         </is>
       </c>
-      <c r="F14" s="213" t="inlineStr">
+      <c r="F14" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G14" s="213" t="inlineStr">
+      <c r="G14" s="215" t="inlineStr">
         <is>
           <t>foaf:Document (IRI)</t>
         </is>
       </c>
-      <c r="H14" s="213" t="inlineStr">
+      <c r="H14" s="215" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I14" s="219" t="inlineStr">
+      <c r="I14" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="219" t="inlineStr">
+      <c r="J14" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K14" s="103" t="n"/>
-      <c r="L14" s="219" t="n"/>
-      <c r="M14" s="219" t="n"/>
+      <c r="L14" s="213" t="n"/>
+      <c r="M14" s="213" t="n"/>
       <c r="O14" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -19806,9 +19856,9 @@
         </is>
       </c>
       <c r="S14" s="69" t="n"/>
-      <c r="T14" s="217" t="n"/>
-      <c r="U14" s="217" t="n"/>
-      <c r="V14" s="217" t="n"/>
+      <c r="T14" s="218" t="n"/>
+      <c r="U14" s="218" t="n"/>
+      <c r="V14" s="218" t="n"/>
     </row>
     <row r="15" ht="64" customHeight="1">
       <c r="A15" s="221" t="inlineStr">
@@ -19857,7 +19907,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J15" s="219" t="inlineStr">
+      <c r="J15" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -19871,7 +19921,7 @@
       <c r="M15" s="220" t="n"/>
       <c r="O15" s="214" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="P15" s="214" t="inlineStr">
@@ -19885,7 +19935,7 @@
       <c r="V15" s="221" t="n"/>
     </row>
     <row r="16" ht="85.25" customHeight="1">
-      <c r="A16" s="217" t="inlineStr">
+      <c r="A16" s="218" t="inlineStr">
         <is>
           <t>licence</t>
         </is>
@@ -19911,27 +19961,27 @@
 The licences for Distributions and Data Services are not specified here. They are specified in the licence properties of their respective classes.</t>
         </is>
       </c>
-      <c r="F16" s="213" t="inlineStr">
+      <c r="F16" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G16" s="213" t="inlineStr">
+      <c r="G16" s="215" t="inlineStr">
         <is>
           <t>dct:LicenseDocument (IRI)</t>
         </is>
       </c>
-      <c r="H16" s="213" t="inlineStr">
+      <c r="H16" s="215" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I16" s="219" t="inlineStr">
+      <c r="I16" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J16" s="219" t="inlineStr">
+      <c r="J16" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -19941,8 +19991,8 @@
           <t>custom:licence</t>
         </is>
       </c>
-      <c r="L16" s="219" t="n"/>
-      <c r="M16" s="219" t="n"/>
+      <c r="L16" s="213" t="n"/>
+      <c r="M16" s="213" t="n"/>
       <c r="O16" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -19954,9 +20004,9 @@
         </is>
       </c>
       <c r="S16" s="69" t="n"/>
-      <c r="T16" s="217" t="n"/>
-      <c r="U16" s="217" t="n"/>
-      <c r="V16" s="217" t="n"/>
+      <c r="T16" s="218" t="n"/>
+      <c r="U16" s="218" t="n"/>
+      <c r="V16" s="218" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="221" t="inlineStr">
@@ -20000,7 +20050,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J17" s="219" t="inlineStr">
+      <c r="J17" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -20033,7 +20083,7 @@
       <c r="V17" s="221" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="217" t="inlineStr">
+      <c r="A18" s="218" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
@@ -20058,7 +20108,7 @@
           <t>The organisation or individual that is the holder of the intellectual property rights of a dataset. For more details about the publisher, see the class Agent. Example: Radboudumc.</t>
         </is>
       </c>
-      <c r="F18" s="213" t="inlineStr">
+      <c r="F18" s="215" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -20068,15 +20118,15 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H18" s="213" t="n">
+      <c r="H18" s="215" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="219" t="inlineStr">
+      <c r="I18" s="213" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J18" s="219" t="inlineStr">
+      <c r="J18" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -20086,12 +20136,12 @@
           <t>custom:publisher</t>
         </is>
       </c>
-      <c r="L18" s="219" t="inlineStr">
+      <c r="L18" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="M18" s="219" t="inlineStr">
+      <c r="M18" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -20112,9 +20162,9 @@
         </is>
       </c>
       <c r="S18" s="69" t="n"/>
-      <c r="T18" s="217" t="n"/>
-      <c r="U18" s="217" t="n"/>
-      <c r="V18" s="217" t="n"/>
+      <c r="T18" s="218" t="n"/>
+      <c r="U18" s="218" t="n"/>
+      <c r="V18" s="218" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="221" t="inlineStr">
@@ -20191,7 +20241,7 @@
       <c r="V19" s="221" t="n"/>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="217" t="inlineStr">
+      <c r="A20" s="218" t="inlineStr">
         <is>
           <t>rights</t>
         </is>
@@ -20201,7 +20251,7 @@
           <t>Information about rights held in and over the resource.</t>
         </is>
       </c>
-      <c r="C20" s="217" t="inlineStr">
+      <c r="C20" s="218" t="inlineStr">
         <is>
           <t>dct:rights</t>
         </is>
@@ -20216,34 +20266,34 @@
           <t>The rights statement should be a free-text statement placed at a web-accessible location such that the value of this property is the IRI pointing to that statement.</t>
         </is>
       </c>
-      <c r="F20" s="213" t="inlineStr">
+      <c r="F20" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G20" s="213" t="inlineStr">
+      <c r="G20" s="215" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
       </c>
-      <c r="H20" s="213" t="inlineStr">
+      <c r="H20" s="215" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I20" s="219" t="inlineStr">
+      <c r="I20" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J20" s="219" t="inlineStr">
+      <c r="J20" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K20" s="75" t="n"/>
-      <c r="L20" s="219" t="n"/>
-      <c r="M20" s="219" t="n"/>
+      <c r="L20" s="213" t="n"/>
+      <c r="M20" s="213" t="n"/>
       <c r="O20" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -20255,9 +20305,9 @@
         </is>
       </c>
       <c r="S20" s="69" t="n"/>
-      <c r="T20" s="217" t="n"/>
-      <c r="U20" s="217" t="n"/>
-      <c r="V20" s="217" t="n"/>
+      <c r="T20" s="218" t="n"/>
+      <c r="U20" s="218" t="n"/>
+      <c r="V20" s="218" t="n"/>
     </row>
     <row r="21" ht="64" customHeight="1">
       <c r="A21" s="221" t="inlineStr">
@@ -20333,7 +20383,7 @@
       <c r="V21" s="221" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="217" t="inlineStr">
+      <c r="A22" s="218" t="inlineStr">
         <is>
           <t>temporal coverage</t>
         </is>
@@ -20343,7 +20393,7 @@
           <t>Temporal characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C22" s="217" t="inlineStr">
+      <c r="C22" s="218" t="inlineStr">
         <is>
           <t>dct:temporal</t>
         </is>
@@ -20354,7 +20404,7 @@
         </is>
       </c>
       <c r="E22" s="29" t="n"/>
-      <c r="F22" s="213" t="inlineStr">
+      <c r="F22" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -20364,17 +20414,17 @@
           <t>dct:PeriodOfTime</t>
         </is>
       </c>
-      <c r="H22" s="213" t="inlineStr">
+      <c r="H22" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I22" s="219" t="inlineStr">
+      <c r="I22" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="219" t="inlineStr">
+      <c r="J22" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -20384,8 +20434,8 @@
           <t>custom:temporal_coverage</t>
         </is>
       </c>
-      <c r="L22" s="219" t="n"/>
-      <c r="M22" s="219" t="n"/>
+      <c r="L22" s="213" t="n"/>
+      <c r="M22" s="213" t="n"/>
       <c r="N22" s="214" t="inlineStr">
         <is>
           <t>hri:PeriodOfTimeShape</t>
@@ -20402,9 +20452,9 @@
         </is>
       </c>
       <c r="S22" s="69" t="n"/>
-      <c r="T22" s="217" t="n"/>
-      <c r="U22" s="217" t="n"/>
-      <c r="V22" s="217" t="n"/>
+      <c r="T22" s="218" t="n"/>
+      <c r="U22" s="218" t="n"/>
+      <c r="V22" s="218" t="n"/>
     </row>
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="221" t="inlineStr">
@@ -20462,7 +20512,7 @@
       <c r="M23" s="220" t="n"/>
       <c r="O23" s="214" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="P23" s="214" t="inlineStr">
@@ -20476,7 +20526,7 @@
       <c r="V23" s="221" t="n"/>
     </row>
     <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="217" t="inlineStr">
+      <c r="A24" s="218" t="inlineStr">
         <is>
           <t>title</t>
         </is>
@@ -20486,7 +20536,7 @@
           <t>A name given to the resource.</t>
         </is>
       </c>
-      <c r="C24" s="217" t="inlineStr">
+      <c r="C24" s="218" t="inlineStr">
         <is>
           <t>dct:title</t>
         </is>
@@ -20501,27 +20551,27 @@
           <t>Provide a unique title for your catalogue, which can be repeated in multiple languages. Example: Healthy Brain Study.</t>
         </is>
       </c>
-      <c r="F24" s="213" t="inlineStr">
+      <c r="F24" s="215" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G24" s="213" t="inlineStr">
+      <c r="G24" s="215" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H24" s="213" t="inlineStr">
+      <c r="H24" s="215" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I24" s="219" t="inlineStr">
+      <c r="I24" s="213" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J24" s="219" t="inlineStr">
+      <c r="J24" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -20531,8 +20581,8 @@
           <t>title</t>
         </is>
       </c>
-      <c r="L24" s="219" t="n"/>
-      <c r="M24" s="219" t="n"/>
+      <c r="L24" s="213" t="n"/>
+      <c r="M24" s="213" t="n"/>
       <c r="O24" s="214" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -20546,9 +20596,9 @@
       <c r="S24" s="69" t="b">
         <v>1</v>
       </c>
-      <c r="T24" s="217" t="n"/>
-      <c r="U24" s="217" t="n"/>
-      <c r="V24" s="217" t="n"/>
+      <c r="T24" s="218" t="n"/>
+      <c r="U24" s="218" t="n"/>
+      <c r="V24" s="218" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J24"/>
@@ -20559,10 +20609,10 @@
     <mergeCell ref="E8:E12"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="I8:I12"/>
+    <mergeCell ref="F8:F12"/>
     <mergeCell ref="G8:G12"/>
     <mergeCell ref="L8:L12"/>
     <mergeCell ref="J8:J12"/>
-    <mergeCell ref="F8:F12"/>
     <mergeCell ref="M8:M12"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F8">
@@ -20698,9 +20748,9 @@
   <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col width="25.5" bestFit="1" customWidth="1" style="216" min="1" max="1"/>
-    <col width="40.5" customWidth="1" style="216" min="2" max="2"/>
-    <col width="28.83203125" customWidth="1" style="216" min="3" max="3"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="217" min="1" max="1"/>
+    <col width="40.5" customWidth="1" style="217" min="2" max="2"/>
+    <col width="28.83203125" customWidth="1" style="217" min="3" max="3"/>
     <col width="22.5" customWidth="1" style="223" min="4" max="4"/>
     <col width="68.83203125" customWidth="1" style="223" min="5" max="5"/>
     <col width="18.5" bestFit="1" customWidth="1" style="214" min="6" max="6"/>
@@ -20847,7 +20897,7 @@
           <t>Information about who can access the resource or an indication of its security status.</t>
         </is>
       </c>
-      <c r="C2" s="217" t="inlineStr">
+      <c r="C2" s="218" t="inlineStr">
         <is>
           <t>dct:accessRights</t>
         </is>
@@ -20866,25 +20916,25 @@
 Since most data contain personal information, these datasets will need to take the value 'non-public' for the access rights property.</t>
         </is>
       </c>
-      <c r="F2" s="213" t="inlineStr">
+      <c r="F2" s="215" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G2" s="213" t="inlineStr">
+      <c r="G2" s="215" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
       </c>
-      <c r="H2" s="213" t="n">
+      <c r="H2" s="215" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="219" t="inlineStr">
+      <c r="I2" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="219" t="inlineStr">
+      <c r="J2" s="213" t="inlineStr">
         <is>
           <t>Health and NL</t>
         </is>
@@ -20894,7 +20944,7 @@
           <t>custom:access_rights</t>
         </is>
       </c>
-      <c r="L2" s="219" t="n"/>
+      <c r="L2" s="213" t="n"/>
       <c r="P2" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -20935,7 +20985,7 @@
           <t>This property contains an alternative name for the Dataset. This property can be repeated for parallel language versions of the alternative name.</t>
         </is>
       </c>
-      <c r="F3" s="213" t="inlineStr">
+      <c r="F3" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -20955,7 +21005,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J3" s="219" t="inlineStr">
+      <c r="J3" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -21014,17 +21064,17 @@
           <t>dcat:Distribution (IRI)</t>
         </is>
       </c>
-      <c r="H4" s="213" t="inlineStr">
+      <c r="H4" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I4" s="219" t="inlineStr">
+      <c r="I4" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="219" t="inlineStr">
+      <c r="J4" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -21034,7 +21084,7 @@
           <t>custom:analytics</t>
         </is>
       </c>
-      <c r="L4" s="219" t="inlineStr">
+      <c r="L4" s="213" t="inlineStr">
         <is>
           <t>If available, add the URI for the analytics distribution here.</t>
         </is>
@@ -21096,7 +21146,7 @@
         </is>
       </c>
       <c r="I5" s="220" t="n"/>
-      <c r="J5" s="219" t="n"/>
+      <c r="J5" s="213" t="n"/>
       <c r="K5" s="227" t="n"/>
       <c r="L5" s="100" t="n"/>
       <c r="M5" s="220" t="n"/>
@@ -21111,6 +21161,11 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
+      <c r="R5" s="214" t="inlineStr">
+        <is>
+          <t>^http://snomed\\.info/id/[0-9]{6,18}$</t>
+        </is>
+      </c>
       <c r="U5" s="221" t="n"/>
       <c r="V5" s="221" t="n"/>
       <c r="W5" s="221" t="n"/>
@@ -21126,7 +21181,7 @@
           <t>The legislation that is applicable to this resource.</t>
         </is>
       </c>
-      <c r="C6" s="217" t="inlineStr">
+      <c r="C6" s="218" t="inlineStr">
         <is>
           <t>dcatap:applicableLegislation</t>
         </is>
@@ -21144,12 +21199,12 @@
 While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property (also in Datasets) describes the legal basis for initial collection and processing of (personal) data.</t>
         </is>
       </c>
-      <c r="F6" s="213" t="inlineStr">
+      <c r="F6" s="215" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G6" s="213" t="inlineStr">
+      <c r="G6" s="215" t="inlineStr">
         <is>
           <t>eli:LegalResource (IRI)</t>
         </is>
@@ -21159,12 +21214,12 @@
           <t>1..n</t>
         </is>
       </c>
-      <c r="I6" s="219" t="inlineStr">
+      <c r="I6" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="219" t="inlineStr">
+      <c r="J6" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -21174,7 +21229,7 @@
           <t>custom:applicable_legislation</t>
         </is>
       </c>
-      <c r="L6" s="219" t="n"/>
+      <c r="L6" s="213" t="n"/>
       <c r="P6" s="83" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -21241,7 +21296,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J7" s="219" t="inlineStr">
+      <c r="J7" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -21269,7 +21324,7 @@
       <c r="W7" s="221" t="n"/>
     </row>
     <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="217" t="inlineStr">
+      <c r="A8" s="218" t="inlineStr">
         <is>
           <t>coding system</t>
         </is>
@@ -21279,7 +21334,7 @@
           <t>Coding systems in use (e.g. ICD-10-CM, DGRs, SNOMED CT, ...)</t>
         </is>
       </c>
-      <c r="C8" s="217" t="inlineStr">
+      <c r="C8" s="218" t="inlineStr">
         <is>
           <t>healthdcatap:hasCodingSystem</t>
         </is>
@@ -21295,27 +21350,27 @@
 This property provides information on which coding systems are in use in your dataset. For this, Wikidata URIs must be used.</t>
         </is>
       </c>
-      <c r="F8" s="213" t="inlineStr">
+      <c r="F8" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G8" s="213" t="inlineStr">
+      <c r="G8" s="215" t="inlineStr">
         <is>
           <t>dct:Standard (IRI)</t>
         </is>
       </c>
-      <c r="H8" s="213" t="inlineStr">
+      <c r="H8" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I8" s="219" t="inlineStr">
+      <c r="I8" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="219" t="inlineStr">
+      <c r="J8" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -21325,7 +21380,7 @@
           <t>custom:coding_system</t>
         </is>
       </c>
-      <c r="L8" s="219" t="n"/>
+      <c r="L8" s="213" t="n"/>
       <c r="P8" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -21336,9 +21391,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U8" s="217" t="n"/>
-      <c r="V8" s="217" t="n"/>
-      <c r="W8" s="217" t="n"/>
+      <c r="U8" s="218" t="n"/>
+      <c r="V8" s="218" t="n"/>
+      <c r="W8" s="218" t="n"/>
     </row>
     <row r="9" ht="80" customHeight="1">
       <c r="A9" s="221" t="inlineStr">
@@ -21387,7 +21442,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J9" s="219" t="inlineStr">
+      <c r="J9" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -21415,7 +21470,7 @@
       <c r="W9" s="221" t="n"/>
     </row>
     <row r="10" ht="123.75" customHeight="1">
-      <c r="A10" s="217" t="inlineStr">
+      <c r="A10" s="218" t="inlineStr">
         <is>
           <t>contact point</t>
         </is>
@@ -21425,7 +21480,7 @@
           <t>Relevant contact information for the catalogued resource.</t>
         </is>
       </c>
-      <c r="C10" s="217" t="inlineStr">
+      <c r="C10" s="218" t="inlineStr">
         <is>
           <t>dcat:contactPoint</t>
         </is>
@@ -21441,7 +21496,7 @@
 Whenever possible, use general contact information (for example, from a department) instead of the contact information of an individual.</t>
         </is>
       </c>
-      <c r="F10" s="213" t="inlineStr">
+      <c r="F10" s="215" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -21451,15 +21506,15 @@
           <t>vcard:Kind</t>
         </is>
       </c>
-      <c r="H10" s="213" t="n">
+      <c r="H10" s="215" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="219" t="inlineStr">
+      <c r="I10" s="213" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J10" s="219" t="inlineStr">
+      <c r="J10" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -21469,17 +21524,17 @@
           <t>custom:contact_</t>
         </is>
       </c>
-      <c r="L10" s="219" t="inlineStr">
+      <c r="L10" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
       </c>
-      <c r="M10" s="219" t="inlineStr">
+      <c r="M10" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
       </c>
-      <c r="N10" s="219" t="inlineStr">
+      <c r="N10" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
@@ -21499,9 +21554,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="U10" s="217" t="n"/>
-      <c r="V10" s="217" t="n"/>
-      <c r="W10" s="217" t="n"/>
+      <c r="U10" s="218" t="n"/>
+      <c r="V10" s="218" t="n"/>
+      <c r="W10" s="218" t="n"/>
     </row>
     <row r="11" ht="176" customHeight="1">
       <c r="A11" s="221" t="inlineStr">
@@ -21551,7 +21606,7 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J11" s="219" t="inlineStr">
+      <c r="J11" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -21596,7 +21651,7 @@
       <c r="W11" s="221" t="n"/>
     </row>
     <row r="12" ht="64" customHeight="1">
-      <c r="A12" s="217" t="inlineStr">
+      <c r="A12" s="218" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -21606,7 +21661,7 @@
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C12" s="217" t="inlineStr">
+      <c r="C12" s="218" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -21621,27 +21676,27 @@
           <t>Brief description of the dataset. You can repeat this property in multiple languages. Example: ‘Collection of physiological data of Healthy Brain Study participants. This collection includes measurements via biowearables for heart rate, oxygenation, systolic and diastolic measures and stress levels.’</t>
         </is>
       </c>
-      <c r="F12" s="213" t="inlineStr">
+      <c r="F12" s="215" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G12" s="213" t="inlineStr">
+      <c r="G12" s="215" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H12" s="213" t="inlineStr">
+      <c r="H12" s="215" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I12" s="219" t="inlineStr">
+      <c r="I12" s="213" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J12" s="219" t="inlineStr">
+      <c r="J12" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21651,7 +21706,7 @@
           <t>notes</t>
         </is>
       </c>
-      <c r="L12" s="219" t="n"/>
+      <c r="L12" s="213" t="n"/>
       <c r="P12" s="214" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -21659,15 +21714,15 @@
       </c>
       <c r="Q12" s="214" t="inlineStr">
         <is>
-          <t>dash:TextFieldEditor</t>
+          <t>dash:TextAreaEditor</t>
         </is>
       </c>
       <c r="T12" s="214" t="b">
         <v>1</v>
       </c>
-      <c r="U12" s="217" t="n"/>
-      <c r="V12" s="217" t="n"/>
-      <c r="W12" s="217" t="n"/>
+      <c r="U12" s="218" t="n"/>
+      <c r="V12" s="218" t="n"/>
+      <c r="W12" s="218" t="n"/>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="221" t="inlineStr">
@@ -21754,7 +21809,7 @@
       <c r="W13" s="221" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="217" t="inlineStr">
+      <c r="A14" s="218" t="inlineStr">
         <is>
           <t>documentation</t>
         </is>
@@ -21764,7 +21819,7 @@
           <t>A page or document about this thing.</t>
         </is>
       </c>
-      <c r="C14" s="217" t="inlineStr">
+      <c r="C14" s="218" t="inlineStr">
         <is>
           <t>foaf:page</t>
         </is>
@@ -21779,27 +21834,27 @@
           <t>The value of this property is the IRI pointing to the web page or document about the dataset.</t>
         </is>
       </c>
-      <c r="F14" s="213" t="inlineStr">
+      <c r="F14" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G14" s="213" t="inlineStr">
+      <c r="G14" s="215" t="inlineStr">
         <is>
           <t>foaf:Document (IRI)</t>
         </is>
       </c>
-      <c r="H14" s="213" t="inlineStr">
+      <c r="H14" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I14" s="219" t="inlineStr">
+      <c r="I14" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="219" t="inlineStr">
+      <c r="J14" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -21809,7 +21864,7 @@
           <t>custom:documentation</t>
         </is>
       </c>
-      <c r="L14" s="219" t="n"/>
+      <c r="L14" s="213" t="n"/>
       <c r="P14" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -21820,9 +21875,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U14" s="217" t="n"/>
-      <c r="V14" s="217" t="n"/>
-      <c r="W14" s="217" t="n"/>
+      <c r="U14" s="218" t="n"/>
+      <c r="V14" s="218" t="n"/>
+      <c r="W14" s="218" t="n"/>
     </row>
     <row r="15" ht="160" customHeight="1">
       <c r="A15" s="221" t="inlineStr">
@@ -21853,7 +21908,7 @@
 See the property "measurement technique" for more information about the technique(s) used to generate the data in the Dataset.</t>
         </is>
       </c>
-      <c r="F15" s="213" t="inlineStr">
+      <c r="F15" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -21893,7 +21948,7 @@
       <c r="W15" s="221" t="n"/>
     </row>
     <row r="16" ht="69.75" customHeight="1">
-      <c r="A16" s="217" t="inlineStr">
+      <c r="A16" s="218" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
@@ -21903,7 +21958,7 @@
           <t>The frequency with which items are added to a collection.</t>
         </is>
       </c>
-      <c r="C16" s="217" t="inlineStr">
+      <c r="C16" s="218" t="inlineStr">
         <is>
           <t>dct:accrualPeriodicity</t>
         </is>
@@ -21913,7 +21968,7 @@
           <t>http://publications.europa.eu/resource/authority/frequency</t>
         </is>
       </c>
-      <c r="E16" s="218" t="inlineStr">
+      <c r="E16" s="219" t="inlineStr">
         <is>
           <t>The value of this property should be the IRI from the listed controlled vocabulary indicating the frequency at which the dataset is updated.
 For example: http://publications.europa.eu/resource/authority/frequency/WEEKLY</t>
@@ -21924,22 +21979,22 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G16" s="213" t="inlineStr">
+      <c r="G16" s="215" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H16" s="213" t="inlineStr">
+      <c r="H16" s="215" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I16" s="219" t="inlineStr">
+      <c r="I16" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J16" s="219" t="inlineStr">
+      <c r="J16" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -21950,8 +22005,8 @@
         </is>
       </c>
       <c r="L16" s="107" t="n"/>
-      <c r="M16" s="219" t="n"/>
-      <c r="N16" s="219" t="n"/>
+      <c r="M16" s="213" t="n"/>
+      <c r="N16" s="213" t="n"/>
       <c r="P16" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -21962,9 +22017,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U16" s="217" t="n"/>
-      <c r="V16" s="217" t="n"/>
-      <c r="W16" s="217" t="n"/>
+      <c r="U16" s="218" t="n"/>
+      <c r="V16" s="218" t="n"/>
+      <c r="W16" s="218" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="221" t="inlineStr">
@@ -21992,7 +22047,7 @@
           <t>The EU Vocabularies Named Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, GeoNames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocabulary can be used. However, it might in many cases be desirable to keep the geographical coverage broader (e.g. indicating that NL is covered), to avoid exposing detailed information about subjects' locations.</t>
         </is>
       </c>
-      <c r="F17" s="213" t="inlineStr">
+      <c r="F17" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -22064,7 +22119,7 @@
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="217" t="inlineStr">
+      <c r="A22" s="218" t="inlineStr">
         <is>
           <t>has version</t>
         </is>
@@ -22074,7 +22129,7 @@
           <t>This resource has a more specific, versioned resource.</t>
         </is>
       </c>
-      <c r="C22" s="217" t="inlineStr">
+      <c r="C22" s="218" t="inlineStr">
         <is>
           <t>dcat:hasVersion</t>
         </is>
@@ -22084,7 +22139,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E22" s="218" t="inlineStr">
+      <c r="E22" s="219" t="inlineStr">
         <is>
           <t>Indicate the dataset that is another version of the current dataset.</t>
         </is>
@@ -22099,17 +22154,17 @@
           <t>dcat:Dataset (IRI)</t>
         </is>
       </c>
-      <c r="H22" s="213" t="inlineStr">
+      <c r="H22" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I22" s="219" t="inlineStr">
+      <c r="I22" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="219" t="inlineStr">
+      <c r="J22" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -22124,8 +22179,8 @@
           <t>fill in URI to dcat:Dataset that is another version of current Dataset</t>
         </is>
       </c>
-      <c r="M22" s="219" t="n"/>
-      <c r="N22" s="219" t="n"/>
+      <c r="M22" s="213" t="n"/>
+      <c r="N22" s="213" t="n"/>
       <c r="P22" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -22136,9 +22191,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U22" s="217" t="n"/>
-      <c r="V22" s="217" t="n"/>
-      <c r="W22" s="217" t="n"/>
+      <c r="U22" s="218" t="n"/>
+      <c r="V22" s="218" t="n"/>
+      <c r="W22" s="218" t="n"/>
     </row>
     <row r="23" ht="112" customHeight="1">
       <c r="A23" s="221" t="inlineStr">
@@ -22167,7 +22222,7 @@
 Example: A Dataset concerning myocardial infarction can use http://snomed.info/id/22298006.</t>
         </is>
       </c>
-      <c r="F23" s="213" t="inlineStr">
+      <c r="F23" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -22202,12 +22257,17 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
+      <c r="R23" s="214" t="inlineStr">
+        <is>
+          <t>^(http://snomed\\.info/id/[0-9]{6,18}|http://id\\.who\\.int/icd/entity/[0-9]+|http://www\\.orpha\\.net/ORDO/Orphanet_[0-9]+)$</t>
+        </is>
+      </c>
       <c r="U23" s="221" t="n"/>
       <c r="V23" s="221" t="n"/>
       <c r="W23" s="221" t="n"/>
     </row>
     <row r="24" ht="96" customHeight="1">
-      <c r="A24" s="217" t="inlineStr">
+      <c r="A24" s="218" t="inlineStr">
         <is>
           <t>health theme</t>
         </is>
@@ -22217,7 +22277,7 @@
           <t>A category of the Dataset or tag describing the Dataset.</t>
         </is>
       </c>
-      <c r="C24" s="217" t="inlineStr">
+      <c r="C24" s="218" t="inlineStr">
         <is>
           <t>healthdcatap:healthTheme</t>
         </is>
@@ -22233,27 +22293,27 @@
 This property is a structured way to tag the dataset with different health themes. This could include, for example, the specific disease the dataset is about. More details can be provided, if desirable, in the keywords property.  The Wikidata URI of the health theme must be used here.</t>
         </is>
       </c>
-      <c r="F24" s="213" t="inlineStr">
+      <c r="F24" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G24" s="213" t="inlineStr">
+      <c r="G24" s="215" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H24" s="213" t="inlineStr">
+      <c r="H24" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I24" s="219" t="inlineStr">
+      <c r="I24" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J24" s="219" t="inlineStr">
+      <c r="J24" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -22263,7 +22323,7 @@
           <t>custom:health_theme</t>
         </is>
       </c>
-      <c r="L24" s="219" t="n"/>
+      <c r="L24" s="213" t="n"/>
       <c r="P24" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -22274,9 +22334,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U24" s="217" t="n"/>
-      <c r="V24" s="217" t="n"/>
-      <c r="W24" s="217" t="n"/>
+      <c r="U24" s="218" t="n"/>
+      <c r="V24" s="218" t="n"/>
+      <c r="W24" s="218" t="n"/>
     </row>
     <row r="25" ht="96" customHeight="1">
       <c r="A25" s="221" t="inlineStr">
@@ -22351,7 +22411,7 @@
       <c r="W25" s="221" t="n"/>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="217" t="inlineStr">
+      <c r="A26" s="218" t="inlineStr">
         <is>
           <t>in series</t>
         </is>
@@ -22361,7 +22421,7 @@
           <t>A dataset series of which the dataset is part.</t>
         </is>
       </c>
-      <c r="C26" s="217" t="inlineStr">
+      <c r="C26" s="218" t="inlineStr">
         <is>
           <t>dcat:inSeries</t>
         </is>
@@ -22376,7 +22436,7 @@
           <t xml:space="preserve">This property points to the Dataset Series of which the Dataset is part. </t>
         </is>
       </c>
-      <c r="F26" s="213" t="inlineStr">
+      <c r="F26" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -22386,17 +22446,17 @@
           <t>dcat:DatasetSeries (IRI)</t>
         </is>
       </c>
-      <c r="H26" s="213" t="inlineStr">
+      <c r="H26" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I26" s="219" t="inlineStr">
+      <c r="I26" s="213" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J26" s="219" t="inlineStr">
+      <c r="J26" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -22417,9 +22477,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U26" s="217" t="n"/>
-      <c r="V26" s="217" t="n"/>
-      <c r="W26" s="217" t="n"/>
+      <c r="U26" s="218" t="n"/>
+      <c r="V26" s="218" t="n"/>
+      <c r="W26" s="218" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="221" t="inlineStr">
@@ -22496,7 +22556,7 @@
       <c r="W27" s="221" t="n"/>
     </row>
     <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="217" t="inlineStr">
+      <c r="A28" s="218" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -22521,27 +22581,27 @@
           <t>Add keywords to increase dataset discoverability. You can include keywords in different languages, submitting each keyword as a separate entry. Example: Physiological measures, Heart Rate, Stress Measures.</t>
         </is>
       </c>
-      <c r="F28" s="213" t="inlineStr">
+      <c r="F28" s="215" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G28" s="213" t="inlineStr">
+      <c r="G28" s="215" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H28" s="213" t="inlineStr">
+      <c r="H28" s="215" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I28" s="219" t="inlineStr">
+      <c r="I28" s="213" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J28" s="219" t="inlineStr">
+      <c r="J28" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -22551,7 +22611,7 @@
           <t>tags</t>
         </is>
       </c>
-      <c r="L28" s="219" t="n"/>
+      <c r="L28" s="213" t="n"/>
       <c r="P28" s="214" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -22562,9 +22622,9 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="U28" s="217" t="n"/>
-      <c r="V28" s="217" t="n"/>
-      <c r="W28" s="217" t="n"/>
+      <c r="U28" s="218" t="n"/>
+      <c r="V28" s="218" t="n"/>
+      <c r="W28" s="218" t="n"/>
     </row>
     <row r="29" ht="128" customHeight="1">
       <c r="A29" s="221" t="inlineStr">
@@ -22593,7 +22653,7 @@
 Example: For an EGA Dataset, dcat:landingPage points to the corresponding human-readable EGA Dataset page, like https://ega-archive.org/datasets/EGAD00001005083.</t>
         </is>
       </c>
-      <c r="F29" s="213" t="inlineStr">
+      <c r="F29" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -22637,7 +22697,7 @@
       <c r="W29" s="221" t="n"/>
     </row>
     <row r="30" ht="48" customHeight="1">
-      <c r="A30" s="217" t="inlineStr">
+      <c r="A30" s="218" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -22667,12 +22727,12 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G30" s="213" t="inlineStr">
+      <c r="G30" s="215" t="inlineStr">
         <is>
           <t>dct:LinguisticSystem (IRI)</t>
         </is>
       </c>
-      <c r="H30" s="213" t="inlineStr">
+      <c r="H30" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
@@ -22692,9 +22752,9 @@
           <t>custom:language</t>
         </is>
       </c>
-      <c r="L30" s="219" t="n"/>
-      <c r="M30" s="219" t="n"/>
-      <c r="N30" s="219" t="n"/>
+      <c r="L30" s="213" t="n"/>
+      <c r="M30" s="213" t="n"/>
+      <c r="N30" s="213" t="n"/>
       <c r="P30" s="69" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -22705,9 +22765,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U30" s="217" t="n"/>
-      <c r="V30" s="217" t="n"/>
-      <c r="W30" s="217" t="n"/>
+      <c r="U30" s="218" t="n"/>
+      <c r="V30" s="218" t="n"/>
+      <c r="W30" s="218" t="n"/>
     </row>
     <row r="31" ht="160" customHeight="1">
       <c r="A31" s="221" t="inlineStr">
@@ -22738,7 +22798,7 @@
 An example value for this property could be dpv:Consent.</t>
         </is>
       </c>
-      <c r="F31" s="213" t="inlineStr">
+      <c r="F31" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -22786,7 +22846,7 @@
       <c r="W31" s="221" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="217" t="inlineStr">
+      <c r="A32" s="218" t="inlineStr">
         <is>
           <t>maximum typical age</t>
         </is>
@@ -22796,7 +22856,7 @@
           <t>Maximum typical age of the population within the dataset</t>
         </is>
       </c>
-      <c r="C32" s="217" t="inlineStr">
+      <c r="C32" s="218" t="inlineStr">
         <is>
           <t>healthdcatap:maxTypicalAge</t>
         </is>
@@ -22816,22 +22876,22 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G32" s="213" t="inlineStr">
+      <c r="G32" s="215" t="inlineStr">
         <is>
           <t>xsd:nonNegativeInteger</t>
         </is>
       </c>
-      <c r="H32" s="213" t="inlineStr">
+      <c r="H32" s="215" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I32" s="219" t="inlineStr">
+      <c r="I32" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J32" s="219" t="inlineStr">
+      <c r="J32" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -22841,9 +22901,9 @@
           <t>custom:max_typical_age</t>
         </is>
       </c>
-      <c r="L32" s="219" t="n"/>
-      <c r="M32" s="219" t="n"/>
-      <c r="N32" s="219" t="n"/>
+      <c r="L32" s="213" t="n"/>
+      <c r="M32" s="213" t="n"/>
+      <c r="N32" s="213" t="n"/>
       <c r="P32" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -22854,9 +22914,9 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="U32" s="217" t="n"/>
-      <c r="V32" s="217" t="n"/>
-      <c r="W32" s="217" t="n"/>
+      <c r="U32" s="218" t="n"/>
+      <c r="V32" s="218" t="n"/>
+      <c r="W32" s="218" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="221" t="inlineStr">
@@ -22884,7 +22944,7 @@
           <t>The approximate minimum age of subjects in the dataset, if applicable. Approximate age is given to protect potentially sensitive information of subjects in the dataset.</t>
         </is>
       </c>
-      <c r="F33" s="213" t="inlineStr">
+      <c r="F33" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -22932,7 +22992,7 @@
       <c r="W33" s="221" t="n"/>
     </row>
     <row r="34" ht="209.25" customHeight="1">
-      <c r="A34" s="217" t="inlineStr">
+      <c r="A34" s="218" t="inlineStr">
         <is>
           <t>measurement technique</t>
         </is>
@@ -22959,72 +23019,72 @@
 Note: This is a temporary location and it will change with the next release. </t>
         </is>
       </c>
-      <c r="F34" s="213" t="inlineStr">
+      <c r="F34" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G34" s="213" t="inlineStr">
+      <c r="G34" s="215" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H34" s="213" t="inlineStr">
+      <c r="H34" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I34" s="219" t="n"/>
-      <c r="J34" s="219" t="n"/>
+      <c r="I34" s="213" t="n"/>
+      <c r="J34" s="213" t="n"/>
       <c r="K34" s="75" t="n"/>
-      <c r="L34" s="219" t="n"/>
-      <c r="M34" s="219" t="n"/>
-      <c r="N34" s="219" t="n"/>
-      <c r="O34" s="219" t="n"/>
-      <c r="P34" s="219" t="inlineStr">
+      <c r="L34" s="213" t="n"/>
+      <c r="M34" s="213" t="n"/>
+      <c r="N34" s="213" t="n"/>
+      <c r="O34" s="213" t="n"/>
+      <c r="P34" s="69" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
         </is>
       </c>
-      <c r="Q34" s="219" t="inlineStr">
+      <c r="Q34" s="69" t="inlineStr">
         <is>
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="R34" s="219" t="n"/>
-      <c r="S34" s="219" t="n"/>
-      <c r="T34" s="219" t="n"/>
-      <c r="U34" s="217" t="n"/>
-      <c r="V34" s="217" t="n"/>
-      <c r="W34" s="217" t="n"/>
-      <c r="X34" s="219" t="n"/>
-      <c r="Y34" s="219" t="n"/>
-      <c r="Z34" s="219" t="n"/>
-      <c r="AA34" s="219" t="n"/>
-      <c r="AB34" s="219" t="n"/>
-      <c r="AC34" s="219" t="n"/>
-      <c r="AD34" s="219" t="n"/>
-      <c r="AE34" s="219" t="n"/>
-      <c r="AF34" s="219" t="n"/>
-      <c r="AG34" s="219" t="n"/>
-      <c r="AH34" s="219" t="n"/>
-      <c r="AI34" s="219" t="n"/>
-      <c r="AJ34" s="219" t="n"/>
-      <c r="AK34" s="219" t="n"/>
-      <c r="AL34" s="219" t="n"/>
-      <c r="AM34" s="219" t="n"/>
-      <c r="AN34" s="219" t="n"/>
-      <c r="AO34" s="219" t="n"/>
-      <c r="AP34" s="219" t="n"/>
-      <c r="AQ34" s="219" t="n"/>
-      <c r="AR34" s="219" t="n"/>
-      <c r="AS34" s="219" t="n"/>
-      <c r="AT34" s="219" t="n"/>
-      <c r="AU34" s="219" t="n"/>
-      <c r="AV34" s="219" t="n"/>
-      <c r="AW34" s="219" t="n"/>
-      <c r="AX34" s="219" t="n"/>
-      <c r="AY34" s="219" t="n"/>
+      <c r="R34" s="213" t="n"/>
+      <c r="S34" s="213" t="n"/>
+      <c r="T34" s="213" t="n"/>
+      <c r="U34" s="218" t="n"/>
+      <c r="V34" s="218" t="n"/>
+      <c r="W34" s="218" t="n"/>
+      <c r="X34" s="213" t="n"/>
+      <c r="Y34" s="213" t="n"/>
+      <c r="Z34" s="213" t="n"/>
+      <c r="AA34" s="213" t="n"/>
+      <c r="AB34" s="213" t="n"/>
+      <c r="AC34" s="213" t="n"/>
+      <c r="AD34" s="213" t="n"/>
+      <c r="AE34" s="213" t="n"/>
+      <c r="AF34" s="213" t="n"/>
+      <c r="AG34" s="213" t="n"/>
+      <c r="AH34" s="213" t="n"/>
+      <c r="AI34" s="213" t="n"/>
+      <c r="AJ34" s="213" t="n"/>
+      <c r="AK34" s="213" t="n"/>
+      <c r="AL34" s="213" t="n"/>
+      <c r="AM34" s="213" t="n"/>
+      <c r="AN34" s="213" t="n"/>
+      <c r="AO34" s="213" t="n"/>
+      <c r="AP34" s="213" t="n"/>
+      <c r="AQ34" s="213" t="n"/>
+      <c r="AR34" s="213" t="n"/>
+      <c r="AS34" s="213" t="n"/>
+      <c r="AT34" s="213" t="n"/>
+      <c r="AU34" s="213" t="n"/>
+      <c r="AV34" s="213" t="n"/>
+      <c r="AW34" s="213" t="n"/>
+      <c r="AX34" s="213" t="n"/>
+      <c r="AY34" s="213" t="n"/>
     </row>
     <row r="35" ht="48" customHeight="1">
       <c r="A35" s="221" t="inlineStr">
@@ -23105,7 +23165,7 @@
       <c r="W35" s="221" t="n"/>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="217" t="inlineStr">
+      <c r="A36" s="218" t="inlineStr">
         <is>
           <t>number of records</t>
         </is>
@@ -23115,7 +23175,7 @@
           <t>Size of the dataset in terms of the number of records</t>
         </is>
       </c>
-      <c r="C36" s="217" t="inlineStr">
+      <c r="C36" s="218" t="inlineStr">
         <is>
           <t>healthdcatap:numberOfRecords</t>
         </is>
@@ -23130,27 +23190,27 @@
           <t>Number of records inside a Dataset.</t>
         </is>
       </c>
-      <c r="F36" s="213" t="inlineStr">
+      <c r="F36" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G36" s="213" t="inlineStr">
+      <c r="G36" s="215" t="inlineStr">
         <is>
           <t>xsd:nonNegativeInteger</t>
         </is>
       </c>
-      <c r="H36" s="213" t="inlineStr">
+      <c r="H36" s="215" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I36" s="219" t="inlineStr">
+      <c r="I36" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J36" s="219" t="inlineStr">
+      <c r="J36" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -23160,7 +23220,7 @@
           <t>custom:number_of_records</t>
         </is>
       </c>
-      <c r="L36" s="219" t="n"/>
+      <c r="L36" s="213" t="n"/>
       <c r="P36" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -23171,9 +23231,9 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="U36" s="217" t="n"/>
-      <c r="V36" s="217" t="n"/>
-      <c r="W36" s="217" t="n"/>
+      <c r="U36" s="218" t="n"/>
+      <c r="V36" s="218" t="n"/>
+      <c r="W36" s="218" t="n"/>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="221" t="inlineStr">
@@ -23249,7 +23309,7 @@
       <c r="W37" s="221" t="n"/>
     </row>
     <row r="38" ht="64" customHeight="1">
-      <c r="A38" s="217" t="inlineStr">
+      <c r="A38" s="218" t="inlineStr">
         <is>
           <t>other identifier</t>
         </is>
@@ -23259,7 +23319,7 @@
           <t>Links a resource to an adms:Identifier class.</t>
         </is>
       </c>
-      <c r="C38" s="217" t="inlineStr">
+      <c r="C38" s="218" t="inlineStr">
         <is>
           <t>adms:identifier</t>
         </is>
@@ -23274,27 +23334,27 @@
           <t>Examples of secondary identifiers include MAST/ADS, DataCite, DOI, EZID or W3ID (if not used for the original identifier). This property makes use of another small class: adms:Identifier, where you provide the identifier and the name of the identifier schema (e.g. DOI).</t>
         </is>
       </c>
-      <c r="F38" s="213" t="inlineStr">
+      <c r="F38" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G38" s="213" t="inlineStr">
+      <c r="G38" s="215" t="inlineStr">
         <is>
           <t>adms:Identifier</t>
         </is>
       </c>
-      <c r="H38" s="213" t="inlineStr">
+      <c r="H38" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I38" s="219" t="inlineStr">
+      <c r="I38" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J38" s="219" t="inlineStr">
+      <c r="J38" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -23304,7 +23364,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="L38" s="219" t="n"/>
+      <c r="L38" s="213" t="n"/>
       <c r="O38" s="214" t="inlineStr">
         <is>
           <t>hri:IdentifierShape</t>
@@ -23320,9 +23380,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="U38" s="217" t="n"/>
-      <c r="V38" s="217" t="n"/>
-      <c r="W38" s="217" t="n"/>
+      <c r="U38" s="218" t="n"/>
+      <c r="V38" s="218" t="n"/>
+      <c r="W38" s="218" t="n"/>
     </row>
     <row r="39" ht="64" customHeight="1">
       <c r="A39" s="221" t="inlineStr">
@@ -23399,7 +23459,7 @@
       <c r="W39" s="221" t="n"/>
     </row>
     <row r="40" ht="59" customHeight="1">
-      <c r="A40" s="217" t="inlineStr">
+      <c r="A40" s="218" t="inlineStr">
         <is>
           <t>population coverage</t>
         </is>
@@ -23409,7 +23469,7 @@
           <t>A definition of the population within the dataset</t>
         </is>
       </c>
-      <c r="C40" s="217" t="inlineStr">
+      <c r="C40" s="218" t="inlineStr">
         <is>
           <t>healthdcatap:populationCoverage</t>
         </is>
@@ -23424,27 +23484,27 @@
           <t>This field is a free-text description of the population covered in the dataset. For example, "Adults aged 18–65 diagnosed with type 2 diabetes in the Netherlands between 2015 and 2020".</t>
         </is>
       </c>
-      <c r="F40" s="213" t="inlineStr">
+      <c r="F40" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G40" s="213" t="inlineStr">
+      <c r="G40" s="215" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H40" s="213" t="inlineStr">
+      <c r="H40" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I40" s="219" t="inlineStr">
+      <c r="I40" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J40" s="219" t="inlineStr">
+      <c r="J40" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -23454,7 +23514,7 @@
           <t>custom:populatiion_coverage</t>
         </is>
       </c>
-      <c r="L40" s="219" t="n"/>
+      <c r="L40" s="213" t="n"/>
       <c r="P40" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -23465,9 +23525,9 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="U40" s="217" t="n"/>
-      <c r="V40" s="217" t="n"/>
-      <c r="W40" s="217" t="n"/>
+      <c r="U40" s="218" t="n"/>
+      <c r="V40" s="218" t="n"/>
+      <c r="W40" s="218" t="n"/>
     </row>
     <row r="41" ht="92" customHeight="1">
       <c r="A41" s="221" t="inlineStr">
@@ -23496,7 +23556,7 @@
 This is where the collection-method statements not captured by dedicated properties can be listed.</t>
         </is>
       </c>
-      <c r="F41" s="213" t="inlineStr">
+      <c r="F41" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -23552,7 +23612,7 @@
       <c r="W41" s="221" t="n"/>
     </row>
     <row r="42" ht="112" customHeight="1">
-      <c r="A42" s="217" t="inlineStr">
+      <c r="A42" s="218" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
@@ -23562,7 +23622,7 @@
           <t>An entity responsible for making the resource available.</t>
         </is>
       </c>
-      <c r="C42" s="217" t="inlineStr">
+      <c r="C42" s="218" t="inlineStr">
         <is>
           <t>dct:publisher</t>
         </is>
@@ -23572,7 +23632,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E42" s="218" t="inlineStr">
+      <c r="E42" s="219" t="inlineStr">
         <is>
           <t>This property identifies the organisation or individual responsible for making the dataset available. For datasets, this is typically the employer of the data creators. In simple cases, the dataset publisher may be the same as the catalogue publisher. In more complex settings, such as when datasets come from multiple institutions within a consortium, the consortium should be listed as the publisher where possible. If no formal consortium can be specified, provide information about the contributing organisations or individuals under dct:creator instead. For more details, refer to the Agent class.</t>
         </is>
@@ -23587,15 +23647,15 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H42" s="213" t="n">
+      <c r="H42" s="215" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="219" t="inlineStr">
+      <c r="I42" s="213" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J42" s="219" t="inlineStr">
+      <c r="J42" s="213" t="inlineStr">
         <is>
           <t>Health and NL</t>
         </is>
@@ -23605,17 +23665,17 @@
           <t>custom:publisher</t>
         </is>
       </c>
-      <c r="L42" s="219" t="inlineStr">
+      <c r="L42" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="M42" s="219" t="inlineStr">
+      <c r="M42" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="N42" s="219" t="inlineStr">
+      <c r="N42" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -23635,9 +23695,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="U42" s="217" t="n"/>
-      <c r="V42" s="217" t="n"/>
-      <c r="W42" s="217" t="n"/>
+      <c r="U42" s="218" t="n"/>
+      <c r="V42" s="218" t="n"/>
+      <c r="W42" s="218" t="n"/>
     </row>
     <row r="43" ht="48" customHeight="1">
       <c r="A43" s="221" t="inlineStr">
@@ -23666,7 +23726,7 @@
 An example value could be dpv:ResearchAndDevelopment.</t>
         </is>
       </c>
-      <c r="F43" s="213" t="inlineStr">
+      <c r="F43" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -23714,7 +23774,7 @@
       <c r="W43" s="221" t="n"/>
     </row>
     <row r="44" ht="228" customHeight="1">
-      <c r="A44" s="217" t="inlineStr">
+      <c r="A44" s="218" t="inlineStr">
         <is>
           <t>qualified attribution</t>
         </is>
@@ -23753,33 +23813,33 @@
           <t>prov:Attribution</t>
         </is>
       </c>
-      <c r="H44" s="213" t="inlineStr">
+      <c r="H44" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I44" s="219" t="inlineStr">
+      <c r="I44" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J44" s="219" t="inlineStr">
+      <c r="J44" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K44" s="75" t="n"/>
-      <c r="L44" s="219" t="inlineStr">
+      <c r="L44" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Attribution' tab.</t>
         </is>
       </c>
-      <c r="M44" s="219" t="inlineStr">
+      <c r="M44" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Attribution' tab.</t>
         </is>
       </c>
-      <c r="N44" s="219" t="inlineStr">
+      <c r="N44" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'Attribution' tab.</t>
         </is>
@@ -23799,9 +23859,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="U44" s="217" t="n"/>
-      <c r="V44" s="217" t="n"/>
-      <c r="W44" s="217" t="n"/>
+      <c r="U44" s="218" t="n"/>
+      <c r="V44" s="218" t="n"/>
+      <c r="W44" s="218" t="n"/>
     </row>
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="221" t="inlineStr">
@@ -23829,7 +23889,7 @@
           <t>This property makes use of another small class (dcat:Relationship), in which you can indicate the related resource (via its identifier) and the nature of the relation (based on a controlled vocabulary, which is described in the information of the class).</t>
         </is>
       </c>
-      <c r="F45" s="213" t="inlineStr">
+      <c r="F45" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -23894,7 +23954,7 @@
       <c r="W45" s="221" t="n"/>
     </row>
     <row r="46" ht="48" customHeight="1">
-      <c r="A46" s="217" t="inlineStr">
+      <c r="A46" s="218" t="inlineStr">
         <is>
           <t>quality annotation</t>
         </is>
@@ -23904,7 +23964,7 @@
           <t>Refers to a quality annotation.</t>
         </is>
       </c>
-      <c r="C46" s="217" t="inlineStr">
+      <c r="C46" s="218" t="inlineStr">
         <is>
           <t>dqv:hasQualityAnnotation</t>
         </is>
@@ -23929,33 +23989,33 @@
           <t>dqv:QualityCertificate</t>
         </is>
       </c>
-      <c r="H46" s="213" t="inlineStr">
+      <c r="H46" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I46" s="219" t="inlineStr">
+      <c r="I46" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J46" s="219" t="inlineStr">
+      <c r="J46" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K46" s="75" t="n"/>
-      <c r="L46" s="219" t="inlineStr">
+      <c r="L46" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'QualityCertificate' tab.</t>
         </is>
       </c>
-      <c r="M46" s="219" t="inlineStr">
+      <c r="M46" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'QualityCertificate' tab.</t>
         </is>
       </c>
-      <c r="N46" s="219" t="inlineStr">
+      <c r="N46" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'QualityCertificate' tab.</t>
         </is>
@@ -23975,9 +24035,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="U46" s="217" t="n"/>
-      <c r="V46" s="217" t="n"/>
-      <c r="W46" s="217" t="n"/>
+      <c r="U46" s="218" t="n"/>
+      <c r="V46" s="218" t="n"/>
+      <c r="W46" s="218" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="221" t="inlineStr">
@@ -24005,7 +24065,7 @@
           <t>This property should point to the first known date of issuance, such as the publication date in a data repository. Example: 2023-12-10T13:16:10.246Z.</t>
         </is>
       </c>
-      <c r="F47" s="213" t="inlineStr">
+      <c r="F47" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -24058,7 +24118,7 @@
       <c r="W47" s="221" t="n"/>
     </row>
     <row r="48" ht="160" customHeight="1">
-      <c r="A48" s="217" t="inlineStr">
+      <c r="A48" s="218" t="inlineStr">
         <is>
           <t>retention period</t>
         </is>
@@ -24068,7 +24128,7 @@
           <t>A temporal period during which the dataset is available for secondary use.</t>
         </is>
       </c>
-      <c r="C48" s="217" t="inlineStr">
+      <c r="C48" s="218" t="inlineStr">
         <is>
           <t>healthdcatap:retentionPeriod</t>
         </is>
@@ -24097,17 +24157,17 @@
           <t>dct:PeriodOfTime</t>
         </is>
       </c>
-      <c r="H48" s="213" t="inlineStr">
+      <c r="H48" s="215" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I48" s="219" t="inlineStr">
+      <c r="I48" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J48" s="219" t="inlineStr">
+      <c r="J48" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -24117,17 +24177,17 @@
           <t>custom:retention_period</t>
         </is>
       </c>
-      <c r="L48" s="219" t="inlineStr">
+      <c r="L48" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="M48" s="219" t="inlineStr">
+      <c r="M48" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="N48" s="219" t="inlineStr">
+      <c r="N48" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
@@ -24147,9 +24207,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="U48" s="217" t="n"/>
-      <c r="V48" s="217" t="n"/>
-      <c r="W48" s="217" t="n"/>
+      <c r="U48" s="218" t="n"/>
+      <c r="V48" s="218" t="n"/>
+      <c r="W48" s="218" t="n"/>
     </row>
     <row r="49" ht="80" customHeight="1">
       <c r="A49" s="221" t="inlineStr">
@@ -24177,7 +24237,7 @@
           <t>This property makes use of the dcat:Distribution class to describe a sample distribution of the dataset, which can consist of anonymised or synthetic data, or a data dictionary provided in CSVW format. This is currently being further developed by the TEHDAS2 programme. More information can be found here: https://healthdcat-ap.github.io/#sample-distribution</t>
         </is>
       </c>
-      <c r="F49" s="213" t="inlineStr">
+      <c r="F49" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -24229,7 +24289,7 @@
       <c r="W49" s="221" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="217" t="inlineStr">
+      <c r="A50" s="218" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -24239,7 +24299,7 @@
           <t>A related resource from which the described resource is derived.</t>
         </is>
       </c>
-      <c r="C50" s="217" t="inlineStr">
+      <c r="C50" s="218" t="inlineStr">
         <is>
           <t>dct:source</t>
         </is>
@@ -24249,7 +24309,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E50" s="218" t="inlineStr">
+      <c r="E50" s="219" t="inlineStr">
         <is>
           <t>Indicate the dataset on which this described dataset is based.</t>
         </is>
@@ -24264,17 +24324,17 @@
           <t>dcat:Dataset (IRI)</t>
         </is>
       </c>
-      <c r="H50" s="213" t="inlineStr">
+      <c r="H50" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I50" s="219" t="inlineStr">
+      <c r="I50" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J50" s="219" t="inlineStr">
+      <c r="J50" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -24289,8 +24349,8 @@
           <t>If applicable, add the URI for the source dataset here.</t>
         </is>
       </c>
-      <c r="M50" s="219" t="n"/>
-      <c r="N50" s="219" t="n"/>
+      <c r="M50" s="213" t="n"/>
+      <c r="N50" s="213" t="n"/>
       <c r="P50" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -24301,9 +24361,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U50" s="217" t="n"/>
-      <c r="V50" s="217" t="n"/>
-      <c r="W50" s="217" t="n"/>
+      <c r="U50" s="218" t="n"/>
+      <c r="V50" s="218" t="n"/>
+      <c r="W50" s="218" t="n"/>
     </row>
     <row r="51" ht="64" customHeight="1">
       <c r="A51" s="221" t="inlineStr">
@@ -24332,7 +24392,7 @@
 For example: http://publications.europa.eu/resource/authority/dataset-status/COMPLETED</t>
         </is>
       </c>
-      <c r="F51" s="213" t="inlineStr">
+      <c r="F51" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -24380,7 +24440,7 @@
       <c r="W51" s="221" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="217" t="inlineStr">
+      <c r="A52" s="218" t="inlineStr">
         <is>
           <t>temporal coverage</t>
         </is>
@@ -24390,7 +24450,7 @@
           <t>Temporal characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C52" s="217" t="inlineStr">
+      <c r="C52" s="218" t="inlineStr">
         <is>
           <t>dct:temporal</t>
         </is>
@@ -24415,17 +24475,17 @@
           <t>dct:PeriodOfTime</t>
         </is>
       </c>
-      <c r="H52" s="213" t="inlineStr">
+      <c r="H52" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I52" s="219" t="inlineStr">
+      <c r="I52" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J52" s="219" t="inlineStr">
+      <c r="J52" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -24435,17 +24495,17 @@
           <t>custom:temporal_coverage</t>
         </is>
       </c>
-      <c r="L52" s="219" t="inlineStr">
+      <c r="L52" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="M52" s="219" t="inlineStr">
+      <c r="M52" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="N52" s="219" t="inlineStr">
+      <c r="N52" s="213" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
@@ -24465,9 +24525,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="U52" s="217" t="n"/>
-      <c r="V52" s="217" t="n"/>
-      <c r="W52" s="217" t="n"/>
+      <c r="U52" s="218" t="n"/>
+      <c r="V52" s="218" t="n"/>
+      <c r="W52" s="218" t="n"/>
     </row>
     <row r="53" ht="64" customHeight="1">
       <c r="A53" s="221" t="inlineStr">
@@ -24495,7 +24555,7 @@
           <t>If the dataset is a time-series, this should correspond to the spacing of items in the series. For other kinds of datasets, this property will usually indicate the smallest time difference between items in the dataset. The time period has to be provided in the xsd:duration format.</t>
         </is>
       </c>
-      <c r="F53" s="213" t="inlineStr">
+      <c r="F53" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -24543,7 +24603,7 @@
       <c r="W53" s="221" t="n"/>
     </row>
     <row r="54" ht="74.25" customHeight="1">
-      <c r="A54" s="217" t="inlineStr">
+      <c r="A54" s="218" t="inlineStr">
         <is>
           <t>theme</t>
         </is>
@@ -24553,7 +24613,7 @@
           <t>A main category of the resource. A resource can have multiple themes.</t>
         </is>
       </c>
-      <c r="C54" s="217" t="inlineStr">
+      <c r="C54" s="218" t="inlineStr">
         <is>
           <t>dcat:theme</t>
         </is>
@@ -24573,22 +24633,22 @@
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G54" s="213" t="inlineStr">
+      <c r="G54" s="215" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H54" s="213" t="inlineStr">
+      <c r="H54" s="215" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I54" s="219" t="inlineStr">
+      <c r="I54" s="213" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J54" s="219" t="inlineStr">
+      <c r="J54" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -24598,9 +24658,9 @@
           <t>custom:theme</t>
         </is>
       </c>
-      <c r="L54" s="219" t="n"/>
-      <c r="M54" s="219" t="n"/>
-      <c r="N54" s="219" t="n"/>
+      <c r="L54" s="213" t="n"/>
+      <c r="M54" s="213" t="n"/>
+      <c r="N54" s="213" t="n"/>
       <c r="P54" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -24616,9 +24676,9 @@
           <t>http://publications.europa.eu/resource/authority/data-theme/HEAL</t>
         </is>
       </c>
-      <c r="U54" s="217" t="n"/>
-      <c r="V54" s="217" t="n"/>
-      <c r="W54" s="217" t="n"/>
+      <c r="U54" s="218" t="n"/>
+      <c r="V54" s="218" t="n"/>
+      <c r="W54" s="218" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="221" t="inlineStr">
@@ -24646,7 +24706,7 @@
           <t>Provide a unique title for your Dataset, which can be repeated in multiple languages. Example: Healthy Brain Study - Physiological Data</t>
         </is>
       </c>
-      <c r="F55" s="213" t="inlineStr">
+      <c r="F55" s="215" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -24697,7 +24757,7 @@
       <c r="W55" s="221" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="217" t="inlineStr">
+      <c r="A56" s="218" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -24707,7 +24767,7 @@
           <t>The nature or genre of the resource.</t>
         </is>
       </c>
-      <c r="C56" s="217" t="inlineStr">
+      <c r="C56" s="218" t="inlineStr">
         <is>
           <t>dct:type</t>
         </is>
@@ -24728,22 +24788,22 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G56" s="213" t="inlineStr">
+      <c r="G56" s="215" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H56" s="213" t="inlineStr">
+      <c r="H56" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I56" s="219" t="inlineStr">
+      <c r="I56" s="213" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J56" s="219" t="inlineStr">
+      <c r="J56" s="213" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -24753,9 +24813,9 @@
           <t>custom:dcat_type</t>
         </is>
       </c>
-      <c r="L56" s="219" t="n"/>
-      <c r="M56" s="219" t="n"/>
-      <c r="N56" s="219" t="n"/>
+      <c r="L56" s="213" t="n"/>
+      <c r="M56" s="213" t="n"/>
+      <c r="N56" s="213" t="n"/>
       <c r="O56" s="84" t="n"/>
       <c r="P56" s="214" t="inlineStr">
         <is>
@@ -24769,9 +24829,9 @@
       </c>
       <c r="R56" s="84" t="n"/>
       <c r="T56" s="84" t="n"/>
-      <c r="U56" s="217" t="n"/>
-      <c r="V56" s="217" t="n"/>
-      <c r="W56" s="217" t="n"/>
+      <c r="U56" s="218" t="n"/>
+      <c r="V56" s="218" t="n"/>
+      <c r="W56" s="218" t="n"/>
     </row>
     <row r="57" ht="80" customHeight="1">
       <c r="A57" s="221" t="inlineStr">
@@ -24861,7 +24921,7 @@
       <c r="W57" s="221" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="217" t="inlineStr">
+      <c r="A58" s="218" t="inlineStr">
         <is>
           <t>version</t>
         </is>
@@ -24871,7 +24931,7 @@
           <t>The version indicator (name or identifier) of a resource.</t>
         </is>
       </c>
-      <c r="C58" s="217" t="inlineStr">
+      <c r="C58" s="218" t="inlineStr">
         <is>
           <t>dcat:version</t>
         </is>
@@ -24886,27 +24946,27 @@
           <t>Suggested practice: track major_version.minor_version. Register a new identifier for major changes (e.g., 1.0.0 for an unchanged dataset).</t>
         </is>
       </c>
-      <c r="F58" s="213" t="inlineStr">
+      <c r="F58" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G58" s="213" t="inlineStr">
+      <c r="G58" s="215" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H58" s="213" t="inlineStr">
+      <c r="H58" s="215" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I58" s="219" t="inlineStr">
+      <c r="I58" s="213" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J58" s="219" t="inlineStr">
+      <c r="J58" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -24916,9 +24976,9 @@
           <t>custom:version</t>
         </is>
       </c>
-      <c r="L58" s="219" t="n"/>
-      <c r="M58" s="219" t="n"/>
-      <c r="N58" s="219" t="n"/>
+      <c r="L58" s="213" t="n"/>
+      <c r="M58" s="213" t="n"/>
+      <c r="N58" s="213" t="n"/>
       <c r="P58" s="214" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24930,9 +24990,9 @@
         </is>
       </c>
       <c r="S58" s="84" t="n"/>
-      <c r="U58" s="217" t="n"/>
-      <c r="V58" s="217" t="n"/>
-      <c r="W58" s="217" t="n"/>
+      <c r="U58" s="218" t="n"/>
+      <c r="V58" s="218" t="n"/>
+      <c r="W58" s="218" t="n"/>
     </row>
     <row r="59" ht="32" customHeight="1">
       <c r="A59" s="221" t="inlineStr">
@@ -25011,7 +25071,7 @@
       <c r="W59" s="221" t="n"/>
     </row>
     <row r="60" ht="84.75" customHeight="1">
-      <c r="A60" s="217" t="inlineStr">
+      <c r="A60" s="218" t="inlineStr">
         <is>
           <t>was generated by</t>
         </is>
@@ -25021,7 +25081,7 @@
           <t>Generation is the completion of production of a new entity by an activity. This entity did not exist before generation and becomes available for usage after this generation.</t>
         </is>
       </c>
-      <c r="C60" s="217" t="inlineStr">
+      <c r="C60" s="218" t="inlineStr">
         <is>
           <t>prov:wasGeneratedBy</t>
         </is>
@@ -25031,7 +25091,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="F60" s="213" t="inlineStr">
+      <c r="F60" s="215" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25041,25 +25101,25 @@
           <t>prov:Activity</t>
         </is>
       </c>
-      <c r="H60" s="213" t="inlineStr">
+      <c r="H60" s="215" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I60" s="219" t="inlineStr">
+      <c r="I60" s="213" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J60" s="219" t="inlineStr">
+      <c r="J60" s="213" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K60" s="75" t="n"/>
-      <c r="L60" s="219" t="n"/>
-      <c r="M60" s="219" t="n"/>
-      <c r="N60" s="219" t="n"/>
+      <c r="L60" s="213" t="n"/>
+      <c r="M60" s="213" t="n"/>
+      <c r="N60" s="213" t="n"/>
       <c r="P60" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -25070,9 +25130,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U60" s="217" t="n"/>
-      <c r="V60" s="217" t="n"/>
-      <c r="W60" s="217" t="n"/>
+      <c r="U60" s="218" t="n"/>
+      <c r="V60" s="218" t="n"/>
+      <c r="W60" s="218" t="n"/>
     </row>
     <row r="61" customFormat="1" s="84">
       <c r="A61" s="110" t="n"/>
@@ -25463,7 +25523,7 @@
       </c>
       <c r="J2" s="125" t="n"/>
       <c r="K2" s="126" t="n"/>
-      <c r="L2" s="219" t="n"/>
+      <c r="L2" s="213" t="n"/>
       <c r="X2" s="102" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -25624,7 +25684,7 @@
           <t>_id</t>
         </is>
       </c>
-      <c r="L4" s="219" t="n"/>
+      <c r="L4" s="213" t="n"/>
       <c r="X4" s="102" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -25632,7 +25692,7 @@
       </c>
       <c r="Y4" s="102" t="inlineStr">
         <is>
-          <t>dash:TextAreaEditor</t>
+          <t>dash:TextFieldEditor</t>
         </is>
       </c>
       <c r="AC4" s="45" t="n"/>
@@ -25712,7 +25772,7 @@
       </c>
       <c r="Y5" s="102" t="inlineStr">
         <is>
-          <t>dash:TextAreaEditor</t>
+          <t>dash:TextFieldEditor</t>
         </is>
       </c>
       <c r="AB5" s="102" t="b">
@@ -25728,7 +25788,7 @@
           <t>publisher note</t>
         </is>
       </c>
-      <c r="B6" s="215" t="inlineStr">
+      <c r="B6" s="216" t="inlineStr">
         <is>
           <t>A description of the publisher's activities.</t>
         </is>
@@ -25743,7 +25803,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E6" s="215" t="inlineStr">
+      <c r="E6" s="216" t="inlineStr">
         <is>
           <t>Note: This property will be deprecated in the next major release.
 This property can be repeated for parallel language versions of the publisher notes. Example: "Sciensano is a research institute and the national public health institute of Belgium. It is a so-called federal scientific institution that operates under the authority of the federal minister of Public Health and the federal minister of Agriculture of Belgium."@en</t>
@@ -25775,7 +25835,7 @@
         </is>
       </c>
       <c r="K6" s="126" t="n"/>
-      <c r="L6" s="219" t="n"/>
+      <c r="L6" s="213" t="n"/>
       <c r="X6" s="102" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -25926,7 +25986,7 @@
           <t>_type</t>
         </is>
       </c>
-      <c r="L8" s="219" t="n"/>
+      <c r="L8" s="213" t="n"/>
       <c r="X8" s="102" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -27218,7 +27278,7 @@
       </c>
       <c r="T4" s="102" t="inlineStr">
         <is>
-          <t>dash:TextAreaEditor</t>
+          <t>dash:TextFieldEditor</t>
         </is>
       </c>
       <c r="X4" s="45" t="n"/>

--- a/Documents/Health-RI_v2.1.0-for-FDP.xlsx
+++ b/Documents/Health-RI_v2.1.0-for-FDP.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20" yWindow="-28180" windowWidth="34380" windowHeight="28200" tabRatio="600" firstSheet="8" activeTab="11" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20" yWindow="-28200" windowWidth="34380" windowHeight="28200" tabRatio="600" firstSheet="8" activeTab="20" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" state="visible" r:id="rId1"/>
@@ -1053,13 +1053,10 @@
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1072,6 +1069,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -4899,7 +4899,7 @@
           <t>This property links the distribution class to the corresponding data service(s).</t>
         </is>
       </c>
-      <c r="F2" s="215" t="inlineStr">
+      <c r="F2" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -4919,7 +4919,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J2" s="213" t="inlineStr">
+      <c r="J2" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -4955,7 +4955,7 @@
       <c r="V2" s="221" t="n"/>
     </row>
     <row r="3" ht="64" customHeight="1">
-      <c r="A3" s="218" t="inlineStr">
+      <c r="A3" s="217" t="inlineStr">
         <is>
           <t>access URL</t>
         </is>
@@ -4965,7 +4965,7 @@
           <t>A URL of the resource that gives access to a distribution of the dataset. E.g., landing page, feed, SPARQL endpoint.</t>
         </is>
       </c>
-      <c r="C3" s="218" t="inlineStr">
+      <c r="C3" s="217" t="inlineStr">
         <is>
           <t>dcat:accessURL</t>
         </is>
@@ -4975,7 +4975,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E3" s="219" t="inlineStr">
+      <c r="E3" s="218" t="inlineStr">
         <is>
           <t>Add a link that points to where the dataset can be found. If it’s hosted in a Data Repository, include the link to its entry. For datasets not in a repository (like registries), but still available for secondary use, provide a link to an access request form or a webpage with instructions for accessing the data.</t>
         </is>
@@ -4985,7 +4985,7 @@
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G3" s="215" t="inlineStr">
+      <c r="G3" s="213" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
@@ -4993,12 +4993,12 @@
       <c r="H3" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="213" t="inlineStr">
+      <c r="I3" s="219" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J3" s="213" t="inlineStr">
+      <c r="J3" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -5008,8 +5008,8 @@
           <t>resource:access_url</t>
         </is>
       </c>
-      <c r="L3" s="213" t="n"/>
-      <c r="M3" s="213" t="n"/>
+      <c r="L3" s="219" t="n"/>
+      <c r="M3" s="219" t="n"/>
       <c r="O3" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -5021,9 +5021,9 @@
         </is>
       </c>
       <c r="S3" s="121" t="n"/>
-      <c r="T3" s="218" t="n"/>
-      <c r="U3" s="218" t="n"/>
-      <c r="V3" s="218" t="n"/>
+      <c r="T3" s="217" t="n"/>
+      <c r="U3" s="217" t="n"/>
+      <c r="V3" s="217" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="221" t="inlineStr">
@@ -5051,7 +5051,7 @@
           <t>The legislation that mandates the creation or management of the Distribution.</t>
         </is>
       </c>
-      <c r="F4" s="215" t="inlineStr">
+      <c r="F4" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -5071,7 +5071,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="213" t="inlineStr">
+      <c r="J4" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -5109,7 +5109,7 @@
           <t>An indication of how long it is planned to keep the Distribution of the Dataset available.</t>
         </is>
       </c>
-      <c r="C5" s="218" t="inlineStr">
+      <c r="C5" s="217" t="inlineStr">
         <is>
           <t>dcatap:availability</t>
         </is>
@@ -5124,12 +5124,12 @@
           <t>To indicate the planned availability of the Distribution, the EU planned-availability controlled vocabulary MUST be used.</t>
         </is>
       </c>
-      <c r="F5" s="215" t="inlineStr">
+      <c r="F5" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G5" s="215" t="inlineStr">
+      <c r="G5" s="213" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
@@ -5139,19 +5139,19 @@
           <t>0..1</t>
         </is>
       </c>
-      <c r="I5" s="213" t="inlineStr">
+      <c r="I5" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="213" t="inlineStr">
+      <c r="J5" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K5" s="69" t="n"/>
-      <c r="L5" s="213" t="n"/>
-      <c r="M5" s="213" t="n"/>
+      <c r="L5" s="219" t="n"/>
+      <c r="M5" s="219" t="n"/>
       <c r="O5" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -5213,7 +5213,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="213" t="inlineStr">
+      <c r="J6" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5241,7 +5241,7 @@
       <c r="V6" s="221" t="n"/>
     </row>
     <row r="7" ht="64" customHeight="1">
-      <c r="A7" s="218" t="inlineStr">
+      <c r="A7" s="217" t="inlineStr">
         <is>
           <t>checksum</t>
         </is>
@@ -5251,7 +5251,7 @@
           <t>The checksum property provides a mechanism that can be used to verify that the contents of a file or package have not changed.</t>
         </is>
       </c>
-      <c r="C7" s="218" t="inlineStr">
+      <c r="C7" s="217" t="inlineStr">
         <is>
           <t>spdx:checksum</t>
         </is>
@@ -5266,7 +5266,7 @@
           <t>The checksum is related to the downloadURL. This property makes use of the spdx:Checksum class, which itself has two properties to indicate the checksum algorithm and checksum value (see Checksum class for further details).</t>
         </is>
       </c>
-      <c r="F7" s="215" t="inlineStr">
+      <c r="F7" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -5276,17 +5276,17 @@
           <t>spdx:Checksum</t>
         </is>
       </c>
-      <c r="H7" s="215" t="inlineStr">
+      <c r="H7" s="213" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I7" s="213" t="inlineStr">
+      <c r="I7" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J7" s="213" t="inlineStr">
+      <c r="J7" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5296,12 +5296,12 @@
           <t>resource:hash_algorithm/resource:hash_algorithm</t>
         </is>
       </c>
-      <c r="L7" s="213" t="inlineStr">
+      <c r="L7" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Checksum' tab.</t>
         </is>
       </c>
-      <c r="M7" s="213" t="inlineStr">
+      <c r="M7" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Checksum' tab.</t>
         </is>
@@ -5322,9 +5322,9 @@
         </is>
       </c>
       <c r="S7" s="121" t="n"/>
-      <c r="T7" s="218" t="n"/>
-      <c r="U7" s="218" t="n"/>
-      <c r="V7" s="218" t="n"/>
+      <c r="T7" s="217" t="n"/>
+      <c r="U7" s="217" t="n"/>
+      <c r="V7" s="217" t="n"/>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="221" t="inlineStr">
@@ -5372,7 +5372,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="213" t="inlineStr">
+      <c r="J8" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5400,7 +5400,7 @@
       <c r="V8" s="221" t="n"/>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="218" t="inlineStr">
+      <c r="A9" s="217" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -5410,7 +5410,7 @@
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C9" s="218" t="inlineStr">
+      <c r="C9" s="217" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -5425,27 +5425,27 @@
           <t>Provide specific details about the distribution here, complementing the description of the related Dataset. This field can be repeated for different language versions of the description.</t>
         </is>
       </c>
-      <c r="F9" s="215" t="inlineStr">
+      <c r="F9" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G9" s="215" t="inlineStr">
+      <c r="G9" s="213" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H9" s="215" t="inlineStr">
+      <c r="H9" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I9" s="213" t="inlineStr">
+      <c r="I9" s="219" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J9" s="213" t="inlineStr">
+      <c r="J9" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5455,8 +5455,8 @@
           <t>resource:description</t>
         </is>
       </c>
-      <c r="L9" s="213" t="n"/>
-      <c r="M9" s="213" t="n"/>
+      <c r="L9" s="219" t="n"/>
+      <c r="M9" s="219" t="n"/>
       <c r="O9" s="203" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -5470,9 +5470,9 @@
       <c r="S9" s="121" t="b">
         <v>1</v>
       </c>
-      <c r="T9" s="218" t="n"/>
-      <c r="U9" s="218" t="n"/>
-      <c r="V9" s="218" t="n"/>
+      <c r="T9" s="217" t="n"/>
+      <c r="U9" s="217" t="n"/>
+      <c r="V9" s="217" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="221" t="inlineStr">
@@ -5520,7 +5520,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J10" s="213" t="inlineStr">
+      <c r="J10" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5548,7 +5548,7 @@
       <c r="V10" s="221" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="218" t="inlineStr">
+      <c r="A11" s="217" t="inlineStr">
         <is>
           <t>download URL</t>
         </is>
@@ -5573,27 +5573,27 @@
           <t>If the dataset is openly accessible and available in a repository, you can directly include a link to the downloadable file here.</t>
         </is>
       </c>
-      <c r="F11" s="215" t="inlineStr">
+      <c r="F11" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G11" s="215" t="inlineStr">
+      <c r="G11" s="213" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
       </c>
-      <c r="H11" s="215" t="inlineStr">
+      <c r="H11" s="213" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I11" s="213" t="inlineStr">
+      <c r="I11" s="219" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J11" s="213" t="inlineStr">
+      <c r="J11" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -5603,8 +5603,8 @@
           <t>resource:download_url</t>
         </is>
       </c>
-      <c r="L11" s="213" t="n"/>
-      <c r="M11" s="213" t="n"/>
+      <c r="L11" s="219" t="n"/>
+      <c r="M11" s="219" t="n"/>
       <c r="O11" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -5616,9 +5616,9 @@
         </is>
       </c>
       <c r="S11" s="121" t="n"/>
-      <c r="T11" s="218" t="n"/>
-      <c r="U11" s="218" t="n"/>
-      <c r="V11" s="218" t="n"/>
+      <c r="T11" s="217" t="n"/>
+      <c r="U11" s="217" t="n"/>
+      <c r="V11" s="217" t="n"/>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="221" t="inlineStr">
@@ -5666,7 +5666,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J12" s="213" t="inlineStr">
+      <c r="J12" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5694,7 +5694,7 @@
       <c r="V12" s="221" t="n"/>
     </row>
     <row r="13" ht="99" customHeight="1">
-      <c r="A13" s="218" t="inlineStr">
+      <c r="A13" s="217" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -5704,7 +5704,7 @@
           <t>A language of the resource.</t>
         </is>
       </c>
-      <c r="C13" s="218" t="inlineStr">
+      <c r="C13" s="217" t="inlineStr">
         <is>
           <t>dct:language</t>
         </is>
@@ -5714,33 +5714,33 @@
           <t>http://publications.europa.eu/resource/authority/language</t>
         </is>
       </c>
-      <c r="E13" s="219" t="inlineStr">
+      <c r="E13" s="218" t="inlineStr">
         <is>
           <t>Indicates the natural language used in the Distribution, using a value from the EU controlled vocabulary. Not all distributions might have a language, for example imaging data.
 Note that here the Health-RI model diverges from DCAT-AP NL, which allows a maximum of 1 language per Distribution. The Health-RI model allows multiple languages in the same Distribution.</t>
         </is>
       </c>
-      <c r="F13" s="215" t="inlineStr">
+      <c r="F13" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G13" s="215" t="inlineStr">
+      <c r="G13" s="213" t="inlineStr">
         <is>
           <t>dct:LinguisticSystem (IRI)</t>
         </is>
       </c>
-      <c r="H13" s="215" t="inlineStr">
+      <c r="H13" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I13" s="213" t="inlineStr">
+      <c r="I13" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J13" s="213" t="inlineStr">
+      <c r="J13" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5750,8 +5750,8 @@
           <t>resource:language</t>
         </is>
       </c>
-      <c r="L13" s="213" t="n"/>
-      <c r="M13" s="213" t="n"/>
+      <c r="L13" s="219" t="n"/>
+      <c r="M13" s="219" t="n"/>
       <c r="O13" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -5763,9 +5763,9 @@
         </is>
       </c>
       <c r="S13" s="121" t="n"/>
-      <c r="T13" s="218" t="n"/>
-      <c r="U13" s="218" t="n"/>
-      <c r="V13" s="218" t="n"/>
+      <c r="T13" s="217" t="n"/>
+      <c r="U13" s="217" t="n"/>
+      <c r="V13" s="217" t="n"/>
     </row>
     <row r="14" ht="80" customHeight="1">
       <c r="A14" s="221" t="inlineStr">
@@ -5811,7 +5811,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J14" s="213" t="inlineStr">
+      <c r="J14" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -5839,7 +5839,7 @@
       <c r="V14" s="221" t="n"/>
     </row>
     <row r="15" ht="80" customHeight="1">
-      <c r="A15" s="218" t="inlineStr">
+      <c r="A15" s="217" t="inlineStr">
         <is>
           <t>linked schemas</t>
         </is>
@@ -5849,7 +5849,7 @@
           <t>An established standard to which the described resource conforms.</t>
         </is>
       </c>
-      <c r="C15" s="218" t="inlineStr">
+      <c r="C15" s="217" t="inlineStr">
         <is>
           <t>dct:conformsTo</t>
         </is>
@@ -5864,27 +5864,27 @@
           <t xml:space="preserve">This property SHOULD be used to indicate the model, schema, ontology, view or profile that this representation of a dataset conforms to, in a machine-readable form. This is (generally) a complementary concern to the media-type or format. Use a reference to the official publication of the respective schema. </t>
         </is>
       </c>
-      <c r="F15" s="215" t="inlineStr">
+      <c r="F15" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G15" s="215" t="inlineStr">
+      <c r="G15" s="213" t="inlineStr">
         <is>
           <t>dct:Standard (IRI)</t>
         </is>
       </c>
-      <c r="H15" s="215" t="inlineStr">
+      <c r="H15" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I15" s="213" t="inlineStr">
+      <c r="I15" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J15" s="213" t="inlineStr">
+      <c r="J15" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5894,8 +5894,8 @@
           <t>resource:conforms_to</t>
         </is>
       </c>
-      <c r="L15" s="213" t="n"/>
-      <c r="M15" s="213" t="n"/>
+      <c r="L15" s="219" t="n"/>
+      <c r="M15" s="219" t="n"/>
       <c r="O15" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -5907,9 +5907,9 @@
         </is>
       </c>
       <c r="S15" s="121" t="n"/>
-      <c r="T15" s="218" t="n"/>
-      <c r="U15" s="218" t="n"/>
-      <c r="V15" s="218" t="n"/>
+      <c r="T15" s="217" t="n"/>
+      <c r="U15" s="217" t="n"/>
+      <c r="V15" s="217" t="n"/>
     </row>
     <row r="16" ht="112" customHeight="1">
       <c r="A16" s="221" t="inlineStr">
@@ -5959,7 +5959,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J16" s="213" t="inlineStr">
+      <c r="J16" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -5987,7 +5987,7 @@
       <c r="V16" s="221" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="218" t="inlineStr">
+      <c r="A17" s="217" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
@@ -6008,27 +6008,27 @@
         </is>
       </c>
       <c r="E17" s="98" t="n"/>
-      <c r="F17" s="215" t="inlineStr">
+      <c r="F17" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G17" s="215" t="inlineStr">
+      <c r="G17" s="213" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H17" s="215" t="inlineStr">
+      <c r="H17" s="213" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I17" s="213" t="inlineStr">
+      <c r="I17" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J17" s="213" t="inlineStr">
+      <c r="J17" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6038,8 +6038,8 @@
           <t>resource:modified</t>
         </is>
       </c>
-      <c r="L17" s="213" t="n"/>
-      <c r="M17" s="213" t="n"/>
+      <c r="L17" s="219" t="n"/>
+      <c r="M17" s="219" t="n"/>
       <c r="N17" s="214" t="n"/>
       <c r="O17" s="214" t="inlineStr">
         <is>
@@ -6057,9 +6057,9 @@
         </is>
       </c>
       <c r="S17" s="69" t="n"/>
-      <c r="T17" s="218" t="n"/>
-      <c r="U17" s="218" t="n"/>
-      <c r="V17" s="218" t="n"/>
+      <c r="T17" s="217" t="n"/>
+      <c r="U17" s="217" t="n"/>
+      <c r="V17" s="217" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="221" t="inlineStr">
@@ -6107,7 +6107,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J18" s="213" t="inlineStr">
+      <c r="J18" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6135,7 +6135,7 @@
       <c r="V18" s="221" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="218" t="inlineStr">
+      <c r="A19" s="217" t="inlineStr">
         <is>
           <t>release date</t>
         </is>
@@ -6145,7 +6145,7 @@
           <t>Date of formal issuance of the resource.</t>
         </is>
       </c>
-      <c r="C19" s="218" t="inlineStr">
+      <c r="C19" s="217" t="inlineStr">
         <is>
           <t>dct:issued</t>
         </is>
@@ -6160,27 +6160,27 @@
           <t>The date the dataset distribution was issued.</t>
         </is>
       </c>
-      <c r="F19" s="215" t="inlineStr">
+      <c r="F19" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G19" s="215" t="inlineStr">
+      <c r="G19" s="213" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H19" s="215" t="inlineStr">
+      <c r="H19" s="213" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I19" s="213" t="inlineStr">
+      <c r="I19" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J19" s="213" t="inlineStr">
+      <c r="J19" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6190,8 +6190,8 @@
           <t>resource:issued</t>
         </is>
       </c>
-      <c r="L19" s="213" t="n"/>
-      <c r="M19" s="213" t="n"/>
+      <c r="L19" s="219" t="n"/>
+      <c r="M19" s="219" t="n"/>
       <c r="N19" s="214" t="n"/>
       <c r="O19" s="214" t="inlineStr">
         <is>
@@ -6209,9 +6209,9 @@
         </is>
       </c>
       <c r="S19" s="69" t="n"/>
-      <c r="T19" s="218" t="n"/>
-      <c r="U19" s="218" t="n"/>
-      <c r="V19" s="218" t="n"/>
+      <c r="T19" s="217" t="n"/>
+      <c r="U19" s="217" t="n"/>
+      <c r="V19" s="217" t="n"/>
     </row>
     <row r="20" ht="231" customHeight="1">
       <c r="A20" s="221" t="inlineStr">
@@ -6260,7 +6260,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J20" s="213" t="inlineStr">
+      <c r="J20" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -6297,7 +6297,7 @@
       <c r="V20" s="221" t="n"/>
     </row>
     <row r="21" ht="112" customHeight="1">
-      <c r="A21" s="218" t="inlineStr">
+      <c r="A21" s="217" t="inlineStr">
         <is>
           <t>rights</t>
         </is>
@@ -6307,7 +6307,7 @@
           <t>Information about rights held in and over the resource.</t>
         </is>
       </c>
-      <c r="C21" s="218" t="inlineStr">
+      <c r="C21" s="217" t="inlineStr">
         <is>
           <t>dct:rights</t>
         </is>
@@ -6328,7 +6328,7 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G21" s="215" t="inlineStr">
+      <c r="G21" s="213" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
@@ -6338,12 +6338,12 @@
           <t>0..1</t>
         </is>
       </c>
-      <c r="I21" s="213" t="inlineStr">
+      <c r="I21" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J21" s="213" t="inlineStr">
+      <c r="J21" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6353,8 +6353,8 @@
           <t>resource:rights</t>
         </is>
       </c>
-      <c r="L21" s="213" t="n"/>
-      <c r="M21" s="213" t="n"/>
+      <c r="L21" s="219" t="n"/>
+      <c r="M21" s="219" t="n"/>
       <c r="O21" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -6366,9 +6366,9 @@
         </is>
       </c>
       <c r="S21" s="121" t="n"/>
-      <c r="T21" s="218" t="n"/>
-      <c r="U21" s="218" t="n"/>
-      <c r="V21" s="218" t="n"/>
+      <c r="T21" s="217" t="n"/>
+      <c r="U21" s="217" t="n"/>
+      <c r="V21" s="217" t="n"/>
     </row>
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="221" t="inlineStr">
@@ -6417,7 +6417,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="213" t="inlineStr">
+      <c r="J22" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6445,7 +6445,7 @@
       <c r="V22" s="221" t="n"/>
     </row>
     <row r="23" ht="64" customHeight="1">
-      <c r="A23" s="218" t="inlineStr">
+      <c r="A23" s="217" t="inlineStr">
         <is>
           <t>temporal resolution</t>
         </is>
@@ -6455,7 +6455,7 @@
           <t>Minimum time period resolvable in the dataset.</t>
         </is>
       </c>
-      <c r="C23" s="218" t="inlineStr">
+      <c r="C23" s="217" t="inlineStr">
         <is>
           <t>dcat:temporalResolution</t>
         </is>
@@ -6470,34 +6470,34 @@
           <t>If applicable, this property indicates the minimum time period resolvable in the dataset distribution, expressed in xsd:duration format (for more information, see: https://www.w3schools.com/xml/schema_dtypes_date.asp).</t>
         </is>
       </c>
-      <c r="F23" s="215" t="inlineStr">
+      <c r="F23" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G23" s="215" t="inlineStr">
+      <c r="G23" s="213" t="inlineStr">
         <is>
           <t>xsd:duration</t>
         </is>
       </c>
-      <c r="H23" s="215" t="inlineStr">
+      <c r="H23" s="213" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I23" s="213" t="inlineStr">
+      <c r="I23" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J23" s="213" t="inlineStr">
+      <c r="J23" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K23" s="74" t="n"/>
-      <c r="L23" s="213" t="n"/>
-      <c r="M23" s="213" t="n"/>
+      <c r="L23" s="219" t="n"/>
+      <c r="M23" s="219" t="n"/>
       <c r="O23" s="203" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -6509,9 +6509,9 @@
         </is>
       </c>
       <c r="S23" s="121" t="n"/>
-      <c r="T23" s="218" t="n"/>
-      <c r="U23" s="218" t="n"/>
-      <c r="V23" s="218" t="n"/>
+      <c r="T23" s="217" t="n"/>
+      <c r="U23" s="217" t="n"/>
+      <c r="V23" s="217" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="221" t="inlineStr">
@@ -6559,7 +6559,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J24" s="213" t="inlineStr">
+      <c r="J24" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7119,11 +7119,11 @@
   <dimension ref="A1:U55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col width="22.5" customWidth="1" style="217" min="1" max="1"/>
-    <col width="43.5" bestFit="1" customWidth="1" style="217" min="2" max="2"/>
-    <col width="26.5" customWidth="1" style="217" min="3" max="3"/>
+    <col width="22.5" customWidth="1" style="216" min="1" max="1"/>
+    <col width="43.5" bestFit="1" customWidth="1" style="216" min="2" max="2"/>
+    <col width="26.5" customWidth="1" style="216" min="3" max="3"/>
     <col width="24" customWidth="1" style="223" min="4" max="4"/>
-    <col width="76.5" customWidth="1" style="217" min="5" max="5"/>
+    <col width="76.5" customWidth="1" style="216" min="5" max="5"/>
     <col width="16.5" bestFit="1" customWidth="1" style="214" min="6" max="6"/>
     <col width="20.1640625" bestFit="1" customWidth="1" style="214" min="7" max="7"/>
     <col width="11.83203125" customWidth="1" style="214" min="8" max="8"/>
@@ -7270,7 +7270,7 @@
           <t>The legislation that mandates the creation or management of the Dataset Series.</t>
         </is>
       </c>
-      <c r="F2" s="215" t="inlineStr">
+      <c r="F2" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -7290,7 +7290,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="213" t="inlineStr">
+      <c r="J2" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7316,7 +7316,7 @@
       <c r="U2" s="155" t="n"/>
     </row>
     <row r="3" ht="64" customHeight="1">
-      <c r="A3" s="218" t="inlineStr">
+      <c r="A3" s="217" t="inlineStr">
         <is>
           <t>contact point</t>
         </is>
@@ -7326,7 +7326,7 @@
           <t>Relevant contact information for the catalogued resource.</t>
         </is>
       </c>
-      <c r="C3" s="218" t="inlineStr">
+      <c r="C3" s="217" t="inlineStr">
         <is>
           <t>dcat:contactPoint</t>
         </is>
@@ -7342,7 +7342,7 @@
 Whenever possible, use general contact information (for example, from a department) instead of the contact information of an individual.</t>
         </is>
       </c>
-      <c r="F3" s="215" t="inlineStr">
+      <c r="F3" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -7352,17 +7352,17 @@
           <t>vcard:Kind</t>
         </is>
       </c>
-      <c r="H3" s="215" t="inlineStr">
+      <c r="H3" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I3" s="213" t="inlineStr">
+      <c r="I3" s="219" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J3" s="213" t="inlineStr">
+      <c r="J3" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7372,7 +7372,7 @@
           <t>data_series::contact</t>
         </is>
       </c>
-      <c r="L3" s="213" t="inlineStr">
+      <c r="L3" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
@@ -7392,9 +7392,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S3" s="218" t="n"/>
-      <c r="T3" s="218" t="n"/>
-      <c r="U3" s="218" t="n"/>
+      <c r="S3" s="217" t="n"/>
+      <c r="T3" s="217" t="n"/>
+      <c r="U3" s="217" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="221" t="inlineStr">
@@ -7442,7 +7442,7 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J4" s="213" t="inlineStr">
+      <c r="J4" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7471,7 +7471,7 @@
       <c r="U4" s="221" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="218" t="inlineStr">
+      <c r="A5" s="217" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
@@ -7481,7 +7481,7 @@
           <t>The frequency with which items are added to a collection.</t>
         </is>
       </c>
-      <c r="C5" s="218" t="inlineStr">
+      <c r="C5" s="217" t="inlineStr">
         <is>
           <t>dct:accrualPeriodicity</t>
         </is>
@@ -7496,33 +7496,33 @@
           <t>The frequency of a dataset series is not equal to the frequency of the dataset in the collection.</t>
         </is>
       </c>
-      <c r="F5" s="215" t="inlineStr">
+      <c r="F5" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G5" s="215" t="inlineStr">
+      <c r="G5" s="213" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H5" s="215" t="inlineStr">
+      <c r="H5" s="213" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I5" s="213" t="inlineStr">
+      <c r="I5" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="213" t="inlineStr">
+      <c r="J5" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K5" s="74" t="n"/>
-      <c r="L5" s="213" t="n"/>
+      <c r="L5" s="219" t="n"/>
       <c r="N5" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -7533,9 +7533,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S5" s="218" t="n"/>
-      <c r="T5" s="218" t="n"/>
-      <c r="U5" s="218" t="n"/>
+      <c r="S5" s="217" t="n"/>
+      <c r="T5" s="217" t="n"/>
+      <c r="U5" s="217" t="n"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="221" t="inlineStr">
@@ -7583,7 +7583,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="213" t="inlineStr">
+      <c r="J6" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -7637,7 +7637,7 @@
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="218" t="inlineStr">
+      <c r="A11" s="217" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
@@ -7647,7 +7647,7 @@
           <t>Date on which the resource was changed.</t>
         </is>
       </c>
-      <c r="C11" s="218" t="inlineStr">
+      <c r="C11" s="217" t="inlineStr">
         <is>
           <t>dct:modified</t>
         </is>
@@ -7662,27 +7662,27 @@
           <t>This is not equal to the most recently modified dataset in the collection of the dataset series.</t>
         </is>
       </c>
-      <c r="F11" s="215" t="inlineStr">
+      <c r="F11" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G11" s="215" t="inlineStr">
+      <c r="G11" s="213" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H11" s="215" t="inlineStr">
+      <c r="H11" s="213" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I11" s="213" t="inlineStr">
+      <c r="I11" s="219" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J11" s="213" t="inlineStr">
+      <c r="J11" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7692,7 +7692,7 @@
           <t>data_series::modified</t>
         </is>
       </c>
-      <c r="L11" s="213" t="n"/>
+      <c r="L11" s="219" t="n"/>
       <c r="N11" s="214" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -7708,9 +7708,9 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="S11" s="218" t="n"/>
-      <c r="T11" s="218" t="n"/>
-      <c r="U11" s="218" t="n"/>
+      <c r="S11" s="217" t="n"/>
+      <c r="T11" s="217" t="n"/>
+      <c r="U11" s="217" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="221" t="inlineStr">
@@ -7738,7 +7738,7 @@
           <t xml:space="preserve">The publisher of the dataset series may not be the publisher of all datasets. For example, a digital archive could take over the publishing of older datasets in the series. </t>
         </is>
       </c>
-      <c r="F12" s="215" t="inlineStr">
+      <c r="F12" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -7758,7 +7758,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J12" s="213" t="inlineStr">
+      <c r="J12" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7793,7 +7793,7 @@
       <c r="U12" s="221" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="218" t="inlineStr">
+      <c r="A13" s="217" t="inlineStr">
         <is>
           <t>release date</t>
         </is>
@@ -7803,7 +7803,7 @@
           <t>Date of formal issuance of the resource.</t>
         </is>
       </c>
-      <c r="C13" s="218" t="inlineStr">
+      <c r="C13" s="217" t="inlineStr">
         <is>
           <t>dct:issued</t>
         </is>
@@ -7823,22 +7823,22 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G13" s="215" t="inlineStr">
+      <c r="G13" s="213" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H13" s="215" t="inlineStr">
+      <c r="H13" s="213" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I13" s="215" t="inlineStr">
+      <c r="I13" s="213" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J13" s="213" t="inlineStr">
+      <c r="J13" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7848,7 +7848,7 @@
           <t>data_series:issued</t>
         </is>
       </c>
-      <c r="L13" s="213" t="n"/>
+      <c r="L13" s="219" t="n"/>
       <c r="N13" s="214" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -7864,9 +7864,9 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="S13" s="218" t="n"/>
-      <c r="T13" s="218" t="n"/>
-      <c r="U13" s="218" t="n"/>
+      <c r="S13" s="217" t="n"/>
+      <c r="T13" s="217" t="n"/>
+      <c r="U13" s="217" t="n"/>
     </row>
     <row r="14" ht="49" customHeight="1">
       <c r="A14" s="221" t="inlineStr">
@@ -7894,7 +7894,7 @@
           <t>When temporal coverage is a dimension in the dataset series, the temporal coverage of each dataset in the collection should be part of the series' temporal coverage. In that case, an open-ended value is recommended, e.g. after 2012.</t>
         </is>
       </c>
-      <c r="F14" s="215" t="inlineStr">
+      <c r="F14" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -7914,7 +7914,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="213" t="inlineStr">
+      <c r="J14" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7949,17 +7949,17 @@
       <c r="U14" s="221" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="218" t="inlineStr">
+      <c r="A15" s="217" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B15" s="218" t="inlineStr">
+      <c r="B15" s="217" t="inlineStr">
         <is>
           <t>A name given to the resource.</t>
         </is>
       </c>
-      <c r="C15" s="218" t="inlineStr">
+      <c r="C15" s="217" t="inlineStr">
         <is>
           <t>dct:title</t>
         </is>
@@ -7969,7 +7969,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E15" s="218" t="inlineStr">
+      <c r="E15" s="217" t="inlineStr">
         <is>
           <t xml:space="preserve">Provide a unique title for your Dataset Series, which can be repeated in multiple languages. </t>
         </is>
@@ -7979,22 +7979,22 @@
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G15" s="215" t="inlineStr">
+      <c r="G15" s="213" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H15" s="215" t="inlineStr">
+      <c r="H15" s="213" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I15" s="215" t="inlineStr">
+      <c r="I15" s="213" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J15" s="213" t="inlineStr">
+      <c r="J15" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -8004,7 +8004,7 @@
           <t>title</t>
         </is>
       </c>
-      <c r="L15" s="213" t="n"/>
+      <c r="L15" s="219" t="n"/>
       <c r="N15" s="214" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -8018,9 +8018,9 @@
       <c r="R15" s="214" t="b">
         <v>1</v>
       </c>
-      <c r="S15" s="218" t="n"/>
-      <c r="T15" s="218" t="n"/>
-      <c r="U15" s="218" t="n"/>
+      <c r="S15" s="217" t="n"/>
+      <c r="T15" s="217" t="n"/>
+      <c r="U15" s="217" t="n"/>
     </row>
     <row r="16">
       <c r="K16" s="214" t="n"/>
@@ -8145,16 +8145,16 @@
   </sheetData>
   <autoFilter ref="A1:L15"/>
   <mergeCells count="11">
+    <mergeCell ref="J6:J10"/>
+    <mergeCell ref="G6:G10"/>
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="F6:F10"/>
+    <mergeCell ref="C6:C10"/>
+    <mergeCell ref="H6:H10"/>
+    <mergeCell ref="E6:E10"/>
+    <mergeCell ref="L6:L10"/>
     <mergeCell ref="K6:K10"/>
-    <mergeCell ref="H6:H10"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="E6:E10"/>
-    <mergeCell ref="C6:C10"/>
-    <mergeCell ref="I6:I10"/>
-    <mergeCell ref="G6:G10"/>
-    <mergeCell ref="L6:L10"/>
-    <mergeCell ref="J6:J10"/>
-    <mergeCell ref="F6:F10"/>
     <mergeCell ref="A6:A10"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F6 F11:F15">
@@ -8399,7 +8399,7 @@
           <t>Information about who can access the resource or an indication of its security status.</t>
         </is>
       </c>
-      <c r="C2" s="218" t="inlineStr">
+      <c r="C2" s="217" t="inlineStr">
         <is>
           <t>dct:accessRights</t>
         </is>
@@ -8414,30 +8414,30 @@
           <t>Information that indicates whether the Dataset is publicly accessible, has access restrictions or is not public. This property must take one of the predefined values listed in the Access Rights Named Authority List provided by the Publications Office. This designation informs data users whether the dataset is considered open data or is classified as non-public. For example, for non-public data, use the value: http://publications.europa.eu/resource/authority/access-right/NON_PUBLIC</t>
         </is>
       </c>
-      <c r="F2" s="215" t="inlineStr">
+      <c r="F2" s="213" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G2" s="215" t="inlineStr">
+      <c r="G2" s="213" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
       </c>
-      <c r="H2" s="215" t="n">
+      <c r="H2" s="213" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="213" t="inlineStr">
+      <c r="I2" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="213" t="inlineStr">
+      <c r="J2" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K2" s="213" t="inlineStr">
+      <c r="K2" s="219" t="inlineStr">
         <is>
           <t>access_service:access_rights</t>
         </is>
@@ -8499,7 +8499,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J3" s="213" t="inlineStr">
+      <c r="J3" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -8521,7 +8521,7 @@
       <c r="U3" s="221" t="n"/>
     </row>
     <row r="4" ht="92.25" customHeight="1">
-      <c r="A4" s="218" t="inlineStr">
+      <c r="A4" s="217" t="inlineStr">
         <is>
           <t>application profile</t>
         </is>
@@ -8531,7 +8531,7 @@
           <t>An established standard to which the described resource conforms.</t>
         </is>
       </c>
-      <c r="C4" s="218" t="inlineStr">
+      <c r="C4" s="217" t="inlineStr">
         <is>
           <t>dct:conformsTo</t>
         </is>
@@ -8546,33 +8546,33 @@
           <t>The standards referred to here SHOULD describe the Data Service and not the data it serves. The latter is provided by the dataset with which this Data Service is connected. For instance, the data service adheres to the OGC WFS API standard, while the associated dataset adheres to the INSPIRE Address data model.</t>
         </is>
       </c>
-      <c r="F4" s="215" t="inlineStr">
+      <c r="F4" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G4" s="215" t="inlineStr">
+      <c r="G4" s="213" t="inlineStr">
         <is>
           <t>dct:Standard (IRI)</t>
         </is>
       </c>
-      <c r="H4" s="215" t="inlineStr">
+      <c r="H4" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I4" s="213" t="inlineStr">
+      <c r="I4" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="213" t="inlineStr">
+      <c r="J4" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K4" s="213" t="n"/>
-      <c r="L4" s="213" t="n"/>
+      <c r="K4" s="219" t="n"/>
+      <c r="L4" s="219" t="n"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -8583,9 +8583,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S4" s="218" t="n"/>
-      <c r="T4" s="218" t="n"/>
-      <c r="U4" s="218" t="n"/>
+      <c r="S4" s="217" t="n"/>
+      <c r="T4" s="217" t="n"/>
+      <c r="U4" s="217" t="n"/>
     </row>
     <row r="5" ht="64" customHeight="1">
       <c r="A5" s="155" t="inlineStr">
@@ -8632,7 +8632,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="213" t="inlineStr">
+      <c r="J5" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -8663,7 +8663,7 @@
       <c r="U5" s="155" t="n"/>
     </row>
     <row r="6" ht="160" customHeight="1">
-      <c r="A6" s="218" t="inlineStr">
+      <c r="A6" s="217" t="inlineStr">
         <is>
           <t>creator</t>
         </is>
@@ -8673,7 +8673,7 @@
           <t>An entity responsible for making the resource.</t>
         </is>
       </c>
-      <c r="C6" s="218" t="inlineStr">
+      <c r="C6" s="217" t="inlineStr">
         <is>
           <t>dct:creator</t>
         </is>
@@ -8690,7 +8690,7 @@
 Note that the Health-RI model diverges from DCAT-AP NL here, which reduces the maximum number of creators to 1. The Health-RI model allows the specification of multiple creators of a catalogue.</t>
         </is>
       </c>
-      <c r="F6" s="215" t="inlineStr">
+      <c r="F6" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -8700,23 +8700,23 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H6" s="215" t="inlineStr">
+      <c r="H6" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I6" s="213" t="inlineStr">
+      <c r="I6" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="213" t="inlineStr">
+      <c r="J6" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K6" s="75" t="n"/>
-      <c r="L6" s="213" t="inlineStr">
+      <c r="L6" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -8736,9 +8736,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S6" s="218" t="n"/>
-      <c r="T6" s="218" t="n"/>
-      <c r="U6" s="218" t="n"/>
+      <c r="S6" s="217" t="n"/>
+      <c r="T6" s="217" t="n"/>
+      <c r="U6" s="217" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="221" t="inlineStr">
@@ -8782,12 +8782,12 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J7" s="213" t="inlineStr">
+      <c r="J7" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K7" s="213" t="n"/>
+      <c r="K7" s="219" t="n"/>
       <c r="L7" s="220" t="n"/>
       <c r="N7" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C8" s="218" t="inlineStr">
+      <c r="C8" s="217" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -8829,43 +8829,43 @@
           <t>Briefly describe the data service provided. You can repeat this description in multiple languages. Example: A data service that provides API access to real-time electrocardiogram (ECG) monitoring data for clinical research applications.</t>
         </is>
       </c>
-      <c r="F8" s="215" t="inlineStr">
+      <c r="F8" s="213" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G8" s="215" t="inlineStr">
+      <c r="G8" s="213" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H8" s="215" t="inlineStr">
+      <c r="H8" s="213" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I8" s="213" t="inlineStr">
+      <c r="I8" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="213" t="inlineStr">
+      <c r="J8" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K8" s="213" t="inlineStr">
+      <c r="K8" s="219" t="inlineStr">
         <is>
           <t>access_service:description</t>
         </is>
       </c>
-      <c r="L8" s="213" t="n"/>
-      <c r="N8" s="213" t="inlineStr">
+      <c r="L8" s="219" t="n"/>
+      <c r="N8" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O8" s="213" t="inlineStr">
+      <c r="O8" s="219" t="inlineStr">
         <is>
           <t>dash:TextAreaEditor</t>
         </is>
@@ -8921,7 +8921,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J9" s="213" t="inlineStr">
+      <c r="J9" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -8947,7 +8947,7 @@
       <c r="U9" s="221" t="n"/>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="218" t="inlineStr">
+      <c r="A10" s="217" t="inlineStr">
         <is>
           <t>endpoint URL</t>
         </is>
@@ -8957,7 +8957,7 @@
           <t>The root location or primary endpoint of the service (a Web-resolvable IRI).</t>
         </is>
       </c>
-      <c r="C10" s="218" t="inlineStr">
+      <c r="C10" s="217" t="inlineStr">
         <is>
           <t>dcat:endpointURL</t>
         </is>
@@ -8972,12 +8972,12 @@
           <t>Provide the URL of the endpoint that users can interact with to access the data service. This should be a direct link to the service's endpoint, such as an API URL, SPARQL endpoint, or similar.</t>
         </is>
       </c>
-      <c r="F10" s="215" t="inlineStr">
+      <c r="F10" s="213" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G10" s="215" t="inlineStr">
+      <c r="G10" s="213" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
@@ -8985,12 +8985,12 @@
       <c r="H10" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="213" t="inlineStr">
+      <c r="I10" s="219" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J10" s="213" t="inlineStr">
+      <c r="J10" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -9000,7 +9000,7 @@
           <t>access_service:endpoint_url</t>
         </is>
       </c>
-      <c r="L10" s="213" t="n"/>
+      <c r="L10" s="219" t="n"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -9011,9 +9011,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S10" s="218" t="n"/>
-      <c r="T10" s="218" t="n"/>
-      <c r="U10" s="218" t="n"/>
+      <c r="S10" s="217" t="n"/>
+      <c r="T10" s="217" t="n"/>
+      <c r="U10" s="217" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="221" t="inlineStr">
@@ -9057,12 +9057,12 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J11" s="213" t="inlineStr">
+      <c r="J11" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K11" s="213" t="n"/>
+      <c r="K11" s="219" t="n"/>
       <c r="L11" s="220" t="n"/>
       <c r="N11" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
       <c r="U11" s="221" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="218" t="inlineStr">
+      <c r="A12" s="217" t="inlineStr">
         <is>
           <t>HVD Category</t>
         </is>
@@ -9089,7 +9089,7 @@
           <t>A data category defined in the High Value Dataset Implementing Regulation.</t>
         </is>
       </c>
-      <c r="C12" s="218" t="inlineStr">
+      <c r="C12" s="217" t="inlineStr">
         <is>
           <t>dcatap:hvdCategory</t>
         </is>
@@ -9100,33 +9100,33 @@
         </is>
       </c>
       <c r="E12" s="98" t="n"/>
-      <c r="F12" s="215" t="inlineStr">
+      <c r="F12" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G12" s="215" t="inlineStr">
+      <c r="G12" s="213" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H12" s="215" t="inlineStr">
+      <c r="H12" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I12" s="213" t="inlineStr">
+      <c r="I12" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J12" s="213" t="inlineStr">
+      <c r="J12" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K12" s="75" t="n"/>
-      <c r="L12" s="213" t="n"/>
+      <c r="L12" s="219" t="n"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -9137,9 +9137,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S12" s="218" t="n"/>
-      <c r="T12" s="218" t="n"/>
-      <c r="U12" s="218" t="n"/>
+      <c r="S12" s="217" t="n"/>
+      <c r="T12" s="217" t="n"/>
+      <c r="U12" s="217" t="n"/>
     </row>
     <row r="13" ht="64" customHeight="1">
       <c r="A13" s="155" t="inlineStr">
@@ -9185,19 +9185,19 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J13" s="213" t="inlineStr">
+      <c r="J13" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K13" s="75" t="n"/>
       <c r="L13" s="220" t="n"/>
-      <c r="N13" s="213" t="inlineStr">
+      <c r="N13" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O13" s="213" t="inlineStr">
+      <c r="O13" s="219" t="inlineStr">
         <is>
           <t>dash:TextFieldEditor</t>
         </is>
@@ -9207,7 +9207,7 @@
       <c r="U13" s="155" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="218" t="inlineStr">
+      <c r="A14" s="217" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -9217,7 +9217,7 @@
           <t>A keyword or tag describing the resource.</t>
         </is>
       </c>
-      <c r="C14" s="218" t="inlineStr">
+      <c r="C14" s="217" t="inlineStr">
         <is>
           <t>dcat:keyword</t>
         </is>
@@ -9228,46 +9228,46 @@
         </is>
       </c>
       <c r="E14" s="29" t="n"/>
-      <c r="F14" s="215" t="inlineStr">
+      <c r="F14" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G14" s="215" t="inlineStr">
+      <c r="G14" s="213" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H14" s="215" t="inlineStr">
+      <c r="H14" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I14" s="213" t="inlineStr">
+      <c r="I14" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="213" t="inlineStr">
+      <c r="J14" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K14" s="75" t="n"/>
-      <c r="L14" s="213" t="n"/>
-      <c r="N14" s="213" t="inlineStr">
+      <c r="L14" s="219" t="n"/>
+      <c r="N14" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O14" s="213" t="inlineStr">
+      <c r="O14" s="219" t="inlineStr">
         <is>
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="S14" s="218" t="n"/>
-      <c r="T14" s="218" t="n"/>
-      <c r="U14" s="218" t="n"/>
+      <c r="S14" s="217" t="n"/>
+      <c r="T14" s="217" t="n"/>
+      <c r="U14" s="217" t="n"/>
     </row>
     <row r="15" ht="64" customHeight="1">
       <c r="A15" s="221" t="inlineStr">
@@ -9315,7 +9315,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J15" s="213" t="inlineStr">
+      <c r="J15" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9337,7 +9337,7 @@
       <c r="U15" s="221" t="n"/>
     </row>
     <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="218" t="inlineStr">
+      <c r="A16" s="217" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -9347,7 +9347,7 @@
           <t>A language of the resource.</t>
         </is>
       </c>
-      <c r="C16" s="218" t="inlineStr">
+      <c r="C16" s="217" t="inlineStr">
         <is>
           <t>dct:language</t>
         </is>
@@ -9362,33 +9362,33 @@
           <t>Indicates the natural language used in the data service, indicated with a value from the EU controlled vocabulary.</t>
         </is>
       </c>
-      <c r="F16" s="215" t="inlineStr">
+      <c r="F16" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G16" s="215" t="inlineStr">
+      <c r="G16" s="213" t="inlineStr">
         <is>
           <t>dct:LinguisticSystem (IRI)</t>
         </is>
       </c>
-      <c r="H16" s="215" t="inlineStr">
+      <c r="H16" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I16" s="213" t="inlineStr">
+      <c r="I16" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J16" s="213" t="inlineStr">
+      <c r="J16" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K16" s="75" t="n"/>
-      <c r="L16" s="213" t="n"/>
+      <c r="L16" s="219" t="n"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -9399,9 +9399,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S16" s="218" t="n"/>
-      <c r="T16" s="218" t="n"/>
-      <c r="U16" s="218" t="n"/>
+      <c r="S16" s="217" t="n"/>
+      <c r="T16" s="217" t="n"/>
+      <c r="U16" s="217" t="n"/>
     </row>
     <row r="17" ht="64" customHeight="1">
       <c r="A17" s="221" t="inlineStr">
@@ -9447,12 +9447,12 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J17" s="213" t="inlineStr">
+      <c r="J17" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K17" s="213" t="inlineStr">
+      <c r="K17" s="219" t="inlineStr">
         <is>
           <t>access_service:license</t>
         </is>
@@ -9473,7 +9473,7 @@
       <c r="U17" s="221" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="218" t="inlineStr">
+      <c r="A18" s="217" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
@@ -9483,7 +9483,7 @@
           <t>Date on which the resource was changed.</t>
         </is>
       </c>
-      <c r="C18" s="218" t="inlineStr">
+      <c r="C18" s="217" t="inlineStr">
         <is>
           <t>dct:modified</t>
         </is>
@@ -9498,33 +9498,33 @@
           <t>This property indicates the date of the last changes to the dataset, not the metadata record. An absent value may mean the resource hasn't changed since publication, the modification date is unknown, or the resource is continuously updated.</t>
         </is>
       </c>
-      <c r="F18" s="215" t="inlineStr">
+      <c r="F18" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G18" s="215" t="inlineStr">
+      <c r="G18" s="213" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H18" s="215" t="inlineStr">
+      <c r="H18" s="213" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I18" s="213" t="inlineStr">
+      <c r="I18" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J18" s="213" t="inlineStr">
+      <c r="J18" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K18" s="75" t="n"/>
-      <c r="L18" s="213" t="n"/>
+      <c r="L18" s="219" t="n"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -9540,9 +9540,9 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="S18" s="218" t="n"/>
-      <c r="T18" s="218" t="n"/>
-      <c r="U18" s="218" t="n"/>
+      <c r="S18" s="217" t="n"/>
+      <c r="T18" s="217" t="n"/>
+      <c r="U18" s="217" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="221" t="inlineStr">
@@ -9586,7 +9586,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J19" s="213" t="inlineStr">
+      <c r="J19" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -9617,7 +9617,7 @@
       <c r="U19" s="221" t="n"/>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="218" t="inlineStr">
+      <c r="A20" s="217" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
@@ -9627,7 +9627,7 @@
           <t>An entity responsible for making the resource available.</t>
         </is>
       </c>
-      <c r="C20" s="218" t="inlineStr">
+      <c r="C20" s="217" t="inlineStr">
         <is>
           <t>dct:publisher</t>
         </is>
@@ -9642,7 +9642,7 @@
           <t>The organisation or individual responsible for making the data service available. In the context of data services, the publisher is typically the organisation that manages or provides access to the service. For details, see the class Agent.</t>
         </is>
       </c>
-      <c r="F20" s="215" t="inlineStr">
+      <c r="F20" s="213" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -9652,21 +9652,21 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H20" s="215" t="n">
+      <c r="H20" s="213" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="213" t="inlineStr">
+      <c r="I20" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J20" s="213" t="inlineStr">
+      <c r="J20" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K20" s="213" t="n"/>
-      <c r="L20" s="213" t="inlineStr">
+      <c r="K20" s="219" t="n"/>
+      <c r="L20" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -9686,9 +9686,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S20" s="218" t="n"/>
-      <c r="T20" s="218" t="n"/>
-      <c r="U20" s="218" t="n"/>
+      <c r="S20" s="217" t="n"/>
+      <c r="T20" s="217" t="n"/>
+      <c r="U20" s="217" t="n"/>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="221" t="inlineStr">
@@ -9736,12 +9736,12 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J21" s="213" t="inlineStr">
+      <c r="J21" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K21" s="213" t="inlineStr">
+      <c r="K21" s="219" t="inlineStr">
         <is>
           <t>access_service:serves_dataset</t>
         </is>
@@ -9766,7 +9766,7 @@
       <c r="U21" s="221" t="n"/>
     </row>
     <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="218" t="inlineStr">
+      <c r="A22" s="217" t="inlineStr">
         <is>
           <t>theme</t>
         </is>
@@ -9776,7 +9776,7 @@
           <t>A main category of the resource. A resource can have multiple themes.</t>
         </is>
       </c>
-      <c r="C22" s="218" t="inlineStr">
+      <c r="C22" s="217" t="inlineStr">
         <is>
           <t>dcat:theme</t>
         </is>
@@ -9791,33 +9791,33 @@
           <t>This property should use a controlled vocabulary. In the Health Data Catalogue, most data services will use NAL:data-theme 'HEAL', but additional values from the same vocabulary are allowed.</t>
         </is>
       </c>
-      <c r="F22" s="215" t="inlineStr">
+      <c r="F22" s="213" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G22" s="215" t="inlineStr">
+      <c r="G22" s="213" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H22" s="215" t="inlineStr">
+      <c r="H22" s="213" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I22" s="213" t="inlineStr">
+      <c r="I22" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="213" t="inlineStr">
+      <c r="J22" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K22" s="75" t="n"/>
-      <c r="L22" s="213" t="n"/>
+      <c r="L22" s="219" t="n"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -9833,9 +9833,9 @@
           <t>http://publications.europa.eu/resource/authority/data-theme/HEAL</t>
         </is>
       </c>
-      <c r="S22" s="218" t="n"/>
-      <c r="T22" s="218" t="n"/>
-      <c r="U22" s="218" t="n"/>
+      <c r="S22" s="217" t="n"/>
+      <c r="T22" s="217" t="n"/>
+      <c r="U22" s="217" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="221" t="inlineStr">
@@ -9883,7 +9883,7 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J23" s="213" t="inlineStr">
+      <c r="J23" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9894,12 +9894,12 @@
         </is>
       </c>
       <c r="L23" s="159" t="n"/>
-      <c r="N23" s="213" t="inlineStr">
+      <c r="N23" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O23" s="213" t="inlineStr">
+      <c r="O23" s="219" t="inlineStr">
         <is>
           <t>dash:TextFieldEditor</t>
         </is>
@@ -15057,15 +15057,70 @@
       <c r="V2" s="31" t="n"/>
       <c r="W2" s="31" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="13" t="n"/>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="4" t="n"/>
+    <row r="3" ht="56" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Table group title.</t>
+        </is>
+      </c>
+      <c r="C3" s="41" t="inlineStr">
+        <is>
+          <t>dct:title</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Used to provide a human-readable title for the table group. Can appear in multiple languages.</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>rdfs:Literal</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>1..n</t>
+        </is>
+      </c>
+      <c r="I3" s="229" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="J3" s="229" t="inlineStr">
+        <is>
+          <t>HealthDCAT-AP</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>dash:LiteralViewer</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>dash:TextFieldEditor</t>
+        </is>
+      </c>
+      <c r="T3" s="229" t="b">
+        <v>1</v>
+      </c>
       <c r="U3" s="13" t="n"/>
       <c r="V3" s="13" t="n"/>
       <c r="W3" s="13" t="n"/>
@@ -19022,11 +19077,11 @@
   <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col width="20" bestFit="1" customWidth="1" style="217" min="1" max="1"/>
-    <col width="40.5" customWidth="1" style="217" min="2" max="2"/>
-    <col width="25.5" bestFit="1" customWidth="1" style="217" min="3" max="3"/>
+    <col width="20" bestFit="1" customWidth="1" style="216" min="1" max="1"/>
+    <col width="40.5" customWidth="1" style="216" min="2" max="2"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="216" min="3" max="3"/>
     <col width="25.5" customWidth="1" style="223" min="4" max="4"/>
-    <col width="54.5" customWidth="1" style="217" min="5" max="5"/>
+    <col width="54.5" customWidth="1" style="216" min="5" max="5"/>
     <col width="22.1640625" customWidth="1" style="214" min="6" max="6"/>
     <col width="24" bestFit="1" customWidth="1" style="214" min="7" max="7"/>
     <col width="10.5" bestFit="1" customWidth="1" style="214" min="8" max="8"/>
@@ -19175,12 +19230,12 @@
         </is>
       </c>
       <c r="E2" s="98" t="n"/>
-      <c r="F2" s="215" t="inlineStr">
+      <c r="F2" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G2" s="215" t="inlineStr">
+      <c r="G2" s="213" t="inlineStr">
         <is>
           <t>eli:LegalResource (IRI)</t>
         </is>
@@ -19190,12 +19245,12 @@
           <t>0..n</t>
         </is>
       </c>
-      <c r="I2" s="213" t="inlineStr">
+      <c r="I2" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="213" t="inlineStr">
+      <c r="J2" s="219" t="inlineStr">
         <is>
           <t>Health and NL</t>
         </is>
@@ -19205,8 +19260,8 @@
           <t>custom:applicable_legislation</t>
         </is>
       </c>
-      <c r="L2" s="213" t="n"/>
-      <c r="M2" s="213" t="n"/>
+      <c r="L2" s="219" t="n"/>
+      <c r="M2" s="219" t="n"/>
       <c r="O2" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -19268,7 +19323,7 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J3" s="213" t="inlineStr">
+      <c r="J3" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -19306,7 +19361,7 @@
           <t>Relevant contact information for the catalogued resource.</t>
         </is>
       </c>
-      <c r="C4" s="218" t="inlineStr">
+      <c r="C4" s="217" t="inlineStr">
         <is>
           <t>dcat:contactPoint</t>
         </is>
@@ -19322,7 +19377,7 @@
 Whenever possible, use general contact information (for example, from a department) instead of the contact information of an individual.</t>
         </is>
       </c>
-      <c r="F4" s="215" t="inlineStr">
+      <c r="F4" s="213" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -19332,30 +19387,30 @@
           <t>vcard:Kind</t>
         </is>
       </c>
-      <c r="H4" s="215" t="n">
+      <c r="H4" s="213" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="213" t="inlineStr">
+      <c r="I4" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="213" t="inlineStr">
+      <c r="J4" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K4" s="213" t="inlineStr">
+      <c r="K4" s="219" t="inlineStr">
         <is>
           <t>custom:contact</t>
         </is>
       </c>
-      <c r="L4" s="213" t="inlineStr">
+      <c r="L4" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
       </c>
-      <c r="M4" s="213" t="inlineStr">
+      <c r="M4" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
@@ -19428,7 +19483,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="213" t="n"/>
+      <c r="J5" s="219" t="n"/>
       <c r="K5" s="227" t="inlineStr">
         <is>
           <t>custom:creator</t>
@@ -19465,7 +19520,7 @@
       <c r="V5" s="221" t="n"/>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="218" t="inlineStr">
+      <c r="A6" s="217" t="inlineStr">
         <is>
           <t>dataset</t>
         </is>
@@ -19475,7 +19530,7 @@
           <t>A dataset that is listed in the catalogue.</t>
         </is>
       </c>
-      <c r="C6" s="218" t="inlineStr">
+      <c r="C6" s="217" t="inlineStr">
         <is>
           <t>dcat:dataset</t>
         </is>
@@ -19490,7 +19545,7 @@
           <t>Each catalogue contains one or more datasets. This property serves to link datasets to a catalogue. Therefore, a dataset is always contained inside a catalogue.</t>
         </is>
       </c>
-      <c r="F6" s="215" t="inlineStr">
+      <c r="F6" s="213" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -19505,12 +19560,12 @@
           <t>0..n</t>
         </is>
       </c>
-      <c r="I6" s="213" t="inlineStr">
+      <c r="I6" s="219" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J6" s="213" t="inlineStr">
+      <c r="J6" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -19521,7 +19576,7 @@
           <t>Add URI to all datasets contained in this catalogue</t>
         </is>
       </c>
-      <c r="M6" s="213" t="n"/>
+      <c r="M6" s="219" t="n"/>
       <c r="O6" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -19533,9 +19588,9 @@
         </is>
       </c>
       <c r="S6" s="69" t="n"/>
-      <c r="T6" s="218" t="n"/>
-      <c r="U6" s="218" t="n"/>
-      <c r="V6" s="218" t="n"/>
+      <c r="T6" s="217" t="n"/>
+      <c r="U6" s="217" t="n"/>
+      <c r="V6" s="217" t="n"/>
     </row>
     <row r="7" ht="29" customHeight="1">
       <c r="A7" s="221" t="inlineStr">
@@ -19583,7 +19638,7 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J7" s="213" t="inlineStr">
+      <c r="J7" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -19613,17 +19668,17 @@
       <c r="V7" s="221" t="n"/>
     </row>
     <row r="8" ht="29" customHeight="1">
-      <c r="A8" s="218" t="inlineStr">
+      <c r="A8" s="217" t="inlineStr">
         <is>
           <t>geographical coverage</t>
         </is>
       </c>
-      <c r="B8" s="216" t="inlineStr">
+      <c r="B8" s="215" t="inlineStr">
         <is>
           <t>Spatial characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C8" s="218" t="inlineStr">
+      <c r="C8" s="217" t="inlineStr">
         <is>
           <t>dct:spatial</t>
         </is>
@@ -19633,39 +19688,39 @@
           <t>EU Vocabularies Continents Named Authority List</t>
         </is>
       </c>
-      <c r="E8" s="219" t="inlineStr">
+      <c r="E8" s="218" t="inlineStr">
         <is>
           <t>The EU Vocabularies Named Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, GeoNames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocabulary can be used.</t>
         </is>
       </c>
-      <c r="F8" s="215" t="inlineStr">
+      <c r="F8" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G8" s="215" t="inlineStr">
+      <c r="G8" s="213" t="inlineStr">
         <is>
           <t>dct:Location (IRI)</t>
         </is>
       </c>
-      <c r="H8" s="215" t="inlineStr">
+      <c r="H8" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I8" s="213" t="inlineStr">
+      <c r="I8" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="213" t="inlineStr">
+      <c r="J8" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K8" s="103" t="n"/>
-      <c r="L8" s="213" t="n"/>
-      <c r="M8" s="213" t="n"/>
+      <c r="L8" s="219" t="n"/>
+      <c r="M8" s="219" t="n"/>
       <c r="O8" s="214" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -19677,9 +19732,9 @@
         </is>
       </c>
       <c r="S8" s="69" t="n"/>
-      <c r="T8" s="218" t="n"/>
-      <c r="U8" s="218" t="n"/>
-      <c r="V8" s="218" t="n"/>
+      <c r="T8" s="217" t="n"/>
+      <c r="U8" s="217" t="n"/>
+      <c r="V8" s="217" t="n"/>
     </row>
     <row r="9" ht="29" customHeight="1">
       <c r="D9" s="177" t="inlineStr">
@@ -19764,7 +19819,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J13" s="213" t="inlineStr">
+      <c r="J13" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -19792,7 +19847,7 @@
       <c r="V13" s="221" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="218" t="inlineStr">
+      <c r="A14" s="217" t="inlineStr">
         <is>
           <t>home page</t>
         </is>
@@ -19802,7 +19857,7 @@
           <t>A homepage for some thing.</t>
         </is>
       </c>
-      <c r="C14" s="218" t="inlineStr">
+      <c r="C14" s="217" t="inlineStr">
         <is>
           <t>foaf:homepage</t>
         </is>
@@ -19817,34 +19872,34 @@
           <t>The home page of the catalogue, if available.</t>
         </is>
       </c>
-      <c r="F14" s="215" t="inlineStr">
+      <c r="F14" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G14" s="215" t="inlineStr">
+      <c r="G14" s="213" t="inlineStr">
         <is>
           <t>foaf:Document (IRI)</t>
         </is>
       </c>
-      <c r="H14" s="215" t="inlineStr">
+      <c r="H14" s="213" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I14" s="213" t="inlineStr">
+      <c r="I14" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="213" t="inlineStr">
+      <c r="J14" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K14" s="103" t="n"/>
-      <c r="L14" s="213" t="n"/>
-      <c r="M14" s="213" t="n"/>
+      <c r="L14" s="219" t="n"/>
+      <c r="M14" s="219" t="n"/>
       <c r="O14" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -19856,9 +19911,9 @@
         </is>
       </c>
       <c r="S14" s="69" t="n"/>
-      <c r="T14" s="218" t="n"/>
-      <c r="U14" s="218" t="n"/>
-      <c r="V14" s="218" t="n"/>
+      <c r="T14" s="217" t="n"/>
+      <c r="U14" s="217" t="n"/>
+      <c r="V14" s="217" t="n"/>
     </row>
     <row r="15" ht="64" customHeight="1">
       <c r="A15" s="221" t="inlineStr">
@@ -19907,7 +19962,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J15" s="213" t="inlineStr">
+      <c r="J15" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -19935,7 +19990,7 @@
       <c r="V15" s="221" t="n"/>
     </row>
     <row r="16" ht="85.25" customHeight="1">
-      <c r="A16" s="218" t="inlineStr">
+      <c r="A16" s="217" t="inlineStr">
         <is>
           <t>licence</t>
         </is>
@@ -19961,27 +20016,27 @@
 The licences for Distributions and Data Services are not specified here. They are specified in the licence properties of their respective classes.</t>
         </is>
       </c>
-      <c r="F16" s="215" t="inlineStr">
+      <c r="F16" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G16" s="215" t="inlineStr">
+      <c r="G16" s="213" t="inlineStr">
         <is>
           <t>dct:LicenseDocument (IRI)</t>
         </is>
       </c>
-      <c r="H16" s="215" t="inlineStr">
+      <c r="H16" s="213" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I16" s="213" t="inlineStr">
+      <c r="I16" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J16" s="213" t="inlineStr">
+      <c r="J16" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -19991,8 +20046,8 @@
           <t>custom:licence</t>
         </is>
       </c>
-      <c r="L16" s="213" t="n"/>
-      <c r="M16" s="213" t="n"/>
+      <c r="L16" s="219" t="n"/>
+      <c r="M16" s="219" t="n"/>
       <c r="O16" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -20004,9 +20059,9 @@
         </is>
       </c>
       <c r="S16" s="69" t="n"/>
-      <c r="T16" s="218" t="n"/>
-      <c r="U16" s="218" t="n"/>
-      <c r="V16" s="218" t="n"/>
+      <c r="T16" s="217" t="n"/>
+      <c r="U16" s="217" t="n"/>
+      <c r="V16" s="217" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="221" t="inlineStr">
@@ -20050,7 +20105,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J17" s="213" t="inlineStr">
+      <c r="J17" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -20083,7 +20138,7 @@
       <c r="V17" s="221" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="218" t="inlineStr">
+      <c r="A18" s="217" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
@@ -20108,7 +20163,7 @@
           <t>The organisation or individual that is the holder of the intellectual property rights of a dataset. For more details about the publisher, see the class Agent. Example: Radboudumc.</t>
         </is>
       </c>
-      <c r="F18" s="215" t="inlineStr">
+      <c r="F18" s="213" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -20118,15 +20173,15 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H18" s="215" t="n">
+      <c r="H18" s="213" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="213" t="inlineStr">
+      <c r="I18" s="219" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J18" s="213" t="inlineStr">
+      <c r="J18" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -20136,12 +20191,12 @@
           <t>custom:publisher</t>
         </is>
       </c>
-      <c r="L18" s="213" t="inlineStr">
+      <c r="L18" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="M18" s="213" t="inlineStr">
+      <c r="M18" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -20162,9 +20217,9 @@
         </is>
       </c>
       <c r="S18" s="69" t="n"/>
-      <c r="T18" s="218" t="n"/>
-      <c r="U18" s="218" t="n"/>
-      <c r="V18" s="218" t="n"/>
+      <c r="T18" s="217" t="n"/>
+      <c r="U18" s="217" t="n"/>
+      <c r="V18" s="217" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="221" t="inlineStr">
@@ -20241,7 +20296,7 @@
       <c r="V19" s="221" t="n"/>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="218" t="inlineStr">
+      <c r="A20" s="217" t="inlineStr">
         <is>
           <t>rights</t>
         </is>
@@ -20251,7 +20306,7 @@
           <t>Information about rights held in and over the resource.</t>
         </is>
       </c>
-      <c r="C20" s="218" t="inlineStr">
+      <c r="C20" s="217" t="inlineStr">
         <is>
           <t>dct:rights</t>
         </is>
@@ -20266,34 +20321,34 @@
           <t>The rights statement should be a free-text statement placed at a web-accessible location such that the value of this property is the IRI pointing to that statement.</t>
         </is>
       </c>
-      <c r="F20" s="215" t="inlineStr">
+      <c r="F20" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G20" s="215" t="inlineStr">
+      <c r="G20" s="213" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
       </c>
-      <c r="H20" s="215" t="inlineStr">
+      <c r="H20" s="213" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I20" s="213" t="inlineStr">
+      <c r="I20" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J20" s="213" t="inlineStr">
+      <c r="J20" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K20" s="75" t="n"/>
-      <c r="L20" s="213" t="n"/>
-      <c r="M20" s="213" t="n"/>
+      <c r="L20" s="219" t="n"/>
+      <c r="M20" s="219" t="n"/>
       <c r="O20" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -20305,9 +20360,9 @@
         </is>
       </c>
       <c r="S20" s="69" t="n"/>
-      <c r="T20" s="218" t="n"/>
-      <c r="U20" s="218" t="n"/>
-      <c r="V20" s="218" t="n"/>
+      <c r="T20" s="217" t="n"/>
+      <c r="U20" s="217" t="n"/>
+      <c r="V20" s="217" t="n"/>
     </row>
     <row r="21" ht="64" customHeight="1">
       <c r="A21" s="221" t="inlineStr">
@@ -20383,7 +20438,7 @@
       <c r="V21" s="221" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="218" t="inlineStr">
+      <c r="A22" s="217" t="inlineStr">
         <is>
           <t>temporal coverage</t>
         </is>
@@ -20393,7 +20448,7 @@
           <t>Temporal characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C22" s="218" t="inlineStr">
+      <c r="C22" s="217" t="inlineStr">
         <is>
           <t>dct:temporal</t>
         </is>
@@ -20404,7 +20459,7 @@
         </is>
       </c>
       <c r="E22" s="29" t="n"/>
-      <c r="F22" s="215" t="inlineStr">
+      <c r="F22" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -20414,17 +20469,17 @@
           <t>dct:PeriodOfTime</t>
         </is>
       </c>
-      <c r="H22" s="215" t="inlineStr">
+      <c r="H22" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I22" s="213" t="inlineStr">
+      <c r="I22" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="213" t="inlineStr">
+      <c r="J22" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -20434,8 +20489,8 @@
           <t>custom:temporal_coverage</t>
         </is>
       </c>
-      <c r="L22" s="213" t="n"/>
-      <c r="M22" s="213" t="n"/>
+      <c r="L22" s="219" t="n"/>
+      <c r="M22" s="219" t="n"/>
       <c r="N22" s="214" t="inlineStr">
         <is>
           <t>hri:PeriodOfTimeShape</t>
@@ -20452,9 +20507,9 @@
         </is>
       </c>
       <c r="S22" s="69" t="n"/>
-      <c r="T22" s="218" t="n"/>
-      <c r="U22" s="218" t="n"/>
-      <c r="V22" s="218" t="n"/>
+      <c r="T22" s="217" t="n"/>
+      <c r="U22" s="217" t="n"/>
+      <c r="V22" s="217" t="n"/>
     </row>
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="221" t="inlineStr">
@@ -20526,7 +20581,7 @@
       <c r="V23" s="221" t="n"/>
     </row>
     <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="218" t="inlineStr">
+      <c r="A24" s="217" t="inlineStr">
         <is>
           <t>title</t>
         </is>
@@ -20536,7 +20591,7 @@
           <t>A name given to the resource.</t>
         </is>
       </c>
-      <c r="C24" s="218" t="inlineStr">
+      <c r="C24" s="217" t="inlineStr">
         <is>
           <t>dct:title</t>
         </is>
@@ -20551,27 +20606,27 @@
           <t>Provide a unique title for your catalogue, which can be repeated in multiple languages. Example: Healthy Brain Study.</t>
         </is>
       </c>
-      <c r="F24" s="215" t="inlineStr">
+      <c r="F24" s="213" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G24" s="215" t="inlineStr">
+      <c r="G24" s="213" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H24" s="215" t="inlineStr">
+      <c r="H24" s="213" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I24" s="213" t="inlineStr">
+      <c r="I24" s="219" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J24" s="213" t="inlineStr">
+      <c r="J24" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -20581,8 +20636,8 @@
           <t>title</t>
         </is>
       </c>
-      <c r="L24" s="213" t="n"/>
-      <c r="M24" s="213" t="n"/>
+      <c r="L24" s="219" t="n"/>
+      <c r="M24" s="219" t="n"/>
       <c r="O24" s="214" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -20596,9 +20651,9 @@
       <c r="S24" s="69" t="b">
         <v>1</v>
       </c>
-      <c r="T24" s="218" t="n"/>
-      <c r="U24" s="218" t="n"/>
-      <c r="V24" s="218" t="n"/>
+      <c r="T24" s="217" t="n"/>
+      <c r="U24" s="217" t="n"/>
+      <c r="V24" s="217" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J24"/>
@@ -20609,10 +20664,10 @@
     <mergeCell ref="E8:E12"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="I8:I12"/>
-    <mergeCell ref="F8:F12"/>
     <mergeCell ref="G8:G12"/>
     <mergeCell ref="L8:L12"/>
     <mergeCell ref="J8:J12"/>
+    <mergeCell ref="F8:F12"/>
     <mergeCell ref="M8:M12"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F8">
@@ -20748,9 +20803,9 @@
   <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col width="25.5" bestFit="1" customWidth="1" style="217" min="1" max="1"/>
-    <col width="40.5" customWidth="1" style="217" min="2" max="2"/>
-    <col width="28.83203125" customWidth="1" style="217" min="3" max="3"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="216" min="1" max="1"/>
+    <col width="40.5" customWidth="1" style="216" min="2" max="2"/>
+    <col width="28.83203125" customWidth="1" style="216" min="3" max="3"/>
     <col width="22.5" customWidth="1" style="223" min="4" max="4"/>
     <col width="68.83203125" customWidth="1" style="223" min="5" max="5"/>
     <col width="18.5" bestFit="1" customWidth="1" style="214" min="6" max="6"/>
@@ -20897,7 +20952,7 @@
           <t>Information about who can access the resource or an indication of its security status.</t>
         </is>
       </c>
-      <c r="C2" s="218" t="inlineStr">
+      <c r="C2" s="217" t="inlineStr">
         <is>
           <t>dct:accessRights</t>
         </is>
@@ -20916,25 +20971,25 @@
 Since most data contain personal information, these datasets will need to take the value 'non-public' for the access rights property.</t>
         </is>
       </c>
-      <c r="F2" s="215" t="inlineStr">
+      <c r="F2" s="213" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G2" s="215" t="inlineStr">
+      <c r="G2" s="213" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
       </c>
-      <c r="H2" s="215" t="n">
+      <c r="H2" s="213" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="213" t="inlineStr">
+      <c r="I2" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="213" t="inlineStr">
+      <c r="J2" s="219" t="inlineStr">
         <is>
           <t>Health and NL</t>
         </is>
@@ -20944,7 +20999,7 @@
           <t>custom:access_rights</t>
         </is>
       </c>
-      <c r="L2" s="213" t="n"/>
+      <c r="L2" s="219" t="n"/>
       <c r="P2" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -20985,7 +21040,7 @@
           <t>This property contains an alternative name for the Dataset. This property can be repeated for parallel language versions of the alternative name.</t>
         </is>
       </c>
-      <c r="F3" s="215" t="inlineStr">
+      <c r="F3" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -21005,7 +21060,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J3" s="213" t="inlineStr">
+      <c r="J3" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -21064,17 +21119,17 @@
           <t>dcat:Distribution (IRI)</t>
         </is>
       </c>
-      <c r="H4" s="215" t="inlineStr">
+      <c r="H4" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I4" s="213" t="inlineStr">
+      <c r="I4" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="213" t="inlineStr">
+      <c r="J4" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -21084,7 +21139,7 @@
           <t>custom:analytics</t>
         </is>
       </c>
-      <c r="L4" s="213" t="inlineStr">
+      <c r="L4" s="219" t="inlineStr">
         <is>
           <t>If available, add the URI for the analytics distribution here.</t>
         </is>
@@ -21146,7 +21201,7 @@
         </is>
       </c>
       <c r="I5" s="220" t="n"/>
-      <c r="J5" s="213" t="n"/>
+      <c r="J5" s="219" t="n"/>
       <c r="K5" s="227" t="n"/>
       <c r="L5" s="100" t="n"/>
       <c r="M5" s="220" t="n"/>
@@ -21181,7 +21236,7 @@
           <t>The legislation that is applicable to this resource.</t>
         </is>
       </c>
-      <c r="C6" s="218" t="inlineStr">
+      <c r="C6" s="217" t="inlineStr">
         <is>
           <t>dcatap:applicableLegislation</t>
         </is>
@@ -21199,12 +21254,12 @@
 While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property (also in Datasets) describes the legal basis for initial collection and processing of (personal) data.</t>
         </is>
       </c>
-      <c r="F6" s="215" t="inlineStr">
+      <c r="F6" s="213" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G6" s="215" t="inlineStr">
+      <c r="G6" s="213" t="inlineStr">
         <is>
           <t>eli:LegalResource (IRI)</t>
         </is>
@@ -21214,12 +21269,12 @@
           <t>1..n</t>
         </is>
       </c>
-      <c r="I6" s="213" t="inlineStr">
+      <c r="I6" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="213" t="inlineStr">
+      <c r="J6" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -21229,7 +21284,7 @@
           <t>custom:applicable_legislation</t>
         </is>
       </c>
-      <c r="L6" s="213" t="n"/>
+      <c r="L6" s="219" t="n"/>
       <c r="P6" s="83" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -21296,7 +21351,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J7" s="213" t="inlineStr">
+      <c r="J7" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -21324,7 +21379,7 @@
       <c r="W7" s="221" t="n"/>
     </row>
     <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="218" t="inlineStr">
+      <c r="A8" s="217" t="inlineStr">
         <is>
           <t>coding system</t>
         </is>
@@ -21334,7 +21389,7 @@
           <t>Coding systems in use (e.g. ICD-10-CM, DGRs, SNOMED CT, ...)</t>
         </is>
       </c>
-      <c r="C8" s="218" t="inlineStr">
+      <c r="C8" s="217" t="inlineStr">
         <is>
           <t>healthdcatap:hasCodingSystem</t>
         </is>
@@ -21350,27 +21405,27 @@
 This property provides information on which coding systems are in use in your dataset. For this, Wikidata URIs must be used.</t>
         </is>
       </c>
-      <c r="F8" s="215" t="inlineStr">
+      <c r="F8" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G8" s="215" t="inlineStr">
+      <c r="G8" s="213" t="inlineStr">
         <is>
           <t>dct:Standard (IRI)</t>
         </is>
       </c>
-      <c r="H8" s="215" t="inlineStr">
+      <c r="H8" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I8" s="213" t="inlineStr">
+      <c r="I8" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="213" t="inlineStr">
+      <c r="J8" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -21380,7 +21435,7 @@
           <t>custom:coding_system</t>
         </is>
       </c>
-      <c r="L8" s="213" t="n"/>
+      <c r="L8" s="219" t="n"/>
       <c r="P8" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -21391,9 +21446,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U8" s="218" t="n"/>
-      <c r="V8" s="218" t="n"/>
-      <c r="W8" s="218" t="n"/>
+      <c r="U8" s="217" t="n"/>
+      <c r="V8" s="217" t="n"/>
+      <c r="W8" s="217" t="n"/>
     </row>
     <row r="9" ht="80" customHeight="1">
       <c r="A9" s="221" t="inlineStr">
@@ -21442,7 +21497,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J9" s="213" t="inlineStr">
+      <c r="J9" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -21470,7 +21525,7 @@
       <c r="W9" s="221" t="n"/>
     </row>
     <row r="10" ht="123.75" customHeight="1">
-      <c r="A10" s="218" t="inlineStr">
+      <c r="A10" s="217" t="inlineStr">
         <is>
           <t>contact point</t>
         </is>
@@ -21480,7 +21535,7 @@
           <t>Relevant contact information for the catalogued resource.</t>
         </is>
       </c>
-      <c r="C10" s="218" t="inlineStr">
+      <c r="C10" s="217" t="inlineStr">
         <is>
           <t>dcat:contactPoint</t>
         </is>
@@ -21496,7 +21551,7 @@
 Whenever possible, use general contact information (for example, from a department) instead of the contact information of an individual.</t>
         </is>
       </c>
-      <c r="F10" s="215" t="inlineStr">
+      <c r="F10" s="213" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -21506,15 +21561,15 @@
           <t>vcard:Kind</t>
         </is>
       </c>
-      <c r="H10" s="215" t="n">
+      <c r="H10" s="213" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="213" t="inlineStr">
+      <c r="I10" s="219" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J10" s="213" t="inlineStr">
+      <c r="J10" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -21524,17 +21579,17 @@
           <t>custom:contact_</t>
         </is>
       </c>
-      <c r="L10" s="213" t="inlineStr">
+      <c r="L10" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
       </c>
-      <c r="M10" s="213" t="inlineStr">
+      <c r="M10" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
       </c>
-      <c r="N10" s="213" t="inlineStr">
+      <c r="N10" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
@@ -21554,9 +21609,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="U10" s="218" t="n"/>
-      <c r="V10" s="218" t="n"/>
-      <c r="W10" s="218" t="n"/>
+      <c r="U10" s="217" t="n"/>
+      <c r="V10" s="217" t="n"/>
+      <c r="W10" s="217" t="n"/>
     </row>
     <row r="11" ht="176" customHeight="1">
       <c r="A11" s="221" t="inlineStr">
@@ -21606,7 +21661,7 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J11" s="213" t="inlineStr">
+      <c r="J11" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -21651,7 +21706,7 @@
       <c r="W11" s="221" t="n"/>
     </row>
     <row r="12" ht="64" customHeight="1">
-      <c r="A12" s="218" t="inlineStr">
+      <c r="A12" s="217" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -21661,7 +21716,7 @@
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C12" s="218" t="inlineStr">
+      <c r="C12" s="217" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -21676,27 +21731,27 @@
           <t>Brief description of the dataset. You can repeat this property in multiple languages. Example: ‘Collection of physiological data of Healthy Brain Study participants. This collection includes measurements via biowearables for heart rate, oxygenation, systolic and diastolic measures and stress levels.’</t>
         </is>
       </c>
-      <c r="F12" s="215" t="inlineStr">
+      <c r="F12" s="213" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G12" s="215" t="inlineStr">
+      <c r="G12" s="213" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H12" s="215" t="inlineStr">
+      <c r="H12" s="213" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I12" s="213" t="inlineStr">
+      <c r="I12" s="219" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J12" s="213" t="inlineStr">
+      <c r="J12" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21706,7 +21761,7 @@
           <t>notes</t>
         </is>
       </c>
-      <c r="L12" s="213" t="n"/>
+      <c r="L12" s="219" t="n"/>
       <c r="P12" s="214" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -21720,9 +21775,9 @@
       <c r="T12" s="214" t="b">
         <v>1</v>
       </c>
-      <c r="U12" s="218" t="n"/>
-      <c r="V12" s="218" t="n"/>
-      <c r="W12" s="218" t="n"/>
+      <c r="U12" s="217" t="n"/>
+      <c r="V12" s="217" t="n"/>
+      <c r="W12" s="217" t="n"/>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="221" t="inlineStr">
@@ -21809,7 +21864,7 @@
       <c r="W13" s="221" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="218" t="inlineStr">
+      <c r="A14" s="217" t="inlineStr">
         <is>
           <t>documentation</t>
         </is>
@@ -21819,7 +21874,7 @@
           <t>A page or document about this thing.</t>
         </is>
       </c>
-      <c r="C14" s="218" t="inlineStr">
+      <c r="C14" s="217" t="inlineStr">
         <is>
           <t>foaf:page</t>
         </is>
@@ -21834,27 +21889,27 @@
           <t>The value of this property is the IRI pointing to the web page or document about the dataset.</t>
         </is>
       </c>
-      <c r="F14" s="215" t="inlineStr">
+      <c r="F14" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G14" s="215" t="inlineStr">
+      <c r="G14" s="213" t="inlineStr">
         <is>
           <t>foaf:Document (IRI)</t>
         </is>
       </c>
-      <c r="H14" s="215" t="inlineStr">
+      <c r="H14" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I14" s="213" t="inlineStr">
+      <c r="I14" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="213" t="inlineStr">
+      <c r="J14" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -21864,7 +21919,7 @@
           <t>custom:documentation</t>
         </is>
       </c>
-      <c r="L14" s="213" t="n"/>
+      <c r="L14" s="219" t="n"/>
       <c r="P14" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -21875,9 +21930,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U14" s="218" t="n"/>
-      <c r="V14" s="218" t="n"/>
-      <c r="W14" s="218" t="n"/>
+      <c r="U14" s="217" t="n"/>
+      <c r="V14" s="217" t="n"/>
+      <c r="W14" s="217" t="n"/>
     </row>
     <row r="15" ht="160" customHeight="1">
       <c r="A15" s="221" t="inlineStr">
@@ -21908,7 +21963,7 @@
 See the property "measurement technique" for more information about the technique(s) used to generate the data in the Dataset.</t>
         </is>
       </c>
-      <c r="F15" s="215" t="inlineStr">
+      <c r="F15" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -21948,7 +22003,7 @@
       <c r="W15" s="221" t="n"/>
     </row>
     <row r="16" ht="69.75" customHeight="1">
-      <c r="A16" s="218" t="inlineStr">
+      <c r="A16" s="217" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
@@ -21958,7 +22013,7 @@
           <t>The frequency with which items are added to a collection.</t>
         </is>
       </c>
-      <c r="C16" s="218" t="inlineStr">
+      <c r="C16" s="217" t="inlineStr">
         <is>
           <t>dct:accrualPeriodicity</t>
         </is>
@@ -21968,7 +22023,7 @@
           <t>http://publications.europa.eu/resource/authority/frequency</t>
         </is>
       </c>
-      <c r="E16" s="219" t="inlineStr">
+      <c r="E16" s="218" t="inlineStr">
         <is>
           <t>The value of this property should be the IRI from the listed controlled vocabulary indicating the frequency at which the dataset is updated.
 For example: http://publications.europa.eu/resource/authority/frequency/WEEKLY</t>
@@ -21979,22 +22034,22 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G16" s="215" t="inlineStr">
+      <c r="G16" s="213" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H16" s="215" t="inlineStr">
+      <c r="H16" s="213" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I16" s="213" t="inlineStr">
+      <c r="I16" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J16" s="213" t="inlineStr">
+      <c r="J16" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -22005,8 +22060,8 @@
         </is>
       </c>
       <c r="L16" s="107" t="n"/>
-      <c r="M16" s="213" t="n"/>
-      <c r="N16" s="213" t="n"/>
+      <c r="M16" s="219" t="n"/>
+      <c r="N16" s="219" t="n"/>
       <c r="P16" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -22017,9 +22072,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U16" s="218" t="n"/>
-      <c r="V16" s="218" t="n"/>
-      <c r="W16" s="218" t="n"/>
+      <c r="U16" s="217" t="n"/>
+      <c r="V16" s="217" t="n"/>
+      <c r="W16" s="217" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="221" t="inlineStr">
@@ -22047,7 +22102,7 @@
           <t>The EU Vocabularies Named Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, GeoNames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocabulary can be used. However, it might in many cases be desirable to keep the geographical coverage broader (e.g. indicating that NL is covered), to avoid exposing detailed information about subjects' locations.</t>
         </is>
       </c>
-      <c r="F17" s="215" t="inlineStr">
+      <c r="F17" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -22119,7 +22174,7 @@
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="218" t="inlineStr">
+      <c r="A22" s="217" t="inlineStr">
         <is>
           <t>has version</t>
         </is>
@@ -22129,7 +22184,7 @@
           <t>This resource has a more specific, versioned resource.</t>
         </is>
       </c>
-      <c r="C22" s="218" t="inlineStr">
+      <c r="C22" s="217" t="inlineStr">
         <is>
           <t>dcat:hasVersion</t>
         </is>
@@ -22139,7 +22194,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E22" s="219" t="inlineStr">
+      <c r="E22" s="218" t="inlineStr">
         <is>
           <t>Indicate the dataset that is another version of the current dataset.</t>
         </is>
@@ -22154,17 +22209,17 @@
           <t>dcat:Dataset (IRI)</t>
         </is>
       </c>
-      <c r="H22" s="215" t="inlineStr">
+      <c r="H22" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I22" s="213" t="inlineStr">
+      <c r="I22" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="213" t="inlineStr">
+      <c r="J22" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -22179,8 +22234,8 @@
           <t>fill in URI to dcat:Dataset that is another version of current Dataset</t>
         </is>
       </c>
-      <c r="M22" s="213" t="n"/>
-      <c r="N22" s="213" t="n"/>
+      <c r="M22" s="219" t="n"/>
+      <c r="N22" s="219" t="n"/>
       <c r="P22" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -22191,9 +22246,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U22" s="218" t="n"/>
-      <c r="V22" s="218" t="n"/>
-      <c r="W22" s="218" t="n"/>
+      <c r="U22" s="217" t="n"/>
+      <c r="V22" s="217" t="n"/>
+      <c r="W22" s="217" t="n"/>
     </row>
     <row r="23" ht="112" customHeight="1">
       <c r="A23" s="221" t="inlineStr">
@@ -22222,7 +22277,7 @@
 Example: A Dataset concerning myocardial infarction can use http://snomed.info/id/22298006.</t>
         </is>
       </c>
-      <c r="F23" s="215" t="inlineStr">
+      <c r="F23" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -22267,7 +22322,7 @@
       <c r="W23" s="221" t="n"/>
     </row>
     <row r="24" ht="96" customHeight="1">
-      <c r="A24" s="218" t="inlineStr">
+      <c r="A24" s="217" t="inlineStr">
         <is>
           <t>health theme</t>
         </is>
@@ -22277,7 +22332,7 @@
           <t>A category of the Dataset or tag describing the Dataset.</t>
         </is>
       </c>
-      <c r="C24" s="218" t="inlineStr">
+      <c r="C24" s="217" t="inlineStr">
         <is>
           <t>healthdcatap:healthTheme</t>
         </is>
@@ -22293,27 +22348,27 @@
 This property is a structured way to tag the dataset with different health themes. This could include, for example, the specific disease the dataset is about. More details can be provided, if desirable, in the keywords property.  The Wikidata URI of the health theme must be used here.</t>
         </is>
       </c>
-      <c r="F24" s="215" t="inlineStr">
+      <c r="F24" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G24" s="215" t="inlineStr">
+      <c r="G24" s="213" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H24" s="215" t="inlineStr">
+      <c r="H24" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I24" s="213" t="inlineStr">
+      <c r="I24" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J24" s="213" t="inlineStr">
+      <c r="J24" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -22323,7 +22378,7 @@
           <t>custom:health_theme</t>
         </is>
       </c>
-      <c r="L24" s="213" t="n"/>
+      <c r="L24" s="219" t="n"/>
       <c r="P24" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -22334,9 +22389,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U24" s="218" t="n"/>
-      <c r="V24" s="218" t="n"/>
-      <c r="W24" s="218" t="n"/>
+      <c r="U24" s="217" t="n"/>
+      <c r="V24" s="217" t="n"/>
+      <c r="W24" s="217" t="n"/>
     </row>
     <row r="25" ht="96" customHeight="1">
       <c r="A25" s="221" t="inlineStr">
@@ -22411,7 +22466,7 @@
       <c r="W25" s="221" t="n"/>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="218" t="inlineStr">
+      <c r="A26" s="217" t="inlineStr">
         <is>
           <t>in series</t>
         </is>
@@ -22421,7 +22476,7 @@
           <t>A dataset series of which the dataset is part.</t>
         </is>
       </c>
-      <c r="C26" s="218" t="inlineStr">
+      <c r="C26" s="217" t="inlineStr">
         <is>
           <t>dcat:inSeries</t>
         </is>
@@ -22436,7 +22491,7 @@
           <t xml:space="preserve">This property points to the Dataset Series of which the Dataset is part. </t>
         </is>
       </c>
-      <c r="F26" s="215" t="inlineStr">
+      <c r="F26" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -22446,17 +22501,17 @@
           <t>dcat:DatasetSeries (IRI)</t>
         </is>
       </c>
-      <c r="H26" s="215" t="inlineStr">
+      <c r="H26" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I26" s="213" t="inlineStr">
+      <c r="I26" s="219" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J26" s="213" t="inlineStr">
+      <c r="J26" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -22477,9 +22532,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U26" s="218" t="n"/>
-      <c r="V26" s="218" t="n"/>
-      <c r="W26" s="218" t="n"/>
+      <c r="U26" s="217" t="n"/>
+      <c r="V26" s="217" t="n"/>
+      <c r="W26" s="217" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="221" t="inlineStr">
@@ -22556,7 +22611,7 @@
       <c r="W27" s="221" t="n"/>
     </row>
     <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="218" t="inlineStr">
+      <c r="A28" s="217" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -22581,27 +22636,27 @@
           <t>Add keywords to increase dataset discoverability. You can include keywords in different languages, submitting each keyword as a separate entry. Example: Physiological measures, Heart Rate, Stress Measures.</t>
         </is>
       </c>
-      <c r="F28" s="215" t="inlineStr">
+      <c r="F28" s="213" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G28" s="215" t="inlineStr">
+      <c r="G28" s="213" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H28" s="215" t="inlineStr">
+      <c r="H28" s="213" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I28" s="213" t="inlineStr">
+      <c r="I28" s="219" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J28" s="213" t="inlineStr">
+      <c r="J28" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -22611,7 +22666,7 @@
           <t>tags</t>
         </is>
       </c>
-      <c r="L28" s="213" t="n"/>
+      <c r="L28" s="219" t="n"/>
       <c r="P28" s="214" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -22622,9 +22677,9 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="U28" s="218" t="n"/>
-      <c r="V28" s="218" t="n"/>
-      <c r="W28" s="218" t="n"/>
+      <c r="U28" s="217" t="n"/>
+      <c r="V28" s="217" t="n"/>
+      <c r="W28" s="217" t="n"/>
     </row>
     <row r="29" ht="128" customHeight="1">
       <c r="A29" s="221" t="inlineStr">
@@ -22653,7 +22708,7 @@
 Example: For an EGA Dataset, dcat:landingPage points to the corresponding human-readable EGA Dataset page, like https://ega-archive.org/datasets/EGAD00001005083.</t>
         </is>
       </c>
-      <c r="F29" s="215" t="inlineStr">
+      <c r="F29" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -22697,7 +22752,7 @@
       <c r="W29" s="221" t="n"/>
     </row>
     <row r="30" ht="48" customHeight="1">
-      <c r="A30" s="218" t="inlineStr">
+      <c r="A30" s="217" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -22727,12 +22782,12 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G30" s="215" t="inlineStr">
+      <c r="G30" s="213" t="inlineStr">
         <is>
           <t>dct:LinguisticSystem (IRI)</t>
         </is>
       </c>
-      <c r="H30" s="215" t="inlineStr">
+      <c r="H30" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
@@ -22752,9 +22807,9 @@
           <t>custom:language</t>
         </is>
       </c>
-      <c r="L30" s="213" t="n"/>
-      <c r="M30" s="213" t="n"/>
-      <c r="N30" s="213" t="n"/>
+      <c r="L30" s="219" t="n"/>
+      <c r="M30" s="219" t="n"/>
+      <c r="N30" s="219" t="n"/>
       <c r="P30" s="69" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -22765,9 +22820,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U30" s="218" t="n"/>
-      <c r="V30" s="218" t="n"/>
-      <c r="W30" s="218" t="n"/>
+      <c r="U30" s="217" t="n"/>
+      <c r="V30" s="217" t="n"/>
+      <c r="W30" s="217" t="n"/>
     </row>
     <row r="31" ht="160" customHeight="1">
       <c r="A31" s="221" t="inlineStr">
@@ -22798,7 +22853,7 @@
 An example value for this property could be dpv:Consent.</t>
         </is>
       </c>
-      <c r="F31" s="215" t="inlineStr">
+      <c r="F31" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -22846,7 +22901,7 @@
       <c r="W31" s="221" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="218" t="inlineStr">
+      <c r="A32" s="217" t="inlineStr">
         <is>
           <t>maximum typical age</t>
         </is>
@@ -22856,7 +22911,7 @@
           <t>Maximum typical age of the population within the dataset</t>
         </is>
       </c>
-      <c r="C32" s="218" t="inlineStr">
+      <c r="C32" s="217" t="inlineStr">
         <is>
           <t>healthdcatap:maxTypicalAge</t>
         </is>
@@ -22876,22 +22931,22 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G32" s="215" t="inlineStr">
+      <c r="G32" s="213" t="inlineStr">
         <is>
           <t>xsd:nonNegativeInteger</t>
         </is>
       </c>
-      <c r="H32" s="215" t="inlineStr">
+      <c r="H32" s="213" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I32" s="213" t="inlineStr">
+      <c r="I32" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J32" s="213" t="inlineStr">
+      <c r="J32" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -22901,9 +22956,9 @@
           <t>custom:max_typical_age</t>
         </is>
       </c>
-      <c r="L32" s="213" t="n"/>
-      <c r="M32" s="213" t="n"/>
-      <c r="N32" s="213" t="n"/>
+      <c r="L32" s="219" t="n"/>
+      <c r="M32" s="219" t="n"/>
+      <c r="N32" s="219" t="n"/>
       <c r="P32" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -22914,9 +22969,9 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="U32" s="218" t="n"/>
-      <c r="V32" s="218" t="n"/>
-      <c r="W32" s="218" t="n"/>
+      <c r="U32" s="217" t="n"/>
+      <c r="V32" s="217" t="n"/>
+      <c r="W32" s="217" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="221" t="inlineStr">
@@ -22944,7 +22999,7 @@
           <t>The approximate minimum age of subjects in the dataset, if applicable. Approximate age is given to protect potentially sensitive information of subjects in the dataset.</t>
         </is>
       </c>
-      <c r="F33" s="215" t="inlineStr">
+      <c r="F33" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -22992,7 +23047,7 @@
       <c r="W33" s="221" t="n"/>
     </row>
     <row r="34" ht="209.25" customHeight="1">
-      <c r="A34" s="218" t="inlineStr">
+      <c r="A34" s="217" t="inlineStr">
         <is>
           <t>measurement technique</t>
         </is>
@@ -23019,28 +23074,28 @@
 Note: This is a temporary location and it will change with the next release. </t>
         </is>
       </c>
-      <c r="F34" s="215" t="inlineStr">
+      <c r="F34" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G34" s="215" t="inlineStr">
+      <c r="G34" s="213" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H34" s="215" t="inlineStr">
+      <c r="H34" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I34" s="213" t="n"/>
-      <c r="J34" s="213" t="n"/>
+      <c r="I34" s="219" t="n"/>
+      <c r="J34" s="219" t="n"/>
       <c r="K34" s="75" t="n"/>
-      <c r="L34" s="213" t="n"/>
-      <c r="M34" s="213" t="n"/>
-      <c r="N34" s="213" t="n"/>
-      <c r="O34" s="213" t="n"/>
+      <c r="L34" s="219" t="n"/>
+      <c r="M34" s="219" t="n"/>
+      <c r="N34" s="219" t="n"/>
+      <c r="O34" s="219" t="n"/>
       <c r="P34" s="69" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -23051,40 +23106,40 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="R34" s="213" t="n"/>
-      <c r="S34" s="213" t="n"/>
-      <c r="T34" s="213" t="n"/>
-      <c r="U34" s="218" t="n"/>
-      <c r="V34" s="218" t="n"/>
-      <c r="W34" s="218" t="n"/>
-      <c r="X34" s="213" t="n"/>
-      <c r="Y34" s="213" t="n"/>
-      <c r="Z34" s="213" t="n"/>
-      <c r="AA34" s="213" t="n"/>
-      <c r="AB34" s="213" t="n"/>
-      <c r="AC34" s="213" t="n"/>
-      <c r="AD34" s="213" t="n"/>
-      <c r="AE34" s="213" t="n"/>
-      <c r="AF34" s="213" t="n"/>
-      <c r="AG34" s="213" t="n"/>
-      <c r="AH34" s="213" t="n"/>
-      <c r="AI34" s="213" t="n"/>
-      <c r="AJ34" s="213" t="n"/>
-      <c r="AK34" s="213" t="n"/>
-      <c r="AL34" s="213" t="n"/>
-      <c r="AM34" s="213" t="n"/>
-      <c r="AN34" s="213" t="n"/>
-      <c r="AO34" s="213" t="n"/>
-      <c r="AP34" s="213" t="n"/>
-      <c r="AQ34" s="213" t="n"/>
-      <c r="AR34" s="213" t="n"/>
-      <c r="AS34" s="213" t="n"/>
-      <c r="AT34" s="213" t="n"/>
-      <c r="AU34" s="213" t="n"/>
-      <c r="AV34" s="213" t="n"/>
-      <c r="AW34" s="213" t="n"/>
-      <c r="AX34" s="213" t="n"/>
-      <c r="AY34" s="213" t="n"/>
+      <c r="R34" s="219" t="n"/>
+      <c r="S34" s="219" t="n"/>
+      <c r="T34" s="219" t="n"/>
+      <c r="U34" s="217" t="n"/>
+      <c r="V34" s="217" t="n"/>
+      <c r="W34" s="217" t="n"/>
+      <c r="X34" s="219" t="n"/>
+      <c r="Y34" s="219" t="n"/>
+      <c r="Z34" s="219" t="n"/>
+      <c r="AA34" s="219" t="n"/>
+      <c r="AB34" s="219" t="n"/>
+      <c r="AC34" s="219" t="n"/>
+      <c r="AD34" s="219" t="n"/>
+      <c r="AE34" s="219" t="n"/>
+      <c r="AF34" s="219" t="n"/>
+      <c r="AG34" s="219" t="n"/>
+      <c r="AH34" s="219" t="n"/>
+      <c r="AI34" s="219" t="n"/>
+      <c r="AJ34" s="219" t="n"/>
+      <c r="AK34" s="219" t="n"/>
+      <c r="AL34" s="219" t="n"/>
+      <c r="AM34" s="219" t="n"/>
+      <c r="AN34" s="219" t="n"/>
+      <c r="AO34" s="219" t="n"/>
+      <c r="AP34" s="219" t="n"/>
+      <c r="AQ34" s="219" t="n"/>
+      <c r="AR34" s="219" t="n"/>
+      <c r="AS34" s="219" t="n"/>
+      <c r="AT34" s="219" t="n"/>
+      <c r="AU34" s="219" t="n"/>
+      <c r="AV34" s="219" t="n"/>
+      <c r="AW34" s="219" t="n"/>
+      <c r="AX34" s="219" t="n"/>
+      <c r="AY34" s="219" t="n"/>
     </row>
     <row r="35" ht="48" customHeight="1">
       <c r="A35" s="221" t="inlineStr">
@@ -23165,7 +23220,7 @@
       <c r="W35" s="221" t="n"/>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="218" t="inlineStr">
+      <c r="A36" s="217" t="inlineStr">
         <is>
           <t>number of records</t>
         </is>
@@ -23175,7 +23230,7 @@
           <t>Size of the dataset in terms of the number of records</t>
         </is>
       </c>
-      <c r="C36" s="218" t="inlineStr">
+      <c r="C36" s="217" t="inlineStr">
         <is>
           <t>healthdcatap:numberOfRecords</t>
         </is>
@@ -23190,27 +23245,27 @@
           <t>Number of records inside a Dataset.</t>
         </is>
       </c>
-      <c r="F36" s="215" t="inlineStr">
+      <c r="F36" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G36" s="215" t="inlineStr">
+      <c r="G36" s="213" t="inlineStr">
         <is>
           <t>xsd:nonNegativeInteger</t>
         </is>
       </c>
-      <c r="H36" s="215" t="inlineStr">
+      <c r="H36" s="213" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I36" s="213" t="inlineStr">
+      <c r="I36" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J36" s="213" t="inlineStr">
+      <c r="J36" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -23220,7 +23275,7 @@
           <t>custom:number_of_records</t>
         </is>
       </c>
-      <c r="L36" s="213" t="n"/>
+      <c r="L36" s="219" t="n"/>
       <c r="P36" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -23231,9 +23286,9 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="U36" s="218" t="n"/>
-      <c r="V36" s="218" t="n"/>
-      <c r="W36" s="218" t="n"/>
+      <c r="U36" s="217" t="n"/>
+      <c r="V36" s="217" t="n"/>
+      <c r="W36" s="217" t="n"/>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="221" t="inlineStr">
@@ -23309,7 +23364,7 @@
       <c r="W37" s="221" t="n"/>
     </row>
     <row r="38" ht="64" customHeight="1">
-      <c r="A38" s="218" t="inlineStr">
+      <c r="A38" s="217" t="inlineStr">
         <is>
           <t>other identifier</t>
         </is>
@@ -23319,7 +23374,7 @@
           <t>Links a resource to an adms:Identifier class.</t>
         </is>
       </c>
-      <c r="C38" s="218" t="inlineStr">
+      <c r="C38" s="217" t="inlineStr">
         <is>
           <t>adms:identifier</t>
         </is>
@@ -23334,27 +23389,27 @@
           <t>Examples of secondary identifiers include MAST/ADS, DataCite, DOI, EZID or W3ID (if not used for the original identifier). This property makes use of another small class: adms:Identifier, where you provide the identifier and the name of the identifier schema (e.g. DOI).</t>
         </is>
       </c>
-      <c r="F38" s="215" t="inlineStr">
+      <c r="F38" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G38" s="215" t="inlineStr">
+      <c r="G38" s="213" t="inlineStr">
         <is>
           <t>adms:Identifier</t>
         </is>
       </c>
-      <c r="H38" s="215" t="inlineStr">
+      <c r="H38" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I38" s="213" t="inlineStr">
+      <c r="I38" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J38" s="213" t="inlineStr">
+      <c r="J38" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -23364,7 +23419,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="L38" s="213" t="n"/>
+      <c r="L38" s="219" t="n"/>
       <c r="O38" s="214" t="inlineStr">
         <is>
           <t>hri:IdentifierShape</t>
@@ -23380,9 +23435,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="U38" s="218" t="n"/>
-      <c r="V38" s="218" t="n"/>
-      <c r="W38" s="218" t="n"/>
+      <c r="U38" s="217" t="n"/>
+      <c r="V38" s="217" t="n"/>
+      <c r="W38" s="217" t="n"/>
     </row>
     <row r="39" ht="64" customHeight="1">
       <c r="A39" s="221" t="inlineStr">
@@ -23459,7 +23514,7 @@
       <c r="W39" s="221" t="n"/>
     </row>
     <row r="40" ht="59" customHeight="1">
-      <c r="A40" s="218" t="inlineStr">
+      <c r="A40" s="217" t="inlineStr">
         <is>
           <t>population coverage</t>
         </is>
@@ -23469,7 +23524,7 @@
           <t>A definition of the population within the dataset</t>
         </is>
       </c>
-      <c r="C40" s="218" t="inlineStr">
+      <c r="C40" s="217" t="inlineStr">
         <is>
           <t>healthdcatap:populationCoverage</t>
         </is>
@@ -23484,27 +23539,27 @@
           <t>This field is a free-text description of the population covered in the dataset. For example, "Adults aged 18–65 diagnosed with type 2 diabetes in the Netherlands between 2015 and 2020".</t>
         </is>
       </c>
-      <c r="F40" s="215" t="inlineStr">
+      <c r="F40" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G40" s="215" t="inlineStr">
+      <c r="G40" s="213" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H40" s="215" t="inlineStr">
+      <c r="H40" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I40" s="213" t="inlineStr">
+      <c r="I40" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J40" s="213" t="inlineStr">
+      <c r="J40" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -23514,7 +23569,7 @@
           <t>custom:populatiion_coverage</t>
         </is>
       </c>
-      <c r="L40" s="213" t="n"/>
+      <c r="L40" s="219" t="n"/>
       <c r="P40" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -23525,9 +23580,9 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="U40" s="218" t="n"/>
-      <c r="V40" s="218" t="n"/>
-      <c r="W40" s="218" t="n"/>
+      <c r="U40" s="217" t="n"/>
+      <c r="V40" s="217" t="n"/>
+      <c r="W40" s="217" t="n"/>
     </row>
     <row r="41" ht="92" customHeight="1">
       <c r="A41" s="221" t="inlineStr">
@@ -23556,7 +23611,7 @@
 This is where the collection-method statements not captured by dedicated properties can be listed.</t>
         </is>
       </c>
-      <c r="F41" s="215" t="inlineStr">
+      <c r="F41" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -23612,7 +23667,7 @@
       <c r="W41" s="221" t="n"/>
     </row>
     <row r="42" ht="112" customHeight="1">
-      <c r="A42" s="218" t="inlineStr">
+      <c r="A42" s="217" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
@@ -23622,7 +23677,7 @@
           <t>An entity responsible for making the resource available.</t>
         </is>
       </c>
-      <c r="C42" s="218" t="inlineStr">
+      <c r="C42" s="217" t="inlineStr">
         <is>
           <t>dct:publisher</t>
         </is>
@@ -23632,7 +23687,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E42" s="219" t="inlineStr">
+      <c r="E42" s="218" t="inlineStr">
         <is>
           <t>This property identifies the organisation or individual responsible for making the dataset available. For datasets, this is typically the employer of the data creators. In simple cases, the dataset publisher may be the same as the catalogue publisher. In more complex settings, such as when datasets come from multiple institutions within a consortium, the consortium should be listed as the publisher where possible. If no formal consortium can be specified, provide information about the contributing organisations or individuals under dct:creator instead. For more details, refer to the Agent class.</t>
         </is>
@@ -23647,15 +23702,15 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H42" s="215" t="n">
+      <c r="H42" s="213" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="213" t="inlineStr">
+      <c r="I42" s="219" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J42" s="213" t="inlineStr">
+      <c r="J42" s="219" t="inlineStr">
         <is>
           <t>Health and NL</t>
         </is>
@@ -23665,17 +23720,17 @@
           <t>custom:publisher</t>
         </is>
       </c>
-      <c r="L42" s="213" t="inlineStr">
+      <c r="L42" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="M42" s="213" t="inlineStr">
+      <c r="M42" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="N42" s="213" t="inlineStr">
+      <c r="N42" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -23695,9 +23750,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="U42" s="218" t="n"/>
-      <c r="V42" s="218" t="n"/>
-      <c r="W42" s="218" t="n"/>
+      <c r="U42" s="217" t="n"/>
+      <c r="V42" s="217" t="n"/>
+      <c r="W42" s="217" t="n"/>
     </row>
     <row r="43" ht="48" customHeight="1">
       <c r="A43" s="221" t="inlineStr">
@@ -23726,7 +23781,7 @@
 An example value could be dpv:ResearchAndDevelopment.</t>
         </is>
       </c>
-      <c r="F43" s="215" t="inlineStr">
+      <c r="F43" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -23774,7 +23829,7 @@
       <c r="W43" s="221" t="n"/>
     </row>
     <row r="44" ht="228" customHeight="1">
-      <c r="A44" s="218" t="inlineStr">
+      <c r="A44" s="217" t="inlineStr">
         <is>
           <t>qualified attribution</t>
         </is>
@@ -23813,33 +23868,33 @@
           <t>prov:Attribution</t>
         </is>
       </c>
-      <c r="H44" s="215" t="inlineStr">
+      <c r="H44" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I44" s="213" t="inlineStr">
+      <c r="I44" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J44" s="213" t="inlineStr">
+      <c r="J44" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K44" s="75" t="n"/>
-      <c r="L44" s="213" t="inlineStr">
+      <c r="L44" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Attribution' tab.</t>
         </is>
       </c>
-      <c r="M44" s="213" t="inlineStr">
+      <c r="M44" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Attribution' tab.</t>
         </is>
       </c>
-      <c r="N44" s="213" t="inlineStr">
+      <c r="N44" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'Attribution' tab.</t>
         </is>
@@ -23859,9 +23914,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="U44" s="218" t="n"/>
-      <c r="V44" s="218" t="n"/>
-      <c r="W44" s="218" t="n"/>
+      <c r="U44" s="217" t="n"/>
+      <c r="V44" s="217" t="n"/>
+      <c r="W44" s="217" t="n"/>
     </row>
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="221" t="inlineStr">
@@ -23889,7 +23944,7 @@
           <t>This property makes use of another small class (dcat:Relationship), in which you can indicate the related resource (via its identifier) and the nature of the relation (based on a controlled vocabulary, which is described in the information of the class).</t>
         </is>
       </c>
-      <c r="F45" s="215" t="inlineStr">
+      <c r="F45" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -23954,7 +24009,7 @@
       <c r="W45" s="221" t="n"/>
     </row>
     <row r="46" ht="48" customHeight="1">
-      <c r="A46" s="218" t="inlineStr">
+      <c r="A46" s="217" t="inlineStr">
         <is>
           <t>quality annotation</t>
         </is>
@@ -23964,7 +24019,7 @@
           <t>Refers to a quality annotation.</t>
         </is>
       </c>
-      <c r="C46" s="218" t="inlineStr">
+      <c r="C46" s="217" t="inlineStr">
         <is>
           <t>dqv:hasQualityAnnotation</t>
         </is>
@@ -23989,33 +24044,33 @@
           <t>dqv:QualityCertificate</t>
         </is>
       </c>
-      <c r="H46" s="215" t="inlineStr">
+      <c r="H46" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I46" s="213" t="inlineStr">
+      <c r="I46" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J46" s="213" t="inlineStr">
+      <c r="J46" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K46" s="75" t="n"/>
-      <c r="L46" s="213" t="inlineStr">
+      <c r="L46" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'QualityCertificate' tab.</t>
         </is>
       </c>
-      <c r="M46" s="213" t="inlineStr">
+      <c r="M46" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'QualityCertificate' tab.</t>
         </is>
       </c>
-      <c r="N46" s="213" t="inlineStr">
+      <c r="N46" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'QualityCertificate' tab.</t>
         </is>
@@ -24035,9 +24090,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="U46" s="218" t="n"/>
-      <c r="V46" s="218" t="n"/>
-      <c r="W46" s="218" t="n"/>
+      <c r="U46" s="217" t="n"/>
+      <c r="V46" s="217" t="n"/>
+      <c r="W46" s="217" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="221" t="inlineStr">
@@ -24065,7 +24120,7 @@
           <t>This property should point to the first known date of issuance, such as the publication date in a data repository. Example: 2023-12-10T13:16:10.246Z.</t>
         </is>
       </c>
-      <c r="F47" s="215" t="inlineStr">
+      <c r="F47" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -24118,7 +24173,7 @@
       <c r="W47" s="221" t="n"/>
     </row>
     <row r="48" ht="160" customHeight="1">
-      <c r="A48" s="218" t="inlineStr">
+      <c r="A48" s="217" t="inlineStr">
         <is>
           <t>retention period</t>
         </is>
@@ -24128,7 +24183,7 @@
           <t>A temporal period during which the dataset is available for secondary use.</t>
         </is>
       </c>
-      <c r="C48" s="218" t="inlineStr">
+      <c r="C48" s="217" t="inlineStr">
         <is>
           <t>healthdcatap:retentionPeriod</t>
         </is>
@@ -24157,17 +24212,17 @@
           <t>dct:PeriodOfTime</t>
         </is>
       </c>
-      <c r="H48" s="215" t="inlineStr">
+      <c r="H48" s="213" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I48" s="213" t="inlineStr">
+      <c r="I48" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J48" s="213" t="inlineStr">
+      <c r="J48" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -24177,17 +24232,17 @@
           <t>custom:retention_period</t>
         </is>
       </c>
-      <c r="L48" s="213" t="inlineStr">
+      <c r="L48" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="M48" s="213" t="inlineStr">
+      <c r="M48" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="N48" s="213" t="inlineStr">
+      <c r="N48" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
@@ -24207,9 +24262,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="U48" s="218" t="n"/>
-      <c r="V48" s="218" t="n"/>
-      <c r="W48" s="218" t="n"/>
+      <c r="U48" s="217" t="n"/>
+      <c r="V48" s="217" t="n"/>
+      <c r="W48" s="217" t="n"/>
     </row>
     <row r="49" ht="80" customHeight="1">
       <c r="A49" s="221" t="inlineStr">
@@ -24237,7 +24292,7 @@
           <t>This property makes use of the dcat:Distribution class to describe a sample distribution of the dataset, which can consist of anonymised or synthetic data, or a data dictionary provided in CSVW format. This is currently being further developed by the TEHDAS2 programme. More information can be found here: https://healthdcat-ap.github.io/#sample-distribution</t>
         </is>
       </c>
-      <c r="F49" s="215" t="inlineStr">
+      <c r="F49" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -24289,7 +24344,7 @@
       <c r="W49" s="221" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="218" t="inlineStr">
+      <c r="A50" s="217" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -24299,7 +24354,7 @@
           <t>A related resource from which the described resource is derived.</t>
         </is>
       </c>
-      <c r="C50" s="218" t="inlineStr">
+      <c r="C50" s="217" t="inlineStr">
         <is>
           <t>dct:source</t>
         </is>
@@ -24309,7 +24364,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E50" s="219" t="inlineStr">
+      <c r="E50" s="218" t="inlineStr">
         <is>
           <t>Indicate the dataset on which this described dataset is based.</t>
         </is>
@@ -24324,17 +24379,17 @@
           <t>dcat:Dataset (IRI)</t>
         </is>
       </c>
-      <c r="H50" s="215" t="inlineStr">
+      <c r="H50" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I50" s="213" t="inlineStr">
+      <c r="I50" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J50" s="213" t="inlineStr">
+      <c r="J50" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -24349,8 +24404,8 @@
           <t>If applicable, add the URI for the source dataset here.</t>
         </is>
       </c>
-      <c r="M50" s="213" t="n"/>
-      <c r="N50" s="213" t="n"/>
+      <c r="M50" s="219" t="n"/>
+      <c r="N50" s="219" t="n"/>
       <c r="P50" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -24361,9 +24416,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U50" s="218" t="n"/>
-      <c r="V50" s="218" t="n"/>
-      <c r="W50" s="218" t="n"/>
+      <c r="U50" s="217" t="n"/>
+      <c r="V50" s="217" t="n"/>
+      <c r="W50" s="217" t="n"/>
     </row>
     <row r="51" ht="64" customHeight="1">
       <c r="A51" s="221" t="inlineStr">
@@ -24392,7 +24447,7 @@
 For example: http://publications.europa.eu/resource/authority/dataset-status/COMPLETED</t>
         </is>
       </c>
-      <c r="F51" s="215" t="inlineStr">
+      <c r="F51" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -24440,7 +24495,7 @@
       <c r="W51" s="221" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="218" t="inlineStr">
+      <c r="A52" s="217" t="inlineStr">
         <is>
           <t>temporal coverage</t>
         </is>
@@ -24450,7 +24505,7 @@
           <t>Temporal characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C52" s="218" t="inlineStr">
+      <c r="C52" s="217" t="inlineStr">
         <is>
           <t>dct:temporal</t>
         </is>
@@ -24475,17 +24530,17 @@
           <t>dct:PeriodOfTime</t>
         </is>
       </c>
-      <c r="H52" s="215" t="inlineStr">
+      <c r="H52" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I52" s="213" t="inlineStr">
+      <c r="I52" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J52" s="213" t="inlineStr">
+      <c r="J52" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -24495,17 +24550,17 @@
           <t>custom:temporal_coverage</t>
         </is>
       </c>
-      <c r="L52" s="213" t="inlineStr">
+      <c r="L52" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="M52" s="213" t="inlineStr">
+      <c r="M52" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="N52" s="213" t="inlineStr">
+      <c r="N52" s="219" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
@@ -24525,9 +24580,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="U52" s="218" t="n"/>
-      <c r="V52" s="218" t="n"/>
-      <c r="W52" s="218" t="n"/>
+      <c r="U52" s="217" t="n"/>
+      <c r="V52" s="217" t="n"/>
+      <c r="W52" s="217" t="n"/>
     </row>
     <row r="53" ht="64" customHeight="1">
       <c r="A53" s="221" t="inlineStr">
@@ -24555,7 +24610,7 @@
           <t>If the dataset is a time-series, this should correspond to the spacing of items in the series. For other kinds of datasets, this property will usually indicate the smallest time difference between items in the dataset. The time period has to be provided in the xsd:duration format.</t>
         </is>
       </c>
-      <c r="F53" s="215" t="inlineStr">
+      <c r="F53" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -24603,7 +24658,7 @@
       <c r="W53" s="221" t="n"/>
     </row>
     <row r="54" ht="74.25" customHeight="1">
-      <c r="A54" s="218" t="inlineStr">
+      <c r="A54" s="217" t="inlineStr">
         <is>
           <t>theme</t>
         </is>
@@ -24613,7 +24668,7 @@
           <t>A main category of the resource. A resource can have multiple themes.</t>
         </is>
       </c>
-      <c r="C54" s="218" t="inlineStr">
+      <c r="C54" s="217" t="inlineStr">
         <is>
           <t>dcat:theme</t>
         </is>
@@ -24633,22 +24688,22 @@
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G54" s="215" t="inlineStr">
+      <c r="G54" s="213" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H54" s="215" t="inlineStr">
+      <c r="H54" s="213" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I54" s="213" t="inlineStr">
+      <c r="I54" s="219" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J54" s="213" t="inlineStr">
+      <c r="J54" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -24658,9 +24713,9 @@
           <t>custom:theme</t>
         </is>
       </c>
-      <c r="L54" s="213" t="n"/>
-      <c r="M54" s="213" t="n"/>
-      <c r="N54" s="213" t="n"/>
+      <c r="L54" s="219" t="n"/>
+      <c r="M54" s="219" t="n"/>
+      <c r="N54" s="219" t="n"/>
       <c r="P54" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -24676,9 +24731,9 @@
           <t>http://publications.europa.eu/resource/authority/data-theme/HEAL</t>
         </is>
       </c>
-      <c r="U54" s="218" t="n"/>
-      <c r="V54" s="218" t="n"/>
-      <c r="W54" s="218" t="n"/>
+      <c r="U54" s="217" t="n"/>
+      <c r="V54" s="217" t="n"/>
+      <c r="W54" s="217" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="221" t="inlineStr">
@@ -24706,7 +24761,7 @@
           <t>Provide a unique title for your Dataset, which can be repeated in multiple languages. Example: Healthy Brain Study - Physiological Data</t>
         </is>
       </c>
-      <c r="F55" s="215" t="inlineStr">
+      <c r="F55" s="213" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -24757,7 +24812,7 @@
       <c r="W55" s="221" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="218" t="inlineStr">
+      <c r="A56" s="217" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -24767,7 +24822,7 @@
           <t>The nature or genre of the resource.</t>
         </is>
       </c>
-      <c r="C56" s="218" t="inlineStr">
+      <c r="C56" s="217" t="inlineStr">
         <is>
           <t>dct:type</t>
         </is>
@@ -24788,22 +24843,22 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G56" s="215" t="inlineStr">
+      <c r="G56" s="213" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H56" s="215" t="inlineStr">
+      <c r="H56" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I56" s="213" t="inlineStr">
+      <c r="I56" s="219" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J56" s="213" t="inlineStr">
+      <c r="J56" s="219" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -24813,9 +24868,9 @@
           <t>custom:dcat_type</t>
         </is>
       </c>
-      <c r="L56" s="213" t="n"/>
-      <c r="M56" s="213" t="n"/>
-      <c r="N56" s="213" t="n"/>
+      <c r="L56" s="219" t="n"/>
+      <c r="M56" s="219" t="n"/>
+      <c r="N56" s="219" t="n"/>
       <c r="O56" s="84" t="n"/>
       <c r="P56" s="214" t="inlineStr">
         <is>
@@ -24829,9 +24884,9 @@
       </c>
       <c r="R56" s="84" t="n"/>
       <c r="T56" s="84" t="n"/>
-      <c r="U56" s="218" t="n"/>
-      <c r="V56" s="218" t="n"/>
-      <c r="W56" s="218" t="n"/>
+      <c r="U56" s="217" t="n"/>
+      <c r="V56" s="217" t="n"/>
+      <c r="W56" s="217" t="n"/>
     </row>
     <row r="57" ht="80" customHeight="1">
       <c r="A57" s="221" t="inlineStr">
@@ -24921,7 +24976,7 @@
       <c r="W57" s="221" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="218" t="inlineStr">
+      <c r="A58" s="217" t="inlineStr">
         <is>
           <t>version</t>
         </is>
@@ -24931,7 +24986,7 @@
           <t>The version indicator (name or identifier) of a resource.</t>
         </is>
       </c>
-      <c r="C58" s="218" t="inlineStr">
+      <c r="C58" s="217" t="inlineStr">
         <is>
           <t>dcat:version</t>
         </is>
@@ -24946,27 +25001,27 @@
           <t>Suggested practice: track major_version.minor_version. Register a new identifier for major changes (e.g., 1.0.0 for an unchanged dataset).</t>
         </is>
       </c>
-      <c r="F58" s="215" t="inlineStr">
+      <c r="F58" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G58" s="215" t="inlineStr">
+      <c r="G58" s="213" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H58" s="215" t="inlineStr">
+      <c r="H58" s="213" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I58" s="213" t="inlineStr">
+      <c r="I58" s="219" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J58" s="213" t="inlineStr">
+      <c r="J58" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -24976,9 +25031,9 @@
           <t>custom:version</t>
         </is>
       </c>
-      <c r="L58" s="213" t="n"/>
-      <c r="M58" s="213" t="n"/>
-      <c r="N58" s="213" t="n"/>
+      <c r="L58" s="219" t="n"/>
+      <c r="M58" s="219" t="n"/>
+      <c r="N58" s="219" t="n"/>
       <c r="P58" s="214" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24990,9 +25045,9 @@
         </is>
       </c>
       <c r="S58" s="84" t="n"/>
-      <c r="U58" s="218" t="n"/>
-      <c r="V58" s="218" t="n"/>
-      <c r="W58" s="218" t="n"/>
+      <c r="U58" s="217" t="n"/>
+      <c r="V58" s="217" t="n"/>
+      <c r="W58" s="217" t="n"/>
     </row>
     <row r="59" ht="32" customHeight="1">
       <c r="A59" s="221" t="inlineStr">
@@ -25071,7 +25126,7 @@
       <c r="W59" s="221" t="n"/>
     </row>
     <row r="60" ht="84.75" customHeight="1">
-      <c r="A60" s="218" t="inlineStr">
+      <c r="A60" s="217" t="inlineStr">
         <is>
           <t>was generated by</t>
         </is>
@@ -25081,7 +25136,7 @@
           <t>Generation is the completion of production of a new entity by an activity. This entity did not exist before generation and becomes available for usage after this generation.</t>
         </is>
       </c>
-      <c r="C60" s="218" t="inlineStr">
+      <c r="C60" s="217" t="inlineStr">
         <is>
           <t>prov:wasGeneratedBy</t>
         </is>
@@ -25091,7 +25146,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="F60" s="215" t="inlineStr">
+      <c r="F60" s="213" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25101,25 +25156,25 @@
           <t>prov:Activity</t>
         </is>
       </c>
-      <c r="H60" s="215" t="inlineStr">
+      <c r="H60" s="213" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I60" s="213" t="inlineStr">
+      <c r="I60" s="219" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J60" s="213" t="inlineStr">
+      <c r="J60" s="219" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K60" s="75" t="n"/>
-      <c r="L60" s="213" t="n"/>
-      <c r="M60" s="213" t="n"/>
-      <c r="N60" s="213" t="n"/>
+      <c r="L60" s="219" t="n"/>
+      <c r="M60" s="219" t="n"/>
+      <c r="N60" s="219" t="n"/>
       <c r="P60" s="214" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -25130,9 +25185,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="U60" s="218" t="n"/>
-      <c r="V60" s="218" t="n"/>
-      <c r="W60" s="218" t="n"/>
+      <c r="U60" s="217" t="n"/>
+      <c r="V60" s="217" t="n"/>
+      <c r="W60" s="217" t="n"/>
     </row>
     <row r="61" customFormat="1" s="84">
       <c r="A61" s="110" t="n"/>
@@ -25523,7 +25578,7 @@
       </c>
       <c r="J2" s="125" t="n"/>
       <c r="K2" s="126" t="n"/>
-      <c r="L2" s="213" t="n"/>
+      <c r="L2" s="219" t="n"/>
       <c r="X2" s="102" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -25684,7 +25739,7 @@
           <t>_id</t>
         </is>
       </c>
-      <c r="L4" s="213" t="n"/>
+      <c r="L4" s="219" t="n"/>
       <c r="X4" s="102" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -25788,7 +25843,7 @@
           <t>publisher note</t>
         </is>
       </c>
-      <c r="B6" s="216" t="inlineStr">
+      <c r="B6" s="215" t="inlineStr">
         <is>
           <t>A description of the publisher's activities.</t>
         </is>
@@ -25803,7 +25858,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E6" s="216" t="inlineStr">
+      <c r="E6" s="215" t="inlineStr">
         <is>
           <t>Note: This property will be deprecated in the next major release.
 This property can be repeated for parallel language versions of the publisher notes. Example: "Sciensano is a research institute and the national public health institute of Belgium. It is a so-called federal scientific institution that operates under the authority of the federal minister of Public Health and the federal minister of Agriculture of Belgium."@en</t>
@@ -25835,7 +25890,7 @@
         </is>
       </c>
       <c r="K6" s="126" t="n"/>
-      <c r="L6" s="213" t="n"/>
+      <c r="L6" s="219" t="n"/>
       <c r="X6" s="102" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -25986,7 +26041,7 @@
           <t>_type</t>
         </is>
       </c>
-      <c r="L8" s="213" t="n"/>
+      <c r="L8" s="219" t="n"/>
       <c r="X8" s="102" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>

--- a/Documents/Health-RI_v2.1.0-for-FDP.xlsx
+++ b/Documents/Health-RI_v2.1.0-for-FDP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexanderharms/Documents/Repositories/health-ri-metadata/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C34B43-D8D6-C44B-8E68-06E4A63F32E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9AEE0A-296B-6F46-A51B-5A794C5098E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="20540" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34400" yWindow="-28200" windowWidth="34400" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2734" uniqueCount="879">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2722" uniqueCount="871">
   <si>
     <t>Property label</t>
   </si>
@@ -136,7 +136,7 @@
     <t>http://publications.europa.eu/resource/authority/access-right</t>
   </si>
   <si>
-    <t>Information that indicates whether the Dataset is publicly accessible, has access restrictions or is not public. It is foreseen that one of the three options has to be used: public, restricted, non-public.
+    <t>Information that indicates whether the Dataset is publicly accessible, has access restrictions or is not public. One of the three options must be used: public, restricted, non-public.
     Open Data (Public): The dataset is available under general open data rules, such as those covered by the High Value Datasets Implementing Regulation.
     Protected Data (Restricted): The dataset contains protected data and is accessible only under specific conditions, as outlined in regulations like the Data Governance Act.
     Sensitive Data (Non-public): The dataset includes resources that may contain sensitive or personal information, falling under regulations such as the EHDS Regulation.
@@ -206,7 +206,7 @@
     <t>healthdcatap:analytics</t>
   </si>
   <si>
-    <t>Publishers are encouraged to provide URLs pointing to document repositories where users can access or request associated resources such as technical reports of the dataset, quality measurements, usability indicators, etc. Note that HealthDCAT-AP also mentions API endpoints or analytics services, but these would not be Distributions but rather DatasetServices.</t>
+    <t>Publishers are encouraged to provide URLs pointing to document repositories where users can access or request associated resources such as technical reports of the dataset, quality measurements, usability indicators, etc. Note that HealthDCAT-AP also mentions API endpoints or analytics services, but these would be Data Services rather than Distributions.</t>
   </si>
   <si>
     <t>dcat:Distribution (IRI)</t>
@@ -526,23 +526,25 @@
     <t>custom:has_version</t>
   </si>
   <si>
-    <t>fill in URI to dcat:Dataset that is another version of current Dataset</t>
+    <t>Enter the URI for the dcat:Dataset that is another version of the current Dataset.</t>
   </si>
   <si>
     <t>health condition of interest</t>
   </si>
   <si>
-    <t>Relates a dataset to a SNOMED CT, ICD-10, or ORPHAcode concept representing a disease, disorder, or other clinical condition that the dataset concerns as a whole.</t>
+    <t xml:space="preserve">	
+Relates a dataset to a SNOMED CT, ICD-10, ICD-11, or ORPHAcode concept representing a disease, disorder, or other clinical condition that the dataset concerns as a whole.</t>
   </si>
   <si>
     <t>hri:healthConditionOfInterest</t>
   </si>
   <si>
-    <t>Use this property to describe health conditions of interest in dataset-level metadata. Multiple values may be provided. Select only SNOMED CT, ICD-10, or ORPHAcode concepts that represent diseases, disorders, or other clinical conditions. The relation does not assert that any individual participant has been diagnosed with a condition and is not intended to enumerate diagnoses in individual records.
+    <t xml:space="preserve">	
+Use this property to describe health conditions of interest in dataset-level metadata. Multiple values may be provided. Select only SNOMED CT, ICD-10, ICD-11, or ORPHAcode concepts that represent diseases, disorders, or other clinical conditions. The relation does not assert that any individual participant has been diagnosed with a condition and is not intended to enumerate diagnoses in individual records.
 Example: A Dataset concerning myocardial infarction can use http://snomed.info/id/22298006.</t>
   </si>
   <si>
-    <t>^(http://snomed\.info/id/[0-9]{6,18}|http://id\.who\.int/icd/entity/[0-9]+|http://www\.orpha\.net/ORDO/Orphanet_[0-9]+)$</t>
+    <t>^(http://snomed[.]info/id/[0-9]+|http://id[.]who[.]int/icd/release/10/([0-9]{4}/)?[A-Za-z0-9][A-Za-z0-9.-]* |http://id[.]who[.]int/icd/release/11/.+ |http://www[.]orpha[.]net/ORDO/Orphanet_[0-9]+)$</t>
   </si>
   <si>
     <t>health theme</t>
@@ -919,8 +921,8 @@
   <si>
     <t>This property makes use of another small class (prov:Attribution). There, you can choose one of the roles as listed in the controlled vocabulary and link that to a specific Agent (expressed with foaf:Agent).
 Repeat this property if you wish to specify multiple roles for the same agent.
-Refer to the Attribution class for more information how to fill this.
-Use this property if you would like to indicate the funder of the (research project that resulted in creation of the) dataset.
+Refer to the Attribution class for more information on how to fill this in.
+Use this property if you would like to indicate the funder of the dataset (or of the research project that resulted in its creation).
 The value for role in the Attribution class then becomes: https://standards.iso.org/iso/19115/resources/Codelists/gml/CI_RoleCode.xml#funder</t>
   </si>
   <si>
@@ -1177,354 +1179,354 @@
 Use this property to link a structured dataset to a CSVW TableGroup that documents its data variables, columns, or fields in a machine-readable way.</t>
   </si>
   <si>
+    <t>csvw:TableGroup (IRI)</t>
+  </si>
+  <si>
+    <t>Enter the value on the 'TableGroup' tab.</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>The version indicator (name or identifier) of a resource.</t>
+  </si>
+  <si>
+    <t>dcat:version</t>
+  </si>
+  <si>
+    <t>Suggested practice: track major_version.minor_version. Register a new identifier for major changes (e.g., 1.0.0 for an unchanged dataset).</t>
+  </si>
+  <si>
+    <t>custom:version</t>
+  </si>
+  <si>
+    <t>version notes</t>
+  </si>
+  <si>
+    <t>A description of changes between this version and the previous version of the Asset.</t>
+  </si>
+  <si>
+    <t>adms:versionNotes</t>
+  </si>
+  <si>
+    <t>Provide a short description of changes made to the dataset since the previous version.</t>
+  </si>
+  <si>
+    <t>custom:version_notes</t>
+  </si>
+  <si>
+    <t>was generated by</t>
+  </si>
+  <si>
+    <t>Generation is the completion of production of a new entity by an activity. This entity did not exist before generation and becomes available for usage after this generation.</t>
+  </si>
+  <si>
+    <t>prov:wasGeneratedBy</t>
+  </si>
+  <si>
+    <t>prov:Activity</t>
+  </si>
+  <si>
+    <t>hrishapes:ActivityShape</t>
+  </si>
+  <si>
+    <t>prefix</t>
+  </si>
+  <si>
+    <t>namespace</t>
+  </si>
+  <si>
+    <t>adms</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/adms#</t>
+  </si>
+  <si>
+    <t>csvw</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/csvw#</t>
+  </si>
+  <si>
+    <t>dash</t>
+  </si>
+  <si>
+    <t>http://datashapes.org/dash#</t>
+  </si>
+  <si>
+    <t>dcat</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/dcat#</t>
+  </si>
+  <si>
+    <t>dcatap</t>
+  </si>
+  <si>
+    <t>http://data.europa.eu/r5r/</t>
+  </si>
+  <si>
+    <t>dct</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/</t>
+  </si>
+  <si>
+    <t>dpv</t>
+  </si>
+  <si>
+    <t>https://w3id.org/dpv#</t>
+  </si>
+  <si>
+    <t>dqv</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/TR/vocab-dqv/</t>
+  </si>
+  <si>
+    <t>eli</t>
+  </si>
+  <si>
+    <t>http://data.europa.eu/eli/ontology#</t>
+  </si>
+  <si>
+    <t>foaf</t>
+  </si>
+  <si>
+    <t>http://xmlns.com/foaf/0.1/</t>
+  </si>
+  <si>
+    <t>healthdcatap</t>
+  </si>
+  <si>
+    <t>http://healthdataportal.eu/ns/health#</t>
+  </si>
+  <si>
+    <t>hri</t>
+  </si>
+  <si>
+    <t>https://w3id.org/health-ri/metadata-vocabulary#</t>
+  </si>
+  <si>
+    <t>owl</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2002/07/owl#</t>
+  </si>
+  <si>
+    <t>rdf</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/1999/02/22-rdf-syntax-ns#</t>
+  </si>
+  <si>
+    <t>rdfs</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2000/01/rdf-schema#</t>
+  </si>
+  <si>
+    <t>sh</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/shacl#</t>
+  </si>
+  <si>
+    <t>skos</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2004/02/skos/core#</t>
+  </si>
+  <si>
+    <t>spdx</t>
+  </si>
+  <si>
+    <t>http://spdx.org/rdf/terms#</t>
+  </si>
+  <si>
+    <t>vcard</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2006/vcard/ns#</t>
+  </si>
+  <si>
+    <t>xsd</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2001/XMLSchema#</t>
+  </si>
+  <si>
+    <t>edam</t>
+  </si>
+  <si>
+    <t>http://edamontology.org/</t>
+  </si>
+  <si>
+    <t>oa</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/oa#</t>
+  </si>
+  <si>
+    <t>prov</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/prov#</t>
+  </si>
+  <si>
+    <t>schema</t>
+  </si>
+  <si>
+    <t>http://schema.org/</t>
+  </si>
+  <si>
+    <t>hrishapes</t>
+  </si>
+  <si>
+    <t>http://data.health-ri.nl/core/p2/</t>
+  </si>
+  <si>
+    <t>sheet_name</t>
+  </si>
+  <si>
+    <t>class_URI</t>
+  </si>
+  <si>
+    <t>SHACL_target_ontology_name</t>
+  </si>
+  <si>
+    <t>SHACL_independent_class</t>
+  </si>
+  <si>
+    <t>SeMPyRO_inherits_from</t>
+  </si>
+  <si>
+    <t>SeMPyRO_import_classes</t>
+  </si>
+  <si>
+    <t>SeMPyRO_annotations_ontology</t>
+  </si>
+  <si>
+    <t>SeMPyRO_annotations_IRI</t>
+  </si>
+  <si>
+    <t>SeMPyRO_add_rdf_model</t>
+  </si>
+  <si>
+    <t>Resource</t>
+  </si>
+  <si>
+    <t>hrishapes:Resource</t>
+  </si>
+  <si>
+    <t>dcat:Resource</t>
+  </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>hrishapes:Dataset</t>
+  </si>
+  <si>
+    <t>dcat:Dataset</t>
+  </si>
+  <si>
+    <t>Catalogue</t>
+  </si>
+  <si>
+    <t>hrishapes:Catalog</t>
+  </si>
+  <si>
+    <t>dcat:Catalog</t>
+  </si>
+  <si>
+    <t>Agent</t>
+  </si>
+  <si>
+    <t>hrishapes:Agent</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>hrishapes:Kind</t>
+  </si>
+  <si>
+    <t>Distribution</t>
+  </si>
+  <si>
+    <t>hrishapes:Distribution</t>
+  </si>
+  <si>
+    <t>dcat:Distribution</t>
+  </si>
+  <si>
+    <t>DatasetSeries</t>
+  </si>
+  <si>
+    <t>hrishapes:DatasetSeries</t>
+  </si>
+  <si>
+    <t>dcat:DatasetSeries</t>
+  </si>
+  <si>
+    <t>DataService</t>
+  </si>
+  <si>
+    <t>hrishapes:DataService</t>
+  </si>
+  <si>
+    <t>dcat:DataService</t>
+  </si>
+  <si>
+    <t>adms_Identifier</t>
+  </si>
+  <si>
+    <t>hrishapes:Identifier</t>
+  </si>
+  <si>
+    <t>PeriodOfTime</t>
+  </si>
+  <si>
+    <t>hrishapes:PeriodOfTime</t>
+  </si>
+  <si>
+    <t>Attribution</t>
+  </si>
+  <si>
+    <t>hrishapes:Attribution</t>
+  </si>
+  <si>
+    <t>Relationship</t>
+  </si>
+  <si>
+    <t>hrishapes:Relationship</t>
+  </si>
+  <si>
+    <t>QualityCertificate</t>
+  </si>
+  <si>
+    <t>hrishapes:QualityCertificate</t>
+  </si>
+  <si>
+    <t>Checksum</t>
+  </si>
+  <si>
+    <t>hrishapes:Checksum</t>
+  </si>
+  <si>
+    <t>spdx:Checksum</t>
+  </si>
+  <si>
+    <t>TableGroup</t>
+  </si>
+  <si>
+    <t>hrishapes:TableGroup</t>
+  </si>
+  <si>
     <t>csvw:TableGroup</t>
   </si>
   <si>
-    <t>Enter the value on the 'TableGroup' tab.</t>
-  </si>
-  <si>
-    <t>hrishapes:TableGroupShape</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>The version indicator (name or identifier) of a resource.</t>
-  </si>
-  <si>
-    <t>dcat:version</t>
-  </si>
-  <si>
-    <t>Suggested practice: track major_version.minor_version. Register a new identifier for major changes (e.g., 1.0.0 for an unchanged dataset).</t>
-  </si>
-  <si>
-    <t>custom:version</t>
-  </si>
-  <si>
-    <t>version notes</t>
-  </si>
-  <si>
-    <t>A description of changes between this version and the previous version of the Asset.</t>
-  </si>
-  <si>
-    <t>adms:versionNotes</t>
-  </si>
-  <si>
-    <t>Provide a short description of changes made to the dataset since the previous version.</t>
-  </si>
-  <si>
-    <t>custom:version_notes</t>
-  </si>
-  <si>
-    <t>was generated by</t>
-  </si>
-  <si>
-    <t>Generation is the completion of production of a new entity by an activity. This entity did not exist before generation and becomes available for usage after this generation.</t>
-  </si>
-  <si>
-    <t>prov:wasGeneratedBy</t>
-  </si>
-  <si>
-    <t>prov:Activity</t>
-  </si>
-  <si>
-    <t>hrishapes:ActivityShape</t>
-  </si>
-  <si>
-    <t>prefix</t>
-  </si>
-  <si>
-    <t>namespace</t>
-  </si>
-  <si>
-    <t>adms</t>
-  </si>
-  <si>
-    <t>http://www.w3.org/ns/adms#</t>
-  </si>
-  <si>
-    <t>csvw</t>
-  </si>
-  <si>
-    <t>http://www.w3.org/ns/csvw#</t>
-  </si>
-  <si>
-    <t>dash</t>
-  </si>
-  <si>
-    <t>http://datashapes.org/dash#</t>
-  </si>
-  <si>
-    <t>dcat</t>
-  </si>
-  <si>
-    <t>http://www.w3.org/ns/dcat#</t>
-  </si>
-  <si>
-    <t>dcatap</t>
-  </si>
-  <si>
-    <t>http://data.europa.eu/r5r/</t>
-  </si>
-  <si>
-    <t>dct</t>
-  </si>
-  <si>
-    <t>http://purl.org/dc/terms/</t>
-  </si>
-  <si>
-    <t>dpv</t>
-  </si>
-  <si>
-    <t>https://w3id.org/dpv#</t>
-  </si>
-  <si>
-    <t>dqv</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/TR/vocab-dqv/</t>
-  </si>
-  <si>
-    <t>eli</t>
-  </si>
-  <si>
-    <t>http://data.europa.eu/eli/ontology#</t>
-  </si>
-  <si>
-    <t>foaf</t>
-  </si>
-  <si>
-    <t>http://xmlns.com/foaf/0.1/</t>
-  </si>
-  <si>
-    <t>healthdcatap</t>
-  </si>
-  <si>
-    <t>http://healthdataportal.eu/ns/health#</t>
-  </si>
-  <si>
-    <t>hri</t>
-  </si>
-  <si>
-    <t>https://w3id.org/health-ri/metadata-vocabulary#</t>
-  </si>
-  <si>
-    <t>owl</t>
-  </si>
-  <si>
-    <t>http://www.w3.org/2002/07/owl#</t>
-  </si>
-  <si>
-    <t>rdf</t>
-  </si>
-  <si>
-    <t>http://www.w3.org/1999/02/22-rdf-syntax-ns#</t>
-  </si>
-  <si>
-    <t>rdfs</t>
-  </si>
-  <si>
-    <t>http://www.w3.org/2000/01/rdf-schema#</t>
-  </si>
-  <si>
-    <t>sh</t>
-  </si>
-  <si>
-    <t>http://www.w3.org/ns/shacl#</t>
-  </si>
-  <si>
-    <t>skos</t>
-  </si>
-  <si>
-    <t>http://www.w3.org/2004/02/skos/core#</t>
-  </si>
-  <si>
-    <t>spdx</t>
-  </si>
-  <si>
-    <t>http://spdx.org/rdf/terms#</t>
-  </si>
-  <si>
-    <t>vcard</t>
-  </si>
-  <si>
-    <t>http://www.w3.org/2006/vcard/ns#</t>
-  </si>
-  <si>
-    <t>xsd</t>
-  </si>
-  <si>
-    <t>http://www.w3.org/2001/XMLSchema#</t>
-  </si>
-  <si>
-    <t>edam</t>
-  </si>
-  <si>
-    <t>http://edamontology.org/</t>
-  </si>
-  <si>
-    <t>oa</t>
-  </si>
-  <si>
-    <t>http://www.w3.org/ns/oa#</t>
-  </si>
-  <si>
-    <t>prov</t>
-  </si>
-  <si>
-    <t>http://www.w3.org/ns/prov#</t>
-  </si>
-  <si>
-    <t>schema</t>
-  </si>
-  <si>
-    <t>http://schema.org/</t>
-  </si>
-  <si>
-    <t>hrishapes</t>
-  </si>
-  <si>
-    <t>http://data.health-ri.nl/core/p2/</t>
-  </si>
-  <si>
-    <t>sheet_name</t>
-  </si>
-  <si>
-    <t>class_URI</t>
-  </si>
-  <si>
-    <t>SHACL_target_ontology_name</t>
-  </si>
-  <si>
-    <t>SHACL_independent_class</t>
-  </si>
-  <si>
-    <t>SeMPyRO_inherits_from</t>
-  </si>
-  <si>
-    <t>SeMPyRO_import_classes</t>
-  </si>
-  <si>
-    <t>SeMPyRO_annotations_ontology</t>
-  </si>
-  <si>
-    <t>SeMPyRO_annotations_IRI</t>
-  </si>
-  <si>
-    <t>SeMPyRO_add_rdf_model</t>
-  </si>
-  <si>
-    <t>Resource</t>
-  </si>
-  <si>
-    <t>hrishapes:Resource</t>
-  </si>
-  <si>
-    <t>dcat:Resource</t>
-  </si>
-  <si>
-    <t>Dataset</t>
-  </si>
-  <si>
-    <t>hrishapes:Dataset</t>
-  </si>
-  <si>
-    <t>dcat:Dataset</t>
-  </si>
-  <si>
-    <t>Catalogue</t>
-  </si>
-  <si>
-    <t>hrishapes:Catalog</t>
-  </si>
-  <si>
-    <t>dcat:Catalog</t>
-  </si>
-  <si>
-    <t>Agent</t>
-  </si>
-  <si>
-    <t>hrishapes:Agent</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>hrishapes:Kind</t>
-  </si>
-  <si>
-    <t>Distribution</t>
-  </si>
-  <si>
-    <t>hrishapes:Distribution</t>
-  </si>
-  <si>
-    <t>dcat:Distribution</t>
-  </si>
-  <si>
-    <t>DatasetSeries</t>
-  </si>
-  <si>
-    <t>hrishapes:DatasetSeries</t>
-  </si>
-  <si>
-    <t>dcat:DatasetSeries</t>
-  </si>
-  <si>
-    <t>DataService</t>
-  </si>
-  <si>
-    <t>hrishapes:DataService</t>
-  </si>
-  <si>
-    <t>dcat:DataService</t>
-  </si>
-  <si>
-    <t>adms_Identifier</t>
-  </si>
-  <si>
-    <t>hrishapes:Identifier</t>
-  </si>
-  <si>
-    <t>PeriodOfTime</t>
-  </si>
-  <si>
-    <t>hrishapes:PeriodOfTime</t>
-  </si>
-  <si>
-    <t>Attribution</t>
-  </si>
-  <si>
-    <t>hrishapes:Attribution</t>
-  </si>
-  <si>
-    <t>Relationship</t>
-  </si>
-  <si>
-    <t>hrishapes:Relationship</t>
-  </si>
-  <si>
-    <t>QualityCertificate</t>
-  </si>
-  <si>
-    <t>hrishapes:QualityCertificate</t>
-  </si>
-  <si>
-    <t>Checksum</t>
-  </si>
-  <si>
-    <t>hrishapes:Checksum</t>
-  </si>
-  <si>
-    <t>spdx:Checksum</t>
-  </si>
-  <si>
-    <t>TableGroup</t>
-  </si>
-  <si>
-    <t>hrishapes:TableGroup</t>
-  </si>
-  <si>
     <t>Table</t>
   </si>
   <si>
@@ -1579,7 +1581,7 @@
     <t>dcat:Catalog (IRI)</t>
   </si>
   <si>
-    <t>If applicable, add URI to connected dcat:Catalog</t>
+    <t>If applicable, enter the URI of the connected dcat:Catalog.</t>
   </si>
   <si>
     <t>custom:contact</t>
@@ -1605,7 +1607,7 @@
     <t>Each catalogue contains one or more datasets. This property serves to link datasets to a catalogue. Therefore, a dataset is always contained inside a catalogue.</t>
   </si>
   <si>
-    <t>Add URI to all datasets contained in this catalogue</t>
+    <t>Enter the URI for all datasets contained in this catalogue.</t>
   </si>
   <si>
     <t>Briefly describe the catalogue and what it contains. You can repeat this in multiple languages.</t>
@@ -1658,7 +1660,7 @@
     <t>https://definities.geostandaarden.nl/dcat-ap-nl/nl/</t>
   </si>
   <si>
-    <t>The licence under which the catalogue (with resource description) is made available.
+    <t>The licence under which the catalogue (with its resource description) is made available.
 The licences for Distributions and Data Services are not specified here. They are specified in the licence properties of their respective classes.</t>
   </si>
   <si>
@@ -1698,7 +1700,7 @@
     <t>dcat:DataService (IRI)</t>
   </si>
   <si>
-    <t>If applicable, add URI to dcat:DataService</t>
+    <t>If applicable, enter the URI for dcat:DataService.</t>
   </si>
   <si>
     <t>themes</t>
@@ -1837,7 +1839,7 @@
   </si>
   <si>
     <t>Note: This property will be deprecated in the next major release.
-Choose a term from the controlled vocabulary, which includes the following types: Academia-ScientificOrganisation, Company, IndustryConsortium, LocalAuthority, NationalAuthority, NonGovernmentalOrganisation, NonProfitOrganisation, PrivateIndividual, RegionalAuthority, StandardisationBody and SupraNationalAuthority. These should use the following URL: http://purl.org/adms/publishertype/[type].</t>
+Choose a term from the controlled vocabulary, which includes the following types: Academia-ScientificOrganisation, Company, IndustryConsortium, LocalAuthority, NationalAuthority, NonGovernmentalOrganisation, NonProfitOrganisation, PrivateIndividual, RegionalAuthority, StandardisationBody and SupraNationalAuthority. These should use URLs of the following form: http://purl.org/adms/publishertype/[type].</t>
   </si>
   <si>
     <t>This property should be filled using ADMS vocabulary (http://purl.org/adms/publishertype/1.0).</t>
@@ -1945,7 +1947,7 @@
     <t>resource:access_services</t>
   </si>
   <si>
-    <t>If applicable, enter the URI for dcat:DataService.</t>
+    <t>Data Service</t>
   </si>
   <si>
     <t>access URL</t>
@@ -2086,7 +2088,7 @@
     <t>resource:format</t>
   </si>
   <si>
-    <t>Indicates the natural language used in the Distribution, using a value from the EU controlled vocabulary. Not all distributions might have a language, for example imaging data.
+    <t>Indicates the natural language used in the Distribution, using a value from the EU controlled vocabulary. Not all distributions necessarily have a language; for example, those containing imaging data may not.
 Note that here the Health-RI model diverges from DCAT-AP NL, which allows a maximum of 1 language per Distribution. The Health-RI model allows multiple languages in the same Distribution.</t>
   </si>
   <si>
@@ -2578,19 +2580,6 @@
     <t>Choose the type of Activity that was used to generate the Dataset from the Health Activity controlled vocabulary.</t>
   </si>
   <si>
-    <t>study design</t>
-  </si>
-  <si>
-    <t>Specifics about the observational study design.</t>
-  </si>
-  <si>
-    <t>schema:studyDesign</t>
-  </si>
-  <si>
-    <t>Select the study design that was used from the predefined list.
-Note: The exact value list is still in progress and will be added with the new release.</t>
-  </si>
-  <si>
     <t>Value: checksum (Distribution 1)</t>
   </si>
   <si>
@@ -2627,9 +2616,6 @@
     <t>spdx:checksumValue</t>
   </si>
   <si>
-    <t>xsd:hexBinary</t>
-  </si>
-  <si>
     <t>Value: table 1</t>
   </si>
   <si>
@@ -2675,9 +2661,6 @@
     <t>The URL should be a valid IRI and should point to the CSV file (a synthetic, anonymised representation of the real data) for this table.</t>
   </si>
   <si>
-    <t>xsd:anyURI</t>
-  </si>
-  <si>
     <t>Table title.</t>
   </si>
   <si>
@@ -2717,7 +2700,7 @@
     <t>csvw:name</t>
   </si>
   <si>
-    <t>Technical variable name required to match a column header in the CSV file (synthetic, anonymized representation of the real data), can appear in multiple languages.</t>
+    <t>A technical variable name is required to match a column header in the CSV file (a synthetic, anonymised representation of the real data).</t>
   </si>
   <si>
     <t>A human-readable name given to the Variable.</t>
@@ -2760,13 +2743,8 @@
     <t>csvw:propertyUrl</t>
   </si>
   <si>
-    <t>The propertyUrl may point to standard, controlled vocabularies, or ontologies that define the semantic meaning of the column. For example: csvw:propertyUrl http://publications.europa.eu/resource/authority/country For advanced usage, refer to the official specification: https://www.w3.org/TR/tabular-metadata/#propertyurl</t>
-  </si>
-  <si>
-    <t>rdfs:Literal (IRI)</t>
-  </si>
-  <si>
-    <t>Data Service</t>
+    <t>The propertyUrl may point to standard vocabularies, controlled vocabularies or ontologies that define the semantic meaning of the column. For example: csvw:propertyUrl http://publications.europa.eu/resource/authority/country
+For advanced usage, refer to the official specification: https://www.w3.org/TR/tabular-metadata/#propertyurl</t>
   </si>
 </sst>
 </file>
@@ -3868,7 +3846,37 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="326">
+  <dxfs count="318">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -3881,6 +3889,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3915,6 +3953,16 @@
       </font>
       <fill>
         <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor theme="4" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
@@ -3951,6 +3999,26 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -3961,6 +4029,106 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3971,6 +4139,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -4111,6 +4289,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -4121,6 +4319,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -4131,6 +4359,26 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -4141,6 +4389,36 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -4155,6 +4433,16 @@
       </font>
       <fill>
         <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor theme="4" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
@@ -4191,6 +4479,36 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -4201,6 +4519,96 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4211,6 +4619,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -4305,7 +4723,17 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4321,6 +4749,46 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -4345,7 +4813,37 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="2"/>
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4395,6 +4893,16 @@
       </font>
       <fill>
         <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor theme="4" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
@@ -4431,6 +4939,26 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -4441,6 +4969,246 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4451,6 +5219,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -4545,7 +5323,67 @@
       </font>
       <fill>
         <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4556,946 +5394,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7140,6 +7038,1333 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>432434</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>544829</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Tekstvak 1">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E12B015E-1FE9-8144-B2B5-99465A9CA0AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="432434" y="205740"/>
+          <a:ext cx="8862695" cy="2851785"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100"/>
+            <a:t>This spreadsheet includes the classes (see individual tabs) and properties</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0"/>
+            <a:t> (listed per class in each tab) of the v2 Health-RI core metadata schema, as also described on Github</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> (click this box to be directed here)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0"/>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="nl-NL" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0"/>
+            <a:t>You can view a simplified overview of the classes and the relations between them to the right. Below that you find the UML diagram of the model, which displays all classes and their respective properties.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="nl-NL" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100"/>
+            <a:t>As</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0"/>
+            <a:t> visible in the UML diagram to the right, there are a number of main classes (top; red and yellow tabs in this spreadsheet) and supporting classes (bottom; blue tabs in this spreadsheet).</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0"/>
+            <a:t>	In the UML, each class is depicted by a box. The mandatory properties of each class are listed at the top, below that the 	recommended properties.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0"/>
+            <a:t>	Properties marked in blue are introduces in the v2 model based on HealthDCAT-AP.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="1" baseline="0"/>
+            <a:t>While mapping your metadata to this schema, it is possible that you will not (have to) make use of all main classes. You may for example only use the dcat:Catalog and dcat:Dataset (and since they both use Kind and Agent, those will be needed as well).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0"/>
+            <a:t>Please see also Github for further information (click this box to be directed here).</a:t>
+          </a:r>
+          <a:endParaRPr lang="nl-NL" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A71F9689-DA02-1D4A-BC92-14F0CC46C293}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6057900" y="5905500"/>
+          <a:ext cx="304800" cy="320040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{123719C6-4376-2046-95E3-56693C8AA855}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4038600" y="4191000"/>
+          <a:ext cx="304800" cy="320040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>401955</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>34292</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>586740</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Tekstvak 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63300382-1DD4-0449-ABE5-19A3B3CB5B82}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="401955" y="3272792"/>
+          <a:ext cx="8935085" cy="2766058"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>What</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> do you see for each class and properties?</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="nl-NL" sz="1100" b="1" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Each tab represents the mandatory and recommended properties of the class.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- For each property, the label, definitions, property URI and usage note is stated.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- If applicable, the controlled vocabulary to be used in the class is stated.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- The requirement level (mandatory / recommended) and cardinality (how often the property must and may be filled) and range (how the property should be filled) are stated for each property.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Whenever a property points to another class, the range of that class is marked in orange (for example: publisher uses the foaf:Agent class)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>	If this is the case, go to the respective tab of that class and fille the properties of that class</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>	If you need to use that class multiple times (multiple instances), add extra columns per instance of that class you need</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- The history of the property (same as in v1 of the Health-RI schema, adjusted or new) as well as source of constraint (DCAT-AP / DCAT-AP NL / HealthDCAT-AP) are stated.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Next to that, there is room for your values / metadata (green column).</a:t>
+          </a:r>
+          <a:endParaRPr lang="nl-NL" b="0">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>300990</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>102870</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>414655</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A389E954-0D2D-1D4E-B441-48A06B770430}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{0779C778-DD79-4F08-9ADE-49A2BD526986}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9724390" y="102870"/>
+          <a:ext cx="6171565" cy="4606290"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>434340</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Tekstvak 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74735584-9128-D24B-A14E-26B916528AA1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="209550" y="312420"/>
+          <a:ext cx="9648190" cy="4926330"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Quick guide on</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> how to use</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> this</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> document for your Metadata </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Mapping</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> (see also general information below in green or mapping tutorial in yellow):</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="nl-NL">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- The tabs</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> indicated in red below are the mandatory classes (Catalog, Dataset, Agent and Kind). You will always have to provide metadata for these classes for onboarding.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- You might use one or more of the remaining classes (indicated in orange and blue tabs in this file), depending on the context and structure of your data. Again, it is possible that not all classes are required to describe your data. For more information, see recommendations page linked below in blue.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- On the tab of each class, you can filter on "mandatory" in the "Requirement level" column to view only mandatory properties.</a:t>
+          </a:r>
+          <a:endParaRPr lang="nl-NL">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Enter the values for your resource.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Whenever a </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>property points to another class</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>, the range of that class is marked in orange (for example: publisher uses the foaf:Agent class)</a:t>
+          </a:r>
+          <a:endParaRPr lang="nl-NL">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>	If this is the case, go to the respective tab of that class and fille the properties of that class</a:t>
+          </a:r>
+          <a:endParaRPr lang="nl-NL">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>	If you need to use that class multiple times (multiple instances), </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>add extra columns</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> per instance of that class you need</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>	This is the case if you want to </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>describe multiple datasets</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>	This is also the case </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>for foaf:Agent</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> which is used by dct:publisher and dct:creator in several classes, so it could be you need to 	describe separate Agents for different purposes (for example if the publisher of your catalogue is differernt from the publisher of 	your dataset, or if you would like to add all members of a consortium as separate creators)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>	</a:t>
+          </a:r>
+          <a:endParaRPr lang="nl-NL">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:br>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Remove the "requirement level" filter and check whether you have additional information to add for the recommended properties</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>	⚠ ️It is important to realise that the more complete your metadata is, the better findable and reusable your resource 	becomes. Filing in recommended classes and fields is therefore recommended</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Repeat the process for all mandatory classes.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>If you need the same class multiple times (to describe multiple datasets, or to describe the Agent class for the publisher of your dataset and the publisher of your catalogue), add new columns for the values of each instance of the required class.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Continue with other classes you want to use to describe your resource.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="nl-NL" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:endParaRPr lang="nl-NL">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>356235</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>354331</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Tekstvak 2">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5338863D-C508-2241-8A89-50B0262C8742}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="356235" y="5457825"/>
+          <a:ext cx="2690496" cy="628650"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1400" b="1">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>Metadata mapping</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1400" b="1" baseline="0">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> - G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1400" b="1">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>eneral</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1400" b="1" baseline="0">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> Information (click here)</a:t>
+          </a:r>
+          <a:endParaRPr lang="nl-NL" sz="1400" b="1">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>59055</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>60961</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Tekstvak 3">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DC73B57-220A-4943-902E-D6F3D0C8FE78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3424555" y="5476875"/>
+          <a:ext cx="2694306" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1400" b="1">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>Metadata mapping</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1400" b="1" baseline="0">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> - Step-by-step tutorial (click here)</a:t>
+          </a:r>
+          <a:endParaRPr lang="nl-NL" sz="1400" b="1">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>146685</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>28576</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Tekstvak 4">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FA0CAB0-179B-514B-A592-E17EC26C469E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6610350" y="5480685"/>
+          <a:ext cx="2841626" cy="626745"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1400" b="1">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>Recommendations for mapping to classes (click here)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7466,6 +8691,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7490,8 +8716,7 @@
     <col min="11" max="11" width="39.5" style="2" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="28.1640625" style="2" customWidth="1"/>
     <col min="13" max="13" width="28.83203125" style="2" customWidth="1"/>
-    <col min="14" max="19" width="9.1640625" style="2" customWidth="1"/>
-    <col min="20" max="20" width="9.1640625" style="2"/>
+    <col min="14" max="20" width="9.1640625" style="2" customWidth="1"/>
     <col min="21" max="23" width="19.1640625" customWidth="1"/>
     <col min="24" max="24" width="9.1640625" style="2" customWidth="1"/>
     <col min="25" max="16384" width="9.1640625" style="2"/>
@@ -7603,10 +8828,10 @@
         <v>610</v>
       </c>
       <c r="L2" s="156" t="s">
-        <v>611</v>
+        <v>533</v>
       </c>
       <c r="M2" s="156" t="s">
-        <v>611</v>
+        <v>533</v>
       </c>
       <c r="O2" s="27" t="s">
         <v>54</v>
@@ -7616,7 +8841,7 @@
       </c>
       <c r="S2" s="121"/>
       <c r="T2" s="2" t="s">
-        <v>878</v>
+        <v>611</v>
       </c>
       <c r="U2" s="91"/>
       <c r="V2" s="91"/>
@@ -7828,7 +9053,7 @@
         <v>41</v>
       </c>
       <c r="G7" s="94" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H7" s="90" t="s">
         <v>134</v>
@@ -9101,68 +10326,54 @@
   </sheetData>
   <autoFilter ref="A1:J24" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
   <conditionalFormatting sqref="F2:F54">
-    <cfRule type="cellIs" dxfId="244" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="236" priority="20" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H54">
-    <cfRule type="cellIs" dxfId="243" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="235" priority="21" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="242" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="234" priority="22" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F54">
-    <cfRule type="cellIs" dxfId="241" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="233" priority="9" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="240" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="232" priority="10" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="239" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="231" priority="11" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="238" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="230" priority="12" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J54">
-    <cfRule type="containsText" dxfId="237" priority="17" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="229" priority="17" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="236" priority="18" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="228" priority="18" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="235" priority="19" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="227" priority="19" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:S1">
-    <cfRule type="cellIs" dxfId="234" priority="5" operator="equal">
+  <conditionalFormatting sqref="N1:T1">
+    <cfRule type="cellIs" dxfId="226" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="233" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="225" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="232" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="224" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="231" priority="8" operator="equal">
-      <formula>"Conditional"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="223" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9962,76 +11173,76 @@
   <mergeCells count="11">
     <mergeCell ref="L6:L10"/>
     <mergeCell ref="K6:K10"/>
-    <mergeCell ref="J6:J10"/>
-    <mergeCell ref="C6:C10"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="I6:I10"/>
     <mergeCell ref="B6:B10"/>
     <mergeCell ref="F6:F10"/>
-    <mergeCell ref="E6:E10"/>
+    <mergeCell ref="C6:C10"/>
     <mergeCell ref="H6:H10"/>
     <mergeCell ref="G6:G10"/>
+    <mergeCell ref="E6:E10"/>
+    <mergeCell ref="J6:J10"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F6 F11:F15">
-    <cfRule type="cellIs" dxfId="230" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="222" priority="11" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H6 H11 G12:I12">
-    <cfRule type="cellIs" dxfId="229" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="221" priority="12" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="228" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="220" priority="13" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F6 F11:F15">
-    <cfRule type="cellIs" dxfId="227" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="219" priority="14" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="226" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="218" priority="15" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="225" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="217" priority="16" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="224" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="216" priority="17" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="containsText" dxfId="223" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="215" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="222" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="214" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="221" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="213" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J15">
-    <cfRule type="containsText" dxfId="220" priority="8" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="212" priority="8" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="219" priority="9" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="211" priority="9" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="218" priority="10" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="210" priority="10" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:R1">
-    <cfRule type="cellIs" dxfId="217" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="209" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="216" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="208" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="215" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="207" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="214" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="206" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11636,54 +12847,54 @@
   </sheetData>
   <autoFilter ref="A1:J23" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
   <conditionalFormatting sqref="F2:F53">
-    <cfRule type="cellIs" dxfId="213" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="205" priority="12" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H53">
-    <cfRule type="cellIs" dxfId="212" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="204" priority="13" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="211" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="203" priority="14" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F53">
-    <cfRule type="cellIs" dxfId="210" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="202" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="209" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="201" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="208" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="200" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="207" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="199" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J53">
-    <cfRule type="containsText" dxfId="206" priority="9" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="198" priority="9" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="205" priority="10" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="197" priority="10" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="204" priority="11" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="196" priority="11" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:R1">
-    <cfRule type="cellIs" dxfId="203" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="195" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="202" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="194" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="201" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="193" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="200" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="192" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11902,49 +13113,49 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="199" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="191" priority="9" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="198" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="190" priority="10" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="197" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="189" priority="11" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="196" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="188" priority="12" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="195" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="187" priority="13" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="194" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="186" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="193" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="185" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="192" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="184" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="191" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="183" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1:U1">
-    <cfRule type="cellIs" dxfId="190" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="182" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="189" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="181" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="188" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="180" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="187" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="179" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12804,85 +14015,85 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A41:B42">
-    <cfRule type="cellIs" dxfId="186" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="178" priority="15" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="185" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="177" priority="16" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="184" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="176" priority="17" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="183" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="175" priority="18" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E42">
-    <cfRule type="cellIs" dxfId="182" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="174" priority="19" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="181" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="173" priority="20" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="180" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="172" priority="21" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="179" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="171" priority="22" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F52">
-    <cfRule type="cellIs" dxfId="178" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="170" priority="9" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="177" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="169" priority="10" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="176" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="168" priority="11" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="175" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="167" priority="12" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="174" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="166" priority="13" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H9 H11:H15 H17:H25 H27:H41 H50:H52">
-    <cfRule type="cellIs" dxfId="173" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="165" priority="23" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="172" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="164" priority="24" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F52">
-    <cfRule type="cellIs" dxfId="171" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="163" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="170" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="162" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="161" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="160" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S1:X1">
-    <cfRule type="cellIs" dxfId="167" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="159" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="158" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="165" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="157" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="164" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="156" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13021,7 +14232,7 @@
         <v>773</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G2" s="168" t="s">
         <v>42</v>
@@ -13320,89 +14531,89 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D11:E13">
-    <cfRule type="cellIs" dxfId="163" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="155" priority="19" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="154" priority="22" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="153" priority="21" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="152" priority="20" operator="equal">
       <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="161" priority="21" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="22" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2">
-    <cfRule type="cellIs" dxfId="159" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="151" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="150" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="149" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="156" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="148" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="155" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="147" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F23 A12:B13">
-    <cfRule type="cellIs" dxfId="154" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="146" priority="15" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="145" priority="16" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="152" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="144" priority="17" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="143" priority="18" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F23">
-    <cfRule type="cellIs" dxfId="150" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="142" priority="10" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2">
-    <cfRule type="cellIs" dxfId="149" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="141" priority="11" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="148" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="12" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="139" priority="13" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="146" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="138" priority="14" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H12 H21:H23">
-    <cfRule type="cellIs" dxfId="145" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="137" priority="24" operator="equal">
+      <formula>"needs review"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="136" priority="23" operator="greaterThan">
       <formula>"reviewd"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="24" operator="equal">
-      <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1">
-    <cfRule type="cellIs" dxfId="143" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="135" priority="4" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="134" priority="3" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="133" priority="2" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="132" priority="1" operator="equal">
       <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="2" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="3" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="4" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -13626,35 +14837,35 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="139" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="138" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="127" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="134" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="125" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="123" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13857,35 +15068,35 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="130" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="129" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="128" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="120" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="125" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="117" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14088,35 +15299,35 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="121" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="120" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="116" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14144,7 +15355,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="20.1640625" customWidth="1"/>
@@ -14268,103 +15479,48 @@
       <c r="W2" s="58"/>
       <c r="X2" s="58"/>
     </row>
-    <row r="3" spans="1:24" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="35" t="s">
-        <v>816</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>817</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>818</v>
-      </c>
-      <c r="D3" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="37" t="s">
-        <v>819</v>
-      </c>
-      <c r="F3" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="H3" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
-      <c r="Q3" t="s">
-        <v>34</v>
-      </c>
-      <c r="R3" t="s">
-        <v>35</v>
-      </c>
-      <c r="V3" s="35"/>
-      <c r="W3" s="35"/>
-      <c r="X3" s="35"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A3:E3">
-    <cfRule type="cellIs" dxfId="112" priority="1" operator="equal">
+  <conditionalFormatting sqref="F2">
+    <cfRule type="cellIs" dxfId="104" priority="13" operator="equal">
+      <formula>"Not added"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2">
+    <cfRule type="cellIs" dxfId="103" priority="14" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="15" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="16" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="17" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="108" priority="13" operator="equal">
-      <formula>"Not added"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="107" priority="14" operator="equal">
+  <conditionalFormatting sqref="H1:I1 F1:F2">
+    <cfRule type="cellIs" dxfId="99" priority="9" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="10" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="11" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="17" operator="equal">
-      <formula>"Conditional"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="103" priority="9" operator="equal">
-      <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="10" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="11" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="12" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3" xr:uid="{00000000-0002-0000-1200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{00000000-0002-0000-1200-000000000000}">
       <formula1>"Mandatory, Recommended, Optional, Conditional, Not added"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3" xr:uid="{00000000-0002-0000-1200-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2" xr:uid="{00000000-0002-0000-1200-000001000000}">
       <formula1>"DCAT-AP v3, HealthDCAT-AP, DCAT-AP NL, HRI v1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I3" xr:uid="{00000000-0002-0000-1200-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{00000000-0002-0000-1200-000002000000}">
       <formula1>"Identical to v1, Adapted from v1, new"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{00000000-0002-0000-1200-000003000000}">
@@ -14385,6 +15541,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -14448,13 +15605,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="181" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="M1" s="188" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="N1" s="195" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="O1" s="67" t="s">
         <v>14</v>
@@ -14486,25 +15643,25 @@
     </row>
     <row r="2" spans="1:23" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
+        <v>819</v>
+      </c>
+      <c r="B2" s="40" t="s">
+        <v>820</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>821</v>
+      </c>
+      <c r="D2" s="52" t="s">
+        <v>822</v>
+      </c>
+      <c r="E2" s="161" t="s">
         <v>823</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>824</v>
-      </c>
-      <c r="C2" s="41" t="s">
-        <v>825</v>
-      </c>
-      <c r="D2" s="52" t="s">
-        <v>826</v>
-      </c>
-      <c r="E2" s="161" t="s">
-        <v>827</v>
       </c>
       <c r="F2" s="33" t="s">
         <v>29</v>
       </c>
       <c r="G2" s="168" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="H2" s="34">
         <v>1</v>
@@ -14527,13 +15684,13 @@
     </row>
     <row r="3" spans="1:23" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="36" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="D3" s="37" t="s">
         <v>39</v>
@@ -14543,7 +15700,7 @@
         <v>29</v>
       </c>
       <c r="G3" s="38" t="s">
-        <v>832</v>
+        <v>42</v>
       </c>
       <c r="H3" s="39">
         <v>1</v>
@@ -15198,89 +16355,89 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A41:B42">
-    <cfRule type="cellIs" dxfId="99" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="21" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="22" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="23" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="24" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E42">
-    <cfRule type="cellIs" dxfId="95" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="25" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="28" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="89" priority="27" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="88" priority="26" operator="equal">
       <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="27" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="28" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E3">
-    <cfRule type="cellIs" dxfId="91" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F52">
-    <cfRule type="cellIs" dxfId="86" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="10" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G3">
-    <cfRule type="cellIs" dxfId="85" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="16" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="17" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="18" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="19" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H9 H11:H15 H17:H25 H27:H41 H50:H52">
-    <cfRule type="cellIs" dxfId="81" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="77" priority="30" operator="equal">
+      <formula>"needs review"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="29" operator="greaterThan">
       <formula>"reviewd"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="30" operator="equal">
-      <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F52">
-    <cfRule type="cellIs" dxfId="79" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="4" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="3" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="2" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="1" operator="equal">
       <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="2" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="3" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="4" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -15368,13 +16525,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="181" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="M1" s="188" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="N1" s="195" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="O1" s="67" t="s">
         <v>14</v>
@@ -15406,19 +16563,19 @@
     </row>
     <row r="2" spans="1:23" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="D2" s="52" t="s">
         <v>39</v>
       </c>
       <c r="E2" s="161" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="F2" s="33" t="s">
         <v>29</v>
@@ -15436,7 +16593,7 @@
         <v>44</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="P2" s="27" t="s">
         <v>96</v>
@@ -15453,7 +16610,7 @@
         <v>347</v>
       </c>
       <c r="B3" s="140" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="C3" s="160" t="s">
         <v>349</v>
@@ -15462,7 +16619,7 @@
         <v>39</v>
       </c>
       <c r="E3" s="214" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="F3" s="215" t="s">
         <v>29</v>
@@ -16107,91 +17264,91 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D39:E41">
-    <cfRule type="cellIs" dxfId="75" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="19" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="22" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="69" priority="21" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="68" priority="20" operator="equal">
       <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="21" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="22" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2">
-    <cfRule type="cellIs" dxfId="71" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:F2">
-    <cfRule type="cellIs" dxfId="67" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F2 F4:F51 A40:B41">
-    <cfRule type="cellIs" dxfId="66" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="15" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="16" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="17" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="18" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F51">
-    <cfRule type="cellIs" dxfId="62" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="10" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2">
-    <cfRule type="cellIs" dxfId="61" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="11" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="12" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="13" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="14" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H8 H10:H14 H16:H24 H26:H40 H49:H51">
-    <cfRule type="cellIs" dxfId="57" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="53" priority="24" operator="equal">
+      <formula>"needs review"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="23" operator="greaterThan">
       <formula>"reviewd"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="24" operator="equal">
-      <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1">
-    <cfRule type="cellIs" dxfId="55" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="4" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="50" priority="3" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="2" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="48" priority="1" operator="equal">
       <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="2" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="3" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="4" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -16276,13 +17433,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="181" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="M1" s="188" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="N1" s="195" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="O1" s="67" t="s">
         <v>14</v>
@@ -16314,25 +17471,25 @@
     </row>
     <row r="2" spans="1:23" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="D2" s="52" t="s">
         <v>39</v>
       </c>
       <c r="E2" s="161" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="F2" s="33" t="s">
         <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>848</v>
+        <v>179</v>
       </c>
       <c r="H2" s="168" t="s">
         <v>134</v>
@@ -16358,7 +17515,7 @@
         <v>347</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="C3" s="35" t="s">
         <v>349</v>
@@ -16367,7 +17524,7 @@
         <v>39</v>
       </c>
       <c r="E3" s="127" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="F3" s="33" t="s">
         <v>29</v>
@@ -16402,7 +17559,7 @@
         <v>181</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>183</v>
@@ -16411,7 +17568,7 @@
         <v>39</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>41</v>
@@ -16440,19 +17597,19 @@
     </row>
     <row r="5" spans="1:23" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="209" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="B5" s="210" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="C5" s="209" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="D5" s="211" t="s">
         <v>39</v>
       </c>
       <c r="E5" s="210" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>29</v>
@@ -16470,7 +17627,7 @@
         <v>44</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="P5" s="27" t="s">
         <v>96</v>
@@ -17087,89 +18244,89 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D40:E42">
-    <cfRule type="cellIs" dxfId="51" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="19" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="22" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="21" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="44" priority="20" operator="equal">
       <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="21" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="22" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E3">
-    <cfRule type="cellIs" dxfId="47" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F52 A41:B42">
-    <cfRule type="cellIs" dxfId="42" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="15" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="16" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="17" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="18" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F52">
-    <cfRule type="cellIs" dxfId="38" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="10" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="37" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="11" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="12" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="13" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="14" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H9 H11:H15 H17:H25 H27:H41 H50:H52">
-    <cfRule type="cellIs" dxfId="33" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="24" operator="equal">
+      <formula>"needs review"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="23" operator="greaterThan">
       <formula>"reviewd"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="24" operator="equal">
-      <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="4" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="2" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="3" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="4" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -17254,13 +18411,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="181" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="M1" s="188" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="N1" s="195" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="O1" s="67" t="s">
         <v>14</v>
@@ -17295,16 +18452,16 @@
         <v>563</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="D2" s="52" t="s">
         <v>39</v>
       </c>
       <c r="E2" s="161" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="F2" s="33" t="s">
         <v>29</v>
@@ -17312,8 +18469,8 @@
       <c r="G2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="168" t="s">
-        <v>750</v>
+      <c r="H2" s="168">
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>31</v>
@@ -17336,16 +18493,16 @@
         <v>347</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="D3" s="207" t="s">
         <v>39</v>
       </c>
       <c r="E3" s="127" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="F3" s="33" t="s">
         <v>29</v>
@@ -17380,7 +18537,7 @@
         <v>107</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>109</v>
@@ -17389,7 +18546,7 @@
         <v>39</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>29</v>
@@ -17421,19 +18578,19 @@
     </row>
     <row r="5" spans="1:23" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="209" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="B5" s="210" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="C5" s="209" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="D5" s="211" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="E5" s="210" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>29</v>
@@ -17462,25 +18619,25 @@
     </row>
     <row r="6" spans="1:23" ht="154" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="D6" s="52" t="s">
         <v>39</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>877</v>
+        <v>179</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>134</v>
@@ -18093,89 +19250,89 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D40:E42">
-    <cfRule type="cellIs" dxfId="27" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="19" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="22" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="20" operator="equal">
       <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="21" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="22" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E3">
-    <cfRule type="cellIs" dxfId="23" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F52 A41:B42">
-    <cfRule type="cellIs" dxfId="18" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="15" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="16" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="17" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="18" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F52">
-    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="13" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="14" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H9 H11:H15 H17:H25 H27:H41 H50:H52">
-    <cfRule type="cellIs" dxfId="9" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="24" operator="equal">
+      <formula>"needs review"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="23" operator="greaterThan">
       <formula>"reviewd"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="24" operator="equal">
-      <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -18210,210 +19367,210 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1" t="s">
         <v>379</v>
-      </c>
-      <c r="B1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B2" s="200" t="s">
         <v>381</v>
-      </c>
-      <c r="B2" s="200" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B3" s="200" t="s">
         <v>383</v>
-      </c>
-      <c r="B3" s="200" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>384</v>
+      </c>
+      <c r="B4" s="200" t="s">
         <v>385</v>
-      </c>
-      <c r="B4" s="200" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B5" s="200" t="s">
         <v>387</v>
-      </c>
-      <c r="B5" s="200" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B6" s="200" t="s">
         <v>389</v>
-      </c>
-      <c r="B6" s="200" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>390</v>
+      </c>
+      <c r="B7" s="200" t="s">
         <v>391</v>
-      </c>
-      <c r="B7" s="200" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>392</v>
+      </c>
+      <c r="B8" s="200" t="s">
         <v>393</v>
-      </c>
-      <c r="B8" s="200" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>394</v>
+      </c>
+      <c r="B9" t="s">
         <v>395</v>
-      </c>
-      <c r="B9" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>396</v>
+      </c>
+      <c r="B10" t="s">
         <v>397</v>
-      </c>
-      <c r="B10" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>398</v>
+      </c>
+      <c r="B11" s="200" t="s">
         <v>399</v>
-      </c>
-      <c r="B11" s="200" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>400</v>
+      </c>
+      <c r="B12" s="200" t="s">
         <v>401</v>
-      </c>
-      <c r="B12" s="200" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>402</v>
+      </c>
+      <c r="B13" s="200" t="s">
         <v>403</v>
-      </c>
-      <c r="B13" s="200" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>404</v>
+      </c>
+      <c r="B14" s="200" t="s">
         <v>405</v>
-      </c>
-      <c r="B14" s="200" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>406</v>
+      </c>
+      <c r="B15" s="200" t="s">
         <v>407</v>
-      </c>
-      <c r="B15" s="200" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>408</v>
+      </c>
+      <c r="B16" s="200" t="s">
         <v>409</v>
-      </c>
-      <c r="B16" s="200" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B17" s="200" t="s">
         <v>411</v>
-      </c>
-      <c r="B17" s="200" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>412</v>
+      </c>
+      <c r="B18" s="200" t="s">
         <v>413</v>
-      </c>
-      <c r="B18" s="200" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>414</v>
+      </c>
+      <c r="B19" s="200" t="s">
         <v>415</v>
-      </c>
-      <c r="B19" s="200" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B20" s="200" t="s">
         <v>417</v>
-      </c>
-      <c r="B20" s="200" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>418</v>
+      </c>
+      <c r="B21" s="200" t="s">
         <v>419</v>
-      </c>
-      <c r="B21" s="200" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>420</v>
+      </c>
+      <c r="B22" s="200" t="s">
         <v>421</v>
-      </c>
-      <c r="B22" s="200" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>422</v>
+      </c>
+      <c r="B23" s="200" t="s">
         <v>423</v>
-      </c>
-      <c r="B23" s="200" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>424</v>
+      </c>
+      <c r="B24" s="200" t="s">
         <v>425</v>
-      </c>
-      <c r="B24" s="200" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>426</v>
+      </c>
+      <c r="B25" s="200" t="s">
         <v>427</v>
-      </c>
-      <c r="B25" s="200" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>428</v>
+      </c>
+      <c r="B26" s="200" t="s">
         <v>429</v>
-      </c>
-      <c r="B26" s="200" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -18486,45 +19643,45 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B1" t="s">
         <v>107</v>
       </c>
       <c r="C1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1" t="s">
         <v>432</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>433</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>434</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>435</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>436</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>437</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>438</v>
-      </c>
-      <c r="J1" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C2" t="s">
         <v>440</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>441</v>
-      </c>
-      <c r="D2" t="s">
-        <v>442</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -18532,13 +19689,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C3" t="s">
         <v>443</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>444</v>
-      </c>
-      <c r="D3" t="s">
-        <v>445</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -18546,13 +19703,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C4" t="s">
         <v>446</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>447</v>
-      </c>
-      <c r="D4" t="s">
-        <v>448</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -18560,10 +19717,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>448</v>
+      </c>
+      <c r="C5" t="s">
         <v>449</v>
-      </c>
-      <c r="C5" t="s">
-        <v>450</v>
       </c>
       <c r="D5" t="s">
         <v>102</v>
@@ -18571,10 +19728,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>450</v>
+      </c>
+      <c r="C6" t="s">
         <v>451</v>
-      </c>
-      <c r="C6" t="s">
-        <v>452</v>
       </c>
       <c r="D6" t="s">
         <v>90</v>
@@ -18582,13 +19739,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>452</v>
+      </c>
+      <c r="C7" t="s">
         <v>453</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>454</v>
-      </c>
-      <c r="D7" t="s">
-        <v>455</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -18596,13 +19753,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>455</v>
+      </c>
+      <c r="C8" s="217" t="s">
         <v>456</v>
       </c>
-      <c r="C8" s="217" t="s">
+      <c r="D8" t="s">
         <v>457</v>
-      </c>
-      <c r="D8" t="s">
-        <v>458</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -18610,13 +19767,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C9" t="s">
         <v>459</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>460</v>
-      </c>
-      <c r="D9" t="s">
-        <v>461</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -18624,10 +19781,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>461</v>
+      </c>
+      <c r="C10" t="s">
         <v>462</v>
-      </c>
-      <c r="C10" t="s">
-        <v>463</v>
       </c>
       <c r="D10" t="s">
         <v>241</v>
@@ -18635,10 +19792,10 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>463</v>
+      </c>
+      <c r="C11" t="s">
         <v>464</v>
-      </c>
-      <c r="C11" t="s">
-        <v>465</v>
       </c>
       <c r="D11" t="s">
         <v>306</v>
@@ -18646,10 +19803,10 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>465</v>
+      </c>
+      <c r="C12" t="s">
         <v>466</v>
-      </c>
-      <c r="C12" t="s">
-        <v>467</v>
       </c>
       <c r="D12" t="s">
         <v>279</v>
@@ -18657,10 +19814,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>467</v>
+      </c>
+      <c r="C13" t="s">
         <v>468</v>
-      </c>
-      <c r="C13" t="s">
-        <v>469</v>
       </c>
       <c r="D13" t="s">
         <v>286</v>
@@ -18668,10 +19825,10 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>469</v>
+      </c>
+      <c r="C14" t="s">
         <v>470</v>
-      </c>
-      <c r="C14" t="s">
-        <v>471</v>
       </c>
       <c r="D14" t="s">
         <v>294</v>
@@ -18679,24 +19836,27 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>471</v>
+      </c>
+      <c r="C15" t="s">
         <v>472</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>473</v>
-      </c>
-      <c r="D15" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>474</v>
+      </c>
+      <c r="C16" t="s">
         <v>475</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>476</v>
       </c>
-      <c r="D16" t="s">
-        <v>361</v>
+      <c r="E16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -18729,7 +19889,7 @@
         <v>484</v>
       </c>
       <c r="D19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -18824,44 +19984,44 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F1 H1:I1">
-    <cfRule type="cellIs" dxfId="325" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="317" priority="9" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="324" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="316" priority="10" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="323" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="315" priority="11" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="322" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="314" priority="12" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1">
-    <cfRule type="cellIs" dxfId="321" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="313" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="320" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="312" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="319" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="311" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="318" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="310" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:Q1">
-    <cfRule type="cellIs" dxfId="317" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="309" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="316" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="308" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="315" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="307" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="314" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="306" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19967,85 +21127,85 @@
     <mergeCell ref="C8:C12"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F8">
-    <cfRule type="cellIs" dxfId="313" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="305" priority="20" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13:F24">
-    <cfRule type="cellIs" dxfId="312" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="304" priority="30" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="311" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="303" priority="33" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="310" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="302" priority="34" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="309" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="301" priority="35" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="308" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="300" priority="36" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H8 H13:H24">
-    <cfRule type="cellIs" dxfId="307" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="299" priority="21" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="306" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="298" priority="22" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F8">
-    <cfRule type="cellIs" dxfId="305" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="297" priority="9" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="304" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="296" priority="10" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="303" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="295" priority="11" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="302" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="294" priority="12" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J8 J13:J24">
-    <cfRule type="containsText" dxfId="301" priority="17" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="293" priority="17" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="300" priority="18" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="292" priority="18" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="299" priority="19" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="291" priority="19" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1">
-    <cfRule type="cellIs" dxfId="298" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="290" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="297" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="289" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="296" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="288" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="295" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="287" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:S1">
-    <cfRule type="cellIs" dxfId="294" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="286" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="293" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="285" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="292" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="284" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="291" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="283" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21079,7 +22239,7 @@
       <c r="W22" s="87"/>
       <c r="X22" s="87"/>
     </row>
-    <row r="23" spans="1:24" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" ht="124" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="91" t="s">
         <v>153</v>
       </c>
@@ -22815,14 +23975,11 @@
       <c r="N57" s="95" t="s">
         <v>362</v>
       </c>
-      <c r="O57" s="27" t="s">
-        <v>363</v>
-      </c>
       <c r="P57" s="27" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="Q57" s="27" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="V57" s="91"/>
       <c r="W57" s="91"/>
@@ -22830,19 +23987,19 @@
     </row>
     <row r="58" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="87" t="s">
+        <v>363</v>
+      </c>
+      <c r="B58" s="29" t="s">
         <v>364</v>
       </c>
-      <c r="B58" s="29" t="s">
+      <c r="C58" s="87" t="s">
         <v>365</v>
-      </c>
-      <c r="C58" s="87" t="s">
-        <v>366</v>
       </c>
       <c r="D58" s="98" t="s">
         <v>39</v>
       </c>
       <c r="E58" s="98" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F58" s="90" t="s">
         <v>41</v>
@@ -22860,7 +24017,7 @@
         <v>92</v>
       </c>
       <c r="K58" s="75" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L58" s="76"/>
       <c r="M58" s="76"/>
@@ -22878,19 +24035,19 @@
     </row>
     <row r="59" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="91" t="s">
+        <v>368</v>
+      </c>
+      <c r="B59" s="48" t="s">
         <v>369</v>
       </c>
-      <c r="B59" s="48" t="s">
+      <c r="C59" s="91" t="s">
         <v>370</v>
-      </c>
-      <c r="C59" s="91" t="s">
-        <v>371</v>
       </c>
       <c r="D59" s="92" t="s">
         <v>39</v>
       </c>
       <c r="E59" s="48" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F59" s="93" t="s">
         <v>41</v>
@@ -22908,7 +24065,7 @@
         <v>111</v>
       </c>
       <c r="K59" s="96" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L59" s="95"/>
       <c r="M59" s="95"/>
@@ -22928,13 +24085,13 @@
     </row>
     <row r="60" spans="1:24" ht="84.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="87" t="s">
+        <v>373</v>
+      </c>
+      <c r="B60" s="29" t="s">
         <v>374</v>
       </c>
-      <c r="B60" s="29" t="s">
+      <c r="C60" s="87" t="s">
         <v>375</v>
-      </c>
-      <c r="C60" s="87" t="s">
-        <v>376</v>
       </c>
       <c r="D60" s="98" t="s">
         <v>39</v>
@@ -22943,7 +24100,7 @@
         <v>41</v>
       </c>
       <c r="G60" s="94" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H60" s="90" t="s">
         <v>43</v>
@@ -22959,7 +24116,7 @@
       <c r="M60" s="76"/>
       <c r="N60" s="76"/>
       <c r="O60" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P60" s="27" t="s">
         <v>96</v>
@@ -23006,68 +24163,68 @@
     <mergeCell ref="I17:I21"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F17 F22:F61">
-    <cfRule type="cellIs" dxfId="290" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="282" priority="12" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H17 H22:H61">
-    <cfRule type="cellIs" dxfId="289" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="281" priority="21" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="288" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="280" priority="22" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F17 F22:F61">
-    <cfRule type="cellIs" dxfId="287" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="279" priority="23" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="286" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="278" priority="24" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="285" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="277" priority="25" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="284" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="276" priority="26" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J17 J22:J61">
-    <cfRule type="containsText" dxfId="283" priority="9" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="275" priority="9" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="282" priority="10" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="274" priority="10" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="281" priority="11" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="273" priority="11" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1">
-    <cfRule type="cellIs" dxfId="280" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="272" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="279" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="271" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="278" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="270" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="277" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="269" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:U1">
-    <cfRule type="cellIs" dxfId="276" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="268" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="275" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="267" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="274" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="266" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="273" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="265" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24382,54 +25539,54 @@
   </sheetData>
   <autoFilter ref="A1:J9" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <conditionalFormatting sqref="F2:F55">
-    <cfRule type="cellIs" dxfId="272" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="264" priority="12" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H55">
-    <cfRule type="cellIs" dxfId="271" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="263" priority="13" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="270" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="262" priority="14" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F55">
-    <cfRule type="cellIs" dxfId="269" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="261" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="268" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="260" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="267" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="259" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="266" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="258" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J55">
-    <cfRule type="containsText" dxfId="265" priority="9" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="257" priority="9" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="264" priority="10" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="256" priority="10" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="263" priority="11" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="255" priority="11" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W1:AB1">
-    <cfRule type="cellIs" dxfId="262" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="254" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="261" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="253" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="260" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="252" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="259" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="251" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25559,54 +26716,54 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F53">
-    <cfRule type="cellIs" dxfId="258" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="250" priority="12" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H53">
-    <cfRule type="cellIs" dxfId="257" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="249" priority="13" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="256" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="248" priority="14" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F53">
-    <cfRule type="cellIs" dxfId="255" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="247" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="254" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="246" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="253" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="245" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="252" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="244" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J53">
-    <cfRule type="containsText" dxfId="251" priority="9" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="243" priority="9" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="250" priority="10" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="242" priority="10" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="249" priority="11" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="241" priority="11" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:W1">
-    <cfRule type="cellIs" dxfId="248" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="240" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="247" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="239" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="246" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="238" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="245" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="237" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
